--- a/artfynd/A 52753-2025 artfynd.xlsx
+++ b/artfynd/A 52753-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129726815</v>
       </c>
       <c r="B2" t="n">
-        <v>83036</v>
+        <v>83037</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129727928</v>
+        <v>129716450</v>
       </c>
       <c r="B3" t="n">
-        <v>57735</v>
+        <v>79076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483704</v>
+        <v>483823</v>
       </c>
       <c r="R3" t="n">
-        <v>7145461</v>
+        <v>7145591</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,11 +855,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -872,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129726936</v>
+        <v>129726952</v>
       </c>
       <c r="B4" t="n">
-        <v>57735</v>
+        <v>79076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,46 +890,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483746</v>
+        <v>483538</v>
       </c>
       <c r="R4" t="n">
-        <v>7145582</v>
+        <v>7145695</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,7 +957,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en levande gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -980,6 +966,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1000,12 +987,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1023,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129716450</v>
+        <v>129726820</v>
       </c>
       <c r="B5" t="n">
-        <v>79075</v>
+        <v>83050</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1034,34 +1021,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483823</v>
+        <v>483921</v>
       </c>
       <c r="R5" t="n">
-        <v>7145591</v>
+        <v>7145571</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,9 +1078,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,22 +1105,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129726952</v>
+        <v>129726936</v>
       </c>
       <c r="B6" t="n">
-        <v>79075</v>
+        <v>57736</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1131,37 +1128,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483538</v>
+        <v>483746</v>
       </c>
       <c r="R6" t="n">
-        <v>7145695</v>
+        <v>7145582</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1204,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, äldre, på stambasen av en levande gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1207,7 +1213,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1228,12 +1233,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1251,10 +1256,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129726820</v>
+        <v>129727928</v>
       </c>
       <c r="B7" t="n">
-        <v>83049</v>
+        <v>57736</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1262,34 +1267,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1467</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483921</v>
+        <v>483704</v>
       </c>
       <c r="R7" t="n">
-        <v>7145571</v>
+        <v>7145461</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,19 +1324,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>09:08</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>09:08</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,22 +1346,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129726805</v>
+        <v>129726791</v>
       </c>
       <c r="B8" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,10 +1393,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483517</v>
+        <v>483607</v>
       </c>
       <c r="R8" t="n">
-        <v>7145580</v>
+        <v>7145404</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1465,10 +1465,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129726791</v>
+        <v>129726803</v>
       </c>
       <c r="B9" t="n">
-        <v>79075</v>
+        <v>83037</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1476,21 +1476,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483607</v>
+        <v>483493</v>
       </c>
       <c r="R9" t="n">
-        <v>7145404</v>
+        <v>7145541</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1535,7 +1535,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1572,10 +1572,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129726955</v>
+        <v>129716452</v>
       </c>
       <c r="B10" t="n">
-        <v>79075</v>
+        <v>91608</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1583,37 +1583,30 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483580</v>
+        <v>483480</v>
       </c>
       <c r="R10" t="n">
-        <v>7145305</v>
+        <v>7145600</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1648,65 +1641,34 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På en levande gran.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129726803</v>
+        <v>129726955</v>
       </c>
       <c r="B11" t="n">
-        <v>83036</v>
+        <v>79076</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1714,34 +1676,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483493</v>
+        <v>483580</v>
       </c>
       <c r="R11" t="n">
-        <v>7145541</v>
+        <v>7145305</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1771,19 +1736,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>10:01</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>10:01</t>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På en levande gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1792,28 +1752,54 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129716452</v>
+        <v>129726805</v>
       </c>
       <c r="B12" t="n">
-        <v>91607</v>
+        <v>79076</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1821,30 +1807,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483480</v>
+        <v>483517</v>
       </c>
       <c r="R12" t="n">
-        <v>7145600</v>
+        <v>7145580</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1874,9 +1864,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1891,12 +1891,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1906,7 +1906,7 @@
         <v>129726819</v>
       </c>
       <c r="B13" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2010,10 +2010,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129716455</v>
+        <v>129716468</v>
       </c>
       <c r="B14" t="n">
-        <v>57735</v>
+        <v>91608</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2021,39 +2021,30 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483975</v>
+        <v>484042</v>
       </c>
       <c r="R14" t="n">
-        <v>7145436</v>
+        <v>7145421</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2112,10 +2103,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129727923</v>
+        <v>129716455</v>
       </c>
       <c r="B15" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2141,16 +2132,21 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483397</v>
+        <v>483975</v>
       </c>
       <c r="R15" t="n">
-        <v>7145483</v>
+        <v>7145436</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2185,11 +2181,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2202,22 +2193,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129726935</v>
+        <v>129727920</v>
       </c>
       <c r="B16" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2243,28 +2234,16 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483601</v>
+        <v>483452</v>
       </c>
       <c r="R16" t="n">
-        <v>7145616</v>
+        <v>7145362</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2301,7 +2280,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en levande gran i barrblandskog.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2312,41 +2291,16 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2356,7 +2310,7 @@
         <v>129727919</v>
       </c>
       <c r="B17" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2455,10 +2409,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129727920</v>
+        <v>129726935</v>
       </c>
       <c r="B18" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2484,16 +2438,28 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483452</v>
+        <v>483601</v>
       </c>
       <c r="R18" t="n">
-        <v>7145362</v>
+        <v>7145616</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2530,7 +2496,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, färska och äldre, på stambasen av en levande gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2541,26 +2507,51 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129716468</v>
+        <v>129727923</v>
       </c>
       <c r="B19" t="n">
-        <v>91607</v>
+        <v>57736</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2568,30 +2559,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>484042</v>
+        <v>483397</v>
       </c>
       <c r="R19" t="n">
-        <v>7145421</v>
+        <v>7145483</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2626,6 +2621,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2638,12 +2638,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2653,7 +2653,7 @@
         <v>129726804</v>
       </c>
       <c r="B20" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>129726941</v>
       </c>
       <c r="B21" t="n">
-        <v>80181</v>
+        <v>80182</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>129726825</v>
       </c>
       <c r="B22" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3002,7 +3002,7 @@
         <v>129726813</v>
       </c>
       <c r="B23" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>129726814</v>
       </c>
       <c r="B24" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3213,10 +3213,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129726818</v>
+        <v>129727934</v>
       </c>
       <c r="B25" t="n">
-        <v>83044</v>
+        <v>57736</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3224,34 +3224,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>483849</v>
+        <v>483619</v>
       </c>
       <c r="R25" t="n">
-        <v>7145605</v>
+        <v>7145595</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3281,19 +3281,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>09:13</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>09:13</t>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3308,44 +3303,44 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129727934</v>
+        <v>129727915</v>
       </c>
       <c r="B26" t="n">
-        <v>57735</v>
+        <v>92306</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3355,10 +3350,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>483619</v>
+        <v>483493</v>
       </c>
       <c r="R26" t="n">
-        <v>7145595</v>
+        <v>7145538</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3391,11 +3386,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3422,45 +3412,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129727915</v>
+        <v>129726818</v>
       </c>
       <c r="B27" t="n">
-        <v>92305</v>
+        <v>83045</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3298</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>483493</v>
+        <v>483849</v>
       </c>
       <c r="R27" t="n">
-        <v>7145538</v>
+        <v>7145605</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3490,9 +3480,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3507,12 +3507,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3522,7 +3522,7 @@
         <v>129726816</v>
       </c>
       <c r="B28" t="n">
-        <v>75059</v>
+        <v>75060</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3626,10 +3626,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129727921</v>
+        <v>129726933</v>
       </c>
       <c r="B29" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3655,16 +3655,28 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>483464</v>
+        <v>483582</v>
       </c>
       <c r="R29" t="n">
-        <v>7145542</v>
+        <v>7145456</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3701,7 +3713,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3712,26 +3724,51 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129726933</v>
+        <v>129727921</v>
       </c>
       <c r="B30" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3757,28 +3794,16 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>483582</v>
+        <v>483464</v>
       </c>
       <c r="R30" t="n">
-        <v>7145456</v>
+        <v>7145542</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3815,7 +3840,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3826,41 +3851,16 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3870,7 +3870,7 @@
         <v>129716460</v>
       </c>
       <c r="B31" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>129726961</v>
       </c>
       <c r="B32" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>129726824</v>
       </c>
       <c r="B33" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         <v>129727931</v>
       </c>
       <c r="B34" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         <v>129726938</v>
       </c>
       <c r="B35" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         <v>129716461</v>
       </c>
       <c r="B36" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
         <v>129726807</v>
       </c>
       <c r="B37" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>129716466</v>
       </c>
       <c r="B38" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4740,7 +4740,7 @@
         <v>129726801</v>
       </c>
       <c r="B39" t="n">
-        <v>83049</v>
+        <v>83050</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4847,7 +4847,7 @@
         <v>129727927</v>
       </c>
       <c r="B40" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4946,45 +4946,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129726821</v>
+        <v>129716464</v>
       </c>
       <c r="B41" t="n">
-        <v>79075</v>
+        <v>92306</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>483922</v>
+        <v>484017</v>
       </c>
       <c r="R41" t="n">
-        <v>7145570</v>
+        <v>7145437</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5014,19 +5014,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>09:05</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>09:05</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5041,12 +5031,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5056,7 +5046,7 @@
         <v>129726946</v>
       </c>
       <c r="B42" t="n">
-        <v>80208</v>
+        <v>80209</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5154,10 +5144,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129726960</v>
+        <v>129726821</v>
       </c>
       <c r="B43" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5183,19 +5173,16 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>483376</v>
+        <v>483922</v>
       </c>
       <c r="R43" t="n">
-        <v>7145540</v>
+        <v>7145570</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5225,14 +5212,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På en levande gran.</t>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5241,54 +5233,28 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129726810</v>
+        <v>129726948</v>
       </c>
       <c r="B44" t="n">
-        <v>57735</v>
+        <v>91608</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5296,48 +5262,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>483760</v>
+        <v>483501</v>
       </c>
       <c r="R44" t="n">
-        <v>7145583</v>
+        <v>7145621</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5367,19 +5322,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>09:41</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>09:41</t>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar i en levande gran.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5388,28 +5338,54 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129727936</v>
+        <v>129726960</v>
       </c>
       <c r="B45" t="n">
-        <v>57735</v>
+        <v>79076</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5417,34 +5393,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>483750</v>
+        <v>483376</v>
       </c>
       <c r="R45" t="n">
-        <v>7145579</v>
+        <v>7145540</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5481,7 +5460,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>På en levande gran.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5490,28 +5469,54 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129727938</v>
+        <v>129727936</v>
       </c>
       <c r="B46" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5543,10 +5548,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>483975</v>
+        <v>483750</v>
       </c>
       <c r="R46" t="n">
-        <v>7145511</v>
+        <v>7145579</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5610,10 +5615,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129726948</v>
+        <v>129727938</v>
       </c>
       <c r="B47" t="n">
-        <v>91607</v>
+        <v>57736</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5621,37 +5626,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>483501</v>
+        <v>483975</v>
       </c>
       <c r="R47" t="n">
-        <v>7145621</v>
+        <v>7145511</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5688,7 +5690,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en levande gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5697,89 +5699,77 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129716464</v>
+        <v>129726810</v>
       </c>
       <c r="B48" t="n">
-        <v>92305</v>
+        <v>57736</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>484017</v>
+        <v>483760</v>
       </c>
       <c r="R48" t="n">
-        <v>7145437</v>
+        <v>7145583</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5809,9 +5799,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5826,22 +5826,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129726800</v>
+        <v>129727935</v>
       </c>
       <c r="B49" t="n">
-        <v>79075</v>
+        <v>57736</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5849,34 +5849,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>483439</v>
+        <v>483723</v>
       </c>
       <c r="R49" t="n">
-        <v>7145513</v>
+        <v>7145593</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5906,19 +5906,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>10:13</t>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5933,22 +5928,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129716462</v>
+        <v>129726800</v>
       </c>
       <c r="B50" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5976,14 +5971,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>483666</v>
+        <v>483439</v>
       </c>
       <c r="R50" t="n">
-        <v>7145612</v>
+        <v>7145513</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6013,9 +6008,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6030,22 +6035,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129727935</v>
+        <v>129716462</v>
       </c>
       <c r="B51" t="n">
-        <v>57735</v>
+        <v>79076</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6053,34 +6058,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>483723</v>
+        <v>483666</v>
       </c>
       <c r="R51" t="n">
-        <v>7145593</v>
+        <v>7145612</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6115,11 +6120,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6132,12 +6132,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6147,7 +6147,7 @@
         <v>129726944</v>
       </c>
       <c r="B52" t="n">
-        <v>80208</v>
+        <v>80209</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>129716458</v>
       </c>
       <c r="B53" t="n">
-        <v>83044</v>
+        <v>83045</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6342,45 +6342,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129726811</v>
+        <v>129727914</v>
       </c>
       <c r="B54" t="n">
-        <v>79075</v>
+        <v>92306</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>483760</v>
+        <v>483577</v>
       </c>
       <c r="R54" t="n">
-        <v>7145575</v>
+        <v>7145438</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6410,19 +6410,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>09:35</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>09:35</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6437,22 +6427,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129727922</v>
+        <v>129726811</v>
       </c>
       <c r="B55" t="n">
-        <v>57735</v>
+        <v>79076</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6460,34 +6450,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>483507</v>
+        <v>483760</v>
       </c>
       <c r="R55" t="n">
-        <v>7145556</v>
+        <v>7145575</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6517,14 +6507,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6539,12 +6534,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6554,7 +6549,7 @@
         <v>129727924</v>
       </c>
       <c r="B56" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6653,32 +6648,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129727914</v>
+        <v>129727922</v>
       </c>
       <c r="B57" t="n">
-        <v>92305</v>
+        <v>57736</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6688,10 +6683,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>483577</v>
+        <v>483507</v>
       </c>
       <c r="R57" t="n">
-        <v>7145438</v>
+        <v>7145556</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6724,6 +6719,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6750,10 +6750,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129726828</v>
+        <v>129727932</v>
       </c>
       <c r="B58" t="n">
-        <v>79075</v>
+        <v>57736</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6761,34 +6761,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>483988</v>
+        <v>483527</v>
       </c>
       <c r="R58" t="n">
-        <v>7145444</v>
+        <v>7145534</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6818,19 +6818,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>08:48</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>08:48</t>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6845,22 +6840,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129716453</v>
+        <v>129727929</v>
       </c>
       <c r="B59" t="n">
-        <v>79075</v>
+        <v>57736</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6868,34 +6863,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>484032</v>
+        <v>483677</v>
       </c>
       <c r="R59" t="n">
-        <v>7145416</v>
+        <v>7145477</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6930,6 +6925,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -6942,22 +6942,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129726953</v>
+        <v>129727930</v>
       </c>
       <c r="B60" t="n">
-        <v>79075</v>
+        <v>57736</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6965,37 +6965,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>483555</v>
+        <v>483658</v>
       </c>
       <c r="R60" t="n">
-        <v>7145531</v>
+        <v>7145503</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7032,7 +7029,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7041,44 +7038,18 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -7088,7 +7059,7 @@
         <v>129716449</v>
       </c>
       <c r="B61" t="n">
-        <v>83044</v>
+        <v>83045</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7182,10 +7153,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129726806</v>
+        <v>129726828</v>
       </c>
       <c r="B62" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7217,10 +7188,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>483558</v>
+        <v>483988</v>
       </c>
       <c r="R62" t="n">
-        <v>7145588</v>
+        <v>7145444</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7252,7 +7223,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7262,7 +7233,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7289,10 +7260,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129726788</v>
+        <v>129716453</v>
       </c>
       <c r="B63" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7320,14 +7291,14 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>483665</v>
+        <v>484032</v>
       </c>
       <c r="R63" t="n">
-        <v>7145479</v>
+        <v>7145416</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7357,19 +7328,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>11:18</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>11:18</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7384,22 +7345,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129727929</v>
+        <v>129726953</v>
       </c>
       <c r="B64" t="n">
-        <v>57735</v>
+        <v>79076</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7407,34 +7368,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>483677</v>
+        <v>483555</v>
       </c>
       <c r="R64" t="n">
-        <v>7145477</v>
+        <v>7145531</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7471,7 +7435,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7480,28 +7444,54 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129727932</v>
+        <v>129726806</v>
       </c>
       <c r="B65" t="n">
-        <v>57735</v>
+        <v>79076</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7509,34 +7499,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>483527</v>
+        <v>483558</v>
       </c>
       <c r="R65" t="n">
-        <v>7145534</v>
+        <v>7145588</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7566,14 +7556,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7588,22 +7583,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129727930</v>
+        <v>129726788</v>
       </c>
       <c r="B66" t="n">
-        <v>57735</v>
+        <v>79076</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7611,34 +7606,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>483658</v>
+        <v>483665</v>
       </c>
       <c r="R66" t="n">
-        <v>7145503</v>
+        <v>7145479</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7668,14 +7663,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7690,12 +7690,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -7705,7 +7705,7 @@
         <v>129716448</v>
       </c>
       <c r="B67" t="n">
-        <v>91538</v>
+        <v>91539</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7799,10 +7799,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129726937</v>
+        <v>129726958</v>
       </c>
       <c r="B68" t="n">
-        <v>57735</v>
+        <v>79076</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7810,46 +7810,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>483749</v>
+        <v>483482</v>
       </c>
       <c r="R68" t="n">
-        <v>7145581</v>
+        <v>7145330</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7886,7 +7877,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en levande gran.</t>
+          <t>På en levande gran.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7895,6 +7886,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7915,12 +7907,12 @@
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -7938,10 +7930,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129727916</v>
+        <v>129726966</v>
       </c>
       <c r="B69" t="n">
-        <v>57735</v>
+        <v>79076</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7949,34 +7941,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>483577</v>
+        <v>483764</v>
       </c>
       <c r="R69" t="n">
-        <v>7145734</v>
+        <v>7145582</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8013,7 +8008,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Långväxta bålar på en levande gran.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8022,28 +8017,54 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129727918</v>
+        <v>129726797</v>
       </c>
       <c r="B70" t="n">
-        <v>57735</v>
+        <v>79076</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8051,34 +8072,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>483580</v>
+        <v>483540</v>
       </c>
       <c r="R70" t="n">
-        <v>7145447</v>
+        <v>7145349</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8108,14 +8129,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8130,22 +8156,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129726958</v>
+        <v>129727916</v>
       </c>
       <c r="B71" t="n">
-        <v>79075</v>
+        <v>57736</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8153,37 +8179,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>483482</v>
+        <v>483577</v>
       </c>
       <c r="R71" t="n">
-        <v>7145330</v>
+        <v>7145734</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8220,7 +8243,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>På en levande gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8229,54 +8252,28 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AH71" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129726966</v>
+        <v>129726937</v>
       </c>
       <c r="B72" t="n">
-        <v>79075</v>
+        <v>57736</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8284,37 +8281,46 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>483764</v>
+        <v>483749</v>
       </c>
       <c r="R72" t="n">
-        <v>7145582</v>
+        <v>7145581</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8351,7 +8357,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en levande gran.</t>
+          <t>Ringhack, äldre, på stambasen av en levande gran.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8360,7 +8366,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8381,12 +8386,12 @@
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -8404,10 +8409,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129726797</v>
+        <v>129727918</v>
       </c>
       <c r="B73" t="n">
-        <v>79075</v>
+        <v>57736</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8415,34 +8420,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>483540</v>
+        <v>483580</v>
       </c>
       <c r="R73" t="n">
-        <v>7145349</v>
+        <v>7145447</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8472,19 +8477,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>10:29</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>10:29</t>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8499,12 +8499,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -8514,7 +8514,7 @@
         <v>129726787</v>
       </c>
       <c r="B74" t="n">
-        <v>78088</v>
+        <v>78089</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8621,7 +8621,7 @@
         <v>129726826</v>
       </c>
       <c r="B75" t="n">
-        <v>78088</v>
+        <v>78089</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8725,10 +8725,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129726964</v>
+        <v>129726947</v>
       </c>
       <c r="B76" t="n">
-        <v>79075</v>
+        <v>91584</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8736,26 +8736,30 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -8763,10 +8767,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>483553</v>
+        <v>483784</v>
       </c>
       <c r="R76" t="n">
-        <v>7145611</v>
+        <v>7145639</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8803,7 +8807,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>På levande gran i barrblandskog.</t>
+          <t>I levande gran i granskog vid brant.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8818,7 +8822,7 @@
       </c>
       <c r="AH76" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ76" t="inlineStr">
@@ -8833,12 +8837,12 @@
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -8856,10 +8860,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129726947</v>
+        <v>129726964</v>
       </c>
       <c r="B77" t="n">
-        <v>91583</v>
+        <v>79076</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8867,30 +8871,26 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -8898,10 +8898,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>483784</v>
+        <v>483553</v>
       </c>
       <c r="R77" t="n">
-        <v>7145639</v>
+        <v>7145611</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>I levande gran i granskog vid brant.</t>
+          <t>På levande gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="AH77" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ77" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -8994,7 +8994,7 @@
         <v>129726831</v>
       </c>
       <c r="B78" t="n">
-        <v>83044</v>
+        <v>83045</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9101,7 +9101,7 @@
         <v>129726796</v>
       </c>
       <c r="B79" t="n">
-        <v>83042</v>
+        <v>83043</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9205,10 +9205,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129726963</v>
+        <v>129726793</v>
       </c>
       <c r="B80" t="n">
-        <v>79075</v>
+        <v>57896</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9216,40 +9216,46 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>483498</v>
+        <v>483572</v>
       </c>
       <c r="R80" t="n">
-        <v>7145585</v>
+        <v>7145322</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9276,14 +9282,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>På levande gran.</t>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9292,54 +9303,28 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
-      </c>
-      <c r="AH80" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK80" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129726812</v>
+        <v>129716465</v>
       </c>
       <c r="B81" t="n">
-        <v>79075</v>
+        <v>91588</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9347,34 +9332,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>483764</v>
+        <v>483983</v>
       </c>
       <c r="R81" t="n">
-        <v>7145589</v>
+        <v>7145507</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9404,19 +9389,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>09:34</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>09:34</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9431,22 +9406,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129726823</v>
+        <v>129727941</v>
       </c>
       <c r="B82" t="n">
-        <v>79075</v>
+        <v>91584</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9454,34 +9429,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>483959</v>
+        <v>483551</v>
       </c>
       <c r="R82" t="n">
-        <v>7145539</v>
+        <v>7145323</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9511,19 +9486,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>09:02</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>09:02</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9538,22 +9503,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129716451</v>
+        <v>129726963</v>
       </c>
       <c r="B83" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9579,16 +9544,19 @@
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>483989</v>
+        <v>483498</v>
       </c>
       <c r="R83" t="n">
-        <v>7145511</v>
+        <v>7145585</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9623,34 +9591,65 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>På levande gran.</t>
+        </is>
+      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129726798</v>
+        <v>129726812</v>
       </c>
       <c r="B84" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9682,10 +9681,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>483429</v>
+        <v>483764</v>
       </c>
       <c r="R84" t="n">
-        <v>7145430</v>
+        <v>7145589</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9717,7 +9716,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9727,7 +9726,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9754,10 +9753,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129716465</v>
+        <v>129726823</v>
       </c>
       <c r="B85" t="n">
-        <v>91587</v>
+        <v>79076</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9765,34 +9764,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>483983</v>
+        <v>483959</v>
       </c>
       <c r="R85" t="n">
-        <v>7145507</v>
+        <v>7145539</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9822,9 +9821,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9839,22 +9848,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129727941</v>
+        <v>129716451</v>
       </c>
       <c r="B86" t="n">
-        <v>91583</v>
+        <v>79076</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9862,34 +9871,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>483551</v>
+        <v>483989</v>
       </c>
       <c r="R86" t="n">
-        <v>7145323</v>
+        <v>7145511</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9936,22 +9945,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129726795</v>
+        <v>129726798</v>
       </c>
       <c r="B87" t="n">
-        <v>83049</v>
+        <v>79076</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9959,21 +9968,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9983,10 +9992,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>483545</v>
+        <v>483429</v>
       </c>
       <c r="R87" t="n">
-        <v>7145343</v>
+        <v>7145430</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10018,7 +10027,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10028,7 +10037,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10058,7 +10067,7 @@
         <v>129727942</v>
       </c>
       <c r="B88" t="n">
-        <v>91607</v>
+        <v>91608</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10148,10 +10157,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129727940</v>
+        <v>129726795</v>
       </c>
       <c r="B89" t="n">
-        <v>57732</v>
+        <v>83050</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10159,34 +10168,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100049</v>
+        <v>1467</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>483677</v>
+        <v>483545</v>
       </c>
       <c r="R89" t="n">
-        <v>7145478</v>
+        <v>7145343</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10216,14 +10225,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Hack ganska färska</t>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10238,22 +10252,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129726793</v>
+        <v>129727940</v>
       </c>
       <c r="B90" t="n">
-        <v>57895</v>
+        <v>57733</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10261,46 +10275,37 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>483572</v>
+        <v>483677</v>
       </c>
       <c r="R90" t="n">
-        <v>7145322</v>
+        <v>7145478</v>
       </c>
       <c r="S90" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10327,19 +10332,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>10:55</t>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Hack ganska färska</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10354,57 +10354,60 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129726832</v>
+        <v>129726945</v>
       </c>
       <c r="B91" t="n">
-        <v>79075</v>
+        <v>80209</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>484041</v>
+        <v>483364</v>
       </c>
       <c r="R91" t="n">
-        <v>7145466</v>
+        <v>7145533</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10434,87 +10437,75 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>08:39</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>08:39</t>
-        </is>
-      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129726945</v>
+        <v>129726832</v>
       </c>
       <c r="B92" t="n">
-        <v>80208</v>
+        <v>79076</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>483364</v>
+        <v>484041</v>
       </c>
       <c r="R92" t="n">
-        <v>7145533</v>
+        <v>7145466</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10544,30 +10535,39 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>08:39</t>
+        </is>
+      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>08:39</t>
+        </is>
+      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
@@ -10577,7 +10577,7 @@
         <v>129726799</v>
       </c>
       <c r="B93" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10681,10 +10681,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129726942</v>
+        <v>129726940</v>
       </c>
       <c r="B94" t="n">
-        <v>80181</v>
+        <v>57733</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10692,28 +10692,29 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N94" t="inlineStr"/>
@@ -10723,10 +10724,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>483377</v>
+        <v>483382</v>
       </c>
       <c r="R94" t="n">
-        <v>7145537</v>
+        <v>7145460</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10763,7 +10764,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>På en levande sälg i granskog.</t>
+          <t>Äldre och färska hackspår i en grov stående död gran av full längd.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10772,33 +10773,32 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM94" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -10816,10 +10816,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129716456</v>
+        <v>129716457</v>
       </c>
       <c r="B95" t="n">
-        <v>82910</v>
+        <v>91608</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10827,23 +10827,19 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -10851,10 +10847,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>483445</v>
+        <v>483922</v>
       </c>
       <c r="R95" t="n">
-        <v>7145393</v>
+        <v>7145565</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10916,7 +10912,7 @@
         <v>129726967</v>
       </c>
       <c r="B96" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11047,7 +11043,7 @@
         <v>129726951</v>
       </c>
       <c r="B97" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11178,7 +11174,7 @@
         <v>129726965</v>
       </c>
       <c r="B98" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11306,10 +11302,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129726940</v>
+        <v>129726942</v>
       </c>
       <c r="B99" t="n">
-        <v>57732</v>
+        <v>80182</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11317,29 +11313,28 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N99" t="inlineStr"/>
@@ -11349,10 +11344,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>483382</v>
+        <v>483377</v>
       </c>
       <c r="R99" t="n">
-        <v>7145460</v>
+        <v>7145537</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11389,7 +11384,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Äldre och färska hackspår i en grov stående död gran av full längd.</t>
+          <t>På en levande sälg i granskog.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11398,32 +11393,33 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>
@@ -11441,10 +11437,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129716457</v>
+        <v>129716456</v>
       </c>
       <c r="B100" t="n">
-        <v>91607</v>
+        <v>82911</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11452,19 +11448,23 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr"/>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
@@ -11472,10 +11472,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>483922</v>
+        <v>483445</v>
       </c>
       <c r="R100" t="n">
-        <v>7145565</v>
+        <v>7145393</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11534,10 +11534,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129726934</v>
+        <v>129726962</v>
       </c>
       <c r="B101" t="n">
-        <v>57735</v>
+        <v>79076</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11545,46 +11545,37 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>483487</v>
+        <v>483460</v>
       </c>
       <c r="R101" t="n">
-        <v>7145568</v>
+        <v>7145602</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11621,7 +11612,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en stående död gran av full längd med 42 cm i brösthöjdsdiameter.</t>
+          <t>På gran i tallskog.</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11630,12 +11621,13 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ101" t="inlineStr">
@@ -11650,12 +11642,12 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -11673,10 +11665,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129726962</v>
+        <v>129726956</v>
       </c>
       <c r="B102" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11711,10 +11703,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>483460</v>
+        <v>483519</v>
       </c>
       <c r="R102" t="n">
-        <v>7145602</v>
+        <v>7145306</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11751,7 +11743,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>På gran i tallskog.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11766,7 +11758,7 @@
       </c>
       <c r="AH102" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ102" t="inlineStr">
@@ -11779,14 +11771,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM102" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -11804,10 +11791,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129726956</v>
+        <v>129716467</v>
       </c>
       <c r="B103" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11833,19 +11820,16 @@
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>483519</v>
+        <v>483805</v>
       </c>
       <c r="R103" t="n">
-        <v>7145306</v>
+        <v>7145587</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11880,60 +11864,34 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD103" t="b">
         <v>0</v>
       </c>
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
-      </c>
-      <c r="AH103" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ103" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK103" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO103" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129716467</v>
+        <v>129726934</v>
       </c>
       <c r="B104" t="n">
-        <v>79075</v>
+        <v>57736</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11941,34 +11899,46 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>483805</v>
+        <v>483487</v>
       </c>
       <c r="R104" t="n">
-        <v>7145587</v>
+        <v>7145568</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12003,6 +11973,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en stående död gran av full längd med 42 cm i brösthöjdsdiameter.</t>
+        </is>
+      </c>
       <c r="AD104" t="b">
         <v>0</v>
       </c>
@@ -12011,26 +11986,51 @@
       </c>
       <c r="AG104" t="b">
         <v>0</v>
+      </c>
+      <c r="AH104" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK104" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM104" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129726830</v>
+        <v>129726957</v>
       </c>
       <c r="B105" t="n">
-        <v>78088</v>
+        <v>79076</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12038,34 +12038,37 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>484008</v>
+        <v>483497</v>
       </c>
       <c r="R105" t="n">
-        <v>7145455</v>
+        <v>7145327</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12095,19 +12098,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>08:43</t>
-        </is>
-      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>08:43</t>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12116,28 +12114,54 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
+      </c>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM105" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129727937</v>
+        <v>129727933</v>
       </c>
       <c r="B106" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12169,10 +12193,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>483824</v>
+        <v>483593</v>
       </c>
       <c r="R106" t="n">
-        <v>7145592</v>
+        <v>7145594</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12209,7 +12233,7 @@
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12236,10 +12260,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129727933</v>
+        <v>129727937</v>
       </c>
       <c r="B107" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12271,10 +12295,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>483593</v>
+        <v>483824</v>
       </c>
       <c r="R107" t="n">
-        <v>7145594</v>
+        <v>7145592</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12311,7 +12335,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12338,10 +12362,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129726957</v>
+        <v>129726830</v>
       </c>
       <c r="B108" t="n">
-        <v>79075</v>
+        <v>78089</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12349,37 +12373,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>483497</v>
+        <v>484008</v>
       </c>
       <c r="R108" t="n">
-        <v>7145327</v>
+        <v>7145455</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12409,14 +12430,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>08:43</t>
+        </is>
+      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12425,54 +12451,28 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
-      </c>
-      <c r="AH108" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ108" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK108" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM108" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO108" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129727939</v>
+        <v>129726792</v>
       </c>
       <c r="B109" t="n">
-        <v>57732</v>
+        <v>79076</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12480,34 +12480,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>483605</v>
+        <v>483571</v>
       </c>
       <c r="R109" t="n">
-        <v>7145281</v>
+        <v>7145360</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12537,14 +12537,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Hack ganska färska</t>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12559,22 +12564,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129727925</v>
+        <v>129726789</v>
       </c>
       <c r="B110" t="n">
-        <v>57735</v>
+        <v>79076</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12582,34 +12587,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>483580</v>
+        <v>483663</v>
       </c>
       <c r="R110" t="n">
-        <v>7145425</v>
+        <v>7145420</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12639,14 +12644,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12661,22 +12671,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129727917</v>
+        <v>129726950</v>
       </c>
       <c r="B111" t="n">
-        <v>57735</v>
+        <v>79076</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12684,34 +12694,37 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>483572</v>
+        <v>483720</v>
       </c>
       <c r="R111" t="n">
-        <v>7145725</v>
+        <v>7145756</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12748,7 +12761,7 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12757,28 +12770,54 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
+      </c>
+      <c r="AH111" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK111" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM111" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO111" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129726949</v>
+        <v>129726959</v>
       </c>
       <c r="B112" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12813,10 +12852,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>483735</v>
+        <v>483422</v>
       </c>
       <c r="R112" t="n">
-        <v>7145746</v>
+        <v>7145360</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12853,7 +12892,7 @@
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På en levande gran.</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12906,10 +12945,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129726792</v>
+        <v>129726817</v>
       </c>
       <c r="B113" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12941,10 +12980,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>483571</v>
+        <v>483834</v>
       </c>
       <c r="R113" t="n">
-        <v>7145360</v>
+        <v>7145605</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12976,7 +13015,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12986,7 +13025,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13013,10 +13052,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129726827</v>
+        <v>129726954</v>
       </c>
       <c r="B114" t="n">
-        <v>83044</v>
+        <v>79076</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13024,34 +13063,37 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>483988</v>
+        <v>483580</v>
       </c>
       <c r="R114" t="n">
-        <v>7145444</v>
+        <v>7145435</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13081,19 +13123,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>08:49</t>
-        </is>
-      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>08:49</t>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>På gran i granskog.</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13102,28 +13139,54 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
+      </c>
+      <c r="AH114" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ114" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK114" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM114" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO114" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129726789</v>
+        <v>129726827</v>
       </c>
       <c r="B115" t="n">
-        <v>79075</v>
+        <v>83045</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13131,21 +13194,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -13155,10 +13218,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>483663</v>
+        <v>483988</v>
       </c>
       <c r="R115" t="n">
-        <v>7145420</v>
+        <v>7145444</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13190,7 +13253,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13200,7 +13263,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13227,10 +13290,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129726950</v>
+        <v>129716454</v>
       </c>
       <c r="B116" t="n">
-        <v>79075</v>
+        <v>91584</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13238,37 +13301,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>483720</v>
+        <v>484017</v>
       </c>
       <c r="R116" t="n">
-        <v>7145756</v>
+        <v>7145437</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13303,65 +13363,34 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
-      </c>
-      <c r="AH116" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ116" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK116" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM116" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO116" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129726959</v>
+        <v>129726949</v>
       </c>
       <c r="B117" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13396,10 +13425,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>483422</v>
+        <v>483735</v>
       </c>
       <c r="R117" t="n">
-        <v>7145360</v>
+        <v>7145746</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13436,7 +13465,7 @@
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>På en levande gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13489,10 +13518,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129726817</v>
+        <v>129727939</v>
       </c>
       <c r="B118" t="n">
-        <v>79075</v>
+        <v>57733</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13500,34 +13529,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>483834</v>
+        <v>483605</v>
       </c>
       <c r="R118" t="n">
-        <v>7145605</v>
+        <v>7145281</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13557,19 +13586,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>09:15</t>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Hack ganska färska</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13584,22 +13608,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129726954</v>
+        <v>129727917</v>
       </c>
       <c r="B119" t="n">
-        <v>79075</v>
+        <v>57736</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13607,37 +13631,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>483580</v>
+        <v>483572</v>
       </c>
       <c r="R119" t="n">
-        <v>7145435</v>
+        <v>7145725</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13674,7 +13695,7 @@
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>På gran i granskog.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13683,54 +13704,28 @@
       <c r="AE119" t="b">
         <v>0</v>
       </c>
-      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
-      </c>
-      <c r="AH119" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ119" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK119" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM119" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO119" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129716454</v>
+        <v>129727925</v>
       </c>
       <c r="B120" t="n">
-        <v>91583</v>
+        <v>57736</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13738,34 +13733,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>484017</v>
+        <v>483580</v>
       </c>
       <c r="R120" t="n">
-        <v>7145437</v>
+        <v>7145425</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13800,6 +13795,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
       <c r="AD120" t="b">
         <v>0</v>
       </c>
@@ -13812,12 +13812,12 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
@@ -13827,7 +13827,7 @@
         <v>129730288</v>
       </c>
       <c r="B121" t="n">
-        <v>91607</v>
+        <v>91608</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13920,7 +13920,7 @@
         <v>129730246</v>
       </c>
       <c r="B122" t="n">
-        <v>80181</v>
+        <v>80182</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14014,10 +14014,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129730292</v>
+        <v>129730241</v>
       </c>
       <c r="B123" t="n">
-        <v>83036</v>
+        <v>57736</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14025,21 +14025,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -14049,10 +14049,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>483314</v>
+        <v>483751</v>
       </c>
       <c r="R123" t="n">
-        <v>7145495</v>
+        <v>7145575</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14085,6 +14085,11 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14111,10 +14116,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129730241</v>
+        <v>129730292</v>
       </c>
       <c r="B124" t="n">
-        <v>57735</v>
+        <v>83037</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14122,21 +14127,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -14146,10 +14151,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>483751</v>
+        <v>483314</v>
       </c>
       <c r="R124" t="n">
-        <v>7145575</v>
+        <v>7145495</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14182,11 +14187,6 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14213,10 +14213,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129730253</v>
+        <v>129730291</v>
       </c>
       <c r="B125" t="n">
-        <v>78832</v>
+        <v>79076</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14224,21 +14224,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14248,10 +14248,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>483421</v>
+        <v>483364</v>
       </c>
       <c r="R125" t="n">
-        <v>7145545</v>
+        <v>7145506</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14310,10 +14310,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129730291</v>
+        <v>129730253</v>
       </c>
       <c r="B126" t="n">
-        <v>79075</v>
+        <v>78833</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14321,21 +14321,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14345,10 +14345,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>483364</v>
+        <v>483421</v>
       </c>
       <c r="R126" t="n">
-        <v>7145506</v>
+        <v>7145545</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14410,7 +14410,7 @@
         <v>129730268</v>
       </c>
       <c r="B127" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14509,10 +14509,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129730248</v>
+        <v>129730290</v>
       </c>
       <c r="B128" t="n">
-        <v>80180</v>
+        <v>91608</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14520,23 +14520,19 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr"/>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
@@ -14544,10 +14540,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>483599</v>
+        <v>483766</v>
       </c>
       <c r="R128" t="n">
-        <v>7145185</v>
+        <v>7145610</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14606,10 +14602,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129730247</v>
+        <v>129730248</v>
       </c>
       <c r="B129" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14641,10 +14637,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>483595</v>
+        <v>483599</v>
       </c>
       <c r="R129" t="n">
-        <v>7145180</v>
+        <v>7145185</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14703,7 +14699,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129730244</v>
+        <v>129730247</v>
       </c>
       <c r="B130" t="n">
         <v>80181</v>
@@ -14714,21 +14710,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14738,10 +14734,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>483599</v>
+        <v>483595</v>
       </c>
       <c r="R130" t="n">
-        <v>7145190</v>
+        <v>7145180</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14803,7 +14799,7 @@
         <v>129730274</v>
       </c>
       <c r="B131" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14902,10 +14898,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129730290</v>
+        <v>129730244</v>
       </c>
       <c r="B132" t="n">
-        <v>91607</v>
+        <v>80182</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14913,19 +14909,23 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr"/>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
@@ -14933,10 +14933,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>483766</v>
+        <v>483599</v>
       </c>
       <c r="R132" t="n">
-        <v>7145610</v>
+        <v>7145190</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14995,10 +14995,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129730252</v>
+        <v>129730242</v>
       </c>
       <c r="B133" t="n">
-        <v>78832</v>
+        <v>79666</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15006,21 +15006,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -15030,10 +15030,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>483407</v>
+        <v>483421</v>
       </c>
       <c r="R133" t="n">
-        <v>7145540</v>
+        <v>7145545</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15095,7 +15095,7 @@
         <v>129730287</v>
       </c>
       <c r="B134" t="n">
-        <v>91583</v>
+        <v>91584</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15192,7 +15192,7 @@
         <v>129730255</v>
       </c>
       <c r="B135" t="n">
-        <v>91607</v>
+        <v>91608</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15282,10 +15282,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129730242</v>
+        <v>129730252</v>
       </c>
       <c r="B136" t="n">
-        <v>79665</v>
+        <v>78833</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15293,21 +15293,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15317,10 +15317,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>483421</v>
+        <v>483407</v>
       </c>
       <c r="R136" t="n">
-        <v>7145545</v>
+        <v>7145540</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15382,7 +15382,7 @@
         <v>129730284</v>
       </c>
       <c r="B137" t="n">
-        <v>78088</v>
+        <v>78089</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15479,7 +15479,7 @@
         <v>129730250</v>
       </c>
       <c r="B138" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15576,7 +15576,7 @@
         <v>129730293</v>
       </c>
       <c r="B139" t="n">
-        <v>83036</v>
+        <v>83037</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15673,7 +15673,7 @@
         <v>129730262</v>
       </c>
       <c r="B140" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15775,7 +15775,7 @@
         <v>129730249</v>
       </c>
       <c r="B141" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15872,7 +15872,7 @@
         <v>129730281</v>
       </c>
       <c r="B142" t="n">
-        <v>80084</v>
+        <v>80085</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15969,7 +15969,7 @@
         <v>129730254</v>
       </c>
       <c r="B143" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16066,7 +16066,7 @@
         <v>129730285</v>
       </c>
       <c r="B144" t="n">
-        <v>83052</v>
+        <v>83053</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16163,7 +16163,7 @@
         <v>129730261</v>
       </c>
       <c r="B145" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16260,7 +16260,7 @@
         <v>129730289</v>
       </c>
       <c r="B146" t="n">
-        <v>91607</v>
+        <v>91608</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16353,7 +16353,7 @@
         <v>129730294</v>
       </c>
       <c r="B147" t="n">
-        <v>83036</v>
+        <v>83037</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16450,7 +16450,7 @@
         <v>129730240</v>
       </c>
       <c r="B148" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16549,10 +16549,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129730260</v>
+        <v>129730295</v>
       </c>
       <c r="B149" t="n">
-        <v>79075</v>
+        <v>83037</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16560,21 +16560,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16584,10 +16584,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>483324</v>
+        <v>483462</v>
       </c>
       <c r="R149" t="n">
-        <v>7145520</v>
+        <v>7145552</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16646,10 +16646,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129730295</v>
+        <v>129730260</v>
       </c>
       <c r="B150" t="n">
-        <v>83036</v>
+        <v>79076</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16657,21 +16657,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16681,10 +16681,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>483462</v>
+        <v>483324</v>
       </c>
       <c r="R150" t="n">
-        <v>7145552</v>
+        <v>7145520</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16746,7 +16746,7 @@
         <v>129730282</v>
       </c>
       <c r="B151" t="n">
-        <v>80084</v>
+        <v>80085</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16843,7 +16843,7 @@
         <v>129730296</v>
       </c>
       <c r="B152" t="n">
-        <v>83036</v>
+        <v>83037</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16937,27 +16937,27 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129730286</v>
+        <v>129730269</v>
       </c>
       <c r="B153" t="n">
-        <v>57839</v>
+        <v>57736</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -16972,10 +16972,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>483251</v>
+        <v>483364</v>
       </c>
       <c r="R153" t="n">
-        <v>7145567</v>
+        <v>7145545</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17008,6 +17008,11 @@
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17037,7 +17042,7 @@
         <v>129730267</v>
       </c>
       <c r="B154" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17136,27 +17141,27 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129730269</v>
+        <v>129730286</v>
       </c>
       <c r="B155" t="n">
-        <v>57735</v>
+        <v>57840</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -17171,10 +17176,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>483364</v>
+        <v>483251</v>
       </c>
       <c r="R155" t="n">
-        <v>7145545</v>
+        <v>7145567</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17207,11 +17212,6 @@
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC155" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17238,10 +17238,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129730264</v>
+        <v>129730258</v>
       </c>
       <c r="B156" t="n">
-        <v>57735</v>
+        <v>79076</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17249,21 +17249,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -17273,10 +17273,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>483665</v>
+        <v>483592</v>
       </c>
       <c r="R156" t="n">
-        <v>7145576</v>
+        <v>7145458</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17309,11 +17309,6 @@
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17340,10 +17335,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129730276</v>
+        <v>129730257</v>
       </c>
       <c r="B157" t="n">
-        <v>57735</v>
+        <v>79076</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17351,54 +17346,34 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L157" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N157" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
           <t>Bodknulen, Jmt</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>483545</v>
+        <v>483635</v>
       </c>
       <c r="R157" t="n">
-        <v>7145332</v>
+        <v>7145484</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17460,7 +17435,7 @@
         <v>129730265</v>
       </c>
       <c r="B158" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17559,10 +17534,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129730258</v>
+        <v>129730276</v>
       </c>
       <c r="B159" t="n">
-        <v>79075</v>
+        <v>57736</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17570,34 +17545,54 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
           <t>Bodknulen, Jmt</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>483592</v>
+        <v>483545</v>
       </c>
       <c r="R159" t="n">
-        <v>7145458</v>
+        <v>7145332</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17656,10 +17651,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129730257</v>
+        <v>129730264</v>
       </c>
       <c r="B160" t="n">
-        <v>79075</v>
+        <v>57736</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17667,21 +17662,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17691,10 +17686,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>483635</v>
+        <v>483665</v>
       </c>
       <c r="R160" t="n">
-        <v>7145484</v>
+        <v>7145576</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17727,6 +17722,11 @@
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17756,7 +17756,7 @@
         <v>129730256</v>
       </c>
       <c r="B161" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17853,7 +17853,7 @@
         <v>129730263</v>
       </c>
       <c r="B162" t="n">
-        <v>83044</v>
+        <v>83045</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17950,7 +17950,7 @@
         <v>129730259</v>
       </c>
       <c r="B163" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18044,10 +18044,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129730273</v>
+        <v>129730271</v>
       </c>
       <c r="B164" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18079,10 +18079,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>483589</v>
+        <v>483461</v>
       </c>
       <c r="R164" t="n">
-        <v>7145604</v>
+        <v>7145552</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18149,7 +18149,7 @@
         <v>129730272</v>
       </c>
       <c r="B165" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18248,10 +18248,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129730271</v>
+        <v>129730273</v>
       </c>
       <c r="B166" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18283,10 +18283,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>483461</v>
+        <v>483589</v>
       </c>
       <c r="R166" t="n">
-        <v>7145552</v>
+        <v>7145604</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18353,7 +18353,7 @@
         <v>129730270</v>
       </c>
       <c r="B167" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>

--- a/artfynd/A 52753-2025 artfynd.xlsx
+++ b/artfynd/A 52753-2025 artfynd.xlsx
@@ -2892,45 +2892,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129726825</v>
+        <v>129727915</v>
       </c>
       <c r="B22" t="n">
-        <v>79076</v>
+        <v>92306</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483962</v>
+        <v>483493</v>
       </c>
       <c r="R22" t="n">
-        <v>7145447</v>
+        <v>7145538</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2960,19 +2960,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>08:51</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>08:51</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2987,22 +2977,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129726813</v>
+        <v>129726818</v>
       </c>
       <c r="B23" t="n">
-        <v>79076</v>
+        <v>83045</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3010,21 +3000,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3034,10 +3024,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483773</v>
+        <v>483849</v>
       </c>
       <c r="R23" t="n">
-        <v>7145613</v>
+        <v>7145605</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3069,7 +3059,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3079,7 +3069,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3106,7 +3096,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129726814</v>
+        <v>129726825</v>
       </c>
       <c r="B24" t="n">
         <v>79076</v>
@@ -3141,10 +3131,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>483796</v>
+        <v>483962</v>
       </c>
       <c r="R24" t="n">
-        <v>7145620</v>
+        <v>7145447</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3176,7 +3166,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3186,7 +3176,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3213,10 +3203,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129727934</v>
+        <v>129726813</v>
       </c>
       <c r="B25" t="n">
-        <v>57736</v>
+        <v>79076</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3224,34 +3214,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>483619</v>
+        <v>483773</v>
       </c>
       <c r="R25" t="n">
-        <v>7145595</v>
+        <v>7145613</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3281,14 +3271,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3303,57 +3298,57 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129727915</v>
+        <v>129726814</v>
       </c>
       <c r="B26" t="n">
-        <v>92306</v>
+        <v>79076</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>483493</v>
+        <v>483796</v>
       </c>
       <c r="R26" t="n">
-        <v>7145538</v>
+        <v>7145620</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3383,9 +3378,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3400,22 +3405,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129726818</v>
+        <v>129727934</v>
       </c>
       <c r="B27" t="n">
-        <v>83045</v>
+        <v>57736</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3423,34 +3428,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>483849</v>
+        <v>483619</v>
       </c>
       <c r="R27" t="n">
-        <v>7145605</v>
+        <v>7145595</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3480,19 +3485,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>09:13</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>09:13</t>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3507,12 +3507,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3867,10 +3867,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129716460</v>
+        <v>129727931</v>
       </c>
       <c r="B31" t="n">
-        <v>79076</v>
+        <v>57736</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3878,34 +3878,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>483445</v>
+        <v>483545</v>
       </c>
       <c r="R31" t="n">
-        <v>7145428</v>
+        <v>7145507</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3940,6 +3940,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -3952,19 +3957,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129726961</v>
+        <v>129716460</v>
       </c>
       <c r="B32" t="n">
         <v>79076</v>
@@ -3993,19 +3998,16 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>483414</v>
+        <v>483445</v>
       </c>
       <c r="R32" t="n">
-        <v>7145535</v>
+        <v>7145428</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4040,62 +4042,31 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På en levande gran.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129726824</v>
+        <v>129726961</v>
       </c>
       <c r="B33" t="n">
         <v>79076</v>
@@ -4124,16 +4095,19 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>483981</v>
+        <v>483414</v>
       </c>
       <c r="R33" t="n">
-        <v>7145521</v>
+        <v>7145535</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4163,19 +4137,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>08:59</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>08:59</t>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På en levande gran.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4184,28 +4153,54 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129727931</v>
+        <v>129726824</v>
       </c>
       <c r="B34" t="n">
-        <v>57736</v>
+        <v>79076</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4213,34 +4208,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>483545</v>
+        <v>483981</v>
       </c>
       <c r="R34" t="n">
-        <v>7145507</v>
+        <v>7145521</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4270,14 +4265,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>08:59</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4292,12 +4292,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -6144,48 +6144,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129726944</v>
+        <v>129727924</v>
       </c>
       <c r="B52" t="n">
-        <v>80209</v>
+        <v>57736</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>483597</v>
+        <v>483548</v>
       </c>
       <c r="R52" t="n">
-        <v>7145735</v>
+        <v>7145488</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6220,35 +6217,39 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129716458</v>
+        <v>129727922</v>
       </c>
       <c r="B53" t="n">
-        <v>83045</v>
+        <v>57736</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6256,34 +6257,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>483701</v>
+        <v>483507</v>
       </c>
       <c r="R53" t="n">
-        <v>7145588</v>
+        <v>7145556</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6318,6 +6319,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6330,57 +6336,57 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129727914</v>
+        <v>129726811</v>
       </c>
       <c r="B54" t="n">
-        <v>92306</v>
+        <v>79076</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>483577</v>
+        <v>483760</v>
       </c>
       <c r="R54" t="n">
-        <v>7145438</v>
+        <v>7145575</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6410,9 +6416,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6427,57 +6443,57 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129726811</v>
+        <v>129727914</v>
       </c>
       <c r="B55" t="n">
-        <v>79076</v>
+        <v>92306</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>483760</v>
+        <v>483577</v>
       </c>
       <c r="R55" t="n">
-        <v>7145575</v>
+        <v>7145438</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6507,19 +6523,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>09:35</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>09:35</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6534,57 +6540,60 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129727924</v>
+        <v>129726944</v>
       </c>
       <c r="B56" t="n">
-        <v>57736</v>
+        <v>80209</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>483548</v>
+        <v>483597</v>
       </c>
       <c r="R56" t="n">
-        <v>7145488</v>
+        <v>7145735</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6619,39 +6628,35 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129727922</v>
+        <v>129716458</v>
       </c>
       <c r="B57" t="n">
-        <v>57736</v>
+        <v>83045</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6659,34 +6664,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>483507</v>
+        <v>483701</v>
       </c>
       <c r="R57" t="n">
-        <v>7145556</v>
+        <v>7145588</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6721,11 +6726,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6738,12 +6738,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -8991,10 +8991,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129726831</v>
+        <v>129716465</v>
       </c>
       <c r="B78" t="n">
-        <v>83045</v>
+        <v>91588</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9002,34 +9002,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>484008</v>
+        <v>483983</v>
       </c>
       <c r="R78" t="n">
-        <v>7145455</v>
+        <v>7145507</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9059,19 +9059,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>08:42</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>08:42</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9086,57 +9076,57 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129726796</v>
+        <v>129727941</v>
       </c>
       <c r="B79" t="n">
-        <v>83043</v>
+        <v>91584</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6486</v>
+        <v>1108</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>483545</v>
+        <v>483551</v>
       </c>
       <c r="R79" t="n">
-        <v>7145343</v>
+        <v>7145323</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9166,19 +9156,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>10:34</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>10:34</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9193,22 +9173,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129726793</v>
+        <v>129726823</v>
       </c>
       <c r="B80" t="n">
-        <v>57896</v>
+        <v>79076</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9216,46 +9196,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>483572</v>
+        <v>483959</v>
       </c>
       <c r="R80" t="n">
-        <v>7145322</v>
+        <v>7145539</v>
       </c>
       <c r="S80" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9284,7 +9255,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9294,7 +9265,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9321,10 +9292,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129716465</v>
+        <v>129726798</v>
       </c>
       <c r="B81" t="n">
-        <v>91588</v>
+        <v>79076</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9332,34 +9303,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>483983</v>
+        <v>483429</v>
       </c>
       <c r="R81" t="n">
-        <v>7145507</v>
+        <v>7145430</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9389,9 +9360,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9406,22 +9387,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129727941</v>
+        <v>129727942</v>
       </c>
       <c r="B82" t="n">
-        <v>91584</v>
+        <v>91608</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9429,23 +9410,19 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -9453,10 +9430,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>483551</v>
+        <v>483495</v>
       </c>
       <c r="R82" t="n">
-        <v>7145323</v>
+        <v>7145618</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9753,7 +9730,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129726823</v>
+        <v>129716451</v>
       </c>
       <c r="B85" t="n">
         <v>79076</v>
@@ -9784,14 +9761,14 @@
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>483959</v>
+        <v>483989</v>
       </c>
       <c r="R85" t="n">
-        <v>7145539</v>
+        <v>7145511</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9821,19 +9798,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>09:02</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>09:02</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9848,22 +9815,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129716451</v>
+        <v>129726795</v>
       </c>
       <c r="B86" t="n">
-        <v>79076</v>
+        <v>83050</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9871,34 +9838,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>483989</v>
+        <v>483545</v>
       </c>
       <c r="R86" t="n">
-        <v>7145511</v>
+        <v>7145343</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9928,9 +9895,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9945,22 +9922,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129726798</v>
+        <v>129727940</v>
       </c>
       <c r="B87" t="n">
-        <v>79076</v>
+        <v>57733</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9968,34 +9945,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>483429</v>
+        <v>483677</v>
       </c>
       <c r="R87" t="n">
-        <v>7145430</v>
+        <v>7145478</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10025,19 +10002,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>10:16</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>10:16</t>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Hack ganska färska</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10052,22 +10024,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129727942</v>
+        <v>129726831</v>
       </c>
       <c r="B88" t="n">
-        <v>91608</v>
+        <v>83045</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10075,30 +10047,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr"/>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>483495</v>
+        <v>484008</v>
       </c>
       <c r="R88" t="n">
-        <v>7145618</v>
+        <v>7145455</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10128,9 +10104,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>08:42</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10145,44 +10131,44 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129726795</v>
+        <v>129726796</v>
       </c>
       <c r="B89" t="n">
-        <v>83050</v>
+        <v>83043</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1467</v>
+        <v>6486</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10227,7 +10213,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10237,7 +10223,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10264,10 +10250,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129727940</v>
+        <v>129726793</v>
       </c>
       <c r="B90" t="n">
-        <v>57733</v>
+        <v>57896</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10275,37 +10261,46 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>483677</v>
+        <v>483572</v>
       </c>
       <c r="R90" t="n">
-        <v>7145478</v>
+        <v>7145322</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10332,14 +10327,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Hack ganska färska</t>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10354,12 +10354,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
@@ -12469,7 +12469,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129726792</v>
+        <v>129726949</v>
       </c>
       <c r="B109" t="n">
         <v>79076</v>
@@ -12498,16 +12498,19 @@
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>483571</v>
+        <v>483735</v>
       </c>
       <c r="R109" t="n">
-        <v>7145360</v>
+        <v>7145746</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12537,19 +12540,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>10:58</t>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12558,25 +12556,51 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK109" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM109" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO109" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129726789</v>
+        <v>129726792</v>
       </c>
       <c r="B110" t="n">
         <v>79076</v>
@@ -12611,10 +12635,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>483663</v>
+        <v>483571</v>
       </c>
       <c r="R110" t="n">
-        <v>7145420</v>
+        <v>7145360</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12646,7 +12670,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12656,7 +12680,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12683,7 +12707,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129726950</v>
+        <v>129726789</v>
       </c>
       <c r="B111" t="n">
         <v>79076</v>
@@ -12712,19 +12736,16 @@
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>483720</v>
+        <v>483663</v>
       </c>
       <c r="R111" t="n">
-        <v>7145756</v>
+        <v>7145420</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12754,14 +12775,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12770,51 +12796,25 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
-      </c>
-      <c r="AH111" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ111" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK111" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM111" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO111" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129726959</v>
+        <v>129726950</v>
       </c>
       <c r="B112" t="n">
         <v>79076</v>
@@ -12852,10 +12852,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>483422</v>
+        <v>483720</v>
       </c>
       <c r="R112" t="n">
-        <v>7145360</v>
+        <v>7145756</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12892,7 +12892,7 @@
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>På en levande gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12945,7 +12945,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129726817</v>
+        <v>129726959</v>
       </c>
       <c r="B113" t="n">
         <v>79076</v>
@@ -12974,16 +12974,19 @@
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>483834</v>
+        <v>483422</v>
       </c>
       <c r="R113" t="n">
-        <v>7145605</v>
+        <v>7145360</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13013,19 +13016,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z113" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB113" t="inlineStr">
-        <is>
-          <t>09:15</t>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>På en levande gran.</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13034,25 +13032,51 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
+      </c>
+      <c r="AH113" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK113" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM113" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO113" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129726954</v>
+        <v>129726817</v>
       </c>
       <c r="B114" t="n">
         <v>79076</v>
@@ -13081,19 +13105,16 @@
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>483580</v>
+        <v>483834</v>
       </c>
       <c r="R114" t="n">
-        <v>7145435</v>
+        <v>7145605</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13123,14 +13144,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>På gran i granskog.</t>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13139,54 +13165,28 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
-      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
-      </c>
-      <c r="AH114" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ114" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK114" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM114" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO114" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129726827</v>
+        <v>129726954</v>
       </c>
       <c r="B115" t="n">
-        <v>83045</v>
+        <v>79076</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13194,34 +13194,37 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>483988</v>
+        <v>483580</v>
       </c>
       <c r="R115" t="n">
-        <v>7145444</v>
+        <v>7145435</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13251,19 +13254,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z115" t="inlineStr">
-        <is>
-          <t>08:49</t>
-        </is>
-      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB115" t="inlineStr">
-        <is>
-          <t>08:49</t>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>På gran i granskog.</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13272,18 +13270,44 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
+      </c>
+      <c r="AH115" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ115" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK115" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM115" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO115" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
@@ -13387,10 +13411,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129726949</v>
+        <v>129726827</v>
       </c>
       <c r="B117" t="n">
-        <v>79076</v>
+        <v>83045</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13398,37 +13422,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>483735</v>
+        <v>483988</v>
       </c>
       <c r="R117" t="n">
-        <v>7145746</v>
+        <v>7145444</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13458,14 +13479,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13474,44 +13500,18 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
-      </c>
-      <c r="AH117" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ117" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK117" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM117" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO117" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
@@ -14014,10 +14014,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129730241</v>
+        <v>129730292</v>
       </c>
       <c r="B123" t="n">
-        <v>57736</v>
+        <v>83037</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14025,21 +14025,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -14049,10 +14049,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>483751</v>
+        <v>483314</v>
       </c>
       <c r="R123" t="n">
-        <v>7145575</v>
+        <v>7145495</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14085,11 +14085,6 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14116,10 +14111,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129730292</v>
+        <v>129730241</v>
       </c>
       <c r="B124" t="n">
-        <v>83037</v>
+        <v>57736</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14127,21 +14122,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -14151,10 +14146,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>483314</v>
+        <v>483751</v>
       </c>
       <c r="R124" t="n">
-        <v>7145495</v>
+        <v>7145575</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14187,6 +14182,11 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14213,10 +14213,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129730291</v>
+        <v>129730253</v>
       </c>
       <c r="B125" t="n">
-        <v>79076</v>
+        <v>78833</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14224,21 +14224,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14248,10 +14248,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>483364</v>
+        <v>483421</v>
       </c>
       <c r="R125" t="n">
-        <v>7145506</v>
+        <v>7145545</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14310,10 +14310,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129730253</v>
+        <v>129730268</v>
       </c>
       <c r="B126" t="n">
-        <v>78833</v>
+        <v>57736</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14321,21 +14321,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14345,10 +14345,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>483421</v>
+        <v>483247</v>
       </c>
       <c r="R126" t="n">
-        <v>7145545</v>
+        <v>7145580</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14381,6 +14381,11 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14407,10 +14412,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129730268</v>
+        <v>129730291</v>
       </c>
       <c r="B127" t="n">
-        <v>57736</v>
+        <v>79076</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14418,21 +14423,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14442,10 +14447,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>483247</v>
+        <v>483364</v>
       </c>
       <c r="R127" t="n">
-        <v>7145580</v>
+        <v>7145506</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14478,11 +14483,6 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14995,10 +14995,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129730242</v>
+        <v>129730287</v>
       </c>
       <c r="B133" t="n">
-        <v>79666</v>
+        <v>91584</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15006,21 +15006,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>229821</v>
+        <v>1108</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -15030,10 +15030,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>483421</v>
+        <v>483608</v>
       </c>
       <c r="R133" t="n">
-        <v>7145545</v>
+        <v>7145490</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15092,10 +15092,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129730287</v>
+        <v>129730255</v>
       </c>
       <c r="B134" t="n">
-        <v>91584</v>
+        <v>91608</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15103,23 +15103,19 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
@@ -15127,10 +15123,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>483608</v>
+        <v>483529</v>
       </c>
       <c r="R134" t="n">
-        <v>7145490</v>
+        <v>7145591</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15189,10 +15185,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129730255</v>
+        <v>129730252</v>
       </c>
       <c r="B135" t="n">
-        <v>91608</v>
+        <v>78833</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15200,19 +15196,23 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5432</v>
+        <v>6446</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr"/>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
@@ -15220,10 +15220,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>483529</v>
+        <v>483407</v>
       </c>
       <c r="R135" t="n">
-        <v>7145591</v>
+        <v>7145540</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15282,10 +15282,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129730252</v>
+        <v>129730242</v>
       </c>
       <c r="B136" t="n">
-        <v>78833</v>
+        <v>79666</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15293,21 +15293,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15317,10 +15317,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>483407</v>
+        <v>483421</v>
       </c>
       <c r="R136" t="n">
-        <v>7145540</v>
+        <v>7145545</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>

--- a/artfynd/A 52753-2025 artfynd.xlsx
+++ b/artfynd/A 52753-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129726815</v>
       </c>
       <c r="B2" t="n">
-        <v>83037</v>
+        <v>83042</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129716450</v>
+        <v>129726820</v>
       </c>
       <c r="B3" t="n">
-        <v>79076</v>
+        <v>83055</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483823</v>
+        <v>483921</v>
       </c>
       <c r="R3" t="n">
-        <v>7145591</v>
+        <v>7145571</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,9 +850,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,22 +877,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129726952</v>
+        <v>129726936</v>
       </c>
       <c r="B4" t="n">
-        <v>79076</v>
+        <v>57736</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,37 +900,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483538</v>
+        <v>483746</v>
       </c>
       <c r="R4" t="n">
-        <v>7145695</v>
+        <v>7145582</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,7 +976,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, äldre, på stambasen av en levande gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -966,7 +985,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -987,12 +1005,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1010,10 +1028,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129726820</v>
+        <v>129727928</v>
       </c>
       <c r="B5" t="n">
-        <v>83050</v>
+        <v>57736</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1021,34 +1039,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1467</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483921</v>
+        <v>483704</v>
       </c>
       <c r="R5" t="n">
-        <v>7145571</v>
+        <v>7145461</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,19 +1096,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>09:08</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>09:08</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1105,22 +1118,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129726936</v>
+        <v>129716450</v>
       </c>
       <c r="B6" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1128,46 +1141,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483746</v>
+        <v>483823</v>
       </c>
       <c r="R6" t="n">
-        <v>7145582</v>
+        <v>7145591</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1202,11 +1203,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en levande gran.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1215,51 +1211,26 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129727928</v>
+        <v>129726952</v>
       </c>
       <c r="B7" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1267,34 +1238,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483704</v>
+        <v>483538</v>
       </c>
       <c r="R7" t="n">
-        <v>7145461</v>
+        <v>7145695</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1331,7 +1305,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1340,28 +1314,54 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129726791</v>
+        <v>129726803</v>
       </c>
       <c r="B8" t="n">
-        <v>79076</v>
+        <v>83042</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,21 +1369,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1393,10 +1393,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483607</v>
+        <v>483493</v>
       </c>
       <c r="R8" t="n">
-        <v>7145404</v>
+        <v>7145541</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1465,10 +1465,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129726803</v>
+        <v>129716452</v>
       </c>
       <c r="B9" t="n">
-        <v>83037</v>
+        <v>91613</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1476,34 +1476,30 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>308</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483493</v>
+        <v>483480</v>
       </c>
       <c r="R9" t="n">
-        <v>7145541</v>
+        <v>7145600</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1533,19 +1529,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>10:01</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>10:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1560,22 +1546,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129716452</v>
+        <v>129726805</v>
       </c>
       <c r="B10" t="n">
-        <v>91608</v>
+        <v>79081</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1583,30 +1569,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483480</v>
+        <v>483517</v>
       </c>
       <c r="R10" t="n">
-        <v>7145600</v>
+        <v>7145580</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1636,9 +1626,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,22 +1653,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129726955</v>
+        <v>129726791</v>
       </c>
       <c r="B11" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1694,19 +1694,16 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483580</v>
+        <v>483607</v>
       </c>
       <c r="R11" t="n">
-        <v>7145305</v>
+        <v>7145404</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1736,14 +1733,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På en levande gran.</t>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1752,54 +1754,28 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129726805</v>
+        <v>129726955</v>
       </c>
       <c r="B12" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,16 +1801,19 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483517</v>
+        <v>483580</v>
       </c>
       <c r="R12" t="n">
-        <v>7145580</v>
+        <v>7145305</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1864,19 +1843,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>09:57</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>09:57</t>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På en levande gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1885,28 +1859,54 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129726819</v>
+        <v>129716468</v>
       </c>
       <c r="B13" t="n">
-        <v>79076</v>
+        <v>91613</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1914,34 +1914,30 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483862</v>
+        <v>484042</v>
       </c>
       <c r="R13" t="n">
-        <v>7145604</v>
+        <v>7145421</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1971,19 +1967,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>09:11</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>09:11</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1998,22 +1984,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129716468</v>
+        <v>129716455</v>
       </c>
       <c r="B14" t="n">
-        <v>91608</v>
+        <v>57736</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2021,30 +2007,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>484042</v>
+        <v>483975</v>
       </c>
       <c r="R14" t="n">
-        <v>7145421</v>
+        <v>7145436</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2103,7 +2098,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129716455</v>
+        <v>129727920</v>
       </c>
       <c r="B15" t="n">
         <v>57736</v>
@@ -2132,21 +2127,16 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483975</v>
+        <v>483452</v>
       </c>
       <c r="R15" t="n">
-        <v>7145436</v>
+        <v>7145362</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2181,6 +2171,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2193,19 +2188,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129727920</v>
+        <v>129727919</v>
       </c>
       <c r="B16" t="n">
         <v>57736</v>
@@ -2240,10 +2235,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483452</v>
+        <v>483535</v>
       </c>
       <c r="R16" t="n">
-        <v>7145362</v>
+        <v>7145332</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2280,7 +2275,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2307,7 +2302,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129727919</v>
+        <v>129726935</v>
       </c>
       <c r="B17" t="n">
         <v>57736</v>
@@ -2336,16 +2331,28 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483535</v>
+        <v>483601</v>
       </c>
       <c r="R17" t="n">
-        <v>7145332</v>
+        <v>7145616</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2382,7 +2389,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, färska och äldre, på stambasen av en levande gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2393,23 +2400,48 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129726935</v>
+        <v>129727923</v>
       </c>
       <c r="B18" t="n">
         <v>57736</v>
@@ -2438,28 +2470,16 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483601</v>
+        <v>483397</v>
       </c>
       <c r="R18" t="n">
-        <v>7145616</v>
+        <v>7145483</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2496,7 +2516,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en levande gran i barrblandskog.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2507,51 +2527,26 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129727923</v>
+        <v>129726819</v>
       </c>
       <c r="B19" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2559,34 +2554,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483397</v>
+        <v>483862</v>
       </c>
       <c r="R19" t="n">
-        <v>7145483</v>
+        <v>7145604</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2616,14 +2611,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2638,22 +2638,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129726804</v>
+        <v>129726941</v>
       </c>
       <c r="B20" t="n">
-        <v>79076</v>
+        <v>80187</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2661,34 +2661,41 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483493</v>
+        <v>483369</v>
       </c>
       <c r="R20" t="n">
-        <v>7145542</v>
+        <v>7145513</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2718,19 +2725,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>10:00</t>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På en levande sälg.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2739,28 +2741,54 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129726941</v>
+        <v>129726804</v>
       </c>
       <c r="B21" t="n">
-        <v>80182</v>
+        <v>79081</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2768,41 +2796,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>483369</v>
+        <v>483493</v>
       </c>
       <c r="R21" t="n">
-        <v>7145513</v>
+        <v>7145542</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2832,14 +2853,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På en levande sälg.</t>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2848,76 +2874,50 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129727915</v>
+        <v>129727934</v>
       </c>
       <c r="B22" t="n">
-        <v>92306</v>
+        <v>57736</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2927,10 +2927,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483493</v>
+        <v>483619</v>
       </c>
       <c r="R22" t="n">
-        <v>7145538</v>
+        <v>7145595</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2963,6 +2963,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2989,45 +2994,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129726818</v>
+        <v>129727915</v>
       </c>
       <c r="B23" t="n">
-        <v>83045</v>
+        <v>92311</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>3298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483849</v>
+        <v>483493</v>
       </c>
       <c r="R23" t="n">
-        <v>7145605</v>
+        <v>7145538</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3057,19 +3062,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>09:13</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>09:13</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3084,12 +3079,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3099,7 +3094,7 @@
         <v>129726825</v>
       </c>
       <c r="B24" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3206,7 +3201,7 @@
         <v>129726813</v>
       </c>
       <c r="B25" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3313,7 +3308,7 @@
         <v>129726814</v>
       </c>
       <c r="B26" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3417,10 +3412,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129727934</v>
+        <v>129726818</v>
       </c>
       <c r="B27" t="n">
-        <v>57736</v>
+        <v>83050</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3428,34 +3423,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>483619</v>
+        <v>483849</v>
       </c>
       <c r="R27" t="n">
-        <v>7145595</v>
+        <v>7145605</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3485,14 +3480,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3507,12 +3507,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3522,7 +3522,7 @@
         <v>129726816</v>
       </c>
       <c r="B28" t="n">
-        <v>75060</v>
+        <v>75065</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3867,10 +3867,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129727931</v>
+        <v>129716460</v>
       </c>
       <c r="B31" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3878,34 +3878,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>483545</v>
+        <v>483445</v>
       </c>
       <c r="R31" t="n">
-        <v>7145507</v>
+        <v>7145428</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3940,11 +3940,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -3957,22 +3952,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129716460</v>
+        <v>129726961</v>
       </c>
       <c r="B32" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3998,16 +3993,19 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>483445</v>
+        <v>483414</v>
       </c>
       <c r="R32" t="n">
-        <v>7145428</v>
+        <v>7145535</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4042,34 +4040,65 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På en levande gran.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129726961</v>
+        <v>129726824</v>
       </c>
       <c r="B33" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4095,19 +4124,16 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>483414</v>
+        <v>483981</v>
       </c>
       <c r="R33" t="n">
-        <v>7145535</v>
+        <v>7145521</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4137,14 +4163,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>08:59</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På en levande gran.</t>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4153,54 +4184,28 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129726824</v>
+        <v>129727931</v>
       </c>
       <c r="B34" t="n">
-        <v>79076</v>
+        <v>57736</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4208,34 +4213,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>483981</v>
+        <v>483545</v>
       </c>
       <c r="R34" t="n">
-        <v>7145521</v>
+        <v>7145507</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4265,19 +4270,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>08:59</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>08:59</t>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4292,12 +4292,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4436,10 +4436,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129716461</v>
+        <v>129727927</v>
       </c>
       <c r="B36" t="n">
-        <v>79076</v>
+        <v>57736</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4447,34 +4447,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>483576</v>
+        <v>483606</v>
       </c>
       <c r="R36" t="n">
-        <v>7145615</v>
+        <v>7145282</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4509,6 +4509,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4521,22 +4526,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129726807</v>
+        <v>129726801</v>
       </c>
       <c r="B37" t="n">
-        <v>79076</v>
+        <v>83055</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4544,21 +4549,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4568,10 +4573,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>483589</v>
+        <v>483487</v>
       </c>
       <c r="R37" t="n">
-        <v>7145582</v>
+        <v>7145541</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4603,7 +4608,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4613,7 +4618,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4640,10 +4645,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129716466</v>
+        <v>129716461</v>
       </c>
       <c r="B38" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4675,10 +4680,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>483481</v>
+        <v>483576</v>
       </c>
       <c r="R38" t="n">
-        <v>7145592</v>
+        <v>7145615</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4737,10 +4742,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129726801</v>
+        <v>129726807</v>
       </c>
       <c r="B39" t="n">
-        <v>83050</v>
+        <v>79081</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4748,21 +4753,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4772,10 +4777,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>483487</v>
+        <v>483589</v>
       </c>
       <c r="R39" t="n">
-        <v>7145541</v>
+        <v>7145582</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4807,7 +4812,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4817,7 +4822,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4844,10 +4849,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129727927</v>
+        <v>129716466</v>
       </c>
       <c r="B40" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4855,34 +4860,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>483606</v>
+        <v>483481</v>
       </c>
       <c r="R40" t="n">
-        <v>7145282</v>
+        <v>7145592</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4917,11 +4922,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -4934,57 +4934,60 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129716464</v>
+        <v>129726948</v>
       </c>
       <c r="B41" t="n">
-        <v>92306</v>
+        <v>91613</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>484017</v>
+        <v>483501</v>
       </c>
       <c r="R41" t="n">
-        <v>7145437</v>
+        <v>7145621</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5019,34 +5022,65 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar i en levande gran.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129726946</v>
+        <v>129716464</v>
       </c>
       <c r="B42" t="n">
-        <v>80209</v>
+        <v>92311</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5054,37 +5088,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6461</v>
+        <v>3298</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>483607</v>
+        <v>484017</v>
       </c>
       <c r="R42" t="n">
-        <v>7145621</v>
+        <v>7145437</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5125,19 +5156,18 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5147,7 +5177,7 @@
         <v>129726821</v>
       </c>
       <c r="B43" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5251,10 +5281,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129726948</v>
+        <v>129726960</v>
       </c>
       <c r="B44" t="n">
-        <v>91608</v>
+        <v>79081</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5262,26 +5292,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5289,10 +5319,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>483501</v>
+        <v>483376</v>
       </c>
       <c r="R44" t="n">
-        <v>7145621</v>
+        <v>7145540</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5329,7 +5359,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en levande gran.</t>
+          <t>På en levande gran.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5359,12 +5389,12 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5382,10 +5412,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129726960</v>
+        <v>129727936</v>
       </c>
       <c r="B45" t="n">
-        <v>79076</v>
+        <v>57736</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5393,37 +5423,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>483376</v>
+        <v>483750</v>
       </c>
       <c r="R45" t="n">
-        <v>7145540</v>
+        <v>7145579</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5460,7 +5487,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På en levande gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5469,51 +5496,25 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129727936</v>
+        <v>129727938</v>
       </c>
       <c r="B46" t="n">
         <v>57736</v>
@@ -5548,10 +5549,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>483750</v>
+        <v>483975</v>
       </c>
       <c r="R46" t="n">
-        <v>7145579</v>
+        <v>7145511</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5615,7 +5616,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129727938</v>
+        <v>129726810</v>
       </c>
       <c r="B47" t="n">
         <v>57736</v>
@@ -5643,17 +5644,31 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>483975</v>
+        <v>483760</v>
       </c>
       <c r="R47" t="n">
-        <v>7145511</v>
+        <v>7145583</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5683,14 +5698,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5705,71 +5725,60 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129726810</v>
+        <v>129726946</v>
       </c>
       <c r="B48" t="n">
-        <v>57736</v>
+        <v>80214</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>483760</v>
+        <v>483607</v>
       </c>
       <c r="R48" t="n">
-        <v>7145583</v>
+        <v>7145621</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5799,49 +5808,40 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>09:41</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>09:41</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129727935</v>
+        <v>129726800</v>
       </c>
       <c r="B49" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5849,34 +5849,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>483723</v>
+        <v>483439</v>
       </c>
       <c r="R49" t="n">
-        <v>7145593</v>
+        <v>7145513</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5906,14 +5906,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5928,22 +5933,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129726800</v>
+        <v>129716462</v>
       </c>
       <c r="B50" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5971,14 +5976,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>483439</v>
+        <v>483666</v>
       </c>
       <c r="R50" t="n">
-        <v>7145513</v>
+        <v>7145612</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6008,19 +6013,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>10:13</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6035,22 +6030,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129716462</v>
+        <v>129727935</v>
       </c>
       <c r="B51" t="n">
-        <v>79076</v>
+        <v>57736</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6058,34 +6053,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>483666</v>
+        <v>483723</v>
       </c>
       <c r="R51" t="n">
-        <v>7145612</v>
+        <v>7145593</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6120,6 +6115,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6132,12 +6132,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6348,45 +6348,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129726811</v>
+        <v>129727914</v>
       </c>
       <c r="B54" t="n">
-        <v>79076</v>
+        <v>92311</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>483760</v>
+        <v>483577</v>
       </c>
       <c r="R54" t="n">
-        <v>7145575</v>
+        <v>7145438</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6416,19 +6416,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>09:35</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>09:35</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6443,22 +6433,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129727914</v>
+        <v>129726944</v>
       </c>
       <c r="B55" t="n">
-        <v>92306</v>
+        <v>80214</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6466,34 +6456,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3298</v>
+        <v>6461</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>483577</v>
+        <v>483597</v>
       </c>
       <c r="R55" t="n">
-        <v>7145438</v>
+        <v>7145735</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6534,66 +6527,64 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129726944</v>
+        <v>129716458</v>
       </c>
       <c r="B56" t="n">
-        <v>80209</v>
+        <v>83050</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6461</v>
+        <v>6440</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>483597</v>
+        <v>483701</v>
       </c>
       <c r="R56" t="n">
-        <v>7145735</v>
+        <v>7145588</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6634,29 +6625,28 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129716458</v>
+        <v>129726811</v>
       </c>
       <c r="B57" t="n">
-        <v>83045</v>
+        <v>79081</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6664,34 +6654,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>483701</v>
+        <v>483760</v>
       </c>
       <c r="R57" t="n">
-        <v>7145588</v>
+        <v>7145575</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6721,9 +6711,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6738,12 +6738,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -7056,10 +7056,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129716449</v>
+        <v>129726828</v>
       </c>
       <c r="B61" t="n">
-        <v>83045</v>
+        <v>79081</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7067,34 +7067,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>483889</v>
+        <v>483988</v>
       </c>
       <c r="R61" t="n">
-        <v>7145589</v>
+        <v>7145444</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7124,9 +7124,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7141,22 +7151,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129726828</v>
+        <v>129716453</v>
       </c>
       <c r="B62" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7184,14 +7194,14 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>483988</v>
+        <v>484032</v>
       </c>
       <c r="R62" t="n">
-        <v>7145444</v>
+        <v>7145416</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7221,19 +7231,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>08:48</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>08:48</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7248,22 +7248,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129716453</v>
+        <v>129726953</v>
       </c>
       <c r="B63" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7289,16 +7289,19 @@
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>484032</v>
+        <v>483555</v>
       </c>
       <c r="R63" t="n">
-        <v>7145416</v>
+        <v>7145531</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7333,34 +7336,65 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129726953</v>
+        <v>129716449</v>
       </c>
       <c r="B64" t="n">
-        <v>79076</v>
+        <v>83050</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7368,37 +7402,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>483555</v>
+        <v>483889</v>
       </c>
       <c r="R64" t="n">
-        <v>7145531</v>
+        <v>7145589</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7433,55 +7464,24 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AH64" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -7491,7 +7491,7 @@
         <v>129726806</v>
       </c>
       <c r="B65" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7598,7 +7598,7 @@
         <v>129726788</v>
       </c>
       <c r="B66" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
         <v>129716448</v>
       </c>
       <c r="B67" t="n">
-        <v>91539</v>
+        <v>91544</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>129726958</v>
       </c>
       <c r="B68" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7933,7 +7933,7 @@
         <v>129726966</v>
       </c>
       <c r="B69" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8064,7 +8064,7 @@
         <v>129726797</v>
       </c>
       <c r="B70" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8514,7 +8514,7 @@
         <v>129726787</v>
       </c>
       <c r="B74" t="n">
-        <v>78089</v>
+        <v>78094</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8621,7 +8621,7 @@
         <v>129726826</v>
       </c>
       <c r="B75" t="n">
-        <v>78089</v>
+        <v>78094</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         <v>129726947</v>
       </c>
       <c r="B76" t="n">
-        <v>91584</v>
+        <v>91589</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         <v>129726964</v>
       </c>
       <c r="B77" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8991,10 +8991,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129716465</v>
+        <v>129726793</v>
       </c>
       <c r="B78" t="n">
-        <v>91588</v>
+        <v>57896</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9002,37 +9002,46 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>483983</v>
+        <v>483572</v>
       </c>
       <c r="R78" t="n">
-        <v>7145507</v>
+        <v>7145322</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9059,9 +9068,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9076,22 +9095,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129727941</v>
+        <v>129716465</v>
       </c>
       <c r="B79" t="n">
-        <v>91584</v>
+        <v>91593</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9099,34 +9118,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>483551</v>
+        <v>483983</v>
       </c>
       <c r="R79" t="n">
-        <v>7145323</v>
+        <v>7145507</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9173,22 +9192,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129726823</v>
+        <v>129727941</v>
       </c>
       <c r="B80" t="n">
-        <v>79076</v>
+        <v>91589</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9196,34 +9215,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>483959</v>
+        <v>483551</v>
       </c>
       <c r="R80" t="n">
-        <v>7145539</v>
+        <v>7145323</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9253,19 +9272,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>09:02</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>09:02</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9280,22 +9289,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129726798</v>
+        <v>129726795</v>
       </c>
       <c r="B81" t="n">
-        <v>79076</v>
+        <v>83055</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9303,21 +9312,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9327,10 +9336,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>483429</v>
+        <v>483545</v>
       </c>
       <c r="R81" t="n">
-        <v>7145430</v>
+        <v>7145343</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9362,7 +9371,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9372,7 +9381,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9402,7 +9411,7 @@
         <v>129727942</v>
       </c>
       <c r="B82" t="n">
-        <v>91608</v>
+        <v>91613</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9492,48 +9501,45 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129726963</v>
+        <v>129726796</v>
       </c>
       <c r="B83" t="n">
-        <v>79076</v>
+        <v>83048</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>6486</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>483498</v>
+        <v>483545</v>
       </c>
       <c r="R83" t="n">
-        <v>7145585</v>
+        <v>7145343</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9563,14 +9569,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>På levande gran.</t>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9579,54 +9590,28 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
-      </c>
-      <c r="AH83" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129726812</v>
+        <v>129726831</v>
       </c>
       <c r="B84" t="n">
-        <v>79076</v>
+        <v>83050</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9634,21 +9619,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9658,10 +9643,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>483764</v>
+        <v>484008</v>
       </c>
       <c r="R84" t="n">
-        <v>7145589</v>
+        <v>7145455</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9693,7 +9678,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9703,7 +9688,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9730,10 +9715,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129716451</v>
+        <v>129726963</v>
       </c>
       <c r="B85" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9759,16 +9744,19 @@
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>483989</v>
+        <v>483498</v>
       </c>
       <c r="R85" t="n">
-        <v>7145511</v>
+        <v>7145585</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9803,34 +9791,65 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>På levande gran.</t>
+        </is>
+      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM85" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129726795</v>
+        <v>129726812</v>
       </c>
       <c r="B86" t="n">
-        <v>83050</v>
+        <v>79081</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9838,21 +9857,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9862,10 +9881,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>483545</v>
+        <v>483764</v>
       </c>
       <c r="R86" t="n">
-        <v>7145343</v>
+        <v>7145589</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9897,7 +9916,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9907,7 +9926,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9934,10 +9953,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129727940</v>
+        <v>129726823</v>
       </c>
       <c r="B87" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9945,34 +9964,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>483677</v>
+        <v>483959</v>
       </c>
       <c r="R87" t="n">
-        <v>7145478</v>
+        <v>7145539</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10002,14 +10021,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Hack ganska färska</t>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10024,22 +10048,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129726831</v>
+        <v>129716451</v>
       </c>
       <c r="B88" t="n">
-        <v>83045</v>
+        <v>79081</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10047,34 +10071,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>484008</v>
+        <v>483989</v>
       </c>
       <c r="R88" t="n">
-        <v>7145455</v>
+        <v>7145511</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10104,19 +10128,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>08:42</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>08:42</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10131,44 +10145,44 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129726796</v>
+        <v>129726798</v>
       </c>
       <c r="B89" t="n">
-        <v>83043</v>
+        <v>79081</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6486</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10178,10 +10192,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>483545</v>
+        <v>483429</v>
       </c>
       <c r="R89" t="n">
-        <v>7145343</v>
+        <v>7145430</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10213,7 +10227,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10223,7 +10237,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10250,10 +10264,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129726793</v>
+        <v>129727940</v>
       </c>
       <c r="B90" t="n">
-        <v>57896</v>
+        <v>57733</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10261,46 +10275,37 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>483572</v>
+        <v>483677</v>
       </c>
       <c r="R90" t="n">
-        <v>7145322</v>
+        <v>7145478</v>
       </c>
       <c r="S90" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10327,19 +10332,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>10:55</t>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Hack ganska färska</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10354,60 +10354,57 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129726945</v>
+        <v>129726832</v>
       </c>
       <c r="B91" t="n">
-        <v>80209</v>
+        <v>79081</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>483364</v>
+        <v>484041</v>
       </c>
       <c r="R91" t="n">
-        <v>7145533</v>
+        <v>7145466</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10437,40 +10434,49 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>08:39</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>08:39</t>
+        </is>
+      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129726832</v>
+        <v>129726799</v>
       </c>
       <c r="B92" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10502,10 +10508,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>484041</v>
+        <v>483426</v>
       </c>
       <c r="R92" t="n">
-        <v>7145466</v>
+        <v>7145464</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10537,7 +10543,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10547,7 +10553,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10574,45 +10580,48 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129726799</v>
+        <v>129726945</v>
       </c>
       <c r="B93" t="n">
-        <v>79076</v>
+        <v>80214</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>483426</v>
+        <v>483364</v>
       </c>
       <c r="R93" t="n">
-        <v>7145464</v>
+        <v>7145533</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10642,49 +10651,40 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129726940</v>
+        <v>129726942</v>
       </c>
       <c r="B94" t="n">
-        <v>57733</v>
+        <v>80187</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10692,29 +10692,28 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N94" t="inlineStr"/>
@@ -10724,10 +10723,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>483382</v>
+        <v>483377</v>
       </c>
       <c r="R94" t="n">
-        <v>7145460</v>
+        <v>7145537</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10764,7 +10763,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Äldre och färska hackspår i en grov stående död gran av full längd.</t>
+          <t>På en levande sälg i granskog.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10773,32 +10772,33 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM94" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -10816,10 +10816,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129716457</v>
+        <v>129716456</v>
       </c>
       <c r="B95" t="n">
-        <v>91608</v>
+        <v>82916</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10827,19 +10827,23 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr"/>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -10847,10 +10851,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>483922</v>
+        <v>483445</v>
       </c>
       <c r="R95" t="n">
-        <v>7145565</v>
+        <v>7145393</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10912,7 +10916,7 @@
         <v>129726967</v>
       </c>
       <c r="B96" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11043,7 +11047,7 @@
         <v>129726951</v>
       </c>
       <c r="B97" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11174,7 +11178,7 @@
         <v>129726965</v>
       </c>
       <c r="B98" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11302,10 +11306,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129726942</v>
+        <v>129726940</v>
       </c>
       <c r="B99" t="n">
-        <v>80182</v>
+        <v>57733</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11313,28 +11317,29 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N99" t="inlineStr"/>
@@ -11344,10 +11349,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>483377</v>
+        <v>483382</v>
       </c>
       <c r="R99" t="n">
-        <v>7145537</v>
+        <v>7145460</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11384,7 +11389,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>På en levande sälg i granskog.</t>
+          <t>Äldre och färska hackspår i en grov stående död gran av full längd.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11393,33 +11398,32 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>
@@ -11437,10 +11441,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129716456</v>
+        <v>129716457</v>
       </c>
       <c r="B100" t="n">
-        <v>82911</v>
+        <v>91613</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11448,23 +11452,19 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
@@ -11472,10 +11472,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>483445</v>
+        <v>483922</v>
       </c>
       <c r="R100" t="n">
-        <v>7145393</v>
+        <v>7145565</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11537,7 +11537,7 @@
         <v>129726962</v>
       </c>
       <c r="B101" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11668,7 +11668,7 @@
         <v>129726956</v>
       </c>
       <c r="B102" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
         <v>129716467</v>
       </c>
       <c r="B103" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12030,7 +12030,7 @@
         <v>129726957</v>
       </c>
       <c r="B105" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12365,7 +12365,7 @@
         <v>129726830</v>
       </c>
       <c r="B108" t="n">
-        <v>78089</v>
+        <v>78094</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12469,10 +12469,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129726949</v>
+        <v>129716454</v>
       </c>
       <c r="B109" t="n">
-        <v>79076</v>
+        <v>91589</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12480,37 +12480,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>483735</v>
+        <v>484017</v>
       </c>
       <c r="R109" t="n">
-        <v>7145746</v>
+        <v>7145437</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12545,65 +12542,34 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
-      </c>
-      <c r="AH109" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ109" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK109" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM109" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO109" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129726792</v>
+        <v>129726949</v>
       </c>
       <c r="B110" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12629,16 +12595,19 @@
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>483571</v>
+        <v>483735</v>
       </c>
       <c r="R110" t="n">
-        <v>7145360</v>
+        <v>7145746</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12668,19 +12637,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>10:58</t>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12689,28 +12653,54 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
+      </c>
+      <c r="AH110" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM110" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129726789</v>
+        <v>129726792</v>
       </c>
       <c r="B111" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12742,10 +12732,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>483663</v>
+        <v>483571</v>
       </c>
       <c r="R111" t="n">
-        <v>7145420</v>
+        <v>7145360</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12777,7 +12767,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12787,7 +12777,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12814,10 +12804,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129726950</v>
+        <v>129726827</v>
       </c>
       <c r="B112" t="n">
-        <v>79076</v>
+        <v>83050</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12825,37 +12815,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>483720</v>
+        <v>483988</v>
       </c>
       <c r="R112" t="n">
-        <v>7145756</v>
+        <v>7145444</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12885,14 +12872,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12901,54 +12893,28 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
-      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
-      </c>
-      <c r="AH112" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ112" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK112" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM112" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO112" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129726959</v>
+        <v>129726789</v>
       </c>
       <c r="B113" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12974,19 +12940,16 @@
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>483422</v>
+        <v>483663</v>
       </c>
       <c r="R113" t="n">
-        <v>7145360</v>
+        <v>7145420</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13016,14 +12979,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>På en levande gran.</t>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13032,54 +13000,28 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
-      </c>
-      <c r="AH113" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ113" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK113" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM113" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO113" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129726817</v>
+        <v>129726950</v>
       </c>
       <c r="B114" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13105,16 +13047,19 @@
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>483834</v>
+        <v>483720</v>
       </c>
       <c r="R114" t="n">
-        <v>7145605</v>
+        <v>7145756</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13144,19 +13089,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>09:15</t>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13165,28 +13105,54 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
+      </c>
+      <c r="AH114" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ114" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK114" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM114" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO114" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129726954</v>
+        <v>129726959</v>
       </c>
       <c r="B115" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13221,10 +13187,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>483580</v>
+        <v>483422</v>
       </c>
       <c r="R115" t="n">
-        <v>7145435</v>
+        <v>7145360</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13261,7 +13227,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>På gran i granskog.</t>
+          <t>På en levande gran.</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13276,7 +13242,7 @@
       </c>
       <c r="AH115" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ115" t="inlineStr">
@@ -13314,10 +13280,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129716454</v>
+        <v>129726817</v>
       </c>
       <c r="B116" t="n">
-        <v>91584</v>
+        <v>79081</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13325,34 +13291,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>484017</v>
+        <v>483834</v>
       </c>
       <c r="R116" t="n">
-        <v>7145437</v>
+        <v>7145605</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13382,9 +13348,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13399,22 +13375,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129726827</v>
+        <v>129726954</v>
       </c>
       <c r="B117" t="n">
-        <v>83045</v>
+        <v>79081</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13422,34 +13398,37 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>483988</v>
+        <v>483580</v>
       </c>
       <c r="R117" t="n">
-        <v>7145444</v>
+        <v>7145435</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13479,19 +13458,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>08:49</t>
-        </is>
-      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>08:49</t>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>På gran i granskog.</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13500,28 +13474,54 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
+      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
+      </c>
+      <c r="AH117" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK117" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM117" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO117" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129727939</v>
+        <v>129727917</v>
       </c>
       <c r="B118" t="n">
-        <v>57733</v>
+        <v>57736</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13529,16 +13529,16 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -13553,10 +13553,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>483605</v>
+        <v>483572</v>
       </c>
       <c r="R118" t="n">
-        <v>7145281</v>
+        <v>7145725</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13593,7 +13593,7 @@
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>Hack ganska färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13620,7 +13620,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129727917</v>
+        <v>129727925</v>
       </c>
       <c r="B119" t="n">
         <v>57736</v>
@@ -13655,10 +13655,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>483572</v>
+        <v>483580</v>
       </c>
       <c r="R119" t="n">
-        <v>7145725</v>
+        <v>7145425</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13695,7 +13695,7 @@
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13722,10 +13722,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129727925</v>
+        <v>129727939</v>
       </c>
       <c r="B120" t="n">
-        <v>57736</v>
+        <v>57733</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13733,16 +13733,16 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -13757,10 +13757,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>483580</v>
+        <v>483605</v>
       </c>
       <c r="R120" t="n">
-        <v>7145425</v>
+        <v>7145281</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13797,7 +13797,7 @@
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Hack ganska färska</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13827,7 +13827,7 @@
         <v>129730288</v>
       </c>
       <c r="B121" t="n">
-        <v>91608</v>
+        <v>91613</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13920,7 +13920,7 @@
         <v>129730246</v>
       </c>
       <c r="B122" t="n">
-        <v>80182</v>
+        <v>80187</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14014,10 +14014,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129730292</v>
+        <v>129730241</v>
       </c>
       <c r="B123" t="n">
-        <v>83037</v>
+        <v>57736</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14025,21 +14025,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -14049,10 +14049,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>483314</v>
+        <v>483751</v>
       </c>
       <c r="R123" t="n">
-        <v>7145495</v>
+        <v>7145575</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14085,6 +14085,11 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14111,10 +14116,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129730241</v>
+        <v>129730292</v>
       </c>
       <c r="B124" t="n">
-        <v>57736</v>
+        <v>83042</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14122,21 +14127,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -14146,10 +14151,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>483751</v>
+        <v>483314</v>
       </c>
       <c r="R124" t="n">
-        <v>7145575</v>
+        <v>7145495</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14182,11 +14187,6 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14213,10 +14213,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129730253</v>
+        <v>129730268</v>
       </c>
       <c r="B125" t="n">
-        <v>78833</v>
+        <v>57736</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14224,21 +14224,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14248,10 +14248,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>483421</v>
+        <v>483247</v>
       </c>
       <c r="R125" t="n">
-        <v>7145545</v>
+        <v>7145580</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14284,6 +14284,11 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14310,10 +14315,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129730268</v>
+        <v>129730253</v>
       </c>
       <c r="B126" t="n">
-        <v>57736</v>
+        <v>78838</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14321,21 +14326,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14345,10 +14350,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>483247</v>
+        <v>483421</v>
       </c>
       <c r="R126" t="n">
-        <v>7145580</v>
+        <v>7145545</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14381,11 +14386,6 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14415,7 +14415,7 @@
         <v>129730291</v>
       </c>
       <c r="B127" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14509,10 +14509,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129730290</v>
+        <v>129730248</v>
       </c>
       <c r="B128" t="n">
-        <v>91608</v>
+        <v>80186</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14520,19 +14520,23 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
@@ -14540,10 +14544,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>483766</v>
+        <v>483599</v>
       </c>
       <c r="R128" t="n">
-        <v>7145610</v>
+        <v>7145185</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14602,10 +14606,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129730248</v>
+        <v>129730290</v>
       </c>
       <c r="B129" t="n">
-        <v>80181</v>
+        <v>91613</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14613,23 +14617,19 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
@@ -14637,10 +14637,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>483599</v>
+        <v>483766</v>
       </c>
       <c r="R129" t="n">
-        <v>7145185</v>
+        <v>7145610</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14699,10 +14699,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129730247</v>
+        <v>129730244</v>
       </c>
       <c r="B130" t="n">
-        <v>80181</v>
+        <v>80187</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14710,21 +14710,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14734,10 +14734,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>483595</v>
+        <v>483599</v>
       </c>
       <c r="R130" t="n">
-        <v>7145180</v>
+        <v>7145190</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14796,10 +14796,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129730274</v>
+        <v>129730247</v>
       </c>
       <c r="B131" t="n">
-        <v>57736</v>
+        <v>80186</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14807,21 +14807,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14831,10 +14831,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>483612</v>
+        <v>483595</v>
       </c>
       <c r="R131" t="n">
-        <v>7145596</v>
+        <v>7145180</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14867,11 +14867,6 @@
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14898,10 +14893,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129730244</v>
+        <v>129730274</v>
       </c>
       <c r="B132" t="n">
-        <v>80182</v>
+        <v>57736</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14909,21 +14904,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14933,10 +14928,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>483599</v>
+        <v>483612</v>
       </c>
       <c r="R132" t="n">
-        <v>7145190</v>
+        <v>7145596</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14969,6 +14964,11 @@
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14995,10 +14995,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129730287</v>
+        <v>129730252</v>
       </c>
       <c r="B133" t="n">
-        <v>91584</v>
+        <v>78838</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15006,21 +15006,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1108</v>
+        <v>6446</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -15030,10 +15030,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>483608</v>
+        <v>483407</v>
       </c>
       <c r="R133" t="n">
-        <v>7145490</v>
+        <v>7145540</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15092,10 +15092,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129730255</v>
+        <v>129730287</v>
       </c>
       <c r="B134" t="n">
-        <v>91608</v>
+        <v>91589</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15103,19 +15103,23 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
@@ -15123,10 +15127,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>483529</v>
+        <v>483608</v>
       </c>
       <c r="R134" t="n">
-        <v>7145591</v>
+        <v>7145490</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15185,10 +15189,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129730252</v>
+        <v>129730255</v>
       </c>
       <c r="B135" t="n">
-        <v>78833</v>
+        <v>91613</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15196,23 +15200,19 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6446</v>
+        <v>5432</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
@@ -15220,10 +15220,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>483407</v>
+        <v>483529</v>
       </c>
       <c r="R135" t="n">
-        <v>7145540</v>
+        <v>7145591</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15285,7 +15285,7 @@
         <v>129730242</v>
       </c>
       <c r="B136" t="n">
-        <v>79666</v>
+        <v>79671</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15382,7 +15382,7 @@
         <v>129730284</v>
       </c>
       <c r="B137" t="n">
-        <v>78089</v>
+        <v>78094</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15479,7 +15479,7 @@
         <v>129730250</v>
       </c>
       <c r="B138" t="n">
-        <v>78833</v>
+        <v>78838</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15573,10 +15573,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129730293</v>
+        <v>129730262</v>
       </c>
       <c r="B139" t="n">
-        <v>83037</v>
+        <v>57736</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15584,21 +15584,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15608,10 +15608,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>483321</v>
+        <v>483284</v>
       </c>
       <c r="R139" t="n">
-        <v>7145559</v>
+        <v>7145578</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15644,6 +15644,11 @@
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15670,10 +15675,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129730262</v>
+        <v>129730293</v>
       </c>
       <c r="B140" t="n">
-        <v>57736</v>
+        <v>83042</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15681,21 +15686,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15705,10 +15710,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>483284</v>
+        <v>483321</v>
       </c>
       <c r="R140" t="n">
-        <v>7145578</v>
+        <v>7145559</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15741,11 +15746,6 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15772,32 +15772,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129730249</v>
+        <v>129730285</v>
       </c>
       <c r="B141" t="n">
-        <v>80181</v>
+        <v>83058</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6458</v>
+        <v>1469</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten blekspik</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sclerophora peronella</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15807,10 +15807,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>483253</v>
+        <v>483470</v>
       </c>
       <c r="R141" t="n">
-        <v>7145561</v>
+        <v>7145348</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15869,32 +15869,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129730281</v>
+        <v>129730249</v>
       </c>
       <c r="B142" t="n">
-        <v>80085</v>
+        <v>80186</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15904,10 +15904,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>483572</v>
+        <v>483253</v>
       </c>
       <c r="R142" t="n">
-        <v>7145441</v>
+        <v>7145561</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15966,32 +15966,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129730254</v>
+        <v>129730281</v>
       </c>
       <c r="B143" t="n">
-        <v>78833</v>
+        <v>80090</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6446</v>
+        <v>6456</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -16001,10 +16001,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>483454</v>
+        <v>483572</v>
       </c>
       <c r="R143" t="n">
-        <v>7145556</v>
+        <v>7145441</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16063,32 +16063,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129730285</v>
+        <v>129730254</v>
       </c>
       <c r="B144" t="n">
-        <v>83053</v>
+        <v>78838</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1469</v>
+        <v>6446</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Liten blekspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Sclerophora peronella</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -16098,10 +16098,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>483470</v>
+        <v>483454</v>
       </c>
       <c r="R144" t="n">
-        <v>7145348</v>
+        <v>7145556</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16160,10 +16160,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129730261</v>
+        <v>129730289</v>
       </c>
       <c r="B145" t="n">
-        <v>79076</v>
+        <v>91613</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16171,23 +16171,19 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr"/>
       <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
@@ -16195,10 +16191,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>483247</v>
+        <v>483238</v>
       </c>
       <c r="R145" t="n">
-        <v>7145585</v>
+        <v>7145599</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16257,10 +16253,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129730289</v>
+        <v>129730261</v>
       </c>
       <c r="B146" t="n">
-        <v>91608</v>
+        <v>79081</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16268,19 +16264,23 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H146" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
@@ -16288,10 +16288,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>483238</v>
+        <v>483247</v>
       </c>
       <c r="R146" t="n">
-        <v>7145599</v>
+        <v>7145585</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16353,7 +16353,7 @@
         <v>129730294</v>
       </c>
       <c r="B147" t="n">
-        <v>83037</v>
+        <v>83042</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16552,7 +16552,7 @@
         <v>129730295</v>
       </c>
       <c r="B149" t="n">
-        <v>83037</v>
+        <v>83042</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16649,7 +16649,7 @@
         <v>129730260</v>
       </c>
       <c r="B150" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16743,32 +16743,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129730282</v>
+        <v>129730296</v>
       </c>
       <c r="B151" t="n">
-        <v>80085</v>
+        <v>83042</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6456</v>
+        <v>308</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16778,10 +16778,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>483534</v>
+        <v>483526</v>
       </c>
       <c r="R151" t="n">
-        <v>7145348</v>
+        <v>7145596</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16840,32 +16840,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129730296</v>
+        <v>129730282</v>
       </c>
       <c r="B152" t="n">
-        <v>83037</v>
+        <v>80090</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>308</v>
+        <v>6456</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16875,10 +16875,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>483526</v>
+        <v>483534</v>
       </c>
       <c r="R152" t="n">
-        <v>7145596</v>
+        <v>7145348</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17241,7 +17241,7 @@
         <v>129730258</v>
       </c>
       <c r="B156" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17338,7 +17338,7 @@
         <v>129730257</v>
       </c>
       <c r="B157" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17756,7 +17756,7 @@
         <v>129730256</v>
       </c>
       <c r="B161" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17853,7 +17853,7 @@
         <v>129730263</v>
       </c>
       <c r="B162" t="n">
-        <v>83045</v>
+        <v>83050</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17950,7 +17950,7 @@
         <v>129730259</v>
       </c>
       <c r="B163" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>

--- a/artfynd/A 52753-2025 artfynd.xlsx
+++ b/artfynd/A 52753-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129727928</v>
+        <v>129726815</v>
       </c>
       <c r="B2" t="n">
-        <v>57736</v>
+        <v>83044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483704</v>
+        <v>483798</v>
       </c>
       <c r="R2" t="n">
-        <v>7145461</v>
+        <v>7145630</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,14 +743,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129726936</v>
+        <v>129716450</v>
       </c>
       <c r="B3" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,46 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483746</v>
+        <v>483823</v>
       </c>
       <c r="R3" t="n">
-        <v>7145582</v>
+        <v>7145591</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,11 +855,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en levande gran.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -875,51 +863,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129726815</v>
+        <v>129726952</v>
       </c>
       <c r="B4" t="n">
-        <v>83042</v>
+        <v>79081</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -927,34 +890,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483798</v>
+        <v>483538</v>
       </c>
       <c r="R4" t="n">
-        <v>7145630</v>
+        <v>7145695</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,19 +950,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>09:22</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>09:22</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,28 +966,54 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129716450</v>
+        <v>129726820</v>
       </c>
       <c r="B5" t="n">
-        <v>79081</v>
+        <v>83057</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1034,34 +1021,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483823</v>
+        <v>483921</v>
       </c>
       <c r="R5" t="n">
-        <v>7145591</v>
+        <v>7145571</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,9 +1078,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,22 +1105,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129726952</v>
+        <v>129726936</v>
       </c>
       <c r="B6" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1131,37 +1128,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483538</v>
+        <v>483746</v>
       </c>
       <c r="R6" t="n">
-        <v>7145695</v>
+        <v>7145582</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1204,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, äldre, på stambasen av en levande gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1207,7 +1213,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1228,12 +1233,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1251,10 +1256,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129726820</v>
+        <v>129727928</v>
       </c>
       <c r="B7" t="n">
-        <v>83055</v>
+        <v>57736</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1262,34 +1267,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1467</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483921</v>
+        <v>483704</v>
       </c>
       <c r="R7" t="n">
-        <v>7145571</v>
+        <v>7145461</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,19 +1324,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>09:08</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>09:08</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,12 +1346,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1361,7 +1361,7 @@
         <v>129726803</v>
       </c>
       <c r="B8" t="n">
-        <v>83042</v>
+        <v>83044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,10 +1465,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129726805</v>
+        <v>129716452</v>
       </c>
       <c r="B9" t="n">
-        <v>79081</v>
+        <v>91619</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1476,34 +1476,30 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483517</v>
+        <v>483480</v>
       </c>
       <c r="R9" t="n">
-        <v>7145580</v>
+        <v>7145600</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1533,19 +1529,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>09:57</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>09:57</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1560,19 +1546,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129726955</v>
+        <v>129726791</v>
       </c>
       <c r="B10" t="n">
         <v>79081</v>
@@ -1601,19 +1587,16 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483580</v>
+        <v>483607</v>
       </c>
       <c r="R10" t="n">
-        <v>7145305</v>
+        <v>7145404</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1643,14 +1626,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På en levande gran.</t>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1659,51 +1647,25 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129726791</v>
+        <v>129726805</v>
       </c>
       <c r="B11" t="n">
         <v>79081</v>
@@ -1738,10 +1700,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483607</v>
+        <v>483517</v>
       </c>
       <c r="R11" t="n">
-        <v>7145404</v>
+        <v>7145580</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1773,7 +1735,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1783,7 +1745,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1810,10 +1772,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129716452</v>
+        <v>129726955</v>
       </c>
       <c r="B12" t="n">
-        <v>91617</v>
+        <v>79081</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1821,30 +1783,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483480</v>
+        <v>483580</v>
       </c>
       <c r="R12" t="n">
-        <v>7145600</v>
+        <v>7145305</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1879,34 +1848,65 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På en levande gran.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129716455</v>
+        <v>129726819</v>
       </c>
       <c r="B13" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1914,39 +1914,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483975</v>
+        <v>483862</v>
       </c>
       <c r="R13" t="n">
-        <v>7145436</v>
+        <v>7145604</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1976,9 +1971,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1993,22 +1998,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129727923</v>
+        <v>129716468</v>
       </c>
       <c r="B14" t="n">
-        <v>57736</v>
+        <v>91619</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2016,34 +2021,30 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483397</v>
+        <v>484042</v>
       </c>
       <c r="R14" t="n">
-        <v>7145483</v>
+        <v>7145421</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2078,11 +2079,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2095,19 +2091,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129726935</v>
+        <v>129716455</v>
       </c>
       <c r="B15" t="n">
         <v>57736</v>
@@ -2136,28 +2132,21 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483601</v>
+        <v>483975</v>
       </c>
       <c r="R15" t="n">
-        <v>7145616</v>
+        <v>7145436</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2192,11 +2181,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, på stambasen av en levande gran i barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2205,48 +2189,23 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129727919</v>
+        <v>129727920</v>
       </c>
       <c r="B16" t="n">
         <v>57736</v>
@@ -2281,10 +2240,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483535</v>
+        <v>483452</v>
       </c>
       <c r="R16" t="n">
-        <v>7145332</v>
+        <v>7145362</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2321,7 +2280,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2348,7 +2307,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129727920</v>
+        <v>129727919</v>
       </c>
       <c r="B17" t="n">
         <v>57736</v>
@@ -2383,10 +2342,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483452</v>
+        <v>483535</v>
       </c>
       <c r="R17" t="n">
-        <v>7145362</v>
+        <v>7145332</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2423,7 +2382,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2450,10 +2409,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129726819</v>
+        <v>129726935</v>
       </c>
       <c r="B18" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2461,34 +2420,46 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483862</v>
+        <v>483601</v>
       </c>
       <c r="R18" t="n">
-        <v>7145604</v>
+        <v>7145616</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2518,19 +2489,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>09:11</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>09:11</t>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, på stambasen av en levande gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2541,26 +2507,51 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129716468</v>
+        <v>129727923</v>
       </c>
       <c r="B19" t="n">
-        <v>91617</v>
+        <v>57736</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2568,30 +2559,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>484042</v>
+        <v>483397</v>
       </c>
       <c r="R19" t="n">
-        <v>7145421</v>
+        <v>7145483</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2626,6 +2621,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2638,22 +2638,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129726941</v>
+        <v>129726804</v>
       </c>
       <c r="B20" t="n">
-        <v>80187</v>
+        <v>79081</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2661,41 +2661,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483369</v>
+        <v>483493</v>
       </c>
       <c r="R20" t="n">
-        <v>7145513</v>
+        <v>7145542</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2725,14 +2718,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På en levande sälg.</t>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2741,54 +2739,28 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129726804</v>
+        <v>129726941</v>
       </c>
       <c r="B21" t="n">
-        <v>79081</v>
+        <v>80187</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2796,34 +2768,41 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>483493</v>
+        <v>483369</v>
       </c>
       <c r="R21" t="n">
-        <v>7145542</v>
+        <v>7145513</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2853,19 +2832,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>10:00</t>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På en levande sälg.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2874,28 +2848,54 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129727934</v>
+        <v>129726825</v>
       </c>
       <c r="B22" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2903,34 +2903,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483619</v>
+        <v>483962</v>
       </c>
       <c r="R22" t="n">
-        <v>7145595</v>
+        <v>7145447</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2960,14 +2960,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2982,12 +2987,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2997,7 +3002,7 @@
         <v>129726818</v>
       </c>
       <c r="B23" t="n">
-        <v>83050</v>
+        <v>83052</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3101,10 +3106,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129726825</v>
+        <v>129727934</v>
       </c>
       <c r="B24" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3112,34 +3117,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>483962</v>
+        <v>483619</v>
       </c>
       <c r="R24" t="n">
-        <v>7145447</v>
+        <v>7145595</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3169,19 +3174,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>08:51</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>08:51</t>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3196,12 +3196,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3425,7 +3425,7 @@
         <v>129727915</v>
       </c>
       <c r="B27" t="n">
-        <v>92315</v>
+        <v>92317</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3519,45 +3519,57 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129726816</v>
+        <v>129726933</v>
       </c>
       <c r="B28" t="n">
-        <v>75065</v>
+        <v>57736</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6428</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>483815</v>
+        <v>483582</v>
       </c>
       <c r="R28" t="n">
-        <v>7145615</v>
+        <v>7145456</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3587,19 +3599,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>09:18</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>09:18</t>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3610,16 +3617,41 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3728,57 +3760,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129726933</v>
+        <v>129726816</v>
       </c>
       <c r="B30" t="n">
-        <v>57736</v>
+        <v>75065</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6428</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>483582</v>
+        <v>483815</v>
       </c>
       <c r="R30" t="n">
-        <v>7145456</v>
+        <v>7145615</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3808,14 +3828,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3826,41 +3851,16 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3964,7 +3964,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129726961</v>
+        <v>129726824</v>
       </c>
       <c r="B32" t="n">
         <v>79081</v>
@@ -3993,19 +3993,16 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>483414</v>
+        <v>483981</v>
       </c>
       <c r="R32" t="n">
-        <v>7145535</v>
+        <v>7145521</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4035,14 +4032,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>08:59</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På en levande gran.</t>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4051,51 +4053,25 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129726824</v>
+        <v>129726961</v>
       </c>
       <c r="B33" t="n">
         <v>79081</v>
@@ -4124,16 +4100,19 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>483981</v>
+        <v>483414</v>
       </c>
       <c r="R33" t="n">
-        <v>7145521</v>
+        <v>7145535</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4163,19 +4142,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>08:59</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>08:59</t>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På en levande gran.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4184,28 +4158,54 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129726938</v>
+        <v>129727931</v>
       </c>
       <c r="B34" t="n">
-        <v>57896</v>
+        <v>57736</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4213,54 +4213,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>483739</v>
+        <v>483545</v>
       </c>
       <c r="R34" t="n">
-        <v>7145743</v>
+        <v>7145507</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4297,7 +4277,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Synobservation av två talltitor med lockläte. Ev. rörde sig fler talltitor runt fyndplatsen som finns i flerskiktad äldre barrblandskog.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4308,36 +4288,26 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>Flerskiktad äldre barrblandskog.</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129727931</v>
+        <v>129726938</v>
       </c>
       <c r="B35" t="n">
-        <v>57736</v>
+        <v>57896</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4345,34 +4315,54 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>483545</v>
+        <v>483739</v>
       </c>
       <c r="R35" t="n">
-        <v>7145507</v>
+        <v>7145743</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4409,7 +4399,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Synobservation av två talltitor med lockläte. Ev. rörde sig fler talltitor runt fyndplatsen som finns i flerskiktad äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4420,26 +4410,36 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Flerskiktad äldre barrblandskog.</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129726801</v>
+        <v>129727927</v>
       </c>
       <c r="B36" t="n">
-        <v>83055</v>
+        <v>57736</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4447,34 +4447,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1467</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>483487</v>
+        <v>483606</v>
       </c>
       <c r="R36" t="n">
-        <v>7145541</v>
+        <v>7145282</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4504,19 +4504,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>10:09</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>10:09</t>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4531,19 +4526,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129716461</v>
+        <v>129726807</v>
       </c>
       <c r="B37" t="n">
         <v>79081</v>
@@ -4574,14 +4569,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>483576</v>
+        <v>483589</v>
       </c>
       <c r="R37" t="n">
-        <v>7145615</v>
+        <v>7145582</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4611,9 +4606,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4628,19 +4633,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129726807</v>
+        <v>129716466</v>
       </c>
       <c r="B38" t="n">
         <v>79081</v>
@@ -4671,14 +4676,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>483589</v>
+        <v>483481</v>
       </c>
       <c r="R38" t="n">
-        <v>7145582</v>
+        <v>7145592</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4708,19 +4713,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>09:50</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4735,19 +4730,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129716466</v>
+        <v>129716461</v>
       </c>
       <c r="B39" t="n">
         <v>79081</v>
@@ -4782,10 +4777,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>483481</v>
+        <v>483576</v>
       </c>
       <c r="R39" t="n">
-        <v>7145592</v>
+        <v>7145615</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4844,10 +4839,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129727927</v>
+        <v>129726801</v>
       </c>
       <c r="B40" t="n">
-        <v>57736</v>
+        <v>83057</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4855,34 +4850,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>1467</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>483606</v>
+        <v>483487</v>
       </c>
       <c r="R40" t="n">
-        <v>7145282</v>
+        <v>7145541</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4912,14 +4907,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4934,57 +4934,57 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129726821</v>
+        <v>129716464</v>
       </c>
       <c r="B41" t="n">
-        <v>79081</v>
+        <v>92317</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>483922</v>
+        <v>484017</v>
       </c>
       <c r="R41" t="n">
-        <v>7145570</v>
+        <v>7145437</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5014,19 +5014,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>09:05</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>09:05</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5041,12 +5031,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5056,7 +5046,7 @@
         <v>129726948</v>
       </c>
       <c r="B42" t="n">
-        <v>91617</v>
+        <v>91619</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5184,48 +5174,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129726946</v>
+        <v>129726821</v>
       </c>
       <c r="B43" t="n">
-        <v>80214</v>
+        <v>79081</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>483607</v>
+        <v>483922</v>
       </c>
       <c r="R43" t="n">
-        <v>7145621</v>
+        <v>7145570</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5255,75 +5242,87 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129716464</v>
+        <v>129726960</v>
       </c>
       <c r="B44" t="n">
-        <v>92315</v>
+        <v>79081</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>484017</v>
+        <v>483376</v>
       </c>
       <c r="R44" t="n">
-        <v>7145437</v>
+        <v>7145540</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5358,56 +5357,87 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På en levande gran.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129726960</v>
+        <v>129726946</v>
       </c>
       <c r="B45" t="n">
-        <v>79081</v>
+        <v>80214</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5420,10 +5450,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>483376</v>
+        <v>483607</v>
       </c>
       <c r="R45" t="n">
-        <v>7145540</v>
+        <v>7145621</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5458,11 +5488,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På en levande gran.</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5472,31 +5497,6 @@
       <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5513,7 +5513,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129726810</v>
+        <v>129727936</v>
       </c>
       <c r="B46" t="n">
         <v>57736</v>
@@ -5541,31 +5541,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>483760</v>
+        <v>483750</v>
       </c>
       <c r="R46" t="n">
-        <v>7145583</v>
+        <v>7145579</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5595,19 +5581,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>09:41</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>09:41</t>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5622,19 +5603,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129727936</v>
+        <v>129727938</v>
       </c>
       <c r="B47" t="n">
         <v>57736</v>
@@ -5669,10 +5650,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>483750</v>
+        <v>483975</v>
       </c>
       <c r="R47" t="n">
-        <v>7145579</v>
+        <v>7145511</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5736,7 +5717,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129727938</v>
+        <v>129726810</v>
       </c>
       <c r="B48" t="n">
         <v>57736</v>
@@ -5764,17 +5745,31 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>483975</v>
+        <v>483760</v>
       </c>
       <c r="R48" t="n">
-        <v>7145511</v>
+        <v>7145583</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5804,14 +5799,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5826,12 +5826,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5945,10 +5945,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129727935</v>
+        <v>129716462</v>
       </c>
       <c r="B50" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5956,34 +5956,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>483723</v>
+        <v>483666</v>
       </c>
       <c r="R50" t="n">
-        <v>7145593</v>
+        <v>7145612</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6018,11 +6018,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6035,22 +6030,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129716462</v>
+        <v>129727935</v>
       </c>
       <c r="B51" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6058,34 +6053,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>483666</v>
+        <v>483723</v>
       </c>
       <c r="R51" t="n">
-        <v>7145612</v>
+        <v>7145593</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6120,6 +6115,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6132,57 +6132,57 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129727914</v>
+        <v>129716458</v>
       </c>
       <c r="B52" t="n">
-        <v>92315</v>
+        <v>83052</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3298</v>
+        <v>6440</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>483577</v>
+        <v>483701</v>
       </c>
       <c r="R52" t="n">
-        <v>7145438</v>
+        <v>7145588</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6229,22 +6229,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129716458</v>
+        <v>129727924</v>
       </c>
       <c r="B53" t="n">
-        <v>83050</v>
+        <v>57736</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6252,34 +6252,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>483701</v>
+        <v>483548</v>
       </c>
       <c r="R53" t="n">
-        <v>7145588</v>
+        <v>7145488</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6314,6 +6314,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6326,22 +6331,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129726811</v>
+        <v>129727922</v>
       </c>
       <c r="B54" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6349,34 +6354,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>483760</v>
+        <v>483507</v>
       </c>
       <c r="R54" t="n">
-        <v>7145575</v>
+        <v>7145556</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6406,19 +6411,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>09:35</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>09:35</t>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6433,22 +6433,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129727922</v>
+        <v>129726811</v>
       </c>
       <c r="B55" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6456,34 +6456,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>483507</v>
+        <v>483760</v>
       </c>
       <c r="R55" t="n">
-        <v>7145556</v>
+        <v>7145575</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6513,14 +6513,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6535,57 +6540,60 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129727924</v>
+        <v>129726944</v>
       </c>
       <c r="B56" t="n">
-        <v>57736</v>
+        <v>80214</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>483548</v>
+        <v>483597</v>
       </c>
       <c r="R56" t="n">
-        <v>7145488</v>
+        <v>7145735</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6620,39 +6628,35 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129726944</v>
+        <v>129727914</v>
       </c>
       <c r="B57" t="n">
-        <v>80214</v>
+        <v>92317</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6660,37 +6664,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6461</v>
+        <v>3298</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>483597</v>
+        <v>483577</v>
       </c>
       <c r="R57" t="n">
-        <v>7145735</v>
+        <v>7145438</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6731,26 +6732,25 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129726806</v>
+        <v>129716453</v>
       </c>
       <c r="B58" t="n">
         <v>79081</v>
@@ -6781,14 +6781,14 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>483558</v>
+        <v>484032</v>
       </c>
       <c r="R58" t="n">
-        <v>7145588</v>
+        <v>7145416</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6818,19 +6818,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>09:51</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>09:51</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6845,22 +6835,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129727929</v>
+        <v>129726953</v>
       </c>
       <c r="B59" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6868,34 +6858,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>483677</v>
+        <v>483555</v>
       </c>
       <c r="R59" t="n">
-        <v>7145477</v>
+        <v>7145531</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6932,7 +6925,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6941,28 +6934,54 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129727932</v>
+        <v>129716449</v>
       </c>
       <c r="B60" t="n">
-        <v>57736</v>
+        <v>83052</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6970,34 +6989,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>483527</v>
+        <v>483889</v>
       </c>
       <c r="R60" t="n">
-        <v>7145534</v>
+        <v>7145589</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7032,11 +7051,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -7049,22 +7063,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129727930</v>
+        <v>129726788</v>
       </c>
       <c r="B61" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7072,34 +7086,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>483658</v>
+        <v>483665</v>
       </c>
       <c r="R61" t="n">
-        <v>7145503</v>
+        <v>7145479</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7129,14 +7143,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7151,12 +7170,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -7270,7 +7289,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129716453</v>
+        <v>129726806</v>
       </c>
       <c r="B63" t="n">
         <v>79081</v>
@@ -7301,14 +7320,14 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>484032</v>
+        <v>483558</v>
       </c>
       <c r="R63" t="n">
-        <v>7145416</v>
+        <v>7145588</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7338,9 +7357,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7355,22 +7384,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129726953</v>
+        <v>129727932</v>
       </c>
       <c r="B64" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7378,37 +7407,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>483555</v>
+        <v>483527</v>
       </c>
       <c r="R64" t="n">
-        <v>7145531</v>
+        <v>7145534</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7445,7 +7471,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7454,54 +7480,28 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AH64" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129716449</v>
+        <v>129727929</v>
       </c>
       <c r="B65" t="n">
-        <v>83050</v>
+        <v>57736</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7509,34 +7509,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>483889</v>
+        <v>483677</v>
       </c>
       <c r="R65" t="n">
-        <v>7145589</v>
+        <v>7145477</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7571,6 +7571,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -7583,22 +7588,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129726788</v>
+        <v>129727930</v>
       </c>
       <c r="B66" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7606,34 +7611,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>483665</v>
+        <v>483658</v>
       </c>
       <c r="R66" t="n">
-        <v>7145479</v>
+        <v>7145503</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7663,19 +7668,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>11:18</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>11:18</t>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7690,12 +7690,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -7705,7 +7705,7 @@
         <v>129716448</v>
       </c>
       <c r="B67" t="n">
-        <v>91548</v>
+        <v>91550</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7799,10 +7799,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129726937</v>
+        <v>129726958</v>
       </c>
       <c r="B68" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7810,46 +7810,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>483749</v>
+        <v>483482</v>
       </c>
       <c r="R68" t="n">
-        <v>7145581</v>
+        <v>7145330</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7886,7 +7877,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en levande gran.</t>
+          <t>På en levande gran.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7895,6 +7886,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7915,12 +7907,12 @@
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -7938,10 +7930,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129727916</v>
+        <v>129726966</v>
       </c>
       <c r="B69" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7949,34 +7941,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>483577</v>
+        <v>483764</v>
       </c>
       <c r="R69" t="n">
-        <v>7145734</v>
+        <v>7145582</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8013,7 +8008,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Långväxta bålar på en levande gran.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8022,28 +8017,54 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129727918</v>
+        <v>129726797</v>
       </c>
       <c r="B70" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8051,34 +8072,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>483580</v>
+        <v>483540</v>
       </c>
       <c r="R70" t="n">
-        <v>7145447</v>
+        <v>7145349</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8108,14 +8129,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8130,22 +8156,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129726958</v>
+        <v>129727916</v>
       </c>
       <c r="B71" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8153,37 +8179,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>483482</v>
+        <v>483577</v>
       </c>
       <c r="R71" t="n">
-        <v>7145330</v>
+        <v>7145734</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8220,7 +8243,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>På en levande gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8229,54 +8252,28 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AH71" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129726966</v>
+        <v>129726937</v>
       </c>
       <c r="B72" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8284,37 +8281,46 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>483764</v>
+        <v>483749</v>
       </c>
       <c r="R72" t="n">
-        <v>7145582</v>
+        <v>7145581</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8351,7 +8357,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en levande gran.</t>
+          <t>Ringhack, äldre, på stambasen av en levande gran.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8360,7 +8366,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8381,12 +8386,12 @@
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -8404,10 +8409,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129726797</v>
+        <v>129727918</v>
       </c>
       <c r="B73" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8415,34 +8420,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>483540</v>
+        <v>483580</v>
       </c>
       <c r="R73" t="n">
-        <v>7145349</v>
+        <v>7145447</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8472,19 +8477,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>10:29</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>10:29</t>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8499,22 +8499,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129726964</v>
+        <v>129726947</v>
       </c>
       <c r="B74" t="n">
-        <v>79081</v>
+        <v>91595</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8522,26 +8522,30 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -8549,10 +8553,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>483553</v>
+        <v>483784</v>
       </c>
       <c r="R74" t="n">
-        <v>7145611</v>
+        <v>7145639</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8589,7 +8593,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>På levande gran i barrblandskog.</t>
+          <t>I levande gran i granskog vid brant.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8604,7 +8608,7 @@
       </c>
       <c r="AH74" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ74" t="inlineStr">
@@ -8619,12 +8623,12 @@
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -8642,10 +8646,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129726826</v>
+        <v>129726964</v>
       </c>
       <c r="B75" t="n">
-        <v>78094</v>
+        <v>79081</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8653,34 +8657,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>483988</v>
+        <v>483553</v>
       </c>
       <c r="R75" t="n">
-        <v>7145444</v>
+        <v>7145611</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8710,19 +8717,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>08:49</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>08:49</t>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>På levande gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8731,18 +8733,44 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM75" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -8856,10 +8884,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129726947</v>
+        <v>129726826</v>
       </c>
       <c r="B77" t="n">
-        <v>91593</v>
+        <v>78094</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8867,41 +8895,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1108</v>
+        <v>228579</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>483784</v>
+        <v>483988</v>
       </c>
       <c r="R77" t="n">
-        <v>7145639</v>
+        <v>7145444</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8931,14 +8952,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>I levande gran i granskog vid brant.</t>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8947,54 +8973,28 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AH77" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129716465</v>
+        <v>129726823</v>
       </c>
       <c r="B78" t="n">
-        <v>91597</v>
+        <v>79081</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9002,34 +9002,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>483983</v>
+        <v>483959</v>
       </c>
       <c r="R78" t="n">
-        <v>7145507</v>
+        <v>7145539</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9059,9 +9059,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9076,22 +9086,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129727941</v>
+        <v>129716451</v>
       </c>
       <c r="B79" t="n">
-        <v>91593</v>
+        <v>79081</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9099,34 +9109,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>483551</v>
+        <v>483989</v>
       </c>
       <c r="R79" t="n">
-        <v>7145323</v>
+        <v>7145511</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9173,22 +9183,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129726795</v>
+        <v>129726963</v>
       </c>
       <c r="B80" t="n">
-        <v>83055</v>
+        <v>79081</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9196,34 +9206,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>483545</v>
+        <v>483498</v>
       </c>
       <c r="R80" t="n">
-        <v>7145343</v>
+        <v>7145585</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9253,19 +9266,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>10:35</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>10:35</t>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>På levande gran.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9274,28 +9282,54 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM80" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129726831</v>
+        <v>129726812</v>
       </c>
       <c r="B81" t="n">
-        <v>83050</v>
+        <v>79081</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9303,21 +9337,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9327,10 +9361,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>484008</v>
+        <v>483764</v>
       </c>
       <c r="R81" t="n">
-        <v>7145455</v>
+        <v>7145589</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9362,7 +9396,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9372,7 +9406,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9399,7 +9433,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129726963</v>
+        <v>129726798</v>
       </c>
       <c r="B82" t="n">
         <v>79081</v>
@@ -9428,19 +9462,16 @@
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>483498</v>
+        <v>483429</v>
       </c>
       <c r="R82" t="n">
-        <v>7145585</v>
+        <v>7145430</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9470,14 +9501,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>På levande gran.</t>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9486,54 +9522,28 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
-      </c>
-      <c r="AH82" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK82" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129716451</v>
+        <v>129716465</v>
       </c>
       <c r="B83" t="n">
-        <v>79081</v>
+        <v>91599</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9541,21 +9551,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9565,10 +9575,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>483989</v>
+        <v>483983</v>
       </c>
       <c r="R83" t="n">
-        <v>7145511</v>
+        <v>7145507</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9627,10 +9637,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129726798</v>
+        <v>129727941</v>
       </c>
       <c r="B84" t="n">
-        <v>79081</v>
+        <v>91595</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9638,34 +9648,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>483429</v>
+        <v>483551</v>
       </c>
       <c r="R84" t="n">
-        <v>7145430</v>
+        <v>7145323</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9695,19 +9705,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>10:16</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>10:16</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9722,22 +9722,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129726812</v>
+        <v>129726795</v>
       </c>
       <c r="B85" t="n">
-        <v>79081</v>
+        <v>83057</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9745,21 +9745,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9769,10 +9769,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>483764</v>
+        <v>483545</v>
       </c>
       <c r="R85" t="n">
-        <v>7145589</v>
+        <v>7145343</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9804,7 +9804,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9841,10 +9841,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129726823</v>
+        <v>129727942</v>
       </c>
       <c r="B86" t="n">
-        <v>79081</v>
+        <v>91619</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9852,34 +9852,30 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>483959</v>
+        <v>483495</v>
       </c>
       <c r="R86" t="n">
-        <v>7145539</v>
+        <v>7145618</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9909,19 +9905,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>09:02</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>09:02</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9936,22 +9922,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129727942</v>
+        <v>129726831</v>
       </c>
       <c r="B87" t="n">
-        <v>91617</v>
+        <v>83052</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9959,30 +9945,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr"/>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>483495</v>
+        <v>484008</v>
       </c>
       <c r="R87" t="n">
-        <v>7145618</v>
+        <v>7145455</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10012,9 +10002,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>08:42</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10029,12 +10029,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -10044,7 +10044,7 @@
         <v>129726796</v>
       </c>
       <c r="B88" t="n">
-        <v>83048</v>
+        <v>83050</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10681,10 +10681,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129716456</v>
+        <v>129726942</v>
       </c>
       <c r="B94" t="n">
-        <v>82916</v>
+        <v>80187</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10692,34 +10692,41 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>483445</v>
+        <v>483377</v>
       </c>
       <c r="R94" t="n">
-        <v>7145393</v>
+        <v>7145537</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10754,34 +10761,65 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>På en levande sälg i granskog.</t>
+        </is>
+      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
+      </c>
+      <c r="AH94" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ94" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK94" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM94" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129726942</v>
+        <v>129716456</v>
       </c>
       <c r="B95" t="n">
-        <v>80187</v>
+        <v>82918</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10789,41 +10827,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>483377</v>
+        <v>483445</v>
       </c>
       <c r="R95" t="n">
-        <v>7145537</v>
+        <v>7145393</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10858,55 +10889,24 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>På en levande sälg i granskog.</t>
-        </is>
-      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
-      </c>
-      <c r="AH95" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ95" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK95" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM95" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO95" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
@@ -11309,7 +11309,7 @@
         <v>129716457</v>
       </c>
       <c r="B99" t="n">
-        <v>91617</v>
+        <v>91619</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129727937</v>
+        <v>129727933</v>
       </c>
       <c r="B106" t="n">
         <v>57736</v>
@@ -12193,10 +12193,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>483824</v>
+        <v>483593</v>
       </c>
       <c r="R106" t="n">
-        <v>7145592</v>
+        <v>7145594</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12233,7 +12233,7 @@
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12260,7 +12260,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129727933</v>
+        <v>129727937</v>
       </c>
       <c r="B107" t="n">
         <v>57736</v>
@@ -12295,10 +12295,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>483593</v>
+        <v>483824</v>
       </c>
       <c r="R107" t="n">
-        <v>7145594</v>
+        <v>7145592</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12335,7 +12335,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12469,10 +12469,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129726827</v>
+        <v>129716454</v>
       </c>
       <c r="B109" t="n">
-        <v>83050</v>
+        <v>91595</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12480,34 +12480,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>483988</v>
+        <v>484017</v>
       </c>
       <c r="R109" t="n">
-        <v>7145444</v>
+        <v>7145437</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12537,19 +12537,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>08:49</t>
-        </is>
-      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>08:49</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12564,12 +12554,12 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
@@ -12814,10 +12804,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129726789</v>
+        <v>129726827</v>
       </c>
       <c r="B112" t="n">
-        <v>79081</v>
+        <v>83052</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12825,21 +12815,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12849,10 +12839,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>483663</v>
+        <v>483988</v>
       </c>
       <c r="R112" t="n">
-        <v>7145420</v>
+        <v>7145444</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12884,7 +12874,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12894,7 +12884,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12921,7 +12911,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129726817</v>
+        <v>129726789</v>
       </c>
       <c r="B113" t="n">
         <v>79081</v>
@@ -12956,10 +12946,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>483834</v>
+        <v>483663</v>
       </c>
       <c r="R113" t="n">
-        <v>7145605</v>
+        <v>7145420</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12991,7 +12981,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -13001,7 +12991,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13028,10 +13018,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129727939</v>
+        <v>129726950</v>
       </c>
       <c r="B114" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13039,34 +13029,37 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>483605</v>
+        <v>483720</v>
       </c>
       <c r="R114" t="n">
-        <v>7145281</v>
+        <v>7145756</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13103,7 +13096,7 @@
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>Hack ganska färska</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13112,28 +13105,54 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
+      </c>
+      <c r="AH114" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ114" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK114" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM114" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO114" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129727925</v>
+        <v>129726959</v>
       </c>
       <c r="B115" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13141,34 +13160,37 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>483580</v>
+        <v>483422</v>
       </c>
       <c r="R115" t="n">
-        <v>7145425</v>
+        <v>7145360</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13205,7 +13227,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>På en levande gran.</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13214,28 +13236,54 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
+      </c>
+      <c r="AH115" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ115" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK115" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM115" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO115" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129727917</v>
+        <v>129726817</v>
       </c>
       <c r="B116" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13243,34 +13291,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>483572</v>
+        <v>483834</v>
       </c>
       <c r="R116" t="n">
-        <v>7145725</v>
+        <v>7145605</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13300,14 +13348,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13322,22 +13375,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129716454</v>
+        <v>129726954</v>
       </c>
       <c r="B117" t="n">
-        <v>91593</v>
+        <v>79081</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13345,34 +13398,37 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>484017</v>
+        <v>483580</v>
       </c>
       <c r="R117" t="n">
-        <v>7145437</v>
+        <v>7145435</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13407,34 +13463,65 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>På gran i granskog.</t>
+        </is>
+      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
       <c r="AE117" t="b">
         <v>0</v>
       </c>
+      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
+      </c>
+      <c r="AH117" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK117" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM117" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO117" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129726950</v>
+        <v>129727917</v>
       </c>
       <c r="B118" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13442,37 +13529,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>483720</v>
+        <v>483572</v>
       </c>
       <c r="R118" t="n">
-        <v>7145756</v>
+        <v>7145725</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13509,7 +13593,7 @@
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13518,54 +13602,28 @@
       <c r="AE118" t="b">
         <v>0</v>
       </c>
-      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
-      </c>
-      <c r="AH118" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ118" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK118" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM118" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO118" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129726959</v>
+        <v>129727925</v>
       </c>
       <c r="B119" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13573,37 +13631,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>483422</v>
+        <v>483580</v>
       </c>
       <c r="R119" t="n">
-        <v>7145360</v>
+        <v>7145425</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13640,7 +13695,7 @@
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>På en levande gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13649,54 +13704,28 @@
       <c r="AE119" t="b">
         <v>0</v>
       </c>
-      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
-      </c>
-      <c r="AH119" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ119" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK119" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM119" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO119" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129726954</v>
+        <v>129727939</v>
       </c>
       <c r="B120" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13704,37 +13733,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>483580</v>
+        <v>483605</v>
       </c>
       <c r="R120" t="n">
-        <v>7145435</v>
+        <v>7145281</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13771,7 +13797,7 @@
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>På gran i granskog.</t>
+          <t>Hack ganska färska</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13780,44 +13806,18 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
-      </c>
-      <c r="AH120" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ120" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK120" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM120" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO120" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
@@ -13827,7 +13827,7 @@
         <v>129730288</v>
       </c>
       <c r="B121" t="n">
-        <v>91617</v>
+        <v>91619</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14119,7 +14119,7 @@
         <v>129730292</v>
       </c>
       <c r="B124" t="n">
-        <v>83042</v>
+        <v>83044</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14213,10 +14213,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129730253</v>
+        <v>129730291</v>
       </c>
       <c r="B125" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14224,21 +14224,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14248,10 +14248,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>483421</v>
+        <v>483364</v>
       </c>
       <c r="R125" t="n">
-        <v>7145545</v>
+        <v>7145506</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14310,10 +14310,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129730291</v>
+        <v>129730268</v>
       </c>
       <c r="B126" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14321,21 +14321,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14345,10 +14345,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>483364</v>
+        <v>483247</v>
       </c>
       <c r="R126" t="n">
-        <v>7145506</v>
+        <v>7145580</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14381,6 +14381,11 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14407,10 +14412,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129730268</v>
+        <v>129730253</v>
       </c>
       <c r="B127" t="n">
-        <v>57736</v>
+        <v>78838</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14418,21 +14423,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14442,10 +14447,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>483247</v>
+        <v>483421</v>
       </c>
       <c r="R127" t="n">
-        <v>7145580</v>
+        <v>7145545</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14478,11 +14483,6 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14509,10 +14509,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129730248</v>
+        <v>129730244</v>
       </c>
       <c r="B128" t="n">
-        <v>80186</v>
+        <v>80187</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14520,21 +14520,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14547,7 +14547,7 @@
         <v>483599</v>
       </c>
       <c r="R128" t="n">
-        <v>7145185</v>
+        <v>7145190</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14606,10 +14606,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129730247</v>
+        <v>129730274</v>
       </c>
       <c r="B129" t="n">
-        <v>80186</v>
+        <v>57736</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14617,21 +14617,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14641,10 +14641,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>483595</v>
+        <v>483612</v>
       </c>
       <c r="R129" t="n">
-        <v>7145180</v>
+        <v>7145596</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14677,6 +14677,11 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14703,10 +14708,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129730244</v>
+        <v>129730290</v>
       </c>
       <c r="B130" t="n">
-        <v>80187</v>
+        <v>91619</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14714,23 +14719,19 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
@@ -14738,10 +14739,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>483599</v>
+        <v>483766</v>
       </c>
       <c r="R130" t="n">
-        <v>7145190</v>
+        <v>7145610</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14800,10 +14801,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129730290</v>
+        <v>129730248</v>
       </c>
       <c r="B131" t="n">
-        <v>91617</v>
+        <v>80186</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14811,19 +14812,23 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
@@ -14831,10 +14836,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>483766</v>
+        <v>483599</v>
       </c>
       <c r="R131" t="n">
-        <v>7145610</v>
+        <v>7145185</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14893,10 +14898,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129730274</v>
+        <v>129730247</v>
       </c>
       <c r="B132" t="n">
-        <v>57736</v>
+        <v>80186</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14904,21 +14909,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14928,10 +14933,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>483612</v>
+        <v>483595</v>
       </c>
       <c r="R132" t="n">
-        <v>7145596</v>
+        <v>7145180</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14964,11 +14969,6 @@
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14995,10 +14995,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129730287</v>
+        <v>129730255</v>
       </c>
       <c r="B133" t="n">
-        <v>91593</v>
+        <v>91619</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15006,23 +15006,19 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
@@ -15030,10 +15026,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>483608</v>
+        <v>483529</v>
       </c>
       <c r="R133" t="n">
-        <v>7145490</v>
+        <v>7145591</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15092,10 +15088,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129730252</v>
+        <v>129730287</v>
       </c>
       <c r="B134" t="n">
-        <v>78838</v>
+        <v>91595</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15103,21 +15099,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6446</v>
+        <v>1108</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -15127,10 +15123,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>483407</v>
+        <v>483608</v>
       </c>
       <c r="R134" t="n">
-        <v>7145540</v>
+        <v>7145490</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15189,10 +15185,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129730255</v>
+        <v>129730252</v>
       </c>
       <c r="B135" t="n">
-        <v>91617</v>
+        <v>78838</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15200,19 +15196,23 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5432</v>
+        <v>6446</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr"/>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
@@ -15220,10 +15220,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>483529</v>
+        <v>483407</v>
       </c>
       <c r="R135" t="n">
-        <v>7145591</v>
+        <v>7145540</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15479,7 +15479,7 @@
         <v>129730293</v>
       </c>
       <c r="B138" t="n">
-        <v>83042</v>
+        <v>83044</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15772,32 +15772,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129730285</v>
+        <v>129730254</v>
       </c>
       <c r="B141" t="n">
-        <v>83058</v>
+        <v>78838</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1469</v>
+        <v>6446</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Liten blekspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Sclerophora peronella</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15807,10 +15807,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>483470</v>
+        <v>483454</v>
       </c>
       <c r="R141" t="n">
-        <v>7145348</v>
+        <v>7145556</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15869,32 +15869,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129730254</v>
+        <v>129730285</v>
       </c>
       <c r="B142" t="n">
-        <v>78838</v>
+        <v>83060</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6446</v>
+        <v>1469</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Liten blekspik</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sclerophora peronella</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15904,10 +15904,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>483454</v>
+        <v>483470</v>
       </c>
       <c r="R142" t="n">
-        <v>7145556</v>
+        <v>7145348</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16160,10 +16160,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129730289</v>
+        <v>129730261</v>
       </c>
       <c r="B145" t="n">
-        <v>91617</v>
+        <v>79081</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16171,19 +16171,23 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
@@ -16191,10 +16195,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>483238</v>
+        <v>483247</v>
       </c>
       <c r="R145" t="n">
-        <v>7145599</v>
+        <v>7145585</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16253,10 +16257,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129730261</v>
+        <v>129730289</v>
       </c>
       <c r="B146" t="n">
-        <v>79081</v>
+        <v>91619</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16264,23 +16268,19 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr"/>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
@@ -16288,10 +16288,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>483247</v>
+        <v>483238</v>
       </c>
       <c r="R146" t="n">
-        <v>7145585</v>
+        <v>7145599</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16353,7 +16353,7 @@
         <v>129730294</v>
       </c>
       <c r="B147" t="n">
-        <v>83042</v>
+        <v>83044</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16549,10 +16549,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129730295</v>
+        <v>129730260</v>
       </c>
       <c r="B149" t="n">
-        <v>83042</v>
+        <v>79081</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16560,21 +16560,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16584,10 +16584,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>483462</v>
+        <v>483324</v>
       </c>
       <c r="R149" t="n">
-        <v>7145552</v>
+        <v>7145520</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16646,10 +16646,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129730260</v>
+        <v>129730295</v>
       </c>
       <c r="B150" t="n">
-        <v>79081</v>
+        <v>83044</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16657,21 +16657,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16681,10 +16681,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>483324</v>
+        <v>483462</v>
       </c>
       <c r="R150" t="n">
-        <v>7145520</v>
+        <v>7145552</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16743,32 +16743,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129730296</v>
+        <v>129730282</v>
       </c>
       <c r="B151" t="n">
-        <v>83042</v>
+        <v>80090</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>308</v>
+        <v>6456</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16778,10 +16778,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>483526</v>
+        <v>483534</v>
       </c>
       <c r="R151" t="n">
-        <v>7145596</v>
+        <v>7145348</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16840,32 +16840,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129730282</v>
+        <v>129730296</v>
       </c>
       <c r="B152" t="n">
-        <v>80090</v>
+        <v>83044</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6456</v>
+        <v>308</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16875,10 +16875,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>483534</v>
+        <v>483526</v>
       </c>
       <c r="R152" t="n">
-        <v>7145348</v>
+        <v>7145596</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17034,7 +17034,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129730267</v>
+        <v>129730269</v>
       </c>
       <c r="B154" t="n">
         <v>57736</v>
@@ -17069,10 +17069,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>483426</v>
+        <v>483364</v>
       </c>
       <c r="R154" t="n">
-        <v>7145362</v>
+        <v>7145545</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17136,7 +17136,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129730269</v>
+        <v>129730267</v>
       </c>
       <c r="B155" t="n">
         <v>57736</v>
@@ -17171,10 +17171,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>483364</v>
+        <v>483426</v>
       </c>
       <c r="R155" t="n">
-        <v>7145545</v>
+        <v>7145362</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17534,7 +17534,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129730276</v>
+        <v>129730265</v>
       </c>
       <c r="B159" t="n">
         <v>57736</v>
@@ -17562,37 +17562,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L159" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N159" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
           <t>Bodknulen, Jmt</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>483545</v>
+        <v>483564</v>
       </c>
       <c r="R159" t="n">
-        <v>7145332</v>
+        <v>7145344</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17625,6 +17605,11 @@
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17651,7 +17636,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129730265</v>
+        <v>129730276</v>
       </c>
       <c r="B160" t="n">
         <v>57736</v>
@@ -17679,17 +17664,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I160" t="inlineStr"/>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
           <t>Bodknulen, Jmt</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>483564</v>
+        <v>483545</v>
       </c>
       <c r="R160" t="n">
-        <v>7145344</v>
+        <v>7145332</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17722,11 +17727,6 @@
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC160" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17753,10 +17753,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129730263</v>
+        <v>129730256</v>
       </c>
       <c r="B161" t="n">
-        <v>83050</v>
+        <v>79081</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17764,21 +17764,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17788,10 +17788,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>483272</v>
+        <v>483772</v>
       </c>
       <c r="R161" t="n">
-        <v>7145579</v>
+        <v>7145571</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17850,10 +17850,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129730256</v>
+        <v>129730263</v>
       </c>
       <c r="B162" t="n">
-        <v>79081</v>
+        <v>83052</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17861,21 +17861,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17885,10 +17885,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>483772</v>
+        <v>483272</v>
       </c>
       <c r="R162" t="n">
-        <v>7145571</v>
+        <v>7145579</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17947,7 +17947,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129730273</v>
+        <v>129730271</v>
       </c>
       <c r="B163" t="n">
         <v>57736</v>
@@ -17982,10 +17982,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>483589</v>
+        <v>483461</v>
       </c>
       <c r="R163" t="n">
-        <v>7145604</v>
+        <v>7145552</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18151,7 +18151,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129730271</v>
+        <v>129730273</v>
       </c>
       <c r="B165" t="n">
         <v>57736</v>
@@ -18186,10 +18186,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>483461</v>
+        <v>483589</v>
       </c>
       <c r="R165" t="n">
-        <v>7145552</v>
+        <v>7145604</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>

--- a/artfynd/A 52753-2025 artfynd.xlsx
+++ b/artfynd/A 52753-2025 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129716450</v>
+        <v>129726820</v>
       </c>
       <c r="B3" t="n">
-        <v>79081</v>
+        <v>83057</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483823</v>
+        <v>483921</v>
       </c>
       <c r="R3" t="n">
-        <v>7145591</v>
+        <v>7145571</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,9 +850,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,19 +877,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129726952</v>
+        <v>129716450</v>
       </c>
       <c r="B4" t="n">
         <v>79081</v>
@@ -908,19 +918,16 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483538</v>
+        <v>483823</v>
       </c>
       <c r="R4" t="n">
-        <v>7145695</v>
+        <v>7145591</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,65 +962,34 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gran.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129726820</v>
+        <v>129726952</v>
       </c>
       <c r="B5" t="n">
-        <v>83057</v>
+        <v>79081</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1021,34 +997,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483921</v>
+        <v>483538</v>
       </c>
       <c r="R5" t="n">
-        <v>7145571</v>
+        <v>7145695</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,19 +1057,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>09:08</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>09:08</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1099,18 +1073,44 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1903,10 +1903,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129726819</v>
+        <v>129716468</v>
       </c>
       <c r="B13" t="n">
-        <v>79081</v>
+        <v>91619</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1914,34 +1914,30 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483862</v>
+        <v>484042</v>
       </c>
       <c r="R13" t="n">
-        <v>7145604</v>
+        <v>7145421</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1971,19 +1967,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>09:11</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>09:11</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1998,22 +1984,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129716468</v>
+        <v>129727923</v>
       </c>
       <c r="B14" t="n">
-        <v>91619</v>
+        <v>57736</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2021,30 +2007,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>484042</v>
+        <v>483397</v>
       </c>
       <c r="R14" t="n">
-        <v>7145421</v>
+        <v>7145483</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2079,6 +2069,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2091,12 +2086,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2548,10 +2543,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129727923</v>
+        <v>129726819</v>
       </c>
       <c r="B19" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2559,34 +2554,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483397</v>
+        <v>483862</v>
       </c>
       <c r="R19" t="n">
-        <v>7145483</v>
+        <v>7145604</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2616,14 +2611,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2638,12 +2638,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2892,7 +2892,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129726825</v>
+        <v>129726813</v>
       </c>
       <c r="B22" t="n">
         <v>79081</v>
@@ -2927,10 +2927,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483962</v>
+        <v>483773</v>
       </c>
       <c r="R22" t="n">
-        <v>7145447</v>
+        <v>7145613</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2999,10 +2999,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129726818</v>
+        <v>129726814</v>
       </c>
       <c r="B23" t="n">
-        <v>83052</v>
+        <v>79081</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3010,21 +3010,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3034,10 +3034,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483849</v>
+        <v>483796</v>
       </c>
       <c r="R23" t="n">
-        <v>7145605</v>
+        <v>7145620</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3069,7 +3069,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3208,45 +3208,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129726813</v>
+        <v>129727915</v>
       </c>
       <c r="B25" t="n">
-        <v>79081</v>
+        <v>92317</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>483773</v>
+        <v>483493</v>
       </c>
       <c r="R25" t="n">
-        <v>7145613</v>
+        <v>7145538</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3276,19 +3276,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>09:32</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>09:32</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3303,19 +3293,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129726814</v>
+        <v>129726825</v>
       </c>
       <c r="B26" t="n">
         <v>79081</v>
@@ -3350,10 +3340,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>483796</v>
+        <v>483962</v>
       </c>
       <c r="R26" t="n">
-        <v>7145620</v>
+        <v>7145447</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3385,7 +3375,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3395,7 +3385,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3422,45 +3412,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129727915</v>
+        <v>129726818</v>
       </c>
       <c r="B27" t="n">
-        <v>92317</v>
+        <v>83052</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3298</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>483493</v>
+        <v>483849</v>
       </c>
       <c r="R27" t="n">
-        <v>7145538</v>
+        <v>7145605</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3490,9 +3480,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3507,12 +3507,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -4436,10 +4436,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129727927</v>
+        <v>129716461</v>
       </c>
       <c r="B36" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4447,34 +4447,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>483606</v>
+        <v>483576</v>
       </c>
       <c r="R36" t="n">
-        <v>7145282</v>
+        <v>7145615</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4509,11 +4509,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4526,22 +4521,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129726807</v>
+        <v>129726801</v>
       </c>
       <c r="B37" t="n">
-        <v>79081</v>
+        <v>83057</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4549,21 +4544,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4573,10 +4568,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>483589</v>
+        <v>483487</v>
       </c>
       <c r="R37" t="n">
-        <v>7145582</v>
+        <v>7145541</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4608,7 +4603,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4618,7 +4613,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4645,7 +4640,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129716466</v>
+        <v>129726807</v>
       </c>
       <c r="B38" t="n">
         <v>79081</v>
@@ -4676,14 +4671,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>483481</v>
+        <v>483589</v>
       </c>
       <c r="R38" t="n">
-        <v>7145592</v>
+        <v>7145582</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4713,9 +4708,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4730,19 +4735,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129716461</v>
+        <v>129716466</v>
       </c>
       <c r="B39" t="n">
         <v>79081</v>
@@ -4777,10 +4782,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>483576</v>
+        <v>483481</v>
       </c>
       <c r="R39" t="n">
-        <v>7145615</v>
+        <v>7145592</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4839,10 +4844,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129726801</v>
+        <v>129727927</v>
       </c>
       <c r="B40" t="n">
-        <v>83057</v>
+        <v>57736</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4850,34 +4855,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1467</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>483487</v>
+        <v>483606</v>
       </c>
       <c r="R40" t="n">
-        <v>7145541</v>
+        <v>7145282</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4907,19 +4912,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>10:09</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>10:09</t>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4934,12 +4934,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -6144,45 +6144,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129716458</v>
+        <v>129727914</v>
       </c>
       <c r="B52" t="n">
-        <v>83052</v>
+        <v>92317</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6440</v>
+        <v>3298</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>483701</v>
+        <v>483577</v>
       </c>
       <c r="R52" t="n">
-        <v>7145588</v>
+        <v>7145438</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6229,22 +6229,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129727924</v>
+        <v>129716458</v>
       </c>
       <c r="B53" t="n">
-        <v>57736</v>
+        <v>83052</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6252,34 +6252,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>483548</v>
+        <v>483701</v>
       </c>
       <c r="R53" t="n">
-        <v>7145488</v>
+        <v>7145588</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6314,11 +6314,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6331,19 +6326,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129727922</v>
+        <v>129727924</v>
       </c>
       <c r="B54" t="n">
         <v>57736</v>
@@ -6378,10 +6373,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>483507</v>
+        <v>483548</v>
       </c>
       <c r="R54" t="n">
-        <v>7145556</v>
+        <v>7145488</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6445,10 +6440,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129726811</v>
+        <v>129727922</v>
       </c>
       <c r="B55" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6456,34 +6451,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>483760</v>
+        <v>483507</v>
       </c>
       <c r="R55" t="n">
-        <v>7145575</v>
+        <v>7145556</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6513,19 +6508,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>09:35</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>09:35</t>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6540,60 +6530,57 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129726944</v>
+        <v>129726811</v>
       </c>
       <c r="B56" t="n">
-        <v>80214</v>
+        <v>79081</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>483597</v>
+        <v>483760</v>
       </c>
       <c r="R56" t="n">
-        <v>7145735</v>
+        <v>7145575</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6623,40 +6610,49 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129727914</v>
+        <v>129726944</v>
       </c>
       <c r="B57" t="n">
-        <v>92317</v>
+        <v>80214</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6664,34 +6660,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3298</v>
+        <v>6461</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>483577</v>
+        <v>483597</v>
       </c>
       <c r="R57" t="n">
-        <v>7145438</v>
+        <v>7145735</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6732,18 +6731,19 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -12469,10 +12469,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129716454</v>
+        <v>129726827</v>
       </c>
       <c r="B109" t="n">
-        <v>91595</v>
+        <v>83052</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12480,34 +12480,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>484017</v>
+        <v>483988</v>
       </c>
       <c r="R109" t="n">
-        <v>7145437</v>
+        <v>7145444</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12537,9 +12537,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12554,19 +12564,19 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129726949</v>
+        <v>129726789</v>
       </c>
       <c r="B110" t="n">
         <v>79081</v>
@@ -12595,19 +12605,16 @@
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>483735</v>
+        <v>483663</v>
       </c>
       <c r="R110" t="n">
-        <v>7145746</v>
+        <v>7145420</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12637,14 +12644,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12653,51 +12665,25 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
-      </c>
-      <c r="AH110" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ110" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK110" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO110" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129726792</v>
+        <v>129726950</v>
       </c>
       <c r="B111" t="n">
         <v>79081</v>
@@ -12726,16 +12712,19 @@
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>483571</v>
+        <v>483720</v>
       </c>
       <c r="R111" t="n">
-        <v>7145360</v>
+        <v>7145756</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12765,19 +12754,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z111" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB111" t="inlineStr">
-        <is>
-          <t>10:58</t>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12786,28 +12770,54 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
+      </c>
+      <c r="AH111" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK111" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM111" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO111" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129726827</v>
+        <v>129727939</v>
       </c>
       <c r="B112" t="n">
-        <v>83052</v>
+        <v>57733</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12815,34 +12825,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6440</v>
+        <v>100049</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>483988</v>
+        <v>483605</v>
       </c>
       <c r="R112" t="n">
-        <v>7145444</v>
+        <v>7145281</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12872,19 +12882,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>08:49</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>08:49</t>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Hack ganska färska</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12899,22 +12904,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129726789</v>
+        <v>129727917</v>
       </c>
       <c r="B113" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12922,34 +12927,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>483663</v>
+        <v>483572</v>
       </c>
       <c r="R113" t="n">
-        <v>7145420</v>
+        <v>7145725</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12979,19 +12984,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z113" t="inlineStr">
-        <is>
-          <t>11:09</t>
-        </is>
-      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB113" t="inlineStr">
-        <is>
-          <t>11:09</t>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13006,22 +13006,22 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129726950</v>
+        <v>129727925</v>
       </c>
       <c r="B114" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13029,37 +13029,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>483720</v>
+        <v>483580</v>
       </c>
       <c r="R114" t="n">
-        <v>7145756</v>
+        <v>7145425</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13096,7 +13093,7 @@
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13105,54 +13102,28 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
-      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
-      </c>
-      <c r="AH114" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ114" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK114" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM114" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO114" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129726959</v>
+        <v>129716454</v>
       </c>
       <c r="B115" t="n">
-        <v>79081</v>
+        <v>91595</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13160,37 +13131,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>483422</v>
+        <v>484017</v>
       </c>
       <c r="R115" t="n">
-        <v>7145360</v>
+        <v>7145437</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13225,62 +13193,31 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>På en levande gran.</t>
-        </is>
-      </c>
       <c r="AD115" t="b">
         <v>0</v>
       </c>
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
-      </c>
-      <c r="AH115" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ115" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK115" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM115" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO115" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129726817</v>
+        <v>129726949</v>
       </c>
       <c r="B116" t="n">
         <v>79081</v>
@@ -13309,16 +13246,19 @@
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>483834</v>
+        <v>483735</v>
       </c>
       <c r="R116" t="n">
-        <v>7145605</v>
+        <v>7145746</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13348,19 +13288,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>09:15</t>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13369,25 +13304,51 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
+      </c>
+      <c r="AH116" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ116" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK116" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM116" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO116" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129726954</v>
+        <v>129726792</v>
       </c>
       <c r="B117" t="n">
         <v>79081</v>
@@ -13416,19 +13377,16 @@
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>483580</v>
+        <v>483571</v>
       </c>
       <c r="R117" t="n">
-        <v>7145435</v>
+        <v>7145360</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13458,14 +13416,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>På gran i granskog.</t>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13474,54 +13437,28 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
-      </c>
-      <c r="AH117" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ117" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK117" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM117" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO117" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129727917</v>
+        <v>129726959</v>
       </c>
       <c r="B118" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13529,34 +13466,37 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>483572</v>
+        <v>483422</v>
       </c>
       <c r="R118" t="n">
-        <v>7145725</v>
+        <v>7145360</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13593,7 +13533,7 @@
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>På en levande gran.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13602,28 +13542,54 @@
       <c r="AE118" t="b">
         <v>0</v>
       </c>
+      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
+      </c>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM118" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO118" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129727925</v>
+        <v>129726817</v>
       </c>
       <c r="B119" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13631,34 +13597,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>483580</v>
+        <v>483834</v>
       </c>
       <c r="R119" t="n">
-        <v>7145425</v>
+        <v>7145605</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13688,14 +13654,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13710,22 +13681,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129727939</v>
+        <v>129726954</v>
       </c>
       <c r="B120" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13733,34 +13704,37 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>483605</v>
+        <v>483580</v>
       </c>
       <c r="R120" t="n">
-        <v>7145281</v>
+        <v>7145435</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13797,7 +13771,7 @@
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>Hack ganska färska</t>
+          <t>På gran i granskog.</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13806,18 +13780,44 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
+      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
+      </c>
+      <c r="AH120" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ120" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK120" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM120" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO120" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
@@ -14014,10 +14014,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129730241</v>
+        <v>129730292</v>
       </c>
       <c r="B123" t="n">
-        <v>57736</v>
+        <v>83044</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14025,21 +14025,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -14049,10 +14049,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>483751</v>
+        <v>483314</v>
       </c>
       <c r="R123" t="n">
-        <v>7145575</v>
+        <v>7145495</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14085,11 +14085,6 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14116,10 +14111,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129730292</v>
+        <v>129730241</v>
       </c>
       <c r="B124" t="n">
-        <v>83044</v>
+        <v>57736</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14127,21 +14122,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -14151,10 +14146,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>483314</v>
+        <v>483751</v>
       </c>
       <c r="R124" t="n">
-        <v>7145495</v>
+        <v>7145575</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14187,6 +14182,11 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14213,10 +14213,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129730291</v>
+        <v>129730253</v>
       </c>
       <c r="B125" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14224,21 +14224,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14248,10 +14248,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>483364</v>
+        <v>483421</v>
       </c>
       <c r="R125" t="n">
-        <v>7145506</v>
+        <v>7145545</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14412,10 +14412,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129730253</v>
+        <v>129730291</v>
       </c>
       <c r="B127" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14423,21 +14423,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14447,10 +14447,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>483421</v>
+        <v>483364</v>
       </c>
       <c r="R127" t="n">
-        <v>7145545</v>
+        <v>7145506</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14995,10 +14995,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129730255</v>
+        <v>129730287</v>
       </c>
       <c r="B133" t="n">
-        <v>91619</v>
+        <v>91595</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15006,19 +15006,23 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
@@ -15026,10 +15030,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>483529</v>
+        <v>483608</v>
       </c>
       <c r="R133" t="n">
-        <v>7145591</v>
+        <v>7145490</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15088,10 +15092,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129730287</v>
+        <v>129730255</v>
       </c>
       <c r="B134" t="n">
-        <v>91595</v>
+        <v>91619</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15099,23 +15103,19 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
@@ -15123,10 +15123,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>483608</v>
+        <v>483529</v>
       </c>
       <c r="R134" t="n">
-        <v>7145490</v>
+        <v>7145591</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15772,32 +15772,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129730254</v>
+        <v>129730281</v>
       </c>
       <c r="B141" t="n">
-        <v>78838</v>
+        <v>80090</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6446</v>
+        <v>6456</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15807,10 +15807,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>483454</v>
+        <v>483572</v>
       </c>
       <c r="R141" t="n">
-        <v>7145556</v>
+        <v>7145441</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15869,32 +15869,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129730285</v>
+        <v>129730254</v>
       </c>
       <c r="B142" t="n">
-        <v>83060</v>
+        <v>78838</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1469</v>
+        <v>6446</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Liten blekspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Sclerophora peronella</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15904,10 +15904,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>483470</v>
+        <v>483454</v>
       </c>
       <c r="R142" t="n">
-        <v>7145348</v>
+        <v>7145556</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16063,32 +16063,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129730281</v>
+        <v>129730285</v>
       </c>
       <c r="B144" t="n">
-        <v>80090</v>
+        <v>83060</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6456</v>
+        <v>1469</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Liten blekspik</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Sclerophora peronella</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -16098,10 +16098,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>483572</v>
+        <v>483470</v>
       </c>
       <c r="R144" t="n">
-        <v>7145441</v>
+        <v>7145348</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16743,32 +16743,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129730282</v>
+        <v>129730296</v>
       </c>
       <c r="B151" t="n">
-        <v>80090</v>
+        <v>83044</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6456</v>
+        <v>308</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16778,10 +16778,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>483534</v>
+        <v>483526</v>
       </c>
       <c r="R151" t="n">
-        <v>7145348</v>
+        <v>7145596</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16840,32 +16840,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129730296</v>
+        <v>129730282</v>
       </c>
       <c r="B152" t="n">
-        <v>83044</v>
+        <v>80090</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>308</v>
+        <v>6456</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16875,10 +16875,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>483526</v>
+        <v>483534</v>
       </c>
       <c r="R152" t="n">
-        <v>7145596</v>
+        <v>7145348</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>

--- a/artfynd/A 52753-2025 artfynd.xlsx
+++ b/artfynd/A 52753-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129726815</v>
+        <v>129726936</v>
       </c>
       <c r="B2" t="n">
-        <v>83044</v>
+        <v>57736</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483798</v>
+        <v>483746</v>
       </c>
       <c r="R2" t="n">
-        <v>7145630</v>
+        <v>7145582</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,19 +755,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>09:22</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>09:22</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en levande gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,26 +773,51 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129726820</v>
+        <v>129727928</v>
       </c>
       <c r="B3" t="n">
-        <v>83057</v>
+        <v>57736</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +825,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1467</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483921</v>
+        <v>483704</v>
       </c>
       <c r="R3" t="n">
-        <v>7145571</v>
+        <v>7145461</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,19 +882,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>09:08</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>09:08</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,22 +904,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129716450</v>
+        <v>129726815</v>
       </c>
       <c r="B4" t="n">
-        <v>79081</v>
+        <v>83044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,34 +927,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483823</v>
+        <v>483798</v>
       </c>
       <c r="R4" t="n">
-        <v>7145591</v>
+        <v>7145630</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,9 +984,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,19 +1011,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129726952</v>
+        <v>129716450</v>
       </c>
       <c r="B5" t="n">
         <v>79081</v>
@@ -1015,19 +1052,16 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483538</v>
+        <v>483823</v>
       </c>
       <c r="R5" t="n">
-        <v>7145695</v>
+        <v>7145591</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,65 +1096,34 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gran.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129726936</v>
+        <v>129726952</v>
       </c>
       <c r="B6" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1128,46 +1131,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483746</v>
+        <v>483538</v>
       </c>
       <c r="R6" t="n">
-        <v>7145582</v>
+        <v>7145695</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1204,7 +1198,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en levande gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1213,6 +1207,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1233,12 +1228,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1256,10 +1251,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129727928</v>
+        <v>129726820</v>
       </c>
       <c r="B7" t="n">
-        <v>57736</v>
+        <v>83057</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1267,34 +1262,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1467</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483704</v>
+        <v>483921</v>
       </c>
       <c r="R7" t="n">
-        <v>7145461</v>
+        <v>7145571</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1324,14 +1319,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,12 +1346,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -2892,7 +2892,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129726813</v>
+        <v>129726825</v>
       </c>
       <c r="B22" t="n">
         <v>79081</v>
@@ -2927,10 +2927,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483773</v>
+        <v>483962</v>
       </c>
       <c r="R22" t="n">
-        <v>7145613</v>
+        <v>7145447</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2999,10 +2999,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129726814</v>
+        <v>129726818</v>
       </c>
       <c r="B23" t="n">
-        <v>79081</v>
+        <v>83052</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3010,21 +3010,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3034,10 +3034,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483796</v>
+        <v>483849</v>
       </c>
       <c r="R23" t="n">
-        <v>7145620</v>
+        <v>7145605</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3069,7 +3069,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3208,45 +3208,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129727915</v>
+        <v>129726813</v>
       </c>
       <c r="B25" t="n">
-        <v>92317</v>
+        <v>79081</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>483493</v>
+        <v>483773</v>
       </c>
       <c r="R25" t="n">
-        <v>7145538</v>
+        <v>7145613</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3276,9 +3276,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3293,19 +3303,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129726825</v>
+        <v>129726814</v>
       </c>
       <c r="B26" t="n">
         <v>79081</v>
@@ -3340,10 +3350,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>483962</v>
+        <v>483796</v>
       </c>
       <c r="R26" t="n">
-        <v>7145447</v>
+        <v>7145620</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3375,7 +3385,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3385,7 +3395,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3412,45 +3422,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129726818</v>
+        <v>129727915</v>
       </c>
       <c r="B27" t="n">
-        <v>83052</v>
+        <v>92317</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>3298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>483849</v>
+        <v>483493</v>
       </c>
       <c r="R27" t="n">
-        <v>7145605</v>
+        <v>7145538</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3480,19 +3490,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>09:13</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>09:13</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3507,12 +3507,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -4202,10 +4202,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129727931</v>
+        <v>129726938</v>
       </c>
       <c r="B34" t="n">
-        <v>57736</v>
+        <v>57896</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4213,34 +4213,54 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>483545</v>
+        <v>483739</v>
       </c>
       <c r="R34" t="n">
-        <v>7145507</v>
+        <v>7145743</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4277,7 +4297,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Synobservation av två talltitor med lockläte. Ev. rörde sig fler talltitor runt fyndplatsen som finns i flerskiktad äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4288,26 +4308,36 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Flerskiktad äldre barrblandskog.</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129726938</v>
+        <v>129727931</v>
       </c>
       <c r="B35" t="n">
-        <v>57896</v>
+        <v>57736</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4315,54 +4345,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>483739</v>
+        <v>483545</v>
       </c>
       <c r="R35" t="n">
-        <v>7145743</v>
+        <v>7145507</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4399,7 +4409,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Synobservation av två talltitor med lockläte. Ev. rörde sig fler talltitor runt fyndplatsen som finns i flerskiktad äldre barrblandskog.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4410,26 +4420,16 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>Flerskiktad äldre barrblandskog.</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -5281,32 +5281,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129726960</v>
+        <v>129726946</v>
       </c>
       <c r="B44" t="n">
-        <v>79081</v>
+        <v>80214</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5319,10 +5319,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>483376</v>
+        <v>483607</v>
       </c>
       <c r="R44" t="n">
-        <v>7145540</v>
+        <v>7145621</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5357,11 +5357,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>På en levande gran.</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5371,31 +5366,6 @@
       <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5412,32 +5382,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129726946</v>
+        <v>129726960</v>
       </c>
       <c r="B45" t="n">
-        <v>80214</v>
+        <v>79081</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5450,10 +5420,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>483607</v>
+        <v>483376</v>
       </c>
       <c r="R45" t="n">
-        <v>7145621</v>
+        <v>7145540</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5488,6 +5458,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På en levande gran.</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5497,6 +5472,31 @@
       <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -6144,45 +6144,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129727914</v>
+        <v>129726811</v>
       </c>
       <c r="B52" t="n">
-        <v>92317</v>
+        <v>79081</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>483577</v>
+        <v>483760</v>
       </c>
       <c r="R52" t="n">
-        <v>7145438</v>
+        <v>7145575</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6212,9 +6212,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6229,57 +6239,57 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129716458</v>
+        <v>129727914</v>
       </c>
       <c r="B53" t="n">
-        <v>83052</v>
+        <v>92317</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6440</v>
+        <v>3298</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>483701</v>
+        <v>483577</v>
       </c>
       <c r="R53" t="n">
-        <v>7145588</v>
+        <v>7145438</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6326,22 +6336,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129727924</v>
+        <v>129716458</v>
       </c>
       <c r="B54" t="n">
-        <v>57736</v>
+        <v>83052</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6349,34 +6359,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>483548</v>
+        <v>483701</v>
       </c>
       <c r="R54" t="n">
-        <v>7145488</v>
+        <v>7145588</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6411,11 +6421,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6428,57 +6433,60 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129727922</v>
+        <v>129726944</v>
       </c>
       <c r="B55" t="n">
-        <v>57736</v>
+        <v>80214</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>483507</v>
+        <v>483597</v>
       </c>
       <c r="R55" t="n">
-        <v>7145556</v>
+        <v>7145735</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6513,39 +6521,35 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129726811</v>
+        <v>129727924</v>
       </c>
       <c r="B56" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6553,34 +6557,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>483760</v>
+        <v>483548</v>
       </c>
       <c r="R56" t="n">
-        <v>7145575</v>
+        <v>7145488</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6610,19 +6614,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>09:35</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>09:35</t>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6637,60 +6636,57 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129726944</v>
+        <v>129727922</v>
       </c>
       <c r="B57" t="n">
-        <v>80214</v>
+        <v>57736</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>483597</v>
+        <v>483507</v>
       </c>
       <c r="R57" t="n">
-        <v>7145735</v>
+        <v>7145556</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6725,25 +6721,29 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -11534,10 +11534,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129726962</v>
+        <v>129726934</v>
       </c>
       <c r="B101" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11545,37 +11545,46 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>483460</v>
+        <v>483487</v>
       </c>
       <c r="R101" t="n">
-        <v>7145602</v>
+        <v>7145568</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11612,7 +11621,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>På gran i tallskog.</t>
+          <t>Ringhack, äldre, på stambasen av en stående död gran av full längd med 42 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11621,13 +11630,12 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ101" t="inlineStr">
@@ -11642,12 +11650,12 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -11665,7 +11673,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129726956</v>
+        <v>129726962</v>
       </c>
       <c r="B102" t="n">
         <v>79081</v>
@@ -11703,10 +11711,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>483519</v>
+        <v>483460</v>
       </c>
       <c r="R102" t="n">
-        <v>7145306</v>
+        <v>7145602</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11743,7 +11751,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På gran i tallskog.</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11758,7 +11766,7 @@
       </c>
       <c r="AH102" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ102" t="inlineStr">
@@ -11771,9 +11779,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM102" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -11791,7 +11804,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129716467</v>
+        <v>129726956</v>
       </c>
       <c r="B103" t="n">
         <v>79081</v>
@@ -11820,16 +11833,19 @@
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>483805</v>
+        <v>483519</v>
       </c>
       <c r="R103" t="n">
-        <v>7145587</v>
+        <v>7145306</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11864,34 +11880,60 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD103" t="b">
         <v>0</v>
       </c>
       <c r="AE103" t="b">
         <v>0</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
+      </c>
+      <c r="AH103" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129726934</v>
+        <v>129716467</v>
       </c>
       <c r="B104" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11899,46 +11941,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N104" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>483487</v>
+        <v>483805</v>
       </c>
       <c r="R104" t="n">
-        <v>7145568</v>
+        <v>7145587</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11973,11 +12003,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en stående död gran av full längd med 42 cm i brösthöjdsdiameter.</t>
-        </is>
-      </c>
       <c r="AD104" t="b">
         <v>0</v>
       </c>
@@ -11986,41 +12011,16 @@
       </c>
       <c r="AG104" t="b">
         <v>0</v>
-      </c>
-      <c r="AH104" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ104" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK104" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM104" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO104" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
@@ -14014,10 +14014,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129730292</v>
+        <v>129730241</v>
       </c>
       <c r="B123" t="n">
-        <v>83044</v>
+        <v>57736</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14025,21 +14025,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -14049,10 +14049,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>483314</v>
+        <v>483751</v>
       </c>
       <c r="R123" t="n">
-        <v>7145495</v>
+        <v>7145575</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14085,6 +14085,11 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14111,10 +14116,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129730241</v>
+        <v>129730292</v>
       </c>
       <c r="B124" t="n">
-        <v>57736</v>
+        <v>83044</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14122,21 +14127,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -14146,10 +14151,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>483751</v>
+        <v>483314</v>
       </c>
       <c r="R124" t="n">
-        <v>7145575</v>
+        <v>7145495</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14182,11 +14187,6 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14995,10 +14995,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129730287</v>
+        <v>129730255</v>
       </c>
       <c r="B133" t="n">
-        <v>91595</v>
+        <v>91619</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15006,23 +15006,19 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
@@ -15030,10 +15026,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>483608</v>
+        <v>483529</v>
       </c>
       <c r="R133" t="n">
-        <v>7145490</v>
+        <v>7145591</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15092,10 +15088,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129730255</v>
+        <v>129730287</v>
       </c>
       <c r="B134" t="n">
-        <v>91619</v>
+        <v>91595</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15103,19 +15099,23 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
@@ -15123,10 +15123,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>483529</v>
+        <v>483608</v>
       </c>
       <c r="R134" t="n">
-        <v>7145591</v>
+        <v>7145490</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -17238,10 +17238,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129730258</v>
+        <v>129730265</v>
       </c>
       <c r="B156" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17249,21 +17249,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -17273,10 +17273,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>483592</v>
+        <v>483564</v>
       </c>
       <c r="R156" t="n">
-        <v>7145458</v>
+        <v>7145344</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17309,6 +17309,11 @@
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17335,10 +17340,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129730257</v>
+        <v>129730276</v>
       </c>
       <c r="B157" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17346,34 +17351,54 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
           <t>Bodknulen, Jmt</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>483635</v>
+        <v>483545</v>
       </c>
       <c r="R157" t="n">
-        <v>7145484</v>
+        <v>7145332</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17534,10 +17559,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129730265</v>
+        <v>129730258</v>
       </c>
       <c r="B159" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17545,21 +17570,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17569,10 +17594,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>483564</v>
+        <v>483592</v>
       </c>
       <c r="R159" t="n">
-        <v>7145344</v>
+        <v>7145458</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17605,11 +17630,6 @@
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC159" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17636,10 +17656,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129730276</v>
+        <v>129730257</v>
       </c>
       <c r="B160" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17647,54 +17667,34 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L160" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N160" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
           <t>Bodknulen, Jmt</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>483545</v>
+        <v>483635</v>
       </c>
       <c r="R160" t="n">
-        <v>7145332</v>
+        <v>7145484</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17947,10 +17947,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129730271</v>
+        <v>129730259</v>
       </c>
       <c r="B163" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17958,21 +17958,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17982,10 +17982,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>483461</v>
+        <v>483432</v>
       </c>
       <c r="R163" t="n">
-        <v>7145552</v>
+        <v>7145357</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18018,11 +18018,6 @@
       <c r="AA163" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC163" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -18049,7 +18044,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129730272</v>
+        <v>129730271</v>
       </c>
       <c r="B164" t="n">
         <v>57736</v>
@@ -18084,10 +18079,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>483583</v>
+        <v>483461</v>
       </c>
       <c r="R164" t="n">
-        <v>7145605</v>
+        <v>7145552</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18151,7 +18146,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129730273</v>
+        <v>129730270</v>
       </c>
       <c r="B165" t="n">
         <v>57736</v>
@@ -18186,10 +18181,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>483589</v>
+        <v>483426</v>
       </c>
       <c r="R165" t="n">
-        <v>7145604</v>
+        <v>7145560</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18253,7 +18248,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129730270</v>
+        <v>129730272</v>
       </c>
       <c r="B166" t="n">
         <v>57736</v>
@@ -18288,10 +18283,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>483426</v>
+        <v>483583</v>
       </c>
       <c r="R166" t="n">
-        <v>7145560</v>
+        <v>7145605</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18355,10 +18350,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129730259</v>
+        <v>129730273</v>
       </c>
       <c r="B167" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18366,21 +18361,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -18390,10 +18385,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>483432</v>
+        <v>483589</v>
       </c>
       <c r="R167" t="n">
-        <v>7145357</v>
+        <v>7145604</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18426,6 +18421,11 @@
       <c r="AA167" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD167" t="b">

--- a/artfynd/A 52753-2025 artfynd.xlsx
+++ b/artfynd/A 52753-2025 artfynd.xlsx
@@ -5281,32 +5281,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129726946</v>
+        <v>129726960</v>
       </c>
       <c r="B44" t="n">
-        <v>80214</v>
+        <v>79081</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5319,10 +5319,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>483607</v>
+        <v>483376</v>
       </c>
       <c r="R44" t="n">
-        <v>7145621</v>
+        <v>7145540</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5357,6 +5357,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På en levande gran.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5366,6 +5371,31 @@
       <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5382,32 +5412,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129726960</v>
+        <v>129726946</v>
       </c>
       <c r="B45" t="n">
-        <v>79081</v>
+        <v>80214</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5420,10 +5450,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>483376</v>
+        <v>483607</v>
       </c>
       <c r="R45" t="n">
-        <v>7145540</v>
+        <v>7145621</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5458,11 +5488,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På en levande gran.</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5472,31 +5497,6 @@
       <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -8991,7 +8991,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129726823</v>
+        <v>129726963</v>
       </c>
       <c r="B78" t="n">
         <v>79081</v>
@@ -9020,16 +9020,19 @@
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>483959</v>
+        <v>483498</v>
       </c>
       <c r="R78" t="n">
-        <v>7145539</v>
+        <v>7145585</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9059,19 +9062,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>09:02</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>09:02</t>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>På levande gran.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9080,25 +9078,51 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM78" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129716451</v>
+        <v>129726812</v>
       </c>
       <c r="B79" t="n">
         <v>79081</v>
@@ -9129,14 +9153,14 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>483989</v>
+        <v>483764</v>
       </c>
       <c r="R79" t="n">
-        <v>7145511</v>
+        <v>7145589</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9166,9 +9190,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9183,19 +9217,19 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129726963</v>
+        <v>129726798</v>
       </c>
       <c r="B80" t="n">
         <v>79081</v>
@@ -9224,19 +9258,16 @@
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>483498</v>
+        <v>483429</v>
       </c>
       <c r="R80" t="n">
-        <v>7145585</v>
+        <v>7145430</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9266,14 +9297,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>På levande gran.</t>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9282,54 +9318,28 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
-      </c>
-      <c r="AH80" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK80" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129726812</v>
+        <v>129716465</v>
       </c>
       <c r="B81" t="n">
-        <v>79081</v>
+        <v>91599</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9337,34 +9347,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>483764</v>
+        <v>483983</v>
       </c>
       <c r="R81" t="n">
-        <v>7145589</v>
+        <v>7145507</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9394,19 +9404,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>09:34</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>09:34</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9421,22 +9421,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129726798</v>
+        <v>129727941</v>
       </c>
       <c r="B82" t="n">
-        <v>79081</v>
+        <v>91595</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9444,34 +9444,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>483429</v>
+        <v>483551</v>
       </c>
       <c r="R82" t="n">
-        <v>7145430</v>
+        <v>7145323</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9501,19 +9501,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>10:16</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>10:16</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9528,22 +9518,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129716465</v>
+        <v>129726795</v>
       </c>
       <c r="B83" t="n">
-        <v>91599</v>
+        <v>83057</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9551,34 +9541,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1202</v>
+        <v>1467</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>483983</v>
+        <v>483545</v>
       </c>
       <c r="R83" t="n">
-        <v>7145507</v>
+        <v>7145343</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9608,9 +9598,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9625,22 +9625,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129727941</v>
+        <v>129726831</v>
       </c>
       <c r="B84" t="n">
-        <v>91595</v>
+        <v>83052</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9648,34 +9648,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>483551</v>
+        <v>484008</v>
       </c>
       <c r="R84" t="n">
-        <v>7145323</v>
+        <v>7145455</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9705,9 +9705,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>08:42</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9722,22 +9732,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129726795</v>
+        <v>129726823</v>
       </c>
       <c r="B85" t="n">
-        <v>83057</v>
+        <v>79081</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9745,21 +9755,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9769,10 +9779,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>483545</v>
+        <v>483959</v>
       </c>
       <c r="R85" t="n">
-        <v>7145343</v>
+        <v>7145539</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9804,7 +9814,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9814,7 +9824,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9841,10 +9851,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129727942</v>
+        <v>129716451</v>
       </c>
       <c r="B86" t="n">
-        <v>91619</v>
+        <v>79081</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9852,30 +9862,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>483495</v>
+        <v>483989</v>
       </c>
       <c r="R86" t="n">
-        <v>7145618</v>
+        <v>7145511</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9922,22 +9936,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129726831</v>
+        <v>129727942</v>
       </c>
       <c r="B87" t="n">
-        <v>83052</v>
+        <v>91619</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9945,34 +9959,30 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>484008</v>
+        <v>483495</v>
       </c>
       <c r="R87" t="n">
-        <v>7145455</v>
+        <v>7145618</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10002,19 +10012,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>08:42</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>08:42</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10029,12 +10029,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -12469,10 +12469,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129726827</v>
+        <v>129716454</v>
       </c>
       <c r="B109" t="n">
-        <v>83052</v>
+        <v>91595</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12480,34 +12480,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>483988</v>
+        <v>484017</v>
       </c>
       <c r="R109" t="n">
-        <v>7145444</v>
+        <v>7145437</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12537,19 +12537,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>08:49</t>
-        </is>
-      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>08:49</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12564,19 +12554,19 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129726789</v>
+        <v>129726949</v>
       </c>
       <c r="B110" t="n">
         <v>79081</v>
@@ -12605,16 +12595,19 @@
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>483663</v>
+        <v>483735</v>
       </c>
       <c r="R110" t="n">
-        <v>7145420</v>
+        <v>7145746</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12644,19 +12637,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>11:09</t>
-        </is>
-      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>11:09</t>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12665,25 +12653,51 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
+      </c>
+      <c r="AH110" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM110" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129726950</v>
+        <v>129726792</v>
       </c>
       <c r="B111" t="n">
         <v>79081</v>
@@ -12712,19 +12726,16 @@
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>483720</v>
+        <v>483571</v>
       </c>
       <c r="R111" t="n">
-        <v>7145756</v>
+        <v>7145360</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12754,14 +12765,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12770,54 +12786,28 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
-      </c>
-      <c r="AH111" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ111" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK111" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM111" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO111" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129727939</v>
+        <v>129726827</v>
       </c>
       <c r="B112" t="n">
-        <v>57733</v>
+        <v>83052</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12825,34 +12815,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100049</v>
+        <v>6440</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>483605</v>
+        <v>483988</v>
       </c>
       <c r="R112" t="n">
-        <v>7145281</v>
+        <v>7145444</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12882,14 +12872,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Hack ganska färska</t>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12904,22 +12899,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129727917</v>
+        <v>129726789</v>
       </c>
       <c r="B113" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12927,34 +12922,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>483572</v>
+        <v>483663</v>
       </c>
       <c r="R113" t="n">
-        <v>7145725</v>
+        <v>7145420</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12984,14 +12979,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13006,22 +13006,22 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129727925</v>
+        <v>129726950</v>
       </c>
       <c r="B114" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13029,34 +13029,37 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>483580</v>
+        <v>483720</v>
       </c>
       <c r="R114" t="n">
-        <v>7145425</v>
+        <v>7145756</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13093,7 +13096,7 @@
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13102,28 +13105,54 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
+      </c>
+      <c r="AH114" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ114" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK114" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM114" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO114" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129716454</v>
+        <v>129726959</v>
       </c>
       <c r="B115" t="n">
-        <v>91595</v>
+        <v>79081</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13131,34 +13160,37 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>484017</v>
+        <v>483422</v>
       </c>
       <c r="R115" t="n">
-        <v>7145437</v>
+        <v>7145360</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13193,31 +13225,62 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>På en levande gran.</t>
+        </is>
+      </c>
       <c r="AD115" t="b">
         <v>0</v>
       </c>
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
+      </c>
+      <c r="AH115" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ115" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK115" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM115" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO115" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129726949</v>
+        <v>129726817</v>
       </c>
       <c r="B116" t="n">
         <v>79081</v>
@@ -13246,19 +13309,16 @@
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>483735</v>
+        <v>483834</v>
       </c>
       <c r="R116" t="n">
-        <v>7145746</v>
+        <v>7145605</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13288,14 +13348,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13304,51 +13369,25 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
-      </c>
-      <c r="AH116" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ116" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK116" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM116" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO116" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129726792</v>
+        <v>129726954</v>
       </c>
       <c r="B117" t="n">
         <v>79081</v>
@@ -13377,16 +13416,19 @@
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>483571</v>
+        <v>483580</v>
       </c>
       <c r="R117" t="n">
-        <v>7145360</v>
+        <v>7145435</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13416,19 +13458,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>10:58</t>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>På gran i granskog.</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13437,28 +13474,54 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
+      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
+      </c>
+      <c r="AH117" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK117" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM117" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO117" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129726959</v>
+        <v>129727917</v>
       </c>
       <c r="B118" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13466,37 +13529,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>483422</v>
+        <v>483572</v>
       </c>
       <c r="R118" t="n">
-        <v>7145360</v>
+        <v>7145725</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13533,7 +13593,7 @@
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>På en levande gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13542,54 +13602,28 @@
       <c r="AE118" t="b">
         <v>0</v>
       </c>
-      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
-      </c>
-      <c r="AH118" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ118" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK118" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM118" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO118" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129726817</v>
+        <v>129727925</v>
       </c>
       <c r="B119" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13597,34 +13631,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>483834</v>
+        <v>483580</v>
       </c>
       <c r="R119" t="n">
-        <v>7145605</v>
+        <v>7145425</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13654,19 +13688,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>09:15</t>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13681,22 +13710,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129726954</v>
+        <v>129727939</v>
       </c>
       <c r="B120" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13704,37 +13733,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>483580</v>
+        <v>483605</v>
       </c>
       <c r="R120" t="n">
-        <v>7145435</v>
+        <v>7145281</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13771,7 +13797,7 @@
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>På gran i granskog.</t>
+          <t>Hack ganska färska</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13780,44 +13806,18 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
-      </c>
-      <c r="AH120" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ120" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK120" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM120" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO120" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
@@ -17947,10 +17947,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129730259</v>
+        <v>129730271</v>
       </c>
       <c r="B163" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17958,21 +17958,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17982,10 +17982,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>483432</v>
+        <v>483461</v>
       </c>
       <c r="R163" t="n">
-        <v>7145357</v>
+        <v>7145552</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18018,6 +18018,11 @@
       <c r="AA163" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC163" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -18044,7 +18049,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129730271</v>
+        <v>129730272</v>
       </c>
       <c r="B164" t="n">
         <v>57736</v>
@@ -18079,10 +18084,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>483461</v>
+        <v>483583</v>
       </c>
       <c r="R164" t="n">
-        <v>7145552</v>
+        <v>7145605</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18146,7 +18151,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129730270</v>
+        <v>129730273</v>
       </c>
       <c r="B165" t="n">
         <v>57736</v>
@@ -18181,10 +18186,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>483426</v>
+        <v>483589</v>
       </c>
       <c r="R165" t="n">
-        <v>7145560</v>
+        <v>7145604</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18248,7 +18253,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129730272</v>
+        <v>129730270</v>
       </c>
       <c r="B166" t="n">
         <v>57736</v>
@@ -18283,10 +18288,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>483583</v>
+        <v>483426</v>
       </c>
       <c r="R166" t="n">
-        <v>7145605</v>
+        <v>7145560</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18350,10 +18355,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129730273</v>
+        <v>129730259</v>
       </c>
       <c r="B167" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18361,21 +18366,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -18385,10 +18390,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>483589</v>
+        <v>483432</v>
       </c>
       <c r="R167" t="n">
-        <v>7145604</v>
+        <v>7145357</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18421,11 +18426,6 @@
       <c r="AA167" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC167" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD167" t="b">

--- a/artfynd/A 52753-2025 artfynd.xlsx
+++ b/artfynd/A 52753-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129726936</v>
+        <v>129726815</v>
       </c>
       <c r="B2" t="n">
-        <v>57736</v>
+        <v>83044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,46 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483746</v>
+        <v>483798</v>
       </c>
       <c r="R2" t="n">
-        <v>7145582</v>
+        <v>7145630</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,14 +743,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en levande gran.</t>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,51 +766,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129727928</v>
+        <v>129726820</v>
       </c>
       <c r="B3" t="n">
-        <v>57736</v>
+        <v>83057</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -825,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1467</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483704</v>
+        <v>483921</v>
       </c>
       <c r="R3" t="n">
-        <v>7145461</v>
+        <v>7145571</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,14 +850,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,22 +877,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129726815</v>
+        <v>129726936</v>
       </c>
       <c r="B4" t="n">
-        <v>83044</v>
+        <v>57736</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -927,34 +900,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483798</v>
+        <v>483746</v>
       </c>
       <c r="R4" t="n">
-        <v>7145630</v>
+        <v>7145582</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,19 +969,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>09:22</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>09:22</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en levande gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,26 +987,51 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129716450</v>
+        <v>129727928</v>
       </c>
       <c r="B5" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1034,34 +1039,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483823</v>
+        <v>483704</v>
       </c>
       <c r="R5" t="n">
-        <v>7145591</v>
+        <v>7145461</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,6 +1101,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1108,19 +1118,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129726952</v>
+        <v>129716450</v>
       </c>
       <c r="B6" t="n">
         <v>79081</v>
@@ -1149,19 +1159,16 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483538</v>
+        <v>483823</v>
       </c>
       <c r="R6" t="n">
-        <v>7145695</v>
+        <v>7145591</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,65 +1203,34 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gran.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129726820</v>
+        <v>129726952</v>
       </c>
       <c r="B7" t="n">
-        <v>83057</v>
+        <v>79081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1262,34 +1238,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483921</v>
+        <v>483538</v>
       </c>
       <c r="R7" t="n">
-        <v>7145571</v>
+        <v>7145695</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,19 +1298,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>09:08</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>09:08</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1340,28 +1314,54 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129726803</v>
+        <v>129726805</v>
       </c>
       <c r="B8" t="n">
-        <v>83044</v>
+        <v>79081</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,21 +1369,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1393,10 +1393,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483493</v>
+        <v>483517</v>
       </c>
       <c r="R8" t="n">
-        <v>7145541</v>
+        <v>7145580</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1465,10 +1465,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129716452</v>
+        <v>129726791</v>
       </c>
       <c r="B9" t="n">
-        <v>91619</v>
+        <v>79081</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1476,30 +1476,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483480</v>
+        <v>483607</v>
       </c>
       <c r="R9" t="n">
-        <v>7145600</v>
+        <v>7145404</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,9 +1533,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1546,19 +1560,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129726791</v>
+        <v>129726955</v>
       </c>
       <c r="B10" t="n">
         <v>79081</v>
@@ -1587,16 +1601,19 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483607</v>
+        <v>483580</v>
       </c>
       <c r="R10" t="n">
-        <v>7145404</v>
+        <v>7145305</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1626,19 +1643,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På en levande gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1647,28 +1659,54 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129726805</v>
+        <v>129726803</v>
       </c>
       <c r="B11" t="n">
-        <v>79081</v>
+        <v>83044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1676,21 +1714,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1700,10 +1738,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483517</v>
+        <v>483493</v>
       </c>
       <c r="R11" t="n">
-        <v>7145580</v>
+        <v>7145541</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,7 +1773,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1745,7 +1783,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1772,10 +1810,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129726955</v>
+        <v>129716452</v>
       </c>
       <c r="B12" t="n">
-        <v>79081</v>
+        <v>91619</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1783,37 +1821,30 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483580</v>
+        <v>483480</v>
       </c>
       <c r="R12" t="n">
-        <v>7145305</v>
+        <v>7145600</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1848,65 +1879,34 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På en levande gran.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129716468</v>
+        <v>129726819</v>
       </c>
       <c r="B13" t="n">
-        <v>91619</v>
+        <v>79081</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1914,30 +1914,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>484042</v>
+        <v>483862</v>
       </c>
       <c r="R13" t="n">
-        <v>7145421</v>
+        <v>7145604</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1967,9 +1971,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1984,19 +1998,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129727923</v>
+        <v>129716455</v>
       </c>
       <c r="B14" t="n">
         <v>57736</v>
@@ -2025,16 +2039,21 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483397</v>
+        <v>483975</v>
       </c>
       <c r="R14" t="n">
-        <v>7145483</v>
+        <v>7145436</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2069,11 +2088,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2086,19 +2100,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129716455</v>
+        <v>129727920</v>
       </c>
       <c r="B15" t="n">
         <v>57736</v>
@@ -2127,21 +2141,16 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483975</v>
+        <v>483452</v>
       </c>
       <c r="R15" t="n">
-        <v>7145436</v>
+        <v>7145362</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2176,6 +2185,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2188,19 +2202,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129727920</v>
+        <v>129727919</v>
       </c>
       <c r="B16" t="n">
         <v>57736</v>
@@ -2235,10 +2249,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483452</v>
+        <v>483535</v>
       </c>
       <c r="R16" t="n">
-        <v>7145362</v>
+        <v>7145332</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2275,7 +2289,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2302,7 +2316,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129727919</v>
+        <v>129727923</v>
       </c>
       <c r="B17" t="n">
         <v>57736</v>
@@ -2337,10 +2351,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483535</v>
+        <v>483397</v>
       </c>
       <c r="R17" t="n">
-        <v>7145332</v>
+        <v>7145483</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2377,7 +2391,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2404,10 +2418,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129726935</v>
+        <v>129716468</v>
       </c>
       <c r="B18" t="n">
-        <v>57736</v>
+        <v>91619</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2415,46 +2429,30 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483601</v>
+        <v>484042</v>
       </c>
       <c r="R18" t="n">
-        <v>7145616</v>
+        <v>7145421</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2489,11 +2487,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, på stambasen av en levande gran i barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2502,51 +2495,26 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129726819</v>
+        <v>129726935</v>
       </c>
       <c r="B19" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2554,34 +2522,46 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483862</v>
+        <v>483601</v>
       </c>
       <c r="R19" t="n">
-        <v>7145604</v>
+        <v>7145616</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2611,19 +2591,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>09:11</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>09:11</t>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, på stambasen av en levande gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2634,16 +2609,41 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2999,10 +2999,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129726818</v>
+        <v>129726813</v>
       </c>
       <c r="B23" t="n">
-        <v>83052</v>
+        <v>79081</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3010,21 +3010,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3034,10 +3034,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483849</v>
+        <v>483773</v>
       </c>
       <c r="R23" t="n">
-        <v>7145605</v>
+        <v>7145613</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3069,7 +3069,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3106,10 +3106,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129727934</v>
+        <v>129726814</v>
       </c>
       <c r="B24" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3117,34 +3117,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>483619</v>
+        <v>483796</v>
       </c>
       <c r="R24" t="n">
-        <v>7145595</v>
+        <v>7145620</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3174,14 +3174,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3196,22 +3201,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129726813</v>
+        <v>129726818</v>
       </c>
       <c r="B25" t="n">
-        <v>79081</v>
+        <v>83052</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3219,21 +3224,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3243,10 +3248,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>483773</v>
+        <v>483849</v>
       </c>
       <c r="R25" t="n">
-        <v>7145613</v>
+        <v>7145605</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3278,7 +3283,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3288,7 +3293,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3315,45 +3320,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129726814</v>
+        <v>129727915</v>
       </c>
       <c r="B26" t="n">
-        <v>79081</v>
+        <v>92317</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>483796</v>
+        <v>483493</v>
       </c>
       <c r="R26" t="n">
-        <v>7145620</v>
+        <v>7145538</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3383,19 +3388,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>09:25</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>09:25</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3410,44 +3405,44 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129727915</v>
+        <v>129727934</v>
       </c>
       <c r="B27" t="n">
-        <v>92317</v>
+        <v>57736</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3457,10 +3452,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>483493</v>
+        <v>483619</v>
       </c>
       <c r="R27" t="n">
-        <v>7145538</v>
+        <v>7145595</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3493,6 +3488,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3519,7 +3519,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129726933</v>
+        <v>129727921</v>
       </c>
       <c r="B28" t="n">
         <v>57736</v>
@@ -3548,28 +3548,16 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>483582</v>
+        <v>483464</v>
       </c>
       <c r="R28" t="n">
-        <v>7145456</v>
+        <v>7145542</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3606,7 +3594,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3617,86 +3605,61 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129727921</v>
+        <v>129726816</v>
       </c>
       <c r="B29" t="n">
-        <v>57736</v>
+        <v>75065</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6428</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>483464</v>
+        <v>483815</v>
       </c>
       <c r="R29" t="n">
-        <v>7145542</v>
+        <v>7145615</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3726,14 +3689,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3748,57 +3716,69 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129726816</v>
+        <v>129726933</v>
       </c>
       <c r="B30" t="n">
-        <v>75065</v>
+        <v>57736</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6428</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>483815</v>
+        <v>483582</v>
       </c>
       <c r="R30" t="n">
-        <v>7145615</v>
+        <v>7145456</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3828,19 +3808,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>09:18</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>09:18</t>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3851,26 +3826,51 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129716460</v>
+        <v>129727931</v>
       </c>
       <c r="B31" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3878,34 +3878,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>483445</v>
+        <v>483545</v>
       </c>
       <c r="R31" t="n">
-        <v>7145428</v>
+        <v>7145507</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3940,6 +3940,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -3952,19 +3957,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129726824</v>
+        <v>129716460</v>
       </c>
       <c r="B32" t="n">
         <v>79081</v>
@@ -3995,14 +4000,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>483981</v>
+        <v>483445</v>
       </c>
       <c r="R32" t="n">
-        <v>7145521</v>
+        <v>7145428</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4032,19 +4037,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>08:59</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>08:59</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4059,12 +4054,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4202,10 +4197,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129726938</v>
+        <v>129726824</v>
       </c>
       <c r="B34" t="n">
-        <v>57896</v>
+        <v>79081</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4213,54 +4208,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>483739</v>
+        <v>483981</v>
       </c>
       <c r="R34" t="n">
-        <v>7145743</v>
+        <v>7145521</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4290,14 +4265,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>08:59</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Synobservation av två talltitor med lockläte. Ev. rörde sig fler talltitor runt fyndplatsen som finns i flerskiktad äldre barrblandskog.</t>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4308,36 +4288,26 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>Flerskiktad äldre barrblandskog.</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129727931</v>
+        <v>129726938</v>
       </c>
       <c r="B35" t="n">
-        <v>57736</v>
+        <v>57896</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4345,34 +4315,54 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>483545</v>
+        <v>483739</v>
       </c>
       <c r="R35" t="n">
-        <v>7145507</v>
+        <v>7145743</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4409,7 +4399,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Synobservation av två talltitor med lockläte. Ev. rörde sig fler talltitor runt fyndplatsen som finns i flerskiktad äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4420,16 +4410,26 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Flerskiktad äldre barrblandskog.</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4533,10 +4533,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129726801</v>
+        <v>129726807</v>
       </c>
       <c r="B37" t="n">
-        <v>83057</v>
+        <v>79081</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4544,21 +4544,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4568,10 +4568,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>483487</v>
+        <v>483589</v>
       </c>
       <c r="R37" t="n">
-        <v>7145541</v>
+        <v>7145582</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4603,7 +4603,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4613,7 +4613,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4640,7 +4640,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129726807</v>
+        <v>129716466</v>
       </c>
       <c r="B38" t="n">
         <v>79081</v>
@@ -4671,14 +4671,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>483589</v>
+        <v>483481</v>
       </c>
       <c r="R38" t="n">
-        <v>7145582</v>
+        <v>7145592</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4708,19 +4708,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>09:50</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4735,22 +4725,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129716466</v>
+        <v>129727927</v>
       </c>
       <c r="B39" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4758,34 +4748,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>483481</v>
+        <v>483606</v>
       </c>
       <c r="R39" t="n">
-        <v>7145592</v>
+        <v>7145282</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4820,6 +4810,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -4832,22 +4827,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129727927</v>
+        <v>129726801</v>
       </c>
       <c r="B40" t="n">
-        <v>57736</v>
+        <v>83057</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4855,34 +4850,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>1467</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>483606</v>
+        <v>483487</v>
       </c>
       <c r="R40" t="n">
-        <v>7145282</v>
+        <v>7145541</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4912,14 +4907,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4934,57 +4934,60 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129716464</v>
+        <v>129726948</v>
       </c>
       <c r="B41" t="n">
-        <v>92317</v>
+        <v>91619</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>484017</v>
+        <v>483501</v>
       </c>
       <c r="R41" t="n">
-        <v>7145437</v>
+        <v>7145621</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5019,72 +5022,100 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar i en levande gran.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129726948</v>
+        <v>129716464</v>
       </c>
       <c r="B42" t="n">
-        <v>91619</v>
+        <v>92317</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>483501</v>
+        <v>484017</v>
       </c>
       <c r="R42" t="n">
-        <v>7145621</v>
+        <v>7145437</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5119,100 +5150,72 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar i en levande gran.</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129726821</v>
+        <v>129726946</v>
       </c>
       <c r="B43" t="n">
-        <v>79081</v>
+        <v>80214</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>483922</v>
+        <v>483607</v>
       </c>
       <c r="R43" t="n">
-        <v>7145570</v>
+        <v>7145621</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5242,46 +5245,37 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>09:05</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>09:05</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129726960</v>
+        <v>129726821</v>
       </c>
       <c r="B44" t="n">
         <v>79081</v>
@@ -5310,19 +5304,16 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>483376</v>
+        <v>483922</v>
       </c>
       <c r="R44" t="n">
-        <v>7145540</v>
+        <v>7145570</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5352,14 +5343,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>På en levande gran.</t>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5368,76 +5364,50 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129726946</v>
+        <v>129726960</v>
       </c>
       <c r="B45" t="n">
-        <v>80214</v>
+        <v>79081</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5450,10 +5420,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>483607</v>
+        <v>483376</v>
       </c>
       <c r="R45" t="n">
-        <v>7145621</v>
+        <v>7145540</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5488,6 +5458,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På en levande gran.</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5497,6 +5472,31 @@
       <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -6144,45 +6144,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129726811</v>
+        <v>129727914</v>
       </c>
       <c r="B52" t="n">
-        <v>79081</v>
+        <v>92317</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>483760</v>
+        <v>483577</v>
       </c>
       <c r="R52" t="n">
-        <v>7145575</v>
+        <v>7145438</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6212,19 +6212,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>09:35</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>09:35</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6239,22 +6229,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129727914</v>
+        <v>129726944</v>
       </c>
       <c r="B53" t="n">
-        <v>92317</v>
+        <v>80214</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6262,34 +6252,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3298</v>
+        <v>6461</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>483577</v>
+        <v>483597</v>
       </c>
       <c r="R53" t="n">
-        <v>7145438</v>
+        <v>7145735</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6330,28 +6323,29 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129716458</v>
+        <v>129727924</v>
       </c>
       <c r="B54" t="n">
-        <v>83052</v>
+        <v>57736</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6359,34 +6353,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>483701</v>
+        <v>483548</v>
       </c>
       <c r="R54" t="n">
-        <v>7145588</v>
+        <v>7145488</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6421,6 +6415,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6433,60 +6432,57 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129726944</v>
+        <v>129727922</v>
       </c>
       <c r="B55" t="n">
-        <v>80214</v>
+        <v>57736</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>483597</v>
+        <v>483507</v>
       </c>
       <c r="R55" t="n">
-        <v>7145735</v>
+        <v>7145556</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6521,35 +6517,39 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129727924</v>
+        <v>129716458</v>
       </c>
       <c r="B56" t="n">
-        <v>57736</v>
+        <v>83052</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6557,34 +6557,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>483548</v>
+        <v>483701</v>
       </c>
       <c r="R56" t="n">
-        <v>7145488</v>
+        <v>7145588</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6619,11 +6619,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -6636,22 +6631,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129727922</v>
+        <v>129726811</v>
       </c>
       <c r="B57" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6659,34 +6654,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>483507</v>
+        <v>483760</v>
       </c>
       <c r="R57" t="n">
-        <v>7145556</v>
+        <v>7145575</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6716,14 +6711,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6738,19 +6738,19 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129716453</v>
+        <v>129726828</v>
       </c>
       <c r="B58" t="n">
         <v>79081</v>
@@ -6781,14 +6781,14 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>484032</v>
+        <v>483988</v>
       </c>
       <c r="R58" t="n">
-        <v>7145416</v>
+        <v>7145444</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6818,9 +6818,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6835,19 +6845,19 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129726953</v>
+        <v>129716453</v>
       </c>
       <c r="B59" t="n">
         <v>79081</v>
@@ -6876,19 +6886,16 @@
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>483555</v>
+        <v>484032</v>
       </c>
       <c r="R59" t="n">
-        <v>7145531</v>
+        <v>7145416</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6923,65 +6930,34 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129716449</v>
+        <v>129726953</v>
       </c>
       <c r="B60" t="n">
-        <v>83052</v>
+        <v>79081</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6989,34 +6965,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>483889</v>
+        <v>483555</v>
       </c>
       <c r="R60" t="n">
-        <v>7145589</v>
+        <v>7145531</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7051,34 +7030,65 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129726788</v>
+        <v>129716449</v>
       </c>
       <c r="B61" t="n">
-        <v>79081</v>
+        <v>83052</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7086,34 +7096,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>483665</v>
+        <v>483889</v>
       </c>
       <c r="R61" t="n">
-        <v>7145479</v>
+        <v>7145589</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7143,19 +7153,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>11:18</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>11:18</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7170,19 +7170,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129726828</v>
+        <v>129726806</v>
       </c>
       <c r="B62" t="n">
         <v>79081</v>
@@ -7217,10 +7217,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>483988</v>
+        <v>483558</v>
       </c>
       <c r="R62" t="n">
-        <v>7145444</v>
+        <v>7145588</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7252,7 +7252,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7262,7 +7262,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7289,7 +7289,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129726806</v>
+        <v>129726788</v>
       </c>
       <c r="B63" t="n">
         <v>79081</v>
@@ -7324,10 +7324,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>483558</v>
+        <v>483665</v>
       </c>
       <c r="R63" t="n">
-        <v>7145588</v>
+        <v>7145479</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7359,7 +7359,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7369,7 +7369,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7799,7 +7799,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129726958</v>
+        <v>129726966</v>
       </c>
       <c r="B68" t="n">
         <v>79081</v>
@@ -7837,10 +7837,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>483482</v>
+        <v>483764</v>
       </c>
       <c r="R68" t="n">
-        <v>7145330</v>
+        <v>7145582</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7877,7 +7877,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>På en levande gran.</t>
+          <t>Långväxta bålar på en levande gran.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7930,7 +7930,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129726966</v>
+        <v>129726797</v>
       </c>
       <c r="B69" t="n">
         <v>79081</v>
@@ -7959,19 +7959,16 @@
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>483764</v>
+        <v>483540</v>
       </c>
       <c r="R69" t="n">
-        <v>7145582</v>
+        <v>7145349</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8001,14 +7998,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på en levande gran.</t>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8017,51 +8019,25 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
-      </c>
-      <c r="AH69" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129726797</v>
+        <v>129726958</v>
       </c>
       <c r="B70" t="n">
         <v>79081</v>
@@ -8090,16 +8066,19 @@
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>483540</v>
+        <v>483482</v>
       </c>
       <c r="R70" t="n">
-        <v>7145349</v>
+        <v>7145330</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8129,19 +8108,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>10:29</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>10:29</t>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>På en levande gran.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8150,18 +8124,44 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM70" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -8991,10 +8991,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129726963</v>
+        <v>129716465</v>
       </c>
       <c r="B78" t="n">
-        <v>79081</v>
+        <v>91599</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9002,37 +9002,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>483498</v>
+        <v>483983</v>
       </c>
       <c r="R78" t="n">
-        <v>7145585</v>
+        <v>7145507</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9067,65 +9064,34 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>På levande gran.</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
-      </c>
-      <c r="AH78" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ78" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK78" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129726812</v>
+        <v>129727941</v>
       </c>
       <c r="B79" t="n">
-        <v>79081</v>
+        <v>91595</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9133,34 +9099,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>483764</v>
+        <v>483551</v>
       </c>
       <c r="R79" t="n">
-        <v>7145589</v>
+        <v>7145323</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9190,19 +9156,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>09:34</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>09:34</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9217,22 +9173,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129726798</v>
+        <v>129727942</v>
       </c>
       <c r="B80" t="n">
-        <v>79081</v>
+        <v>91619</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9240,34 +9196,30 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>483429</v>
+        <v>483495</v>
       </c>
       <c r="R80" t="n">
-        <v>7145430</v>
+        <v>7145618</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9297,19 +9249,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>10:16</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>10:16</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9324,22 +9266,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129716465</v>
+        <v>129726795</v>
       </c>
       <c r="B81" t="n">
-        <v>91599</v>
+        <v>83057</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9347,34 +9289,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>1467</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>483983</v>
+        <v>483545</v>
       </c>
       <c r="R81" t="n">
-        <v>7145507</v>
+        <v>7145343</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9404,9 +9346,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9421,22 +9373,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129727941</v>
+        <v>129726831</v>
       </c>
       <c r="B82" t="n">
-        <v>91595</v>
+        <v>83052</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9444,34 +9396,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>483551</v>
+        <v>484008</v>
       </c>
       <c r="R82" t="n">
-        <v>7145323</v>
+        <v>7145455</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9501,9 +9453,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>08:42</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9518,22 +9480,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129726795</v>
+        <v>129726963</v>
       </c>
       <c r="B83" t="n">
-        <v>83057</v>
+        <v>79081</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9541,34 +9503,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>483545</v>
+        <v>483498</v>
       </c>
       <c r="R83" t="n">
-        <v>7145343</v>
+        <v>7145585</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9598,19 +9563,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>10:35</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>10:35</t>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>På levande gran.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9619,28 +9579,54 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129726831</v>
+        <v>129726812</v>
       </c>
       <c r="B84" t="n">
-        <v>83052</v>
+        <v>79081</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9648,21 +9634,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9672,10 +9658,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>484008</v>
+        <v>483764</v>
       </c>
       <c r="R84" t="n">
-        <v>7145455</v>
+        <v>7145589</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9707,7 +9693,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9717,7 +9703,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9948,10 +9934,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129727942</v>
+        <v>129726798</v>
       </c>
       <c r="B87" t="n">
-        <v>91619</v>
+        <v>79081</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9959,30 +9945,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>483495</v>
+        <v>483429</v>
       </c>
       <c r="R87" t="n">
-        <v>7145618</v>
+        <v>7145430</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10012,9 +10002,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10029,12 +10029,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -10366,45 +10366,48 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129726832</v>
+        <v>129726945</v>
       </c>
       <c r="B91" t="n">
-        <v>79081</v>
+        <v>80214</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>484041</v>
+        <v>483364</v>
       </c>
       <c r="R91" t="n">
-        <v>7145466</v>
+        <v>7145533</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10434,46 +10437,37 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>08:39</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>08:39</t>
-        </is>
-      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129726799</v>
+        <v>129726832</v>
       </c>
       <c r="B92" t="n">
         <v>79081</v>
@@ -10508,10 +10502,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>483426</v>
+        <v>484041</v>
       </c>
       <c r="R92" t="n">
-        <v>7145464</v>
+        <v>7145466</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10543,7 +10537,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10553,7 +10547,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10580,48 +10574,45 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129726945</v>
+        <v>129726799</v>
       </c>
       <c r="B93" t="n">
-        <v>80214</v>
+        <v>79081</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>483364</v>
+        <v>483426</v>
       </c>
       <c r="R93" t="n">
-        <v>7145533</v>
+        <v>7145464</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10651,40 +10642,49 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129726942</v>
+        <v>129726967</v>
       </c>
       <c r="B94" t="n">
-        <v>80187</v>
+        <v>79081</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10692,30 +10692,26 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -10723,10 +10719,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>483377</v>
+        <v>483745</v>
       </c>
       <c r="R94" t="n">
-        <v>7145537</v>
+        <v>7145588</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10763,7 +10759,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>På en levande sälg i granskog.</t>
+          <t>På en levande gran i granskog.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10783,22 +10779,22 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM94" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -10816,10 +10812,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129716456</v>
+        <v>129726951</v>
       </c>
       <c r="B95" t="n">
-        <v>82918</v>
+        <v>79081</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10827,34 +10823,37 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>483445</v>
+        <v>483599</v>
       </c>
       <c r="R95" t="n">
-        <v>7145393</v>
+        <v>7145738</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10889,31 +10888,62 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
+      </c>
+      <c r="AH95" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM95" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129726967</v>
+        <v>129726965</v>
       </c>
       <c r="B96" t="n">
         <v>79081</v>
@@ -10951,10 +10981,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>483745</v>
+        <v>483794</v>
       </c>
       <c r="R96" t="n">
-        <v>7145588</v>
+        <v>7145597</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10991,7 +11021,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>På en levande gran i granskog.</t>
+          <t>På levande granar i granskog.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11044,10 +11074,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129726951</v>
+        <v>129726940</v>
       </c>
       <c r="B97" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11055,26 +11085,31 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
@@ -11082,10 +11117,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>483599</v>
+        <v>483382</v>
       </c>
       <c r="R97" t="n">
-        <v>7145738</v>
+        <v>7145460</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11122,7 +11157,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Äldre och färska hackspår i en grov stående död gran av full längd.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11131,7 +11166,6 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -11152,12 +11186,12 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -11175,10 +11209,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129726965</v>
+        <v>129716457</v>
       </c>
       <c r="B98" t="n">
-        <v>79081</v>
+        <v>91619</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11186,37 +11220,30 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>483794</v>
+        <v>483922</v>
       </c>
       <c r="R98" t="n">
-        <v>7145597</v>
+        <v>7145565</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11251,65 +11278,34 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>På levande granar i granskog.</t>
-        </is>
-      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
-      </c>
-      <c r="AH98" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ98" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK98" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM98" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO98" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129716457</v>
+        <v>129726942</v>
       </c>
       <c r="B99" t="n">
-        <v>91619</v>
+        <v>80187</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11317,30 +11313,41 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr"/>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
       <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>483922</v>
+        <v>483377</v>
       </c>
       <c r="R99" t="n">
-        <v>7145565</v>
+        <v>7145537</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11375,34 +11382,65 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>På en levande sälg i granskog.</t>
+        </is>
+      </c>
       <c r="AD99" t="b">
         <v>0</v>
       </c>
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
+      </c>
+      <c r="AH99" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM99" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129726940</v>
+        <v>129716456</v>
       </c>
       <c r="B100" t="n">
-        <v>57733</v>
+        <v>82918</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11410,42 +11448,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>483382</v>
+        <v>483445</v>
       </c>
       <c r="R100" t="n">
-        <v>7145460</v>
+        <v>7145393</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11480,11 +11510,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Äldre och färska hackspår i en grov stående död gran av full längd.</t>
-        </is>
-      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
@@ -11493,51 +11518,26 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
-      </c>
-      <c r="AH100" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ100" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK100" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO100" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129726934</v>
+        <v>129726962</v>
       </c>
       <c r="B101" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11545,46 +11545,37 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>483487</v>
+        <v>483460</v>
       </c>
       <c r="R101" t="n">
-        <v>7145568</v>
+        <v>7145602</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11621,7 +11612,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en stående död gran av full längd med 42 cm i brösthöjdsdiameter.</t>
+          <t>På gran i tallskog.</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11630,12 +11621,13 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ101" t="inlineStr">
@@ -11650,12 +11642,12 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -11673,7 +11665,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129726962</v>
+        <v>129726956</v>
       </c>
       <c r="B102" t="n">
         <v>79081</v>
@@ -11711,10 +11703,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>483460</v>
+        <v>483519</v>
       </c>
       <c r="R102" t="n">
-        <v>7145602</v>
+        <v>7145306</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11751,7 +11743,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>På gran i tallskog.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11766,7 +11758,7 @@
       </c>
       <c r="AH102" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ102" t="inlineStr">
@@ -11779,14 +11771,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM102" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -11804,7 +11791,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129726956</v>
+        <v>129716467</v>
       </c>
       <c r="B103" t="n">
         <v>79081</v>
@@ -11833,19 +11820,16 @@
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>483519</v>
+        <v>483805</v>
       </c>
       <c r="R103" t="n">
-        <v>7145306</v>
+        <v>7145587</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11880,60 +11864,34 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD103" t="b">
         <v>0</v>
       </c>
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
-      </c>
-      <c r="AH103" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ103" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK103" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO103" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129716467</v>
+        <v>129726934</v>
       </c>
       <c r="B104" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11941,34 +11899,46 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>483805</v>
+        <v>483487</v>
       </c>
       <c r="R104" t="n">
-        <v>7145587</v>
+        <v>7145568</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12003,6 +11973,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en stående död gran av full längd med 42 cm i brösthöjdsdiameter.</t>
+        </is>
+      </c>
       <c r="AD104" t="b">
         <v>0</v>
       </c>
@@ -12011,16 +11986,41 @@
       </c>
       <c r="AG104" t="b">
         <v>0</v>
+      </c>
+      <c r="AH104" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK104" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM104" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
@@ -12158,10 +12158,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129727933</v>
+        <v>129726830</v>
       </c>
       <c r="B106" t="n">
-        <v>57736</v>
+        <v>78094</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12169,34 +12169,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>483593</v>
+        <v>484008</v>
       </c>
       <c r="R106" t="n">
-        <v>7145594</v>
+        <v>7145455</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12226,14 +12226,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>08:43</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12248,19 +12253,19 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129727937</v>
+        <v>129727933</v>
       </c>
       <c r="B107" t="n">
         <v>57736</v>
@@ -12295,10 +12300,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>483824</v>
+        <v>483593</v>
       </c>
       <c r="R107" t="n">
-        <v>7145592</v>
+        <v>7145594</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12335,7 +12340,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12362,10 +12367,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129726830</v>
+        <v>129727937</v>
       </c>
       <c r="B108" t="n">
-        <v>78094</v>
+        <v>57736</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12373,34 +12378,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>484008</v>
+        <v>483824</v>
       </c>
       <c r="R108" t="n">
-        <v>7145455</v>
+        <v>7145592</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12430,19 +12435,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>08:43</t>
-        </is>
-      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>08:43</t>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12457,22 +12457,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129716454</v>
+        <v>129726949</v>
       </c>
       <c r="B109" t="n">
-        <v>91595</v>
+        <v>79081</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12480,34 +12480,37 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>484017</v>
+        <v>483735</v>
       </c>
       <c r="R109" t="n">
-        <v>7145437</v>
+        <v>7145746</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12542,31 +12545,62 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK109" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM109" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO109" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129726949</v>
+        <v>129726792</v>
       </c>
       <c r="B110" t="n">
         <v>79081</v>
@@ -12595,19 +12629,16 @@
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>483735</v>
+        <v>483571</v>
       </c>
       <c r="R110" t="n">
-        <v>7145746</v>
+        <v>7145360</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12637,14 +12668,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12653,54 +12689,28 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
-      </c>
-      <c r="AH110" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ110" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK110" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO110" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129726792</v>
+        <v>129726827</v>
       </c>
       <c r="B111" t="n">
-        <v>79081</v>
+        <v>83052</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12708,21 +12718,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12732,10 +12742,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>483571</v>
+        <v>483988</v>
       </c>
       <c r="R111" t="n">
-        <v>7145360</v>
+        <v>7145444</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12767,7 +12777,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12777,7 +12787,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12804,10 +12814,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129726827</v>
+        <v>129726789</v>
       </c>
       <c r="B112" t="n">
-        <v>83052</v>
+        <v>79081</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12815,21 +12825,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12839,10 +12849,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>483988</v>
+        <v>483663</v>
       </c>
       <c r="R112" t="n">
-        <v>7145444</v>
+        <v>7145420</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12874,7 +12884,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12884,7 +12894,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12911,7 +12921,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129726789</v>
+        <v>129726950</v>
       </c>
       <c r="B113" t="n">
         <v>79081</v>
@@ -12940,16 +12950,19 @@
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>483663</v>
+        <v>483720</v>
       </c>
       <c r="R113" t="n">
-        <v>7145420</v>
+        <v>7145756</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12979,19 +12992,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z113" t="inlineStr">
-        <is>
-          <t>11:09</t>
-        </is>
-      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB113" t="inlineStr">
-        <is>
-          <t>11:09</t>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13000,25 +13008,51 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
+      </c>
+      <c r="AH113" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK113" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM113" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO113" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129726950</v>
+        <v>129726959</v>
       </c>
       <c r="B114" t="n">
         <v>79081</v>
@@ -13056,10 +13090,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>483720</v>
+        <v>483422</v>
       </c>
       <c r="R114" t="n">
-        <v>7145756</v>
+        <v>7145360</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13096,7 +13130,7 @@
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På en levande gran.</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13149,7 +13183,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129726959</v>
+        <v>129726817</v>
       </c>
       <c r="B115" t="n">
         <v>79081</v>
@@ -13178,19 +13212,16 @@
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>483422</v>
+        <v>483834</v>
       </c>
       <c r="R115" t="n">
-        <v>7145360</v>
+        <v>7145605</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13220,14 +13251,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>På en levande gran.</t>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13236,51 +13272,25 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
-      </c>
-      <c r="AH115" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ115" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK115" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM115" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO115" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129726817</v>
+        <v>129726954</v>
       </c>
       <c r="B116" t="n">
         <v>79081</v>
@@ -13309,16 +13319,19 @@
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>483834</v>
+        <v>483580</v>
       </c>
       <c r="R116" t="n">
-        <v>7145605</v>
+        <v>7145435</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13348,19 +13361,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>09:15</t>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>På gran i granskog.</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13369,28 +13377,54 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
+      </c>
+      <c r="AH116" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ116" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK116" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM116" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO116" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129726954</v>
+        <v>129727939</v>
       </c>
       <c r="B117" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13398,37 +13432,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>483580</v>
+        <v>483605</v>
       </c>
       <c r="R117" t="n">
-        <v>7145435</v>
+        <v>7145281</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13465,7 +13496,7 @@
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>På gran i granskog.</t>
+          <t>Hack ganska färska</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13474,54 +13505,28 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
-      </c>
-      <c r="AH117" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ117" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK117" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM117" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO117" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129727917</v>
+        <v>129716454</v>
       </c>
       <c r="B118" t="n">
-        <v>57736</v>
+        <v>91595</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13529,34 +13534,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>483572</v>
+        <v>484017</v>
       </c>
       <c r="R118" t="n">
-        <v>7145725</v>
+        <v>7145437</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13591,11 +13596,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
@@ -13608,19 +13608,19 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129727925</v>
+        <v>129727917</v>
       </c>
       <c r="B119" t="n">
         <v>57736</v>
@@ -13655,10 +13655,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>483580</v>
+        <v>483572</v>
       </c>
       <c r="R119" t="n">
-        <v>7145425</v>
+        <v>7145725</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13695,7 +13695,7 @@
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13722,10 +13722,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129727939</v>
+        <v>129727925</v>
       </c>
       <c r="B120" t="n">
-        <v>57733</v>
+        <v>57736</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13733,16 +13733,16 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -13757,10 +13757,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>483605</v>
+        <v>483580</v>
       </c>
       <c r="R120" t="n">
-        <v>7145281</v>
+        <v>7145425</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13797,7 +13797,7 @@
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>Hack ganska färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14014,10 +14014,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129730241</v>
+        <v>129730292</v>
       </c>
       <c r="B123" t="n">
-        <v>57736</v>
+        <v>83044</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14025,21 +14025,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -14049,10 +14049,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>483751</v>
+        <v>483314</v>
       </c>
       <c r="R123" t="n">
-        <v>7145575</v>
+        <v>7145495</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14085,11 +14085,6 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14116,10 +14111,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129730292</v>
+        <v>129730241</v>
       </c>
       <c r="B124" t="n">
-        <v>83044</v>
+        <v>57736</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14127,21 +14122,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -14151,10 +14146,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>483314</v>
+        <v>483751</v>
       </c>
       <c r="R124" t="n">
-        <v>7145495</v>
+        <v>7145575</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14187,6 +14182,11 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14310,10 +14310,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129730268</v>
+        <v>129730291</v>
       </c>
       <c r="B126" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14321,21 +14321,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14345,10 +14345,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>483247</v>
+        <v>483364</v>
       </c>
       <c r="R126" t="n">
-        <v>7145580</v>
+        <v>7145506</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14381,11 +14381,6 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14412,10 +14407,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129730291</v>
+        <v>129730268</v>
       </c>
       <c r="B127" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14423,21 +14418,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14447,10 +14442,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>483364</v>
+        <v>483247</v>
       </c>
       <c r="R127" t="n">
-        <v>7145506</v>
+        <v>7145580</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14483,6 +14478,11 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14995,10 +14995,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129730255</v>
+        <v>129730287</v>
       </c>
       <c r="B133" t="n">
-        <v>91619</v>
+        <v>91595</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15006,19 +15006,23 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
@@ -15026,10 +15030,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>483529</v>
+        <v>483608</v>
       </c>
       <c r="R133" t="n">
-        <v>7145591</v>
+        <v>7145490</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15088,10 +15092,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129730287</v>
+        <v>129730255</v>
       </c>
       <c r="B134" t="n">
-        <v>91595</v>
+        <v>91619</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15099,23 +15103,19 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
@@ -15123,10 +15123,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>483608</v>
+        <v>483529</v>
       </c>
       <c r="R134" t="n">
-        <v>7145490</v>
+        <v>7145591</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15966,32 +15966,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129730249</v>
+        <v>129730285</v>
       </c>
       <c r="B143" t="n">
-        <v>80186</v>
+        <v>83060</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6458</v>
+        <v>1469</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten blekspik</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sclerophora peronella</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -16001,10 +16001,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>483253</v>
+        <v>483470</v>
       </c>
       <c r="R143" t="n">
-        <v>7145561</v>
+        <v>7145348</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16063,32 +16063,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129730285</v>
+        <v>129730249</v>
       </c>
       <c r="B144" t="n">
-        <v>83060</v>
+        <v>80186</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1469</v>
+        <v>6458</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Liten blekspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Sclerophora peronella</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -16098,10 +16098,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>483470</v>
+        <v>483253</v>
       </c>
       <c r="R144" t="n">
-        <v>7145348</v>
+        <v>7145561</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16160,10 +16160,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129730261</v>
+        <v>129730289</v>
       </c>
       <c r="B145" t="n">
-        <v>79081</v>
+        <v>91619</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16171,23 +16171,19 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr"/>
       <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
@@ -16195,10 +16191,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>483247</v>
+        <v>483238</v>
       </c>
       <c r="R145" t="n">
-        <v>7145585</v>
+        <v>7145599</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16257,10 +16253,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129730289</v>
+        <v>129730261</v>
       </c>
       <c r="B146" t="n">
-        <v>91619</v>
+        <v>79081</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16268,19 +16264,23 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H146" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
@@ -16288,10 +16288,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>483238</v>
+        <v>483247</v>
       </c>
       <c r="R146" t="n">
-        <v>7145599</v>
+        <v>7145585</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16549,10 +16549,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129730260</v>
+        <v>129730295</v>
       </c>
       <c r="B149" t="n">
-        <v>79081</v>
+        <v>83044</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16560,21 +16560,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16584,10 +16584,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>483324</v>
+        <v>483462</v>
       </c>
       <c r="R149" t="n">
-        <v>7145520</v>
+        <v>7145552</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16646,10 +16646,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129730295</v>
+        <v>129730260</v>
       </c>
       <c r="B150" t="n">
-        <v>83044</v>
+        <v>79081</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16657,21 +16657,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16681,10 +16681,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>483462</v>
+        <v>483324</v>
       </c>
       <c r="R150" t="n">
-        <v>7145552</v>
+        <v>7145520</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16743,32 +16743,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129730296</v>
+        <v>129730282</v>
       </c>
       <c r="B151" t="n">
-        <v>83044</v>
+        <v>80090</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>308</v>
+        <v>6456</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16778,10 +16778,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>483526</v>
+        <v>483534</v>
       </c>
       <c r="R151" t="n">
-        <v>7145596</v>
+        <v>7145348</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16840,32 +16840,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129730282</v>
+        <v>129730296</v>
       </c>
       <c r="B152" t="n">
-        <v>80090</v>
+        <v>83044</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6456</v>
+        <v>308</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16875,10 +16875,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>483534</v>
+        <v>483526</v>
       </c>
       <c r="R152" t="n">
-        <v>7145348</v>
+        <v>7145596</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16937,27 +16937,27 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129730286</v>
+        <v>129730269</v>
       </c>
       <c r="B153" t="n">
-        <v>57840</v>
+        <v>57736</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -16972,10 +16972,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>483251</v>
+        <v>483364</v>
       </c>
       <c r="R153" t="n">
-        <v>7145567</v>
+        <v>7145545</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17008,6 +17008,11 @@
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17034,7 +17039,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129730269</v>
+        <v>129730267</v>
       </c>
       <c r="B154" t="n">
         <v>57736</v>
@@ -17069,10 +17074,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>483364</v>
+        <v>483426</v>
       </c>
       <c r="R154" t="n">
-        <v>7145545</v>
+        <v>7145362</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17136,27 +17141,27 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129730267</v>
+        <v>129730286</v>
       </c>
       <c r="B155" t="n">
-        <v>57736</v>
+        <v>57840</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -17171,10 +17176,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>483426</v>
+        <v>483251</v>
       </c>
       <c r="R155" t="n">
-        <v>7145362</v>
+        <v>7145567</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17207,11 +17212,6 @@
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC155" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17947,10 +17947,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129730271</v>
+        <v>129730259</v>
       </c>
       <c r="B163" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17958,21 +17958,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17982,10 +17982,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>483461</v>
+        <v>483432</v>
       </c>
       <c r="R163" t="n">
-        <v>7145552</v>
+        <v>7145357</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18018,11 +18018,6 @@
       <c r="AA163" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC163" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -18049,7 +18044,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129730272</v>
+        <v>129730271</v>
       </c>
       <c r="B164" t="n">
         <v>57736</v>
@@ -18084,10 +18079,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>483583</v>
+        <v>483461</v>
       </c>
       <c r="R164" t="n">
-        <v>7145605</v>
+        <v>7145552</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18151,7 +18146,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129730273</v>
+        <v>129730272</v>
       </c>
       <c r="B165" t="n">
         <v>57736</v>
@@ -18186,10 +18181,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>483589</v>
+        <v>483583</v>
       </c>
       <c r="R165" t="n">
-        <v>7145604</v>
+        <v>7145605</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18253,7 +18248,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129730270</v>
+        <v>129730273</v>
       </c>
       <c r="B166" t="n">
         <v>57736</v>
@@ -18288,10 +18283,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>483426</v>
+        <v>483589</v>
       </c>
       <c r="R166" t="n">
-        <v>7145560</v>
+        <v>7145604</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18355,10 +18350,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129730259</v>
+        <v>129730270</v>
       </c>
       <c r="B167" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18366,21 +18361,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -18390,10 +18385,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>483432</v>
+        <v>483426</v>
       </c>
       <c r="R167" t="n">
-        <v>7145357</v>
+        <v>7145560</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18426,6 +18421,11 @@
       <c r="AA167" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD167" t="b">

--- a/artfynd/A 52753-2025 artfynd.xlsx
+++ b/artfynd/A 52753-2025 artfynd.xlsx
@@ -2999,10 +2999,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129726813</v>
+        <v>129727934</v>
       </c>
       <c r="B23" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3010,34 +3010,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483773</v>
+        <v>483619</v>
       </c>
       <c r="R23" t="n">
-        <v>7145613</v>
+        <v>7145595</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3067,19 +3067,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>09:32</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>09:32</t>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3094,57 +3089,57 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129726814</v>
+        <v>129727915</v>
       </c>
       <c r="B24" t="n">
-        <v>79081</v>
+        <v>92317</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>483796</v>
+        <v>483493</v>
       </c>
       <c r="R24" t="n">
-        <v>7145620</v>
+        <v>7145538</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3174,19 +3169,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>09:25</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>09:25</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3201,22 +3186,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129726818</v>
+        <v>129726813</v>
       </c>
       <c r="B25" t="n">
-        <v>83052</v>
+        <v>79081</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3224,21 +3209,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3248,10 +3233,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>483849</v>
+        <v>483773</v>
       </c>
       <c r="R25" t="n">
-        <v>7145605</v>
+        <v>7145613</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3283,7 +3268,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3293,7 +3278,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3320,45 +3305,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129727915</v>
+        <v>129726814</v>
       </c>
       <c r="B26" t="n">
-        <v>92317</v>
+        <v>79081</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>483493</v>
+        <v>483796</v>
       </c>
       <c r="R26" t="n">
-        <v>7145538</v>
+        <v>7145620</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3388,9 +3373,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3405,22 +3400,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129727934</v>
+        <v>129726818</v>
       </c>
       <c r="B27" t="n">
-        <v>57736</v>
+        <v>83052</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3428,34 +3423,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>483619</v>
+        <v>483849</v>
       </c>
       <c r="R27" t="n">
-        <v>7145595</v>
+        <v>7145605</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3485,14 +3480,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3507,57 +3507,57 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129727921</v>
+        <v>129726816</v>
       </c>
       <c r="B28" t="n">
-        <v>57736</v>
+        <v>75065</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6428</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>483464</v>
+        <v>483815</v>
       </c>
       <c r="R28" t="n">
-        <v>7145542</v>
+        <v>7145615</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3587,14 +3587,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3609,57 +3614,69 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129726816</v>
+        <v>129726933</v>
       </c>
       <c r="B29" t="n">
-        <v>75065</v>
+        <v>57736</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6428</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>483815</v>
+        <v>483582</v>
       </c>
       <c r="R29" t="n">
-        <v>7145615</v>
+        <v>7145456</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3689,19 +3706,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>09:18</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>09:18</t>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3712,23 +3724,48 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129726933</v>
+        <v>129727921</v>
       </c>
       <c r="B30" t="n">
         <v>57736</v>
@@ -3757,28 +3794,16 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>483582</v>
+        <v>483464</v>
       </c>
       <c r="R30" t="n">
-        <v>7145456</v>
+        <v>7145542</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3815,7 +3840,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3826,41 +3851,16 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -8646,10 +8646,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129726964</v>
+        <v>129726787</v>
       </c>
       <c r="B75" t="n">
-        <v>79081</v>
+        <v>78094</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8657,37 +8657,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>483553</v>
+        <v>483914</v>
       </c>
       <c r="R75" t="n">
-        <v>7145611</v>
+        <v>7145602</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8717,14 +8714,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>På levande gran i barrblandskog.</t>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8733,51 +8735,25 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
-      </c>
-      <c r="AH75" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129726787</v>
+        <v>129726826</v>
       </c>
       <c r="B76" t="n">
         <v>78094</v>
@@ -8812,10 +8788,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>483914</v>
+        <v>483988</v>
       </c>
       <c r="R76" t="n">
-        <v>7145602</v>
+        <v>7145444</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8847,7 +8823,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8857,7 +8833,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8884,10 +8860,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129726826</v>
+        <v>129726964</v>
       </c>
       <c r="B77" t="n">
-        <v>78094</v>
+        <v>79081</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8895,34 +8871,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>483988</v>
+        <v>483553</v>
       </c>
       <c r="R77" t="n">
-        <v>7145444</v>
+        <v>7145611</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8952,19 +8931,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>08:49</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>08:49</t>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>På levande gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8973,28 +8947,54 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129716465</v>
+        <v>129726793</v>
       </c>
       <c r="B78" t="n">
-        <v>91599</v>
+        <v>57896</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9002,37 +9002,46 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>483983</v>
+        <v>483572</v>
       </c>
       <c r="R78" t="n">
-        <v>7145507</v>
+        <v>7145322</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9059,9 +9068,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9076,22 +9095,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129727941</v>
+        <v>129726795</v>
       </c>
       <c r="B79" t="n">
-        <v>91595</v>
+        <v>83057</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9099,34 +9118,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1108</v>
+        <v>1467</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>483551</v>
+        <v>483545</v>
       </c>
       <c r="R79" t="n">
-        <v>7145323</v>
+        <v>7145343</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9156,9 +9175,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9173,22 +9202,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129727942</v>
+        <v>129716465</v>
       </c>
       <c r="B80" t="n">
-        <v>91619</v>
+        <v>91599</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9196,30 +9225,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>483495</v>
+        <v>483983</v>
       </c>
       <c r="R80" t="n">
-        <v>7145618</v>
+        <v>7145507</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9266,22 +9299,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129726795</v>
+        <v>129727941</v>
       </c>
       <c r="B81" t="n">
-        <v>83057</v>
+        <v>91595</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9289,34 +9322,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1467</v>
+        <v>1108</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>483545</v>
+        <v>483551</v>
       </c>
       <c r="R81" t="n">
-        <v>7145343</v>
+        <v>7145323</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9346,19 +9379,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>10:35</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>10:35</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9373,22 +9396,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129726831</v>
+        <v>129727942</v>
       </c>
       <c r="B82" t="n">
-        <v>83052</v>
+        <v>91619</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9396,34 +9419,30 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>484008</v>
+        <v>483495</v>
       </c>
       <c r="R82" t="n">
-        <v>7145455</v>
+        <v>7145618</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9453,19 +9472,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>08:42</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>08:42</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9480,60 +9489,57 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129726963</v>
+        <v>129726796</v>
       </c>
       <c r="B83" t="n">
-        <v>79081</v>
+        <v>83050</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>6486</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>483498</v>
+        <v>483545</v>
       </c>
       <c r="R83" t="n">
-        <v>7145585</v>
+        <v>7145343</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9563,14 +9569,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>På levande gran.</t>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9579,54 +9590,28 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
-      </c>
-      <c r="AH83" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129726812</v>
+        <v>129726831</v>
       </c>
       <c r="B84" t="n">
-        <v>79081</v>
+        <v>83052</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9634,21 +9619,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9658,10 +9643,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>483764</v>
+        <v>484008</v>
       </c>
       <c r="R84" t="n">
-        <v>7145589</v>
+        <v>7145455</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9693,7 +9678,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9703,7 +9688,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9730,7 +9715,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129726823</v>
+        <v>129726963</v>
       </c>
       <c r="B85" t="n">
         <v>79081</v>
@@ -9759,16 +9744,19 @@
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>483959</v>
+        <v>483498</v>
       </c>
       <c r="R85" t="n">
-        <v>7145539</v>
+        <v>7145585</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9798,19 +9786,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>09:02</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>09:02</t>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>På levande gran.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9819,25 +9802,51 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM85" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129716451</v>
+        <v>129726812</v>
       </c>
       <c r="B86" t="n">
         <v>79081</v>
@@ -9868,14 +9877,14 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>483989</v>
+        <v>483764</v>
       </c>
       <c r="R86" t="n">
-        <v>7145511</v>
+        <v>7145589</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9905,9 +9914,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9922,19 +9941,19 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129726798</v>
+        <v>129726823</v>
       </c>
       <c r="B87" t="n">
         <v>79081</v>
@@ -9969,10 +9988,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>483429</v>
+        <v>483959</v>
       </c>
       <c r="R87" t="n">
-        <v>7145430</v>
+        <v>7145539</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10004,7 +10023,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10014,7 +10033,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10041,45 +10060,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129726796</v>
+        <v>129716451</v>
       </c>
       <c r="B88" t="n">
-        <v>83050</v>
+        <v>79081</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6486</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>483545</v>
+        <v>483989</v>
       </c>
       <c r="R88" t="n">
-        <v>7145343</v>
+        <v>7145511</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10109,19 +10128,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>10:34</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>10:34</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10136,22 +10145,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129727940</v>
+        <v>129726798</v>
       </c>
       <c r="B89" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10159,34 +10168,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>483677</v>
+        <v>483429</v>
       </c>
       <c r="R89" t="n">
-        <v>7145478</v>
+        <v>7145430</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10216,14 +10225,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Hack ganska färska</t>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10238,22 +10252,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129726793</v>
+        <v>129727940</v>
       </c>
       <c r="B90" t="n">
-        <v>57896</v>
+        <v>57733</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10261,46 +10275,37 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>483572</v>
+        <v>483677</v>
       </c>
       <c r="R90" t="n">
-        <v>7145322</v>
+        <v>7145478</v>
       </c>
       <c r="S90" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10327,19 +10332,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>10:55</t>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Hack ganska färska</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10354,12 +10354,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
@@ -10681,10 +10681,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129726967</v>
+        <v>129716457</v>
       </c>
       <c r="B94" t="n">
-        <v>79081</v>
+        <v>91619</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10692,37 +10692,30 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>483745</v>
+        <v>483922</v>
       </c>
       <c r="R94" t="n">
-        <v>7145588</v>
+        <v>7145565</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10757,65 +10750,34 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>På en levande gran i granskog.</t>
-        </is>
-      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
-      </c>
-      <c r="AH94" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ94" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK94" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM94" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO94" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129726951</v>
+        <v>129726942</v>
       </c>
       <c r="B95" t="n">
-        <v>79081</v>
+        <v>80187</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10823,26 +10785,30 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -10850,10 +10816,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>483599</v>
+        <v>483377</v>
       </c>
       <c r="R95" t="n">
-        <v>7145738</v>
+        <v>7145537</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10890,7 +10856,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På en levande sälg i granskog.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10905,27 +10871,27 @@
       </c>
       <c r="AH95" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -10943,10 +10909,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129726965</v>
+        <v>129716456</v>
       </c>
       <c r="B96" t="n">
-        <v>79081</v>
+        <v>82918</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10954,37 +10920,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>483794</v>
+        <v>483445</v>
       </c>
       <c r="R96" t="n">
-        <v>7145597</v>
+        <v>7145393</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11019,65 +10982,34 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>På levande granar i granskog.</t>
-        </is>
-      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
-      </c>
-      <c r="AH96" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ96" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK96" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO96" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129726940</v>
+        <v>129726967</v>
       </c>
       <c r="B97" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11085,31 +11017,26 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
@@ -11117,10 +11044,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>483382</v>
+        <v>483745</v>
       </c>
       <c r="R97" t="n">
-        <v>7145460</v>
+        <v>7145588</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11157,7 +11084,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Äldre och färska hackspår i en grov stående död gran av full längd.</t>
+          <t>På en levande gran i granskog.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11166,12 +11093,13 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ97" t="inlineStr">
@@ -11186,12 +11114,12 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -11209,10 +11137,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129716457</v>
+        <v>129726951</v>
       </c>
       <c r="B98" t="n">
-        <v>91619</v>
+        <v>79081</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11220,30 +11148,37 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>483922</v>
+        <v>483599</v>
       </c>
       <c r="R98" t="n">
-        <v>7145565</v>
+        <v>7145738</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11278,34 +11213,65 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
+      </c>
+      <c r="AH98" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK98" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM98" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129726942</v>
+        <v>129726965</v>
       </c>
       <c r="B99" t="n">
-        <v>80187</v>
+        <v>79081</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11313,30 +11279,26 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K99" t="inlineStr"/>
       <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
@@ -11344,10 +11306,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>483377</v>
+        <v>483794</v>
       </c>
       <c r="R99" t="n">
-        <v>7145537</v>
+        <v>7145597</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11384,7 +11346,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>På en levande sälg i granskog.</t>
+          <t>På levande granar i granskog.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11404,22 +11366,22 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>
@@ -11437,10 +11399,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129716456</v>
+        <v>129726940</v>
       </c>
       <c r="B100" t="n">
-        <v>82918</v>
+        <v>57733</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11448,34 +11410,42 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>483445</v>
+        <v>483382</v>
       </c>
       <c r="R100" t="n">
-        <v>7145393</v>
+        <v>7145460</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11510,6 +11480,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Äldre och färska hackspår i en grov stående död gran av full längd.</t>
+        </is>
+      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
@@ -11518,16 +11493,41 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
+      </c>
+      <c r="AH100" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM100" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -12027,10 +12027,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129726957</v>
+        <v>129727933</v>
       </c>
       <c r="B105" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12038,37 +12038,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>483497</v>
+        <v>483593</v>
       </c>
       <c r="R105" t="n">
-        <v>7145327</v>
+        <v>7145594</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12105,7 +12102,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12114,54 +12111,28 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
-      </c>
-      <c r="AH105" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ105" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK105" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM105" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO105" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129726830</v>
+        <v>129727937</v>
       </c>
       <c r="B106" t="n">
-        <v>78094</v>
+        <v>57736</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12169,34 +12140,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>484008</v>
+        <v>483824</v>
       </c>
       <c r="R106" t="n">
-        <v>7145455</v>
+        <v>7145592</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12226,19 +12197,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>08:43</t>
-        </is>
-      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>08:43</t>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12253,22 +12219,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129727933</v>
+        <v>129726957</v>
       </c>
       <c r="B107" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12276,34 +12242,37 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>483593</v>
+        <v>483497</v>
       </c>
       <c r="R107" t="n">
-        <v>7145594</v>
+        <v>7145327</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12340,7 +12309,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12349,28 +12318,54 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
+      </c>
+      <c r="AH107" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM107" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129727937</v>
+        <v>129726830</v>
       </c>
       <c r="B108" t="n">
-        <v>57736</v>
+        <v>78094</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12378,34 +12373,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>483824</v>
+        <v>484008</v>
       </c>
       <c r="R108" t="n">
-        <v>7145592</v>
+        <v>7145455</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12435,14 +12430,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>08:43</t>
+        </is>
+      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12457,22 +12457,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129726949</v>
+        <v>129727939</v>
       </c>
       <c r="B109" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12480,37 +12480,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>483735</v>
+        <v>483605</v>
       </c>
       <c r="R109" t="n">
-        <v>7145746</v>
+        <v>7145281</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12547,7 +12544,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Hack ganska färska</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12556,54 +12553,28 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
-      </c>
-      <c r="AH109" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ109" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK109" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM109" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO109" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129726792</v>
+        <v>129716454</v>
       </c>
       <c r="B110" t="n">
-        <v>79081</v>
+        <v>91595</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12611,34 +12582,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>483571</v>
+        <v>484017</v>
       </c>
       <c r="R110" t="n">
-        <v>7145360</v>
+        <v>7145437</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12668,19 +12639,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>10:58</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12695,22 +12656,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129726827</v>
+        <v>129726949</v>
       </c>
       <c r="B111" t="n">
-        <v>83052</v>
+        <v>79081</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12718,34 +12679,37 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>483988</v>
+        <v>483735</v>
       </c>
       <c r="R111" t="n">
-        <v>7145444</v>
+        <v>7145746</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12775,19 +12739,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z111" t="inlineStr">
-        <is>
-          <t>08:49</t>
-        </is>
-      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB111" t="inlineStr">
-        <is>
-          <t>08:49</t>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12796,25 +12755,51 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
+      </c>
+      <c r="AH111" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK111" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM111" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO111" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129726789</v>
+        <v>129726792</v>
       </c>
       <c r="B112" t="n">
         <v>79081</v>
@@ -12849,10 +12834,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>483663</v>
+        <v>483571</v>
       </c>
       <c r="R112" t="n">
-        <v>7145420</v>
+        <v>7145360</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12884,7 +12869,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12894,7 +12879,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12921,10 +12906,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129726950</v>
+        <v>129726827</v>
       </c>
       <c r="B113" t="n">
-        <v>79081</v>
+        <v>83052</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12932,37 +12917,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>483720</v>
+        <v>483988</v>
       </c>
       <c r="R113" t="n">
-        <v>7145756</v>
+        <v>7145444</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12992,14 +12974,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13008,51 +12995,25 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
-      </c>
-      <c r="AH113" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ113" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK113" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM113" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO113" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129726959</v>
+        <v>129726789</v>
       </c>
       <c r="B114" t="n">
         <v>79081</v>
@@ -13081,19 +13042,16 @@
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>483422</v>
+        <v>483663</v>
       </c>
       <c r="R114" t="n">
-        <v>7145360</v>
+        <v>7145420</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13123,14 +13081,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>På en levande gran.</t>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13139,51 +13102,25 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
-      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
-      </c>
-      <c r="AH114" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ114" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK114" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM114" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO114" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129726817</v>
+        <v>129726950</v>
       </c>
       <c r="B115" t="n">
         <v>79081</v>
@@ -13212,16 +13149,19 @@
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>483834</v>
+        <v>483720</v>
       </c>
       <c r="R115" t="n">
-        <v>7145605</v>
+        <v>7145756</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13251,19 +13191,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z115" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB115" t="inlineStr">
-        <is>
-          <t>09:15</t>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13272,25 +13207,51 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
+      </c>
+      <c r="AH115" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ115" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK115" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM115" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO115" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129726954</v>
+        <v>129726959</v>
       </c>
       <c r="B116" t="n">
         <v>79081</v>
@@ -13328,10 +13289,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>483580</v>
+        <v>483422</v>
       </c>
       <c r="R116" t="n">
-        <v>7145435</v>
+        <v>7145360</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13368,7 +13329,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>På gran i granskog.</t>
+          <t>På en levande gran.</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13383,7 +13344,7 @@
       </c>
       <c r="AH116" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ116" t="inlineStr">
@@ -13421,10 +13382,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129727939</v>
+        <v>129726817</v>
       </c>
       <c r="B117" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13432,34 +13393,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>483605</v>
+        <v>483834</v>
       </c>
       <c r="R117" t="n">
-        <v>7145281</v>
+        <v>7145605</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13489,14 +13450,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Hack ganska färska</t>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13511,22 +13477,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129716454</v>
+        <v>129726954</v>
       </c>
       <c r="B118" t="n">
-        <v>91595</v>
+        <v>79081</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13534,34 +13500,37 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>484017</v>
+        <v>483580</v>
       </c>
       <c r="R118" t="n">
-        <v>7145437</v>
+        <v>7145435</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13596,24 +13565,55 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>På gran i granskog.</t>
+        </is>
+      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
       <c r="AE118" t="b">
         <v>0</v>
       </c>
+      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
+      </c>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM118" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO118" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
@@ -14213,10 +14213,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129730253</v>
+        <v>129730268</v>
       </c>
       <c r="B125" t="n">
-        <v>78838</v>
+        <v>57736</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14224,21 +14224,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14248,10 +14248,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>483421</v>
+        <v>483247</v>
       </c>
       <c r="R125" t="n">
-        <v>7145545</v>
+        <v>7145580</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14284,6 +14284,11 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14310,10 +14315,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129730291</v>
+        <v>129730253</v>
       </c>
       <c r="B126" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14321,21 +14326,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14345,10 +14350,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>483364</v>
+        <v>483421</v>
       </c>
       <c r="R126" t="n">
-        <v>7145506</v>
+        <v>7145545</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14407,10 +14412,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129730268</v>
+        <v>129730291</v>
       </c>
       <c r="B127" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14418,21 +14423,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14442,10 +14447,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>483247</v>
+        <v>483364</v>
       </c>
       <c r="R127" t="n">
-        <v>7145580</v>
+        <v>7145506</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14478,11 +14483,6 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14509,10 +14509,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129730244</v>
+        <v>129730290</v>
       </c>
       <c r="B128" t="n">
-        <v>80187</v>
+        <v>91619</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14520,23 +14520,19 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr"/>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
@@ -14544,10 +14540,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>483599</v>
+        <v>483766</v>
       </c>
       <c r="R128" t="n">
-        <v>7145190</v>
+        <v>7145610</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14606,10 +14602,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129730274</v>
+        <v>129730244</v>
       </c>
       <c r="B129" t="n">
-        <v>57736</v>
+        <v>80187</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14617,21 +14613,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14641,10 +14637,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>483612</v>
+        <v>483599</v>
       </c>
       <c r="R129" t="n">
-        <v>7145596</v>
+        <v>7145190</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14677,11 +14673,6 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14708,10 +14699,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129730290</v>
+        <v>129730274</v>
       </c>
       <c r="B130" t="n">
-        <v>91619</v>
+        <v>57736</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14719,19 +14710,23 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
@@ -14739,10 +14734,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>483766</v>
+        <v>483612</v>
       </c>
       <c r="R130" t="n">
-        <v>7145610</v>
+        <v>7145596</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14775,6 +14770,11 @@
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15476,10 +15476,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129730293</v>
+        <v>129730262</v>
       </c>
       <c r="B138" t="n">
-        <v>83044</v>
+        <v>57736</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15487,21 +15487,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15511,10 +15511,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>483321</v>
+        <v>483284</v>
       </c>
       <c r="R138" t="n">
-        <v>7145559</v>
+        <v>7145578</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15547,6 +15547,11 @@
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15573,10 +15578,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129730250</v>
+        <v>129730293</v>
       </c>
       <c r="B139" t="n">
-        <v>78838</v>
+        <v>83044</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15584,21 +15589,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6446</v>
+        <v>308</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15608,10 +15613,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>483564</v>
+        <v>483321</v>
       </c>
       <c r="R139" t="n">
-        <v>7145430</v>
+        <v>7145559</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15670,10 +15675,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129730262</v>
+        <v>129730250</v>
       </c>
       <c r="B140" t="n">
-        <v>57736</v>
+        <v>78838</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15681,21 +15686,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15705,10 +15710,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>483284</v>
+        <v>483564</v>
       </c>
       <c r="R140" t="n">
-        <v>7145578</v>
+        <v>7145430</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15741,11 +15746,6 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16937,27 +16937,27 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129730269</v>
+        <v>129730286</v>
       </c>
       <c r="B153" t="n">
-        <v>57736</v>
+        <v>57840</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -16972,10 +16972,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>483364</v>
+        <v>483251</v>
       </c>
       <c r="R153" t="n">
-        <v>7145545</v>
+        <v>7145567</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17008,11 +17008,6 @@
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17039,7 +17034,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129730267</v>
+        <v>129730269</v>
       </c>
       <c r="B154" t="n">
         <v>57736</v>
@@ -17074,10 +17069,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>483426</v>
+        <v>483364</v>
       </c>
       <c r="R154" t="n">
-        <v>7145362</v>
+        <v>7145545</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17141,27 +17136,27 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129730286</v>
+        <v>129730267</v>
       </c>
       <c r="B155" t="n">
-        <v>57840</v>
+        <v>57736</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -17176,10 +17171,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>483251</v>
+        <v>483426</v>
       </c>
       <c r="R155" t="n">
-        <v>7145567</v>
+        <v>7145362</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17212,6 +17207,11 @@
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17238,10 +17238,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129730265</v>
+        <v>129730258</v>
       </c>
       <c r="B156" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17249,21 +17249,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -17273,10 +17273,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>483564</v>
+        <v>483592</v>
       </c>
       <c r="R156" t="n">
-        <v>7145344</v>
+        <v>7145458</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17309,11 +17309,6 @@
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17340,10 +17335,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129730276</v>
+        <v>129730257</v>
       </c>
       <c r="B157" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17351,54 +17346,34 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L157" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N157" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
           <t>Bodknulen, Jmt</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>483545</v>
+        <v>483635</v>
       </c>
       <c r="R157" t="n">
-        <v>7145332</v>
+        <v>7145484</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17457,7 +17432,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129730264</v>
+        <v>129730265</v>
       </c>
       <c r="B158" t="n">
         <v>57736</v>
@@ -17492,10 +17467,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>483665</v>
+        <v>483564</v>
       </c>
       <c r="R158" t="n">
-        <v>7145576</v>
+        <v>7145344</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17559,10 +17534,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129730258</v>
+        <v>129730276</v>
       </c>
       <c r="B159" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17570,34 +17545,54 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
           <t>Bodknulen, Jmt</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>483592</v>
+        <v>483545</v>
       </c>
       <c r="R159" t="n">
-        <v>7145458</v>
+        <v>7145332</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17656,10 +17651,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129730257</v>
+        <v>129730264</v>
       </c>
       <c r="B160" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17667,21 +17662,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17691,10 +17686,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>483635</v>
+        <v>483665</v>
       </c>
       <c r="R160" t="n">
-        <v>7145484</v>
+        <v>7145576</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17727,6 +17722,11 @@
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD160" t="b">

--- a/artfynd/A 52753-2025 artfynd.xlsx
+++ b/artfynd/A 52753-2025 artfynd.xlsx
@@ -2010,7 +2010,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129716455</v>
+        <v>129726935</v>
       </c>
       <c r="B14" t="n">
         <v>57736</v>
@@ -2039,21 +2039,28 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483975</v>
+        <v>483601</v>
       </c>
       <c r="R14" t="n">
-        <v>7145436</v>
+        <v>7145616</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2088,6 +2095,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, på stambasen av en levande gran i barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2096,26 +2108,51 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129727920</v>
+        <v>129716468</v>
       </c>
       <c r="B15" t="n">
-        <v>57736</v>
+        <v>91619</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2123,34 +2160,30 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483452</v>
+        <v>484042</v>
       </c>
       <c r="R15" t="n">
-        <v>7145362</v>
+        <v>7145421</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2185,11 +2218,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2202,19 +2230,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129727919</v>
+        <v>129716455</v>
       </c>
       <c r="B16" t="n">
         <v>57736</v>
@@ -2243,16 +2271,21 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483535</v>
+        <v>483975</v>
       </c>
       <c r="R16" t="n">
-        <v>7145332</v>
+        <v>7145436</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2287,11 +2320,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2304,19 +2332,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129727923</v>
+        <v>129727920</v>
       </c>
       <c r="B17" t="n">
         <v>57736</v>
@@ -2351,10 +2379,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483397</v>
+        <v>483452</v>
       </c>
       <c r="R17" t="n">
-        <v>7145483</v>
+        <v>7145362</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2418,10 +2446,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129716468</v>
+        <v>129727919</v>
       </c>
       <c r="B18" t="n">
-        <v>91619</v>
+        <v>57736</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2429,30 +2457,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>484042</v>
+        <v>483535</v>
       </c>
       <c r="R18" t="n">
-        <v>7145421</v>
+        <v>7145332</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2487,6 +2519,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2499,19 +2536,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129726935</v>
+        <v>129727923</v>
       </c>
       <c r="B19" t="n">
         <v>57736</v>
@@ -2540,28 +2577,16 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483601</v>
+        <v>483397</v>
       </c>
       <c r="R19" t="n">
-        <v>7145616</v>
+        <v>7145483</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2598,7 +2623,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en levande gran i barrblandskog.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2609,51 +2634,26 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129726804</v>
+        <v>129726941</v>
       </c>
       <c r="B20" t="n">
-        <v>79081</v>
+        <v>80187</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2661,34 +2661,41 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483493</v>
+        <v>483369</v>
       </c>
       <c r="R20" t="n">
-        <v>7145542</v>
+        <v>7145513</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2718,19 +2725,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>10:00</t>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På en levande sälg.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2739,28 +2741,54 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129726941</v>
+        <v>129726804</v>
       </c>
       <c r="B21" t="n">
-        <v>80187</v>
+        <v>79081</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2768,41 +2796,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>483369</v>
+        <v>483493</v>
       </c>
       <c r="R21" t="n">
-        <v>7145513</v>
+        <v>7145542</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2832,14 +2853,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På en levande sälg.</t>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2848,89 +2874,63 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129726825</v>
+        <v>129727915</v>
       </c>
       <c r="B22" t="n">
-        <v>79081</v>
+        <v>92317</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483962</v>
+        <v>483493</v>
       </c>
       <c r="R22" t="n">
-        <v>7145447</v>
+        <v>7145538</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2960,19 +2960,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>08:51</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>08:51</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2987,12 +2977,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3101,45 +3091,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129727915</v>
+        <v>129726825</v>
       </c>
       <c r="B24" t="n">
-        <v>92317</v>
+        <v>79081</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>483493</v>
+        <v>483962</v>
       </c>
       <c r="R24" t="n">
-        <v>7145538</v>
+        <v>7145447</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3169,9 +3159,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3186,12 +3186,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3867,10 +3867,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129727931</v>
+        <v>129716460</v>
       </c>
       <c r="B31" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3878,34 +3878,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>483545</v>
+        <v>483445</v>
       </c>
       <c r="R31" t="n">
-        <v>7145507</v>
+        <v>7145428</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3940,11 +3940,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -3957,19 +3952,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129716460</v>
+        <v>129726961</v>
       </c>
       <c r="B32" t="n">
         <v>79081</v>
@@ -3998,16 +3993,19 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>483445</v>
+        <v>483414</v>
       </c>
       <c r="R32" t="n">
-        <v>7145428</v>
+        <v>7145535</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4042,31 +4040,62 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På en levande gran.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129726961</v>
+        <v>129726824</v>
       </c>
       <c r="B33" t="n">
         <v>79081</v>
@@ -4095,19 +4124,16 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>483414</v>
+        <v>483981</v>
       </c>
       <c r="R33" t="n">
-        <v>7145535</v>
+        <v>7145521</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4137,14 +4163,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>08:59</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På en levande gran.</t>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4153,54 +4184,28 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129726824</v>
+        <v>129726938</v>
       </c>
       <c r="B34" t="n">
-        <v>79081</v>
+        <v>57896</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4208,34 +4213,54 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>483981</v>
+        <v>483739</v>
       </c>
       <c r="R34" t="n">
-        <v>7145521</v>
+        <v>7145743</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4265,19 +4290,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>08:59</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>08:59</t>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Synobservation av två talltitor med lockläte. Ev. rörde sig fler talltitor runt fyndplatsen som finns i flerskiktad äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4288,26 +4308,36 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Flerskiktad äldre barrblandskog.</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129726938</v>
+        <v>129727931</v>
       </c>
       <c r="B35" t="n">
-        <v>57896</v>
+        <v>57736</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4315,54 +4345,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>483739</v>
+        <v>483545</v>
       </c>
       <c r="R35" t="n">
-        <v>7145743</v>
+        <v>7145507</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4399,7 +4409,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Synobservation av två talltitor med lockläte. Ev. rörde sig fler talltitor runt fyndplatsen som finns i flerskiktad äldre barrblandskog.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4410,36 +4420,26 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>Flerskiktad äldre barrblandskog.</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129716461</v>
+        <v>129726801</v>
       </c>
       <c r="B36" t="n">
-        <v>79081</v>
+        <v>83057</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4447,34 +4447,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>483576</v>
+        <v>483487</v>
       </c>
       <c r="R36" t="n">
-        <v>7145615</v>
+        <v>7145541</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4504,9 +4504,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4521,22 +4531,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129726807</v>
+        <v>129727927</v>
       </c>
       <c r="B37" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4544,34 +4554,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>483589</v>
+        <v>483606</v>
       </c>
       <c r="R37" t="n">
-        <v>7145582</v>
+        <v>7145282</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4601,19 +4611,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>09:50</t>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4628,19 +4633,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129716466</v>
+        <v>129716461</v>
       </c>
       <c r="B38" t="n">
         <v>79081</v>
@@ -4675,10 +4680,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>483481</v>
+        <v>483576</v>
       </c>
       <c r="R38" t="n">
-        <v>7145592</v>
+        <v>7145615</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4737,10 +4742,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129727927</v>
+        <v>129726807</v>
       </c>
       <c r="B39" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4748,34 +4753,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>483606</v>
+        <v>483589</v>
       </c>
       <c r="R39" t="n">
-        <v>7145282</v>
+        <v>7145582</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4805,14 +4810,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4827,22 +4837,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129726801</v>
+        <v>129716466</v>
       </c>
       <c r="B40" t="n">
-        <v>83057</v>
+        <v>79081</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4850,34 +4860,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>483487</v>
+        <v>483481</v>
       </c>
       <c r="R40" t="n">
-        <v>7145541</v>
+        <v>7145592</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4907,19 +4917,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>10:09</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>10:09</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4934,12 +4934,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -6144,10 +6144,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129727914</v>
+        <v>129726944</v>
       </c>
       <c r="B52" t="n">
-        <v>92317</v>
+        <v>80214</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6155,34 +6155,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3298</v>
+        <v>6461</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>483577</v>
+        <v>483597</v>
       </c>
       <c r="R52" t="n">
-        <v>7145438</v>
+        <v>7145735</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6223,66 +6226,64 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129726944</v>
+        <v>129716458</v>
       </c>
       <c r="B53" t="n">
-        <v>80214</v>
+        <v>83052</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6461</v>
+        <v>6440</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>483597</v>
+        <v>483701</v>
       </c>
       <c r="R53" t="n">
-        <v>7145735</v>
+        <v>7145588</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6323,29 +6324,28 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129727924</v>
+        <v>129726811</v>
       </c>
       <c r="B54" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6353,34 +6353,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>483548</v>
+        <v>483760</v>
       </c>
       <c r="R54" t="n">
-        <v>7145488</v>
+        <v>7145575</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6410,14 +6410,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6432,19 +6437,19 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129727922</v>
+        <v>129727924</v>
       </c>
       <c r="B55" t="n">
         <v>57736</v>
@@ -6479,10 +6484,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>483507</v>
+        <v>483548</v>
       </c>
       <c r="R55" t="n">
-        <v>7145556</v>
+        <v>7145488</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6546,10 +6551,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129716458</v>
+        <v>129727922</v>
       </c>
       <c r="B56" t="n">
-        <v>83052</v>
+        <v>57736</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6557,34 +6562,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>483701</v>
+        <v>483507</v>
       </c>
       <c r="R56" t="n">
-        <v>7145588</v>
+        <v>7145556</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6619,6 +6624,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -6631,57 +6641,57 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129726811</v>
+        <v>129727914</v>
       </c>
       <c r="B57" t="n">
-        <v>79081</v>
+        <v>92317</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>483760</v>
+        <v>483577</v>
       </c>
       <c r="R57" t="n">
-        <v>7145575</v>
+        <v>7145438</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6711,19 +6721,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>09:35</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>09:35</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6738,12 +6738,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -7702,10 +7702,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129716448</v>
+        <v>129726958</v>
       </c>
       <c r="B67" t="n">
-        <v>91550</v>
+        <v>79081</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7713,34 +7713,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>483443</v>
+        <v>483482</v>
       </c>
       <c r="R67" t="n">
-        <v>7145540</v>
+        <v>7145330</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7775,24 +7778,55 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>På en levande gran.</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -8037,10 +8071,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129726958</v>
+        <v>129727916</v>
       </c>
       <c r="B70" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8048,37 +8082,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>483482</v>
+        <v>483577</v>
       </c>
       <c r="R70" t="n">
-        <v>7145330</v>
+        <v>7145734</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8115,7 +8146,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>På en levande gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8124,51 +8155,25 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AH70" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129727916</v>
+        <v>129726937</v>
       </c>
       <c r="B71" t="n">
         <v>57736</v>
@@ -8197,16 +8202,28 @@
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>483577</v>
+        <v>483749</v>
       </c>
       <c r="R71" t="n">
-        <v>7145734</v>
+        <v>7145581</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8243,7 +8260,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på stambasen av en levande gran.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8254,23 +8271,48 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM71" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129726937</v>
+        <v>129727918</v>
       </c>
       <c r="B72" t="n">
         <v>57736</v>
@@ -8299,28 +8341,16 @@
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>483749</v>
+        <v>483580</v>
       </c>
       <c r="R72" t="n">
-        <v>7145581</v>
+        <v>7145447</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8357,7 +8387,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en levande gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8368,51 +8398,26 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AH72" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129727918</v>
+        <v>129716448</v>
       </c>
       <c r="B73" t="n">
-        <v>57736</v>
+        <v>91550</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8420,34 +8425,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>112</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>483580</v>
+        <v>483443</v>
       </c>
       <c r="R73" t="n">
-        <v>7145447</v>
+        <v>7145540</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8482,11 +8487,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
-        </is>
-      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
@@ -8499,12 +8499,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -8991,10 +8991,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129726793</v>
+        <v>129716465</v>
       </c>
       <c r="B78" t="n">
-        <v>57896</v>
+        <v>91599</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9002,46 +9002,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>483572</v>
+        <v>483983</v>
       </c>
       <c r="R78" t="n">
-        <v>7145322</v>
+        <v>7145507</v>
       </c>
       <c r="S78" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9068,19 +9059,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>10:55</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9095,22 +9076,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129726795</v>
+        <v>129727941</v>
       </c>
       <c r="B79" t="n">
-        <v>83057</v>
+        <v>91595</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9118,34 +9099,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1467</v>
+        <v>1108</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>483545</v>
+        <v>483551</v>
       </c>
       <c r="R79" t="n">
-        <v>7145343</v>
+        <v>7145323</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9175,19 +9156,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>10:35</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>10:35</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9202,22 +9173,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129716465</v>
+        <v>129727942</v>
       </c>
       <c r="B80" t="n">
-        <v>91599</v>
+        <v>91619</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9225,34 +9196,30 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>483983</v>
+        <v>483495</v>
       </c>
       <c r="R80" t="n">
-        <v>7145507</v>
+        <v>7145618</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9299,22 +9266,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129727941</v>
+        <v>129726795</v>
       </c>
       <c r="B81" t="n">
-        <v>91595</v>
+        <v>83057</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9322,34 +9289,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1108</v>
+        <v>1467</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>483551</v>
+        <v>483545</v>
       </c>
       <c r="R81" t="n">
-        <v>7145323</v>
+        <v>7145343</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9379,9 +9346,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9396,22 +9373,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129727942</v>
+        <v>129726831</v>
       </c>
       <c r="B82" t="n">
-        <v>91619</v>
+        <v>83052</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9419,30 +9396,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr"/>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>483495</v>
+        <v>484008</v>
       </c>
       <c r="R82" t="n">
-        <v>7145618</v>
+        <v>7145455</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9472,9 +9453,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>08:42</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9489,57 +9480,60 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129726796</v>
+        <v>129726963</v>
       </c>
       <c r="B83" t="n">
-        <v>83050</v>
+        <v>79081</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6486</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>483545</v>
+        <v>483498</v>
       </c>
       <c r="R83" t="n">
-        <v>7145343</v>
+        <v>7145585</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9569,19 +9563,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>10:34</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>10:34</t>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>På levande gran.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9590,28 +9579,54 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129726831</v>
+        <v>129726812</v>
       </c>
       <c r="B84" t="n">
-        <v>83052</v>
+        <v>79081</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9619,21 +9634,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9643,10 +9658,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>484008</v>
+        <v>483764</v>
       </c>
       <c r="R84" t="n">
-        <v>7145455</v>
+        <v>7145589</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9678,7 +9693,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9688,7 +9703,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9715,7 +9730,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129726963</v>
+        <v>129726823</v>
       </c>
       <c r="B85" t="n">
         <v>79081</v>
@@ -9744,19 +9759,16 @@
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>483498</v>
+        <v>483959</v>
       </c>
       <c r="R85" t="n">
-        <v>7145585</v>
+        <v>7145539</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9786,14 +9798,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>På levande gran.</t>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9802,51 +9819,25 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
-      </c>
-      <c r="AH85" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ85" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK85" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129726812</v>
+        <v>129716451</v>
       </c>
       <c r="B86" t="n">
         <v>79081</v>
@@ -9877,14 +9868,14 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>483764</v>
+        <v>483989</v>
       </c>
       <c r="R86" t="n">
-        <v>7145589</v>
+        <v>7145511</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9914,19 +9905,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>09:34</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>09:34</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9941,19 +9922,19 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129726823</v>
+        <v>129726798</v>
       </c>
       <c r="B87" t="n">
         <v>79081</v>
@@ -9988,10 +9969,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>483959</v>
+        <v>483429</v>
       </c>
       <c r="R87" t="n">
-        <v>7145539</v>
+        <v>7145430</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10023,7 +10004,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10033,7 +10014,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10060,45 +10041,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129716451</v>
+        <v>129726796</v>
       </c>
       <c r="B88" t="n">
-        <v>79081</v>
+        <v>83050</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6486</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>483989</v>
+        <v>483545</v>
       </c>
       <c r="R88" t="n">
-        <v>7145511</v>
+        <v>7145343</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10128,9 +10109,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10145,22 +10136,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129726798</v>
+        <v>129727940</v>
       </c>
       <c r="B89" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10168,34 +10159,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>483429</v>
+        <v>483677</v>
       </c>
       <c r="R89" t="n">
-        <v>7145430</v>
+        <v>7145478</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10225,19 +10216,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>10:16</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>10:16</t>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Hack ganska färska</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10252,22 +10238,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129727940</v>
+        <v>129726793</v>
       </c>
       <c r="B90" t="n">
-        <v>57733</v>
+        <v>57896</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10275,37 +10261,46 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>483677</v>
+        <v>483572</v>
       </c>
       <c r="R90" t="n">
-        <v>7145478</v>
+        <v>7145322</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10332,14 +10327,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Hack ganska färska</t>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10354,12 +10354,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
@@ -10681,10 +10681,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129716457</v>
+        <v>129726967</v>
       </c>
       <c r="B94" t="n">
-        <v>91619</v>
+        <v>79081</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10692,30 +10692,37 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>483922</v>
+        <v>483745</v>
       </c>
       <c r="R94" t="n">
-        <v>7145565</v>
+        <v>7145588</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10750,34 +10757,65 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>På en levande gran i granskog.</t>
+        </is>
+      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
+      </c>
+      <c r="AH94" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ94" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK94" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM94" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129726942</v>
+        <v>129726951</v>
       </c>
       <c r="B95" t="n">
-        <v>80187</v>
+        <v>79081</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10785,30 +10823,26 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K95" t="inlineStr"/>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -10816,10 +10850,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>483377</v>
+        <v>483599</v>
       </c>
       <c r="R95" t="n">
-        <v>7145537</v>
+        <v>7145738</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10856,7 +10890,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>På en levande sälg i granskog.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10871,27 +10905,27 @@
       </c>
       <c r="AH95" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -10909,10 +10943,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129716456</v>
+        <v>129726965</v>
       </c>
       <c r="B96" t="n">
-        <v>82918</v>
+        <v>79081</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10920,34 +10954,37 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>483445</v>
+        <v>483794</v>
       </c>
       <c r="R96" t="n">
-        <v>7145393</v>
+        <v>7145597</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10982,34 +11019,65 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>På levande granar i granskog.</t>
+        </is>
+      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
+      </c>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM96" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129726967</v>
+        <v>129726940</v>
       </c>
       <c r="B97" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11017,26 +11085,31 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
@@ -11044,10 +11117,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>483745</v>
+        <v>483382</v>
       </c>
       <c r="R97" t="n">
-        <v>7145588</v>
+        <v>7145460</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11084,7 +11157,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>På en levande gran i granskog.</t>
+          <t>Äldre och färska hackspår i en grov stående död gran av full längd.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11093,13 +11166,12 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ97" t="inlineStr">
@@ -11114,12 +11186,12 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -11137,10 +11209,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129726951</v>
+        <v>129716457</v>
       </c>
       <c r="B98" t="n">
-        <v>79081</v>
+        <v>91619</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11148,37 +11220,30 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>483599</v>
+        <v>483922</v>
       </c>
       <c r="R98" t="n">
-        <v>7145738</v>
+        <v>7145565</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11213,65 +11278,34 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
-      </c>
-      <c r="AH98" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ98" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK98" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM98" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO98" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129726965</v>
+        <v>129726942</v>
       </c>
       <c r="B99" t="n">
-        <v>79081</v>
+        <v>80187</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11279,26 +11313,30 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
@@ -11306,10 +11344,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>483794</v>
+        <v>483377</v>
       </c>
       <c r="R99" t="n">
-        <v>7145597</v>
+        <v>7145537</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11346,7 +11384,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>På levande granar i granskog.</t>
+          <t>På en levande sälg i granskog.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11366,22 +11404,22 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>
@@ -11399,10 +11437,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129726940</v>
+        <v>129716456</v>
       </c>
       <c r="B100" t="n">
-        <v>57733</v>
+        <v>82918</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11410,42 +11448,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>483382</v>
+        <v>483445</v>
       </c>
       <c r="R100" t="n">
-        <v>7145460</v>
+        <v>7145393</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11480,11 +11510,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Äldre och färska hackspår i en grov stående död gran av full längd.</t>
-        </is>
-      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
@@ -11493,41 +11518,16 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
-      </c>
-      <c r="AH100" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ100" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK100" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO100" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -12027,10 +12027,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129727933</v>
+        <v>129726957</v>
       </c>
       <c r="B105" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12038,34 +12038,37 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>483593</v>
+        <v>483497</v>
       </c>
       <c r="R105" t="n">
-        <v>7145594</v>
+        <v>7145327</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12102,7 +12105,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12111,28 +12114,54 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
+      </c>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM105" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129727937</v>
+        <v>129726830</v>
       </c>
       <c r="B106" t="n">
-        <v>57736</v>
+        <v>78094</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12140,34 +12169,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>483824</v>
+        <v>484008</v>
       </c>
       <c r="R106" t="n">
-        <v>7145592</v>
+        <v>7145455</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12197,14 +12226,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>08:43</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12219,22 +12253,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129726957</v>
+        <v>129727933</v>
       </c>
       <c r="B107" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12242,37 +12276,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>483497</v>
+        <v>483593</v>
       </c>
       <c r="R107" t="n">
-        <v>7145327</v>
+        <v>7145594</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12309,7 +12340,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12318,54 +12349,28 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
-      </c>
-      <c r="AH107" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ107" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK107" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM107" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO107" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129726830</v>
+        <v>129727937</v>
       </c>
       <c r="B108" t="n">
-        <v>78094</v>
+        <v>57736</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12373,34 +12378,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>484008</v>
+        <v>483824</v>
       </c>
       <c r="R108" t="n">
-        <v>7145455</v>
+        <v>7145592</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12430,19 +12435,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>08:43</t>
-        </is>
-      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>08:43</t>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12457,22 +12457,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129727939</v>
+        <v>129726949</v>
       </c>
       <c r="B109" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12480,34 +12480,37 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>483605</v>
+        <v>483735</v>
       </c>
       <c r="R109" t="n">
-        <v>7145281</v>
+        <v>7145746</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12544,7 +12547,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Hack ganska färska</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12553,28 +12556,54 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK109" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM109" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO109" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129716454</v>
+        <v>129726792</v>
       </c>
       <c r="B110" t="n">
-        <v>91595</v>
+        <v>79081</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12582,34 +12611,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>484017</v>
+        <v>483571</v>
       </c>
       <c r="R110" t="n">
-        <v>7145437</v>
+        <v>7145360</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12639,9 +12668,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12656,22 +12695,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129726949</v>
+        <v>129726827</v>
       </c>
       <c r="B111" t="n">
-        <v>79081</v>
+        <v>83052</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12679,37 +12718,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>483735</v>
+        <v>483988</v>
       </c>
       <c r="R111" t="n">
-        <v>7145746</v>
+        <v>7145444</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12739,14 +12775,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12755,51 +12796,25 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
-      </c>
-      <c r="AH111" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ111" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK111" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM111" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO111" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129726792</v>
+        <v>129726789</v>
       </c>
       <c r="B112" t="n">
         <v>79081</v>
@@ -12834,10 +12849,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>483571</v>
+        <v>483663</v>
       </c>
       <c r="R112" t="n">
-        <v>7145360</v>
+        <v>7145420</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12869,7 +12884,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12879,7 +12894,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12906,10 +12921,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129726827</v>
+        <v>129726950</v>
       </c>
       <c r="B113" t="n">
-        <v>83052</v>
+        <v>79081</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12917,34 +12932,37 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>483988</v>
+        <v>483720</v>
       </c>
       <c r="R113" t="n">
-        <v>7145444</v>
+        <v>7145756</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12974,19 +12992,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z113" t="inlineStr">
-        <is>
-          <t>08:49</t>
-        </is>
-      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB113" t="inlineStr">
-        <is>
-          <t>08:49</t>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12995,25 +13008,51 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
+      </c>
+      <c r="AH113" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK113" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM113" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO113" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129726789</v>
+        <v>129726959</v>
       </c>
       <c r="B114" t="n">
         <v>79081</v>
@@ -13042,16 +13081,19 @@
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>483663</v>
+        <v>483422</v>
       </c>
       <c r="R114" t="n">
-        <v>7145420</v>
+        <v>7145360</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13081,19 +13123,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>11:09</t>
-        </is>
-      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>11:09</t>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>På en levande gran.</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13102,25 +13139,51 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
+      </c>
+      <c r="AH114" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ114" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK114" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM114" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO114" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129726950</v>
+        <v>129726817</v>
       </c>
       <c r="B115" t="n">
         <v>79081</v>
@@ -13149,19 +13212,16 @@
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>483720</v>
+        <v>483834</v>
       </c>
       <c r="R115" t="n">
-        <v>7145756</v>
+        <v>7145605</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13191,14 +13251,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13207,51 +13272,25 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
-      </c>
-      <c r="AH115" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ115" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK115" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM115" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO115" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129726959</v>
+        <v>129726954</v>
       </c>
       <c r="B116" t="n">
         <v>79081</v>
@@ -13289,10 +13328,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>483422</v>
+        <v>483580</v>
       </c>
       <c r="R116" t="n">
-        <v>7145360</v>
+        <v>7145435</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13329,7 +13368,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>På en levande gran.</t>
+          <t>På gran i granskog.</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13344,7 +13383,7 @@
       </c>
       <c r="AH116" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ116" t="inlineStr">
@@ -13382,10 +13421,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129726817</v>
+        <v>129727939</v>
       </c>
       <c r="B117" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13393,34 +13432,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>483834</v>
+        <v>483605</v>
       </c>
       <c r="R117" t="n">
-        <v>7145605</v>
+        <v>7145281</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13450,19 +13489,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>09:15</t>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Hack ganska färska</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13477,22 +13511,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129726954</v>
+        <v>129716454</v>
       </c>
       <c r="B118" t="n">
-        <v>79081</v>
+        <v>91595</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13500,37 +13534,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>483580</v>
+        <v>484017</v>
       </c>
       <c r="R118" t="n">
-        <v>7145435</v>
+        <v>7145437</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13565,55 +13596,24 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>På gran i granskog.</t>
-        </is>
-      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
       <c r="AE118" t="b">
         <v>0</v>
       </c>
-      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
-      </c>
-      <c r="AH118" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ118" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK118" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM118" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO118" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
@@ -13827,7 +13827,7 @@
         <v>129730288</v>
       </c>
       <c r="B121" t="n">
-        <v>91619</v>
+        <v>91622</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13920,7 +13920,7 @@
         <v>129730246</v>
       </c>
       <c r="B122" t="n">
-        <v>80187</v>
+        <v>80190</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14014,10 +14014,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129730292</v>
+        <v>129730241</v>
       </c>
       <c r="B123" t="n">
-        <v>83044</v>
+        <v>57737</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14025,21 +14025,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -14049,10 +14049,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>483314</v>
+        <v>483751</v>
       </c>
       <c r="R123" t="n">
-        <v>7145495</v>
+        <v>7145575</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14085,6 +14085,11 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14111,10 +14116,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129730241</v>
+        <v>129730292</v>
       </c>
       <c r="B124" t="n">
-        <v>57736</v>
+        <v>83047</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14122,21 +14127,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -14146,10 +14151,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>483751</v>
+        <v>483314</v>
       </c>
       <c r="R124" t="n">
-        <v>7145575</v>
+        <v>7145495</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14182,11 +14187,6 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14216,7 +14216,7 @@
         <v>129730268</v>
       </c>
       <c r="B125" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14315,10 +14315,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129730253</v>
+        <v>129730291</v>
       </c>
       <c r="B126" t="n">
-        <v>78838</v>
+        <v>79084</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14326,21 +14326,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14350,10 +14350,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>483421</v>
+        <v>483364</v>
       </c>
       <c r="R126" t="n">
-        <v>7145545</v>
+        <v>7145506</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14412,10 +14412,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129730291</v>
+        <v>129730253</v>
       </c>
       <c r="B127" t="n">
-        <v>79081</v>
+        <v>78841</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14423,21 +14423,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14447,10 +14447,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>483364</v>
+        <v>483421</v>
       </c>
       <c r="R127" t="n">
-        <v>7145506</v>
+        <v>7145545</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14509,10 +14509,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129730290</v>
+        <v>129730248</v>
       </c>
       <c r="B128" t="n">
-        <v>91619</v>
+        <v>80189</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14520,19 +14520,23 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
@@ -14540,10 +14544,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>483766</v>
+        <v>483599</v>
       </c>
       <c r="R128" t="n">
-        <v>7145610</v>
+        <v>7145185</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14602,10 +14606,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129730244</v>
+        <v>129730247</v>
       </c>
       <c r="B129" t="n">
-        <v>80187</v>
+        <v>80189</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14613,21 +14617,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14637,10 +14641,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>483599</v>
+        <v>483595</v>
       </c>
       <c r="R129" t="n">
-        <v>7145190</v>
+        <v>7145180</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14699,10 +14703,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129730274</v>
+        <v>129730244</v>
       </c>
       <c r="B130" t="n">
-        <v>57736</v>
+        <v>80190</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14710,21 +14714,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14734,10 +14738,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>483612</v>
+        <v>483599</v>
       </c>
       <c r="R130" t="n">
-        <v>7145596</v>
+        <v>7145190</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14770,11 +14774,6 @@
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14801,10 +14800,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129730248</v>
+        <v>129730290</v>
       </c>
       <c r="B131" t="n">
-        <v>80186</v>
+        <v>91622</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14812,23 +14811,19 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
@@ -14836,10 +14831,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>483599</v>
+        <v>483766</v>
       </c>
       <c r="R131" t="n">
-        <v>7145185</v>
+        <v>7145610</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14898,10 +14893,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129730247</v>
+        <v>129730274</v>
       </c>
       <c r="B132" t="n">
-        <v>80186</v>
+        <v>57737</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14909,21 +14904,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14933,10 +14928,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>483595</v>
+        <v>483612</v>
       </c>
       <c r="R132" t="n">
-        <v>7145180</v>
+        <v>7145596</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14969,6 +14964,11 @@
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14995,10 +14995,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129730287</v>
+        <v>129730242</v>
       </c>
       <c r="B133" t="n">
-        <v>91595</v>
+        <v>79674</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15006,21 +15006,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1108</v>
+        <v>229821</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -15030,10 +15030,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>483608</v>
+        <v>483421</v>
       </c>
       <c r="R133" t="n">
-        <v>7145490</v>
+        <v>7145545</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15092,10 +15092,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129730255</v>
+        <v>129730287</v>
       </c>
       <c r="B134" t="n">
-        <v>91619</v>
+        <v>91598</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15103,19 +15103,23 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
@@ -15123,10 +15127,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>483529</v>
+        <v>483608</v>
       </c>
       <c r="R134" t="n">
-        <v>7145591</v>
+        <v>7145490</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15188,7 +15192,7 @@
         <v>129730252</v>
       </c>
       <c r="B135" t="n">
-        <v>78838</v>
+        <v>78841</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15282,10 +15286,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129730242</v>
+        <v>129730255</v>
       </c>
       <c r="B136" t="n">
-        <v>79671</v>
+        <v>91622</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15293,23 +15297,19 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>229821</v>
+        <v>5432</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
@@ -15317,10 +15317,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>483421</v>
+        <v>483529</v>
       </c>
       <c r="R136" t="n">
-        <v>7145545</v>
+        <v>7145591</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15382,7 +15382,7 @@
         <v>129730284</v>
       </c>
       <c r="B137" t="n">
-        <v>78094</v>
+        <v>78097</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15479,7 +15479,7 @@
         <v>129730262</v>
       </c>
       <c r="B138" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15578,10 +15578,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129730293</v>
+        <v>129730250</v>
       </c>
       <c r="B139" t="n">
-        <v>83044</v>
+        <v>78841</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15589,21 +15589,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>308</v>
+        <v>6446</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15613,10 +15613,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>483321</v>
+        <v>483564</v>
       </c>
       <c r="R139" t="n">
-        <v>7145559</v>
+        <v>7145430</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15675,10 +15675,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129730250</v>
+        <v>129730293</v>
       </c>
       <c r="B140" t="n">
-        <v>78838</v>
+        <v>83047</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15686,21 +15686,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6446</v>
+        <v>308</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15710,10 +15710,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>483564</v>
+        <v>483321</v>
       </c>
       <c r="R140" t="n">
-        <v>7145430</v>
+        <v>7145559</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15772,32 +15772,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129730281</v>
+        <v>129730285</v>
       </c>
       <c r="B141" t="n">
-        <v>80090</v>
+        <v>83063</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6456</v>
+        <v>1469</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Liten blekspik</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Sclerophora peronella</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15807,10 +15807,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>483572</v>
+        <v>483470</v>
       </c>
       <c r="R141" t="n">
-        <v>7145441</v>
+        <v>7145348</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15869,10 +15869,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129730254</v>
+        <v>129730249</v>
       </c>
       <c r="B142" t="n">
-        <v>78838</v>
+        <v>80189</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15880,21 +15880,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15904,10 +15904,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>483454</v>
+        <v>483253</v>
       </c>
       <c r="R142" t="n">
-        <v>7145556</v>
+        <v>7145561</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15966,32 +15966,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129730285</v>
+        <v>129730281</v>
       </c>
       <c r="B143" t="n">
-        <v>83060</v>
+        <v>80093</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1469</v>
+        <v>6456</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Liten blekspik</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Sclerophora peronella</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -16001,10 +16001,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>483470</v>
+        <v>483572</v>
       </c>
       <c r="R143" t="n">
-        <v>7145348</v>
+        <v>7145441</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16063,10 +16063,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129730249</v>
+        <v>129730254</v>
       </c>
       <c r="B144" t="n">
-        <v>80186</v>
+        <v>78841</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16074,21 +16074,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -16098,10 +16098,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>483253</v>
+        <v>483454</v>
       </c>
       <c r="R144" t="n">
-        <v>7145561</v>
+        <v>7145556</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16163,7 +16163,7 @@
         <v>129730289</v>
       </c>
       <c r="B145" t="n">
-        <v>91619</v>
+        <v>91622</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16256,7 +16256,7 @@
         <v>129730261</v>
       </c>
       <c r="B146" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16353,7 +16353,7 @@
         <v>129730294</v>
       </c>
       <c r="B147" t="n">
-        <v>83044</v>
+        <v>83047</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16450,7 +16450,7 @@
         <v>129730240</v>
       </c>
       <c r="B148" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16549,10 +16549,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129730295</v>
+        <v>129730260</v>
       </c>
       <c r="B149" t="n">
-        <v>83044</v>
+        <v>79084</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16560,21 +16560,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16584,10 +16584,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>483462</v>
+        <v>483324</v>
       </c>
       <c r="R149" t="n">
-        <v>7145552</v>
+        <v>7145520</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16646,10 +16646,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129730260</v>
+        <v>129730295</v>
       </c>
       <c r="B150" t="n">
-        <v>79081</v>
+        <v>83047</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16657,21 +16657,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16681,10 +16681,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>483324</v>
+        <v>483462</v>
       </c>
       <c r="R150" t="n">
-        <v>7145520</v>
+        <v>7145552</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16743,32 +16743,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129730282</v>
+        <v>129730296</v>
       </c>
       <c r="B151" t="n">
-        <v>80090</v>
+        <v>83047</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6456</v>
+        <v>308</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16778,10 +16778,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>483534</v>
+        <v>483526</v>
       </c>
       <c r="R151" t="n">
-        <v>7145348</v>
+        <v>7145596</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16840,32 +16840,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129730296</v>
+        <v>129730282</v>
       </c>
       <c r="B152" t="n">
-        <v>83044</v>
+        <v>80093</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>308</v>
+        <v>6456</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16875,10 +16875,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>483526</v>
+        <v>483534</v>
       </c>
       <c r="R152" t="n">
-        <v>7145596</v>
+        <v>7145348</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16937,27 +16937,27 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129730286</v>
+        <v>129730267</v>
       </c>
       <c r="B153" t="n">
-        <v>57840</v>
+        <v>57737</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -16972,10 +16972,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>483251</v>
+        <v>483426</v>
       </c>
       <c r="R153" t="n">
-        <v>7145567</v>
+        <v>7145362</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17008,6 +17008,11 @@
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17037,7 +17042,7 @@
         <v>129730269</v>
       </c>
       <c r="B154" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17136,27 +17141,27 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129730267</v>
+        <v>129730286</v>
       </c>
       <c r="B155" t="n">
-        <v>57736</v>
+        <v>57841</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -17171,10 +17176,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>483426</v>
+        <v>483251</v>
       </c>
       <c r="R155" t="n">
-        <v>7145362</v>
+        <v>7145567</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17207,11 +17212,6 @@
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC155" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17241,7 +17241,7 @@
         <v>129730258</v>
       </c>
       <c r="B156" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17338,7 +17338,7 @@
         <v>129730257</v>
       </c>
       <c r="B157" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17432,10 +17432,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129730265</v>
+        <v>129730264</v>
       </c>
       <c r="B158" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17467,10 +17467,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>483564</v>
+        <v>483665</v>
       </c>
       <c r="R158" t="n">
-        <v>7145344</v>
+        <v>7145576</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17537,7 +17537,7 @@
         <v>129730276</v>
       </c>
       <c r="B159" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17651,10 +17651,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129730264</v>
+        <v>129730265</v>
       </c>
       <c r="B160" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17686,10 +17686,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>483665</v>
+        <v>483564</v>
       </c>
       <c r="R160" t="n">
-        <v>7145576</v>
+        <v>7145344</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17756,7 +17756,7 @@
         <v>129730256</v>
       </c>
       <c r="B161" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17853,7 +17853,7 @@
         <v>129730263</v>
       </c>
       <c r="B162" t="n">
-        <v>83052</v>
+        <v>83055</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17950,7 +17950,7 @@
         <v>129730259</v>
       </c>
       <c r="B163" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18044,10 +18044,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129730271</v>
+        <v>129730273</v>
       </c>
       <c r="B164" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18079,10 +18079,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>483461</v>
+        <v>483589</v>
       </c>
       <c r="R164" t="n">
-        <v>7145552</v>
+        <v>7145604</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18149,7 +18149,7 @@
         <v>129730272</v>
       </c>
       <c r="B165" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18248,10 +18248,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129730273</v>
+        <v>129730271</v>
       </c>
       <c r="B166" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18283,10 +18283,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>483589</v>
+        <v>483461</v>
       </c>
       <c r="R166" t="n">
-        <v>7145604</v>
+        <v>7145552</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18353,7 +18353,7 @@
         <v>129730270</v>
       </c>
       <c r="B167" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>

--- a/artfynd/A 52753-2025 artfynd.xlsx
+++ b/artfynd/A 52753-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129726815</v>
       </c>
       <c r="B2" t="n">
-        <v>83044</v>
+        <v>83047</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129726820</v>
+        <v>129716450</v>
       </c>
       <c r="B3" t="n">
-        <v>83057</v>
+        <v>79084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483921</v>
+        <v>483823</v>
       </c>
       <c r="R3" t="n">
-        <v>7145571</v>
+        <v>7145591</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,19 +850,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>09:08</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>09:08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129726936</v>
+        <v>129726952</v>
       </c>
       <c r="B4" t="n">
-        <v>57736</v>
+        <v>79084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,46 +890,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483746</v>
+        <v>483538</v>
       </c>
       <c r="R4" t="n">
-        <v>7145582</v>
+        <v>7145695</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,7 +957,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en levande gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -985,6 +966,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1005,12 +987,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1028,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129727928</v>
+        <v>129726820</v>
       </c>
       <c r="B5" t="n">
-        <v>57736</v>
+        <v>83060</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,34 +1021,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1467</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483704</v>
+        <v>483921</v>
       </c>
       <c r="R5" t="n">
-        <v>7145461</v>
+        <v>7145571</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,14 +1078,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1118,22 +1105,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129716450</v>
+        <v>129727928</v>
       </c>
       <c r="B6" t="n">
-        <v>79081</v>
+        <v>57737</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1141,34 +1128,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483823</v>
+        <v>483704</v>
       </c>
       <c r="R6" t="n">
-        <v>7145591</v>
+        <v>7145461</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,6 +1190,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1215,22 +1207,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129726952</v>
+        <v>129726936</v>
       </c>
       <c r="B7" t="n">
-        <v>79081</v>
+        <v>57737</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1238,37 +1230,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483538</v>
+        <v>483746</v>
       </c>
       <c r="R7" t="n">
-        <v>7145695</v>
+        <v>7145582</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,7 +1306,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, äldre, på stambasen av en levande gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1314,7 +1315,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1358,10 +1358,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129726805</v>
+        <v>129726803</v>
       </c>
       <c r="B8" t="n">
-        <v>79081</v>
+        <v>83047</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,21 +1369,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1393,10 +1393,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483517</v>
+        <v>483493</v>
       </c>
       <c r="R8" t="n">
-        <v>7145580</v>
+        <v>7145541</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1465,10 +1465,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129726791</v>
+        <v>129716452</v>
       </c>
       <c r="B9" t="n">
-        <v>79081</v>
+        <v>91622</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1476,34 +1476,30 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483607</v>
+        <v>483480</v>
       </c>
       <c r="R9" t="n">
-        <v>7145404</v>
+        <v>7145600</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1533,19 +1529,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1560,12 +1546,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1575,7 +1561,7 @@
         <v>129726955</v>
       </c>
       <c r="B10" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,10 +1689,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129726803</v>
+        <v>129726805</v>
       </c>
       <c r="B11" t="n">
-        <v>83044</v>
+        <v>79084</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1714,21 +1700,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1738,10 +1724,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483493</v>
+        <v>483517</v>
       </c>
       <c r="R11" t="n">
-        <v>7145541</v>
+        <v>7145580</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1773,7 +1759,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1783,7 +1769,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1810,10 +1796,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129716452</v>
+        <v>129726791</v>
       </c>
       <c r="B12" t="n">
-        <v>91619</v>
+        <v>79084</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1821,30 +1807,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483480</v>
+        <v>483607</v>
       </c>
       <c r="R12" t="n">
-        <v>7145600</v>
+        <v>7145404</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1874,9 +1864,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1891,22 +1891,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129726819</v>
+        <v>129716468</v>
       </c>
       <c r="B13" t="n">
-        <v>79081</v>
+        <v>91622</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1914,34 +1914,30 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483862</v>
+        <v>484042</v>
       </c>
       <c r="R13" t="n">
-        <v>7145604</v>
+        <v>7145421</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1971,19 +1967,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>09:11</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>09:11</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1998,22 +1984,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129726935</v>
+        <v>129726819</v>
       </c>
       <c r="B14" t="n">
-        <v>57736</v>
+        <v>79084</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2021,46 +2007,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483601</v>
+        <v>483862</v>
       </c>
       <c r="R14" t="n">
-        <v>7145616</v>
+        <v>7145604</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2090,14 +2064,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, på stambasen av en levande gran i barrblandskog.</t>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2108,51 +2087,26 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129716468</v>
+        <v>129716455</v>
       </c>
       <c r="B15" t="n">
-        <v>91619</v>
+        <v>57737</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2160,30 +2114,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>484042</v>
+        <v>483975</v>
       </c>
       <c r="R15" t="n">
-        <v>7145421</v>
+        <v>7145436</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2242,10 +2205,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129716455</v>
+        <v>129727923</v>
       </c>
       <c r="B16" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2271,21 +2234,16 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483975</v>
+        <v>483397</v>
       </c>
       <c r="R16" t="n">
-        <v>7145436</v>
+        <v>7145483</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2320,6 +2278,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2332,22 +2295,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129727920</v>
+        <v>129726935</v>
       </c>
       <c r="B17" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2373,16 +2336,28 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483452</v>
+        <v>483601</v>
       </c>
       <c r="R17" t="n">
-        <v>7145362</v>
+        <v>7145616</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2419,7 +2394,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, färska och äldre, på stambasen av en levande gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2430,16 +2405,41 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2449,7 +2449,7 @@
         <v>129727919</v>
       </c>
       <c r="B18" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2548,10 +2548,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129727923</v>
+        <v>129727920</v>
       </c>
       <c r="B19" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2583,10 +2583,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483397</v>
+        <v>483452</v>
       </c>
       <c r="R19" t="n">
-        <v>7145483</v>
+        <v>7145362</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2653,7 +2653,7 @@
         <v>129726941</v>
       </c>
       <c r="B20" t="n">
-        <v>80187</v>
+        <v>80190</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>129726804</v>
       </c>
       <c r="B21" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2892,32 +2892,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129727915</v>
+        <v>129727934</v>
       </c>
       <c r="B22" t="n">
-        <v>92317</v>
+        <v>57737</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2927,10 +2927,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483493</v>
+        <v>483619</v>
       </c>
       <c r="R22" t="n">
-        <v>7145538</v>
+        <v>7145595</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2963,6 +2963,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2989,32 +2994,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129727934</v>
+        <v>129727915</v>
       </c>
       <c r="B23" t="n">
-        <v>57736</v>
+        <v>92320</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3024,10 +3029,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483619</v>
+        <v>483493</v>
       </c>
       <c r="R23" t="n">
-        <v>7145595</v>
+        <v>7145538</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3060,11 +3065,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3094,7 +3094,7 @@
         <v>129726825</v>
       </c>
       <c r="B24" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3198,10 +3198,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129726813</v>
+        <v>129726814</v>
       </c>
       <c r="B25" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3233,10 +3233,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>483773</v>
+        <v>483796</v>
       </c>
       <c r="R25" t="n">
-        <v>7145613</v>
+        <v>7145620</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3305,10 +3305,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129726814</v>
+        <v>129726813</v>
       </c>
       <c r="B26" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3340,10 +3340,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>483796</v>
+        <v>483773</v>
       </c>
       <c r="R26" t="n">
-        <v>7145620</v>
+        <v>7145613</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3375,7 +3375,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3415,7 +3415,7 @@
         <v>129726818</v>
       </c>
       <c r="B27" t="n">
-        <v>83052</v>
+        <v>83055</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>129726816</v>
       </c>
       <c r="B28" t="n">
-        <v>75065</v>
+        <v>75068</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3626,10 +3626,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129726933</v>
+        <v>129727921</v>
       </c>
       <c r="B29" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3655,28 +3655,16 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>483582</v>
+        <v>483464</v>
       </c>
       <c r="R29" t="n">
-        <v>7145456</v>
+        <v>7145542</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3713,7 +3701,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3724,51 +3712,26 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129727921</v>
+        <v>129726933</v>
       </c>
       <c r="B30" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3794,16 +3757,28 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>483464</v>
+        <v>483582</v>
       </c>
       <c r="R30" t="n">
-        <v>7145542</v>
+        <v>7145456</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3840,7 +3815,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3851,16 +3826,41 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3870,7 +3870,7 @@
         <v>129716460</v>
       </c>
       <c r="B31" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>129726961</v>
       </c>
       <c r="B32" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>129726824</v>
       </c>
       <c r="B33" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4202,10 +4202,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129726938</v>
+        <v>129727931</v>
       </c>
       <c r="B34" t="n">
-        <v>57896</v>
+        <v>57737</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4213,54 +4213,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>483739</v>
+        <v>483545</v>
       </c>
       <c r="R34" t="n">
-        <v>7145743</v>
+        <v>7145507</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4297,7 +4277,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Synobservation av två talltitor med lockläte. Ev. rörde sig fler talltitor runt fyndplatsen som finns i flerskiktad äldre barrblandskog.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4308,36 +4288,26 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>Flerskiktad äldre barrblandskog.</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129727931</v>
+        <v>129726938</v>
       </c>
       <c r="B35" t="n">
-        <v>57736</v>
+        <v>57895</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4345,34 +4315,54 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>483545</v>
+        <v>483739</v>
       </c>
       <c r="R35" t="n">
-        <v>7145507</v>
+        <v>7145743</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4409,7 +4399,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Synobservation av två talltitor med lockläte. Ev. rörde sig fler talltitor runt fyndplatsen som finns i flerskiktad äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4420,16 +4410,26 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Flerskiktad äldre barrblandskog.</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4439,7 +4439,7 @@
         <v>129726801</v>
       </c>
       <c r="B36" t="n">
-        <v>83057</v>
+        <v>83060</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4543,10 +4543,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129727927</v>
+        <v>129716466</v>
       </c>
       <c r="B37" t="n">
-        <v>57736</v>
+        <v>79084</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4554,34 +4554,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>483606</v>
+        <v>483481</v>
       </c>
       <c r="R37" t="n">
-        <v>7145282</v>
+        <v>7145592</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4616,11 +4616,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4633,22 +4628,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129716461</v>
+        <v>129726807</v>
       </c>
       <c r="B38" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4676,14 +4671,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>483576</v>
+        <v>483589</v>
       </c>
       <c r="R38" t="n">
-        <v>7145615</v>
+        <v>7145582</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4713,9 +4708,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4730,22 +4735,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129726807</v>
+        <v>129727927</v>
       </c>
       <c r="B39" t="n">
-        <v>79081</v>
+        <v>57737</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4753,34 +4758,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>483589</v>
+        <v>483606</v>
       </c>
       <c r="R39" t="n">
-        <v>7145582</v>
+        <v>7145282</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4810,19 +4815,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>09:50</t>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4837,22 +4837,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129716466</v>
+        <v>129716461</v>
       </c>
       <c r="B40" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4884,10 +4884,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>483481</v>
+        <v>483576</v>
       </c>
       <c r="R40" t="n">
-        <v>7145592</v>
+        <v>7145615</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4946,10 +4946,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129726948</v>
+        <v>129726821</v>
       </c>
       <c r="B41" t="n">
-        <v>91619</v>
+        <v>79084</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4957,37 +4957,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>483501</v>
+        <v>483922</v>
       </c>
       <c r="R41" t="n">
-        <v>7145621</v>
+        <v>7145570</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5017,14 +5014,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar i en levande gran.</t>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5033,89 +5035,66 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129716464</v>
+        <v>129726948</v>
       </c>
       <c r="B42" t="n">
-        <v>92317</v>
+        <v>91622</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>484017</v>
+        <v>483501</v>
       </c>
       <c r="R42" t="n">
-        <v>7145437</v>
+        <v>7145621</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5150,24 +5129,55 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar i en levande gran.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5177,7 +5187,7 @@
         <v>129726946</v>
       </c>
       <c r="B43" t="n">
-        <v>80214</v>
+        <v>80217</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5275,10 +5285,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129726821</v>
+        <v>129726960</v>
       </c>
       <c r="B44" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5304,16 +5314,19 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>483922</v>
+        <v>483376</v>
       </c>
       <c r="R44" t="n">
-        <v>7145570</v>
+        <v>7145540</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5343,19 +5356,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>09:05</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>09:05</t>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På en levande gran.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5364,66 +5372,89 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129726960</v>
+        <v>129716464</v>
       </c>
       <c r="B45" t="n">
-        <v>79081</v>
+        <v>92320</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>483376</v>
+        <v>484017</v>
       </c>
       <c r="R45" t="n">
-        <v>7145540</v>
+        <v>7145437</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5458,65 +5489,34 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På en levande gran.</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129727936</v>
+        <v>129726810</v>
       </c>
       <c r="B46" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5541,17 +5541,31 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>483750</v>
+        <v>483760</v>
       </c>
       <c r="R46" t="n">
-        <v>7145579</v>
+        <v>7145583</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5581,14 +5595,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5603,22 +5622,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129727938</v>
+        <v>129727936</v>
       </c>
       <c r="B47" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5650,10 +5669,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>483975</v>
+        <v>483750</v>
       </c>
       <c r="R47" t="n">
-        <v>7145511</v>
+        <v>7145579</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5717,10 +5736,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129726810</v>
+        <v>129727938</v>
       </c>
       <c r="B48" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5745,31 +5764,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>483760</v>
+        <v>483975</v>
       </c>
       <c r="R48" t="n">
-        <v>7145583</v>
+        <v>7145511</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5799,19 +5804,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>09:41</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>09:41</t>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5826,22 +5826,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129726800</v>
+        <v>129716462</v>
       </c>
       <c r="B49" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5869,14 +5869,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>483439</v>
+        <v>483666</v>
       </c>
       <c r="R49" t="n">
-        <v>7145513</v>
+        <v>7145612</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5906,19 +5906,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>10:13</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5933,22 +5923,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129716462</v>
+        <v>129726800</v>
       </c>
       <c r="B50" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5976,14 +5966,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>483666</v>
+        <v>483439</v>
       </c>
       <c r="R50" t="n">
-        <v>7145612</v>
+        <v>7145513</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6013,9 +6003,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6030,12 +6030,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -6045,7 +6045,7 @@
         <v>129727935</v>
       </c>
       <c r="B51" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6144,10 +6144,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129726944</v>
+        <v>129727914</v>
       </c>
       <c r="B52" t="n">
-        <v>80214</v>
+        <v>92320</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6155,37 +6155,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6461</v>
+        <v>3298</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>483597</v>
+        <v>483577</v>
       </c>
       <c r="R52" t="n">
-        <v>7145735</v>
+        <v>7145438</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6226,64 +6223,66 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129716458</v>
+        <v>129726944</v>
       </c>
       <c r="B53" t="n">
-        <v>83052</v>
+        <v>80217</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6440</v>
+        <v>6461</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>483701</v>
+        <v>483597</v>
       </c>
       <c r="R53" t="n">
-        <v>7145588</v>
+        <v>7145735</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6324,28 +6323,29 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129726811</v>
+        <v>129716458</v>
       </c>
       <c r="B54" t="n">
-        <v>79081</v>
+        <v>83055</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6353,34 +6353,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>483760</v>
+        <v>483701</v>
       </c>
       <c r="R54" t="n">
-        <v>7145575</v>
+        <v>7145588</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6410,19 +6410,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>09:35</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>09:35</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6437,22 +6427,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129727924</v>
+        <v>129726811</v>
       </c>
       <c r="B55" t="n">
-        <v>57736</v>
+        <v>79084</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6460,34 +6450,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>483548</v>
+        <v>483760</v>
       </c>
       <c r="R55" t="n">
-        <v>7145488</v>
+        <v>7145575</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6517,14 +6507,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6539,12 +6534,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6554,7 +6549,7 @@
         <v>129727922</v>
       </c>
       <c r="B56" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6653,32 +6648,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129727914</v>
+        <v>129727924</v>
       </c>
       <c r="B57" t="n">
-        <v>92317</v>
+        <v>57737</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6688,10 +6683,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>483577</v>
+        <v>483548</v>
       </c>
       <c r="R57" t="n">
-        <v>7145438</v>
+        <v>7145488</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6724,6 +6719,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6753,7 +6753,7 @@
         <v>129726828</v>
       </c>
       <c r="B58" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6857,10 +6857,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129716453</v>
+        <v>129716449</v>
       </c>
       <c r="B59" t="n">
-        <v>79081</v>
+        <v>83055</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6868,21 +6868,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6892,10 +6892,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>484032</v>
+        <v>483889</v>
       </c>
       <c r="R59" t="n">
-        <v>7145416</v>
+        <v>7145589</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6954,10 +6954,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129726953</v>
+        <v>129726806</v>
       </c>
       <c r="B60" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6983,19 +6983,16 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>483555</v>
+        <v>483558</v>
       </c>
       <c r="R60" t="n">
-        <v>7145531</v>
+        <v>7145588</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7025,14 +7022,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7041,54 +7043,28 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129716449</v>
+        <v>129716453</v>
       </c>
       <c r="B61" t="n">
-        <v>83052</v>
+        <v>79084</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7096,21 +7072,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7120,10 +7096,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>483889</v>
+        <v>484032</v>
       </c>
       <c r="R61" t="n">
-        <v>7145589</v>
+        <v>7145416</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7182,10 +7158,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129726806</v>
+        <v>129726953</v>
       </c>
       <c r="B62" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7211,16 +7187,19 @@
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>483558</v>
+        <v>483555</v>
       </c>
       <c r="R62" t="n">
-        <v>7145588</v>
+        <v>7145531</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7250,19 +7229,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>09:51</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>09:51</t>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7271,18 +7245,44 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7292,7 +7292,7 @@
         <v>129726788</v>
       </c>
       <c r="B63" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7396,10 +7396,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129727932</v>
+        <v>129727929</v>
       </c>
       <c r="B64" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7431,10 +7431,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>483527</v>
+        <v>483677</v>
       </c>
       <c r="R64" t="n">
-        <v>7145534</v>
+        <v>7145477</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7498,10 +7498,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129727929</v>
+        <v>129727932</v>
       </c>
       <c r="B65" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7533,10 +7533,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>483677</v>
+        <v>483527</v>
       </c>
       <c r="R65" t="n">
-        <v>7145477</v>
+        <v>7145534</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7603,7 +7603,7 @@
         <v>129727930</v>
       </c>
       <c r="B66" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
         <v>129726958</v>
       </c>
       <c r="B67" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7836,7 +7836,7 @@
         <v>129726966</v>
       </c>
       <c r="B68" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7964,10 +7964,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129726797</v>
+        <v>129716448</v>
       </c>
       <c r="B69" t="n">
-        <v>79081</v>
+        <v>91553</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7975,34 +7975,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>483540</v>
+        <v>483443</v>
       </c>
       <c r="R69" t="n">
-        <v>7145349</v>
+        <v>7145540</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8032,19 +8032,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>10:29</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>10:29</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8059,22 +8049,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129727916</v>
+        <v>129726797</v>
       </c>
       <c r="B70" t="n">
-        <v>57736</v>
+        <v>79084</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8082,34 +8072,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>483577</v>
+        <v>483540</v>
       </c>
       <c r="R70" t="n">
-        <v>7145734</v>
+        <v>7145349</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8139,14 +8129,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8161,12 +8156,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -8176,7 +8171,7 @@
         <v>129726937</v>
       </c>
       <c r="B71" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8312,10 +8307,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129727918</v>
+        <v>129727916</v>
       </c>
       <c r="B72" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8347,10 +8342,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>483580</v>
+        <v>483577</v>
       </c>
       <c r="R72" t="n">
-        <v>7145447</v>
+        <v>7145734</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8387,7 +8382,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8414,10 +8409,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129716448</v>
+        <v>129727918</v>
       </c>
       <c r="B73" t="n">
-        <v>91550</v>
+        <v>57737</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8425,34 +8420,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>112</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>483443</v>
+        <v>483580</v>
       </c>
       <c r="R73" t="n">
-        <v>7145540</v>
+        <v>7145447</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8487,6 +8482,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
@@ -8499,12 +8499,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -8514,7 +8514,7 @@
         <v>129726947</v>
       </c>
       <c r="B74" t="n">
-        <v>91595</v>
+        <v>91598</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8646,10 +8646,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129726787</v>
+        <v>129726964</v>
       </c>
       <c r="B75" t="n">
-        <v>78094</v>
+        <v>79084</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8657,34 +8657,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>483914</v>
+        <v>483553</v>
       </c>
       <c r="R75" t="n">
-        <v>7145602</v>
+        <v>7145611</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8714,19 +8717,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>11:26</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>11:26</t>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>På levande gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8735,28 +8733,54 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM75" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129726826</v>
+        <v>129726787</v>
       </c>
       <c r="B76" t="n">
-        <v>78094</v>
+        <v>78097</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8788,10 +8812,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>483988</v>
+        <v>483914</v>
       </c>
       <c r="R76" t="n">
-        <v>7145444</v>
+        <v>7145602</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8823,7 +8847,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8833,7 +8857,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8860,10 +8884,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129726964</v>
+        <v>129726826</v>
       </c>
       <c r="B77" t="n">
-        <v>79081</v>
+        <v>78097</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8871,37 +8895,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>483553</v>
+        <v>483988</v>
       </c>
       <c r="R77" t="n">
-        <v>7145611</v>
+        <v>7145444</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8931,14 +8952,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>På levande gran i barrblandskog.</t>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8947,54 +8973,28 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AH77" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129716465</v>
+        <v>129726793</v>
       </c>
       <c r="B78" t="n">
-        <v>91599</v>
+        <v>57895</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9002,37 +9002,46 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>483983</v>
+        <v>483572</v>
       </c>
       <c r="R78" t="n">
-        <v>7145507</v>
+        <v>7145322</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9059,9 +9068,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9076,12 +9095,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -9091,7 +9110,7 @@
         <v>129727941</v>
       </c>
       <c r="B79" t="n">
-        <v>91595</v>
+        <v>91598</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9185,10 +9204,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129727942</v>
+        <v>129716465</v>
       </c>
       <c r="B80" t="n">
-        <v>91619</v>
+        <v>91602</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9196,30 +9215,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>483495</v>
+        <v>483983</v>
       </c>
       <c r="R80" t="n">
-        <v>7145618</v>
+        <v>7145507</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9266,12 +9289,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -9281,7 +9304,7 @@
         <v>129726795</v>
       </c>
       <c r="B81" t="n">
-        <v>83057</v>
+        <v>83060</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9385,10 +9408,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129726831</v>
+        <v>129716451</v>
       </c>
       <c r="B82" t="n">
-        <v>83052</v>
+        <v>79084</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9396,34 +9419,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>484008</v>
+        <v>483989</v>
       </c>
       <c r="R82" t="n">
-        <v>7145455</v>
+        <v>7145511</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9453,19 +9476,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>08:42</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>08:42</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9480,22 +9493,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129726963</v>
+        <v>129726798</v>
       </c>
       <c r="B83" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9521,19 +9534,16 @@
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>483498</v>
+        <v>483429</v>
       </c>
       <c r="R83" t="n">
-        <v>7145585</v>
+        <v>7145430</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9563,14 +9573,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>På levande gran.</t>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9579,54 +9594,28 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
-      </c>
-      <c r="AH83" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129726812</v>
+        <v>129727942</v>
       </c>
       <c r="B84" t="n">
-        <v>79081</v>
+        <v>91622</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9634,34 +9623,30 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>483764</v>
+        <v>483495</v>
       </c>
       <c r="R84" t="n">
-        <v>7145589</v>
+        <v>7145618</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9691,19 +9676,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>09:34</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>09:34</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9718,22 +9693,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129726823</v>
+        <v>129726831</v>
       </c>
       <c r="B85" t="n">
-        <v>79081</v>
+        <v>83055</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9741,21 +9716,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9765,10 +9740,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>483959</v>
+        <v>484008</v>
       </c>
       <c r="R85" t="n">
-        <v>7145539</v>
+        <v>7145455</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9800,7 +9775,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9810,7 +9785,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9837,45 +9812,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129716451</v>
+        <v>129726796</v>
       </c>
       <c r="B86" t="n">
-        <v>79081</v>
+        <v>83053</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6486</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>483989</v>
+        <v>483545</v>
       </c>
       <c r="R86" t="n">
-        <v>7145511</v>
+        <v>7145343</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9905,9 +9880,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9922,22 +9907,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129726798</v>
+        <v>129726963</v>
       </c>
       <c r="B87" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9963,16 +9948,19 @@
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>483429</v>
+        <v>483498</v>
       </c>
       <c r="R87" t="n">
-        <v>7145430</v>
+        <v>7145585</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10002,19 +9990,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>10:16</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>10:16</t>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>På levande gran.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10023,50 +10006,76 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM87" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129726796</v>
+        <v>129726812</v>
       </c>
       <c r="B88" t="n">
-        <v>83050</v>
+        <v>79084</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6486</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10076,10 +10085,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>483545</v>
+        <v>483764</v>
       </c>
       <c r="R88" t="n">
-        <v>7145343</v>
+        <v>7145589</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10111,7 +10120,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10121,7 +10130,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10148,10 +10157,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129727940</v>
+        <v>129726823</v>
       </c>
       <c r="B89" t="n">
-        <v>57733</v>
+        <v>79084</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10159,34 +10168,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>483677</v>
+        <v>483959</v>
       </c>
       <c r="R89" t="n">
-        <v>7145478</v>
+        <v>7145539</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10216,14 +10225,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Hack ganska färska</t>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10238,22 +10252,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129726793</v>
+        <v>129727940</v>
       </c>
       <c r="B90" t="n">
-        <v>57896</v>
+        <v>57734</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10261,46 +10275,37 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>483572</v>
+        <v>483677</v>
       </c>
       <c r="R90" t="n">
-        <v>7145322</v>
+        <v>7145478</v>
       </c>
       <c r="S90" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10327,19 +10332,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>10:55</t>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Hack ganska färska</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10354,60 +10354,57 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129726945</v>
+        <v>129726832</v>
       </c>
       <c r="B91" t="n">
-        <v>80214</v>
+        <v>79084</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>483364</v>
+        <v>484041</v>
       </c>
       <c r="R91" t="n">
-        <v>7145533</v>
+        <v>7145466</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10437,75 +10434,87 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>08:39</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>08:39</t>
+        </is>
+      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129726832</v>
+        <v>129726945</v>
       </c>
       <c r="B92" t="n">
-        <v>79081</v>
+        <v>80217</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>484041</v>
+        <v>483364</v>
       </c>
       <c r="R92" t="n">
-        <v>7145466</v>
+        <v>7145533</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10535,39 +10544,30 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>08:39</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>08:39</t>
-        </is>
-      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
@@ -10577,7 +10577,7 @@
         <v>129726799</v>
       </c>
       <c r="B93" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10681,10 +10681,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129726967</v>
+        <v>129716457</v>
       </c>
       <c r="B94" t="n">
-        <v>79081</v>
+        <v>91622</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10692,37 +10692,30 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>483745</v>
+        <v>483922</v>
       </c>
       <c r="R94" t="n">
-        <v>7145588</v>
+        <v>7145565</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10757,65 +10750,34 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>På en levande gran i granskog.</t>
-        </is>
-      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
-      </c>
-      <c r="AH94" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ94" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK94" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM94" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO94" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129726951</v>
+        <v>129726940</v>
       </c>
       <c r="B95" t="n">
-        <v>79081</v>
+        <v>57734</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10823,26 +10785,31 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -10850,10 +10817,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>483599</v>
+        <v>483382</v>
       </c>
       <c r="R95" t="n">
-        <v>7145738</v>
+        <v>7145460</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10890,7 +10857,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Äldre och färska hackspår i en grov stående död gran av full längd.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10899,7 +10866,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10920,12 +10886,12 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -10943,10 +10909,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129726965</v>
+        <v>129726942</v>
       </c>
       <c r="B96" t="n">
-        <v>79081</v>
+        <v>80190</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10954,26 +10920,30 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
@@ -10981,10 +10951,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>483794</v>
+        <v>483377</v>
       </c>
       <c r="R96" t="n">
-        <v>7145597</v>
+        <v>7145537</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11021,7 +10991,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>På levande granar i granskog.</t>
+          <t>På en levande sälg i granskog.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11041,22 +11011,22 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM96" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -11074,10 +11044,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129726940</v>
+        <v>129716456</v>
       </c>
       <c r="B97" t="n">
-        <v>57733</v>
+        <v>82921</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11085,42 +11055,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>483382</v>
+        <v>483445</v>
       </c>
       <c r="R97" t="n">
-        <v>7145460</v>
+        <v>7145393</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11155,11 +11117,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Äldre och färska hackspår i en grov stående död gran av full längd.</t>
-        </is>
-      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
@@ -11168,51 +11125,26 @@
       </c>
       <c r="AG97" t="b">
         <v>0</v>
-      </c>
-      <c r="AH97" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ97" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK97" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO97" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129716457</v>
+        <v>129726951</v>
       </c>
       <c r="B98" t="n">
-        <v>91619</v>
+        <v>79084</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11220,30 +11152,37 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>483922</v>
+        <v>483599</v>
       </c>
       <c r="R98" t="n">
-        <v>7145565</v>
+        <v>7145738</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11278,34 +11217,65 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
+      </c>
+      <c r="AH98" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK98" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM98" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129726942</v>
+        <v>129726965</v>
       </c>
       <c r="B99" t="n">
-        <v>80187</v>
+        <v>79084</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11313,30 +11283,26 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K99" t="inlineStr"/>
       <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
@@ -11344,10 +11310,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>483377</v>
+        <v>483794</v>
       </c>
       <c r="R99" t="n">
-        <v>7145537</v>
+        <v>7145597</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11384,7 +11350,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>På en levande sälg i granskog.</t>
+          <t>På levande granar i granskog.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11404,22 +11370,22 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>
@@ -11437,10 +11403,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129716456</v>
+        <v>129726967</v>
       </c>
       <c r="B100" t="n">
-        <v>82918</v>
+        <v>79084</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11448,34 +11414,37 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>483445</v>
+        <v>483745</v>
       </c>
       <c r="R100" t="n">
-        <v>7145393</v>
+        <v>7145588</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11510,24 +11479,55 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>På en levande gran i granskog.</t>
+        </is>
+      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
+      </c>
+      <c r="AH100" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM100" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -11537,7 +11537,7 @@
         <v>129726962</v>
       </c>
       <c r="B101" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11665,10 +11665,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129726956</v>
+        <v>129716467</v>
       </c>
       <c r="B102" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11694,19 +11694,16 @@
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>483519</v>
+        <v>483805</v>
       </c>
       <c r="R102" t="n">
-        <v>7145306</v>
+        <v>7145587</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11741,60 +11738,34 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD102" t="b">
         <v>0</v>
       </c>
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
-      </c>
-      <c r="AH102" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ102" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK102" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO102" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129716467</v>
+        <v>129726956</v>
       </c>
       <c r="B103" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11820,16 +11791,19 @@
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>483805</v>
+        <v>483519</v>
       </c>
       <c r="R103" t="n">
-        <v>7145587</v>
+        <v>7145306</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11864,24 +11838,50 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD103" t="b">
         <v>0</v>
       </c>
       <c r="AE103" t="b">
         <v>0</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
+      </c>
+      <c r="AH103" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
@@ -11891,7 +11891,7 @@
         <v>129726934</v>
       </c>
       <c r="B104" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12027,10 +12027,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129726957</v>
+        <v>129727937</v>
       </c>
       <c r="B105" t="n">
-        <v>79081</v>
+        <v>57737</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12038,37 +12038,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>483497</v>
+        <v>483824</v>
       </c>
       <c r="R105" t="n">
-        <v>7145327</v>
+        <v>7145592</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12105,7 +12102,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12114,54 +12111,28 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
-      </c>
-      <c r="AH105" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ105" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK105" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM105" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO105" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129726830</v>
+        <v>129727933</v>
       </c>
       <c r="B106" t="n">
-        <v>78094</v>
+        <v>57737</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12169,34 +12140,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>484008</v>
+        <v>483593</v>
       </c>
       <c r="R106" t="n">
-        <v>7145455</v>
+        <v>7145594</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12226,19 +12197,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>08:43</t>
-        </is>
-      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>08:43</t>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12253,22 +12219,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129727933</v>
+        <v>129726830</v>
       </c>
       <c r="B107" t="n">
-        <v>57736</v>
+        <v>78097</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12276,34 +12242,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>483593</v>
+        <v>484008</v>
       </c>
       <c r="R107" t="n">
-        <v>7145594</v>
+        <v>7145455</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12333,14 +12299,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>08:43</t>
+        </is>
+      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12355,22 +12326,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129727937</v>
+        <v>129726957</v>
       </c>
       <c r="B108" t="n">
-        <v>57736</v>
+        <v>79084</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12378,34 +12349,37 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>483824</v>
+        <v>483497</v>
       </c>
       <c r="R108" t="n">
-        <v>7145592</v>
+        <v>7145327</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12442,7 +12416,7 @@
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12451,28 +12425,54 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
+      </c>
+      <c r="AH108" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ108" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK108" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM108" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO108" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129726949</v>
+        <v>129716454</v>
       </c>
       <c r="B109" t="n">
-        <v>79081</v>
+        <v>91598</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12480,37 +12480,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>483735</v>
+        <v>484017</v>
       </c>
       <c r="R109" t="n">
-        <v>7145746</v>
+        <v>7145437</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12545,65 +12542,34 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
-      </c>
-      <c r="AH109" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ109" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK109" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM109" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO109" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129726792</v>
+        <v>129726789</v>
       </c>
       <c r="B110" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12635,10 +12601,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>483571</v>
+        <v>483663</v>
       </c>
       <c r="R110" t="n">
-        <v>7145360</v>
+        <v>7145420</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12670,7 +12636,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12680,7 +12646,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12707,10 +12673,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129726827</v>
+        <v>129726950</v>
       </c>
       <c r="B111" t="n">
-        <v>83052</v>
+        <v>79084</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12718,34 +12684,37 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>483988</v>
+        <v>483720</v>
       </c>
       <c r="R111" t="n">
-        <v>7145444</v>
+        <v>7145756</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12775,19 +12744,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z111" t="inlineStr">
-        <is>
-          <t>08:49</t>
-        </is>
-      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB111" t="inlineStr">
-        <is>
-          <t>08:49</t>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12796,28 +12760,54 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
+      </c>
+      <c r="AH111" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK111" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM111" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO111" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129726789</v>
+        <v>129726959</v>
       </c>
       <c r="B112" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12843,16 +12833,19 @@
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>483663</v>
+        <v>483422</v>
       </c>
       <c r="R112" t="n">
-        <v>7145420</v>
+        <v>7145360</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12882,19 +12875,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>11:09</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>11:09</t>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>På en levande gran.</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12903,28 +12891,54 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
+      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
+      </c>
+      <c r="AH112" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ112" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK112" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM112" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO112" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129726950</v>
+        <v>129726954</v>
       </c>
       <c r="B113" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12959,10 +12973,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>483720</v>
+        <v>483580</v>
       </c>
       <c r="R113" t="n">
-        <v>7145756</v>
+        <v>7145435</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12999,7 +13013,7 @@
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På gran i granskog.</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13014,7 +13028,7 @@
       </c>
       <c r="AH113" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ113" t="inlineStr">
@@ -13052,10 +13066,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129726959</v>
+        <v>129727939</v>
       </c>
       <c r="B114" t="n">
-        <v>79081</v>
+        <v>57734</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13063,37 +13077,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>483422</v>
+        <v>483605</v>
       </c>
       <c r="R114" t="n">
-        <v>7145360</v>
+        <v>7145281</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13130,7 +13141,7 @@
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>På en levande gran.</t>
+          <t>Hack ganska färska</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13139,54 +13150,28 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
-      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
-      </c>
-      <c r="AH114" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ114" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK114" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM114" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO114" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129726817</v>
+        <v>129726949</v>
       </c>
       <c r="B115" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13212,16 +13197,19 @@
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>483834</v>
+        <v>483735</v>
       </c>
       <c r="R115" t="n">
-        <v>7145605</v>
+        <v>7145746</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13251,19 +13239,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z115" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB115" t="inlineStr">
-        <is>
-          <t>09:15</t>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13272,28 +13255,54 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
+      </c>
+      <c r="AH115" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ115" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK115" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM115" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO115" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129726954</v>
+        <v>129726792</v>
       </c>
       <c r="B116" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13319,19 +13328,16 @@
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>483580</v>
+        <v>483571</v>
       </c>
       <c r="R116" t="n">
-        <v>7145435</v>
+        <v>7145360</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13361,14 +13367,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>På gran i granskog.</t>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13377,54 +13388,28 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
-      </c>
-      <c r="AH116" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ116" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK116" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM116" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO116" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129727939</v>
+        <v>129726827</v>
       </c>
       <c r="B117" t="n">
-        <v>57733</v>
+        <v>83055</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13432,34 +13417,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100049</v>
+        <v>6440</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>483605</v>
+        <v>483988</v>
       </c>
       <c r="R117" t="n">
-        <v>7145281</v>
+        <v>7145444</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13489,14 +13474,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Hack ganska färska</t>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13511,22 +13501,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129716454</v>
+        <v>129726817</v>
       </c>
       <c r="B118" t="n">
-        <v>91595</v>
+        <v>79084</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13534,34 +13524,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>484017</v>
+        <v>483834</v>
       </c>
       <c r="R118" t="n">
-        <v>7145437</v>
+        <v>7145605</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13591,9 +13581,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13608,22 +13608,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129727917</v>
+        <v>129727925</v>
       </c>
       <c r="B119" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13655,10 +13655,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>483572</v>
+        <v>483580</v>
       </c>
       <c r="R119" t="n">
-        <v>7145725</v>
+        <v>7145425</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13695,7 +13695,7 @@
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13722,10 +13722,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129727925</v>
+        <v>129727917</v>
       </c>
       <c r="B120" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13757,10 +13757,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>483580</v>
+        <v>483572</v>
       </c>
       <c r="R120" t="n">
-        <v>7145425</v>
+        <v>7145725</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13797,7 +13797,7 @@
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14014,10 +14014,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129730241</v>
+        <v>129730292</v>
       </c>
       <c r="B123" t="n">
-        <v>57737</v>
+        <v>83047</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14025,21 +14025,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -14049,10 +14049,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>483751</v>
+        <v>483314</v>
       </c>
       <c r="R123" t="n">
-        <v>7145575</v>
+        <v>7145495</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14085,11 +14085,6 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14116,10 +14111,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129730292</v>
+        <v>129730241</v>
       </c>
       <c r="B124" t="n">
-        <v>83047</v>
+        <v>57737</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14127,21 +14122,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -14151,10 +14146,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>483314</v>
+        <v>483751</v>
       </c>
       <c r="R124" t="n">
-        <v>7145495</v>
+        <v>7145575</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14187,6 +14182,11 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14213,10 +14213,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129730268</v>
+        <v>129730291</v>
       </c>
       <c r="B125" t="n">
-        <v>57737</v>
+        <v>79084</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14224,21 +14224,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14248,10 +14248,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>483247</v>
+        <v>483364</v>
       </c>
       <c r="R125" t="n">
-        <v>7145580</v>
+        <v>7145506</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14284,11 +14284,6 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14315,10 +14310,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129730291</v>
+        <v>129730253</v>
       </c>
       <c r="B126" t="n">
-        <v>79084</v>
+        <v>78841</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14326,21 +14321,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14350,10 +14345,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>483364</v>
+        <v>483421</v>
       </c>
       <c r="R126" t="n">
-        <v>7145506</v>
+        <v>7145545</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14412,10 +14407,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129730253</v>
+        <v>129730268</v>
       </c>
       <c r="B127" t="n">
-        <v>78841</v>
+        <v>57737</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14423,21 +14418,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14447,10 +14442,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>483421</v>
+        <v>483247</v>
       </c>
       <c r="R127" t="n">
-        <v>7145545</v>
+        <v>7145580</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14483,6 +14478,11 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14509,10 +14509,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129730248</v>
+        <v>129730244</v>
       </c>
       <c r="B128" t="n">
-        <v>80189</v>
+        <v>80190</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14520,21 +14520,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14547,7 +14547,7 @@
         <v>483599</v>
       </c>
       <c r="R128" t="n">
-        <v>7145185</v>
+        <v>7145190</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14606,7 +14606,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129730247</v>
+        <v>129730248</v>
       </c>
       <c r="B129" t="n">
         <v>80189</v>
@@ -14641,10 +14641,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>483595</v>
+        <v>483599</v>
       </c>
       <c r="R129" t="n">
-        <v>7145180</v>
+        <v>7145185</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14703,10 +14703,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129730244</v>
+        <v>129730247</v>
       </c>
       <c r="B130" t="n">
-        <v>80190</v>
+        <v>80189</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14714,21 +14714,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14738,10 +14738,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>483599</v>
+        <v>483595</v>
       </c>
       <c r="R130" t="n">
-        <v>7145190</v>
+        <v>7145180</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14800,10 +14800,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129730290</v>
+        <v>129730274</v>
       </c>
       <c r="B131" t="n">
-        <v>91622</v>
+        <v>57737</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14811,19 +14811,23 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
@@ -14831,10 +14835,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>483766</v>
+        <v>483612</v>
       </c>
       <c r="R131" t="n">
-        <v>7145610</v>
+        <v>7145596</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14867,6 +14871,11 @@
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14893,10 +14902,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129730274</v>
+        <v>129730290</v>
       </c>
       <c r="B132" t="n">
-        <v>57737</v>
+        <v>91622</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14904,23 +14913,19 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
@@ -14928,10 +14933,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>483612</v>
+        <v>483766</v>
       </c>
       <c r="R132" t="n">
-        <v>7145596</v>
+        <v>7145610</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14964,11 +14969,6 @@
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14995,10 +14995,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129730242</v>
+        <v>129730255</v>
       </c>
       <c r="B133" t="n">
-        <v>79674</v>
+        <v>91622</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15006,23 +15006,19 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>229821</v>
+        <v>5432</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
@@ -15030,10 +15026,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>483421</v>
+        <v>483529</v>
       </c>
       <c r="R133" t="n">
-        <v>7145545</v>
+        <v>7145591</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15092,10 +15088,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129730287</v>
+        <v>129730252</v>
       </c>
       <c r="B134" t="n">
-        <v>91598</v>
+        <v>78841</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15103,21 +15099,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1108</v>
+        <v>6446</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -15127,10 +15123,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>483608</v>
+        <v>483407</v>
       </c>
       <c r="R134" t="n">
-        <v>7145490</v>
+        <v>7145540</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15189,10 +15185,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129730252</v>
+        <v>129730242</v>
       </c>
       <c r="B135" t="n">
-        <v>78841</v>
+        <v>79674</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15200,21 +15196,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15224,10 +15220,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>483407</v>
+        <v>483421</v>
       </c>
       <c r="R135" t="n">
-        <v>7145540</v>
+        <v>7145545</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15286,10 +15282,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129730255</v>
+        <v>129730287</v>
       </c>
       <c r="B136" t="n">
-        <v>91622</v>
+        <v>91598</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15297,19 +15293,23 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
@@ -15317,10 +15317,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>483529</v>
+        <v>483608</v>
       </c>
       <c r="R136" t="n">
-        <v>7145591</v>
+        <v>7145490</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15476,10 +15476,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129730262</v>
+        <v>129730293</v>
       </c>
       <c r="B138" t="n">
-        <v>57737</v>
+        <v>83047</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15487,21 +15487,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15511,10 +15511,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>483284</v>
+        <v>483321</v>
       </c>
       <c r="R138" t="n">
-        <v>7145578</v>
+        <v>7145559</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15547,11 +15547,6 @@
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15675,10 +15670,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129730293</v>
+        <v>129730262</v>
       </c>
       <c r="B140" t="n">
-        <v>83047</v>
+        <v>57737</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15686,21 +15681,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15710,10 +15705,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>483321</v>
+        <v>483284</v>
       </c>
       <c r="R140" t="n">
-        <v>7145559</v>
+        <v>7145578</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15746,6 +15741,11 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15772,32 +15772,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129730285</v>
+        <v>129730249</v>
       </c>
       <c r="B141" t="n">
-        <v>83063</v>
+        <v>80189</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1469</v>
+        <v>6458</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Liten blekspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Sclerophora peronella</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15807,10 +15807,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>483470</v>
+        <v>483253</v>
       </c>
       <c r="R141" t="n">
-        <v>7145348</v>
+        <v>7145561</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15869,32 +15869,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129730249</v>
+        <v>129730281</v>
       </c>
       <c r="B142" t="n">
-        <v>80189</v>
+        <v>80093</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15904,10 +15904,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>483253</v>
+        <v>483572</v>
       </c>
       <c r="R142" t="n">
-        <v>7145561</v>
+        <v>7145441</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15966,32 +15966,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129730281</v>
+        <v>129730254</v>
       </c>
       <c r="B143" t="n">
-        <v>80093</v>
+        <v>78841</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6456</v>
+        <v>6446</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -16001,10 +16001,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>483572</v>
+        <v>483454</v>
       </c>
       <c r="R143" t="n">
-        <v>7145441</v>
+        <v>7145556</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16063,32 +16063,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129730254</v>
+        <v>129730285</v>
       </c>
       <c r="B144" t="n">
-        <v>78841</v>
+        <v>83063</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6446</v>
+        <v>1469</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Liten blekspik</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sclerophora peronella</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -16098,10 +16098,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>483454</v>
+        <v>483470</v>
       </c>
       <c r="R144" t="n">
-        <v>7145556</v>
+        <v>7145348</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16549,10 +16549,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129730260</v>
+        <v>129730295</v>
       </c>
       <c r="B149" t="n">
-        <v>79084</v>
+        <v>83047</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16560,21 +16560,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16584,10 +16584,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>483324</v>
+        <v>483462</v>
       </c>
       <c r="R149" t="n">
-        <v>7145520</v>
+        <v>7145552</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16646,10 +16646,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129730295</v>
+        <v>129730260</v>
       </c>
       <c r="B150" t="n">
-        <v>83047</v>
+        <v>79084</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16657,21 +16657,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16681,10 +16681,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>483462</v>
+        <v>483324</v>
       </c>
       <c r="R150" t="n">
-        <v>7145552</v>
+        <v>7145520</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>

--- a/artfynd/A 52753-2025 artfynd.xlsx
+++ b/artfynd/A 52753-2025 artfynd.xlsx
@@ -3867,7 +3867,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129716460</v>
+        <v>129726824</v>
       </c>
       <c r="B31" t="n">
         <v>79084</v>
@@ -3898,14 +3898,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>483445</v>
+        <v>483981</v>
       </c>
       <c r="R31" t="n">
-        <v>7145428</v>
+        <v>7145521</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3935,9 +3935,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>08:59</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3952,22 +3962,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129726961</v>
+        <v>129727931</v>
       </c>
       <c r="B32" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3975,37 +3985,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>483414</v>
+        <v>483545</v>
       </c>
       <c r="R32" t="n">
-        <v>7145535</v>
+        <v>7145507</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4042,7 +4049,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På en levande gran.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4051,54 +4058,28 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129726824</v>
+        <v>129726938</v>
       </c>
       <c r="B33" t="n">
-        <v>79084</v>
+        <v>57895</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4106,34 +4087,54 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>483981</v>
+        <v>483739</v>
       </c>
       <c r="R33" t="n">
-        <v>7145521</v>
+        <v>7145743</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4163,19 +4164,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>08:59</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>08:59</t>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Synobservation av två talltitor med lockläte. Ev. rörde sig fler talltitor runt fyndplatsen som finns i flerskiktad äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4186,26 +4182,36 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Flerskiktad äldre barrblandskog.</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129727931</v>
+        <v>129716460</v>
       </c>
       <c r="B34" t="n">
-        <v>57737</v>
+        <v>79084</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4213,34 +4219,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>483545</v>
+        <v>483445</v>
       </c>
       <c r="R34" t="n">
-        <v>7145507</v>
+        <v>7145428</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4275,11 +4281,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4292,22 +4293,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129726938</v>
+        <v>129726961</v>
       </c>
       <c r="B35" t="n">
-        <v>57895</v>
+        <v>79084</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4315,54 +4316,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>483739</v>
+        <v>483414</v>
       </c>
       <c r="R35" t="n">
-        <v>7145743</v>
+        <v>7145535</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4399,7 +4383,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Synobservation av två talltitor med lockläte. Ev. rörde sig fler talltitor runt fyndplatsen som finns i flerskiktad äldre barrblandskog.</t>
+          <t>På en levande gran.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4408,6 +4392,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4416,9 +4401,24 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>Flerskiktad äldre barrblandskog.</t>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4543,7 +4543,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129716466</v>
+        <v>129716461</v>
       </c>
       <c r="B37" t="n">
         <v>79084</v>
@@ -4578,10 +4578,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>483481</v>
+        <v>483576</v>
       </c>
       <c r="R37" t="n">
-        <v>7145592</v>
+        <v>7145615</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4640,7 +4640,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129726807</v>
+        <v>129716466</v>
       </c>
       <c r="B38" t="n">
         <v>79084</v>
@@ -4671,14 +4671,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>483589</v>
+        <v>483481</v>
       </c>
       <c r="R38" t="n">
-        <v>7145582</v>
+        <v>7145592</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4708,19 +4708,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>09:50</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4735,22 +4725,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129727927</v>
+        <v>129726807</v>
       </c>
       <c r="B39" t="n">
-        <v>57737</v>
+        <v>79084</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4758,34 +4748,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>483606</v>
+        <v>483589</v>
       </c>
       <c r="R39" t="n">
-        <v>7145282</v>
+        <v>7145582</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4815,14 +4805,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4837,22 +4832,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129716461</v>
+        <v>129727927</v>
       </c>
       <c r="B40" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4860,34 +4855,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>483576</v>
+        <v>483606</v>
       </c>
       <c r="R40" t="n">
-        <v>7145615</v>
+        <v>7145282</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4922,6 +4917,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -4934,57 +4934,57 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129726821</v>
+        <v>129716464</v>
       </c>
       <c r="B41" t="n">
-        <v>79084</v>
+        <v>92320</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>483922</v>
+        <v>484017</v>
       </c>
       <c r="R41" t="n">
-        <v>7145570</v>
+        <v>7145437</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5014,19 +5014,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>09:05</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>09:05</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5041,22 +5031,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129726948</v>
+        <v>129726810</v>
       </c>
       <c r="B42" t="n">
-        <v>91622</v>
+        <v>57737</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5064,37 +5054,48 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>483501</v>
+        <v>483760</v>
       </c>
       <c r="R42" t="n">
-        <v>7145621</v>
+        <v>7145583</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5124,14 +5125,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar i en levande gran.</t>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5140,92 +5146,63 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129726946</v>
+        <v>129727936</v>
       </c>
       <c r="B43" t="n">
-        <v>80217</v>
+        <v>57737</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>483607</v>
+        <v>483750</v>
       </c>
       <c r="R43" t="n">
-        <v>7145621</v>
+        <v>7145579</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5260,35 +5237,39 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129726960</v>
+        <v>129727938</v>
       </c>
       <c r="B44" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5296,37 +5277,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>483376</v>
+        <v>483975</v>
       </c>
       <c r="R44" t="n">
-        <v>7145540</v>
+        <v>7145511</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5363,7 +5341,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På en levande gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5372,89 +5350,63 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129716464</v>
+        <v>129726821</v>
       </c>
       <c r="B45" t="n">
-        <v>92320</v>
+        <v>79084</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>484017</v>
+        <v>483922</v>
       </c>
       <c r="R45" t="n">
-        <v>7145437</v>
+        <v>7145570</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5484,9 +5436,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5501,22 +5463,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129726810</v>
+        <v>129726948</v>
       </c>
       <c r="B46" t="n">
-        <v>57737</v>
+        <v>91622</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5524,48 +5486,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>483760</v>
+        <v>483501</v>
       </c>
       <c r="R46" t="n">
-        <v>7145583</v>
+        <v>7145621</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5595,19 +5546,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>09:41</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>09:41</t>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar i en levande gran.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5616,63 +5562,92 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129727936</v>
+        <v>129726946</v>
       </c>
       <c r="B47" t="n">
-        <v>57737</v>
+        <v>80217</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>483750</v>
+        <v>483607</v>
       </c>
       <c r="R47" t="n">
-        <v>7145579</v>
+        <v>7145621</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5707,39 +5682,35 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129727938</v>
+        <v>129726960</v>
       </c>
       <c r="B48" t="n">
-        <v>57737</v>
+        <v>79084</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5747,34 +5718,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>483975</v>
+        <v>483376</v>
       </c>
       <c r="R48" t="n">
-        <v>7145511</v>
+        <v>7145540</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5811,7 +5785,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>På en levande gran.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5820,18 +5794,44 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -6750,7 +6750,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129726828</v>
+        <v>129716453</v>
       </c>
       <c r="B58" t="n">
         <v>79084</v>
@@ -6781,14 +6781,14 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>483988</v>
+        <v>484032</v>
       </c>
       <c r="R58" t="n">
-        <v>7145444</v>
+        <v>7145416</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6818,19 +6818,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>08:48</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>08:48</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6845,22 +6835,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129716449</v>
+        <v>129726953</v>
       </c>
       <c r="B59" t="n">
-        <v>83055</v>
+        <v>79084</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6868,34 +6858,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>483889</v>
+        <v>483555</v>
       </c>
       <c r="R59" t="n">
-        <v>7145589</v>
+        <v>7145531</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6930,31 +6923,62 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129726806</v>
+        <v>129726788</v>
       </c>
       <c r="B60" t="n">
         <v>79084</v>
@@ -6989,10 +7013,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>483558</v>
+        <v>483665</v>
       </c>
       <c r="R60" t="n">
-        <v>7145588</v>
+        <v>7145479</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7024,7 +7048,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7034,7 +7058,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7061,7 +7085,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129716453</v>
+        <v>129726828</v>
       </c>
       <c r="B61" t="n">
         <v>79084</v>
@@ -7092,14 +7116,14 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>484032</v>
+        <v>483988</v>
       </c>
       <c r="R61" t="n">
-        <v>7145416</v>
+        <v>7145444</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7129,9 +7153,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7146,22 +7180,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129726953</v>
+        <v>129716449</v>
       </c>
       <c r="B62" t="n">
-        <v>79084</v>
+        <v>83055</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7169,37 +7203,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>483555</v>
+        <v>483889</v>
       </c>
       <c r="R62" t="n">
-        <v>7145531</v>
+        <v>7145589</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7234,62 +7265,31 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129726788</v>
+        <v>129726806</v>
       </c>
       <c r="B63" t="n">
         <v>79084</v>
@@ -7324,10 +7324,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>483665</v>
+        <v>483558</v>
       </c>
       <c r="R63" t="n">
-        <v>7145479</v>
+        <v>7145588</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7359,7 +7359,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7369,7 +7369,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -12469,10 +12469,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129716454</v>
+        <v>129726949</v>
       </c>
       <c r="B109" t="n">
-        <v>91598</v>
+        <v>79084</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12480,34 +12480,37 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>484017</v>
+        <v>483735</v>
       </c>
       <c r="R109" t="n">
-        <v>7145437</v>
+        <v>7145746</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12542,31 +12545,62 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK109" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM109" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO109" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129726789</v>
+        <v>129726792</v>
       </c>
       <c r="B110" t="n">
         <v>79084</v>
@@ -12601,10 +12635,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>483663</v>
+        <v>483571</v>
       </c>
       <c r="R110" t="n">
-        <v>7145420</v>
+        <v>7145360</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12636,7 +12670,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12646,7 +12680,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12673,10 +12707,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129726950</v>
+        <v>129726827</v>
       </c>
       <c r="B111" t="n">
-        <v>79084</v>
+        <v>83055</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12684,37 +12718,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>483720</v>
+        <v>483988</v>
       </c>
       <c r="R111" t="n">
-        <v>7145756</v>
+        <v>7145444</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12744,14 +12775,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12760,51 +12796,25 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
-      </c>
-      <c r="AH111" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ111" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK111" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM111" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO111" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129726959</v>
+        <v>129726817</v>
       </c>
       <c r="B112" t="n">
         <v>79084</v>
@@ -12833,19 +12843,16 @@
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>483422</v>
+        <v>483834</v>
       </c>
       <c r="R112" t="n">
-        <v>7145360</v>
+        <v>7145605</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12875,14 +12882,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>På en levande gran.</t>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12891,51 +12903,25 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
-      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
-      </c>
-      <c r="AH112" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ112" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK112" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM112" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO112" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129726954</v>
+        <v>129726789</v>
       </c>
       <c r="B113" t="n">
         <v>79084</v>
@@ -12964,19 +12950,16 @@
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>483580</v>
+        <v>483663</v>
       </c>
       <c r="R113" t="n">
-        <v>7145435</v>
+        <v>7145420</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13006,14 +12989,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>På gran i granskog.</t>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13022,54 +13010,28 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
-      </c>
-      <c r="AH113" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ113" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK113" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM113" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO113" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129727939</v>
+        <v>129716454</v>
       </c>
       <c r="B114" t="n">
-        <v>57734</v>
+        <v>91598</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13077,34 +13039,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>483605</v>
+        <v>484017</v>
       </c>
       <c r="R114" t="n">
-        <v>7145281</v>
+        <v>7145437</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13139,11 +13101,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Hack ganska färska</t>
-        </is>
-      </c>
       <c r="AD114" t="b">
         <v>0</v>
       </c>
@@ -13156,19 +13113,19 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129726949</v>
+        <v>129726950</v>
       </c>
       <c r="B115" t="n">
         <v>79084</v>
@@ -13206,10 +13163,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>483735</v>
+        <v>483720</v>
       </c>
       <c r="R115" t="n">
-        <v>7145746</v>
+        <v>7145756</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13246,7 +13203,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13299,7 +13256,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129726792</v>
+        <v>129726959</v>
       </c>
       <c r="B116" t="n">
         <v>79084</v>
@@ -13328,13 +13285,16 @@
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>483571</v>
+        <v>483422</v>
       </c>
       <c r="R116" t="n">
         <v>7145360</v>
@@ -13367,19 +13327,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>10:58</t>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>På en levande gran.</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13388,28 +13343,54 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
+      </c>
+      <c r="AH116" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ116" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK116" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM116" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO116" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129726827</v>
+        <v>129726954</v>
       </c>
       <c r="B117" t="n">
-        <v>83055</v>
+        <v>79084</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13417,34 +13398,37 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>483988</v>
+        <v>483580</v>
       </c>
       <c r="R117" t="n">
-        <v>7145444</v>
+        <v>7145435</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13474,19 +13458,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>08:49</t>
-        </is>
-      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>08:49</t>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>På gran i granskog.</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13495,28 +13474,54 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
+      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
+      </c>
+      <c r="AH117" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK117" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM117" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO117" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129726817</v>
+        <v>129727939</v>
       </c>
       <c r="B118" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13524,34 +13529,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>483834</v>
+        <v>483605</v>
       </c>
       <c r="R118" t="n">
-        <v>7145605</v>
+        <v>7145281</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13581,19 +13586,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>09:15</t>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Hack ganska färska</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13608,12 +13608,12 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
@@ -15476,10 +15476,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129730293</v>
+        <v>129730262</v>
       </c>
       <c r="B138" t="n">
-        <v>83047</v>
+        <v>57737</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15487,21 +15487,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15511,10 +15511,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>483321</v>
+        <v>483284</v>
       </c>
       <c r="R138" t="n">
-        <v>7145559</v>
+        <v>7145578</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15547,6 +15547,11 @@
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15573,10 +15578,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129730250</v>
+        <v>129730293</v>
       </c>
       <c r="B139" t="n">
-        <v>78841</v>
+        <v>83047</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15584,21 +15589,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6446</v>
+        <v>308</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15608,10 +15613,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>483564</v>
+        <v>483321</v>
       </c>
       <c r="R139" t="n">
-        <v>7145430</v>
+        <v>7145559</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15670,10 +15675,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129730262</v>
+        <v>129730250</v>
       </c>
       <c r="B140" t="n">
-        <v>57737</v>
+        <v>78841</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15681,21 +15686,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15705,10 +15710,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>483284</v>
+        <v>483564</v>
       </c>
       <c r="R140" t="n">
-        <v>7145578</v>
+        <v>7145430</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15741,11 +15746,6 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD140" t="b">

--- a/artfynd/A 52753-2025 artfynd.xlsx
+++ b/artfynd/A 52753-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129726815</v>
       </c>
       <c r="B2" t="n">
-        <v>83047</v>
+        <v>83050</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129716450</v>
+        <v>129727928</v>
       </c>
       <c r="B3" t="n">
-        <v>79084</v>
+        <v>57740</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483823</v>
+        <v>483704</v>
       </c>
       <c r="R3" t="n">
-        <v>7145591</v>
+        <v>7145461</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,6 +855,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -867,22 +872,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129726952</v>
+        <v>129726936</v>
       </c>
       <c r="B4" t="n">
-        <v>79084</v>
+        <v>57740</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,37 +895,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483538</v>
+        <v>483746</v>
       </c>
       <c r="R4" t="n">
-        <v>7145695</v>
+        <v>7145582</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,7 +971,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, äldre, på stambasen av en levande gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -966,7 +980,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -987,12 +1000,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1013,7 +1026,7 @@
         <v>129726820</v>
       </c>
       <c r="B5" t="n">
-        <v>83060</v>
+        <v>83063</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,10 +1130,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129727928</v>
+        <v>129716450</v>
       </c>
       <c r="B6" t="n">
-        <v>57737</v>
+        <v>79087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1128,34 +1141,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483704</v>
+        <v>483823</v>
       </c>
       <c r="R6" t="n">
-        <v>7145461</v>
+        <v>7145591</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,11 +1203,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1207,22 +1215,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129726936</v>
+        <v>129726952</v>
       </c>
       <c r="B7" t="n">
-        <v>57737</v>
+        <v>79087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1230,46 +1238,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483746</v>
+        <v>483538</v>
       </c>
       <c r="R7" t="n">
-        <v>7145582</v>
+        <v>7145695</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1306,7 +1305,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en levande gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1315,6 +1314,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1361,7 +1361,7 @@
         <v>129726803</v>
       </c>
       <c r="B8" t="n">
-        <v>83047</v>
+        <v>83050</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>129716452</v>
       </c>
       <c r="B9" t="n">
-        <v>91622</v>
+        <v>91625</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1558,10 +1558,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129726955</v>
+        <v>129726805</v>
       </c>
       <c r="B10" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,19 +1587,16 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483580</v>
+        <v>483517</v>
       </c>
       <c r="R10" t="n">
-        <v>7145305</v>
+        <v>7145580</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,14 +1626,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På en levande gran.</t>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1645,54 +1647,28 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129726805</v>
+        <v>129726791</v>
       </c>
       <c r="B11" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1724,10 +1700,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483517</v>
+        <v>483607</v>
       </c>
       <c r="R11" t="n">
-        <v>7145580</v>
+        <v>7145404</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1759,7 +1735,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1769,7 +1745,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1796,10 +1772,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129726791</v>
+        <v>129726955</v>
       </c>
       <c r="B12" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,16 +1801,19 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483607</v>
+        <v>483580</v>
       </c>
       <c r="R12" t="n">
-        <v>7145404</v>
+        <v>7145305</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1864,19 +1843,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På en levande gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1885,18 +1859,44 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1906,7 +1906,7 @@
         <v>129716468</v>
       </c>
       <c r="B13" t="n">
-        <v>91622</v>
+        <v>91625</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>129726819</v>
       </c>
       <c r="B14" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129716455</v>
+        <v>129727923</v>
       </c>
       <c r="B15" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2132,21 +2132,16 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483975</v>
+        <v>483397</v>
       </c>
       <c r="R15" t="n">
-        <v>7145436</v>
+        <v>7145483</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2181,6 +2176,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2193,22 +2193,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129727923</v>
+        <v>129726935</v>
       </c>
       <c r="B16" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2234,16 +2234,28 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483397</v>
+        <v>483601</v>
       </c>
       <c r="R16" t="n">
-        <v>7145483</v>
+        <v>7145616</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2280,7 +2292,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, färska och äldre, på stambasen av en levande gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2291,26 +2303,51 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129726935</v>
+        <v>129727919</v>
       </c>
       <c r="B17" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2336,28 +2373,16 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483601</v>
+        <v>483535</v>
       </c>
       <c r="R17" t="n">
-        <v>7145616</v>
+        <v>7145332</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2394,7 +2419,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en levande gran i barrblandskog.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2405,51 +2430,26 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129727919</v>
+        <v>129727920</v>
       </c>
       <c r="B18" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2481,10 +2481,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483535</v>
+        <v>483452</v>
       </c>
       <c r="R18" t="n">
-        <v>7145332</v>
+        <v>7145362</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2548,10 +2548,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129727920</v>
+        <v>129716455</v>
       </c>
       <c r="B19" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2577,16 +2577,21 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483452</v>
+        <v>483975</v>
       </c>
       <c r="R19" t="n">
-        <v>7145362</v>
+        <v>7145436</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2621,11 +2626,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2638,12 +2638,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2653,7 +2653,7 @@
         <v>129726941</v>
       </c>
       <c r="B20" t="n">
-        <v>80190</v>
+        <v>80193</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>129726804</v>
       </c>
       <c r="B21" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2892,32 +2892,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129727934</v>
+        <v>129727915</v>
       </c>
       <c r="B22" t="n">
-        <v>57737</v>
+        <v>92323</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2927,10 +2927,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483619</v>
+        <v>483493</v>
       </c>
       <c r="R22" t="n">
-        <v>7145595</v>
+        <v>7145538</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2963,11 +2963,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2994,32 +2989,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129727915</v>
+        <v>129727934</v>
       </c>
       <c r="B23" t="n">
-        <v>92320</v>
+        <v>57740</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3029,10 +3024,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483493</v>
+        <v>483619</v>
       </c>
       <c r="R23" t="n">
-        <v>7145538</v>
+        <v>7145595</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3065,6 +3060,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3094,7 +3094,7 @@
         <v>129726825</v>
       </c>
       <c r="B24" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3198,10 +3198,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129726814</v>
+        <v>129726813</v>
       </c>
       <c r="B25" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3233,10 +3233,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>483796</v>
+        <v>483773</v>
       </c>
       <c r="R25" t="n">
-        <v>7145620</v>
+        <v>7145613</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3305,10 +3305,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129726813</v>
+        <v>129726814</v>
       </c>
       <c r="B26" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3340,10 +3340,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>483773</v>
+        <v>483796</v>
       </c>
       <c r="R26" t="n">
-        <v>7145613</v>
+        <v>7145620</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3375,7 +3375,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3415,7 +3415,7 @@
         <v>129726818</v>
       </c>
       <c r="B27" t="n">
-        <v>83055</v>
+        <v>83058</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3519,45 +3519,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129726816</v>
+        <v>129727921</v>
       </c>
       <c r="B28" t="n">
-        <v>75068</v>
+        <v>57740</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6428</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>483815</v>
+        <v>483464</v>
       </c>
       <c r="R28" t="n">
-        <v>7145615</v>
+        <v>7145542</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3587,19 +3587,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>09:18</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>09:18</t>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3614,22 +3609,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129727921</v>
+        <v>129726933</v>
       </c>
       <c r="B29" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3655,16 +3650,28 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>483464</v>
+        <v>483582</v>
       </c>
       <c r="R29" t="n">
-        <v>7145542</v>
+        <v>7145456</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3701,7 +3708,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3712,73 +3719,86 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129726933</v>
+        <v>129726816</v>
       </c>
       <c r="B30" t="n">
-        <v>57737</v>
+        <v>75071</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6428</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>483582</v>
+        <v>483815</v>
       </c>
       <c r="R30" t="n">
-        <v>7145456</v>
+        <v>7145615</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3808,14 +3828,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3826,51 +3851,26 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129726824</v>
+        <v>129727931</v>
       </c>
       <c r="B31" t="n">
-        <v>79084</v>
+        <v>57740</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3878,34 +3878,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>483981</v>
+        <v>483545</v>
       </c>
       <c r="R31" t="n">
-        <v>7145521</v>
+        <v>7145507</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3935,19 +3935,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>08:59</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>08:59</t>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3962,22 +3957,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129727931</v>
+        <v>129726938</v>
       </c>
       <c r="B32" t="n">
-        <v>57737</v>
+        <v>57898</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3985,34 +3980,54 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>483545</v>
+        <v>483739</v>
       </c>
       <c r="R32" t="n">
-        <v>7145507</v>
+        <v>7145743</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4049,7 +4064,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Synobservation av två talltitor med lockläte. Ev. rörde sig fler talltitor runt fyndplatsen som finns i flerskiktad äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4060,26 +4075,36 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Flerskiktad äldre barrblandskog.</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129726938</v>
+        <v>129716460</v>
       </c>
       <c r="B33" t="n">
-        <v>57895</v>
+        <v>79087</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4087,54 +4112,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>483739</v>
+        <v>483445</v>
       </c>
       <c r="R33" t="n">
-        <v>7145743</v>
+        <v>7145428</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4169,11 +4174,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Synobservation av två talltitor med lockläte. Ev. rörde sig fler talltitor runt fyndplatsen som finns i flerskiktad äldre barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4182,36 +4182,26 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>Flerskiktad äldre barrblandskog.</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129716460</v>
+        <v>129726961</v>
       </c>
       <c r="B34" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4237,16 +4227,19 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>483445</v>
+        <v>483414</v>
       </c>
       <c r="R34" t="n">
-        <v>7145428</v>
+        <v>7145535</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4281,34 +4274,65 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På en levande gran.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129726961</v>
+        <v>129726824</v>
       </c>
       <c r="B35" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4334,19 +4358,16 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>483414</v>
+        <v>483981</v>
       </c>
       <c r="R35" t="n">
-        <v>7145535</v>
+        <v>7145521</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4376,14 +4397,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>08:59</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På en levande gran.</t>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4392,44 +4418,18 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4439,7 +4439,7 @@
         <v>129726801</v>
       </c>
       <c r="B36" t="n">
-        <v>83060</v>
+        <v>83063</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>129716461</v>
       </c>
       <c r="B37" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4640,10 +4640,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129716466</v>
+        <v>129726807</v>
       </c>
       <c r="B38" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4671,14 +4671,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>483481</v>
+        <v>483589</v>
       </c>
       <c r="R38" t="n">
-        <v>7145592</v>
+        <v>7145582</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4708,9 +4708,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4725,22 +4735,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129726807</v>
+        <v>129716466</v>
       </c>
       <c r="B39" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4768,14 +4778,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>483589</v>
+        <v>483481</v>
       </c>
       <c r="R39" t="n">
-        <v>7145582</v>
+        <v>7145592</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4805,19 +4815,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>09:50</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4832,12 +4832,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4847,7 +4847,7 @@
         <v>129727927</v>
       </c>
       <c r="B40" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4946,10 +4946,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129716464</v>
+        <v>129726946</v>
       </c>
       <c r="B41" t="n">
-        <v>92320</v>
+        <v>80220</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4957,34 +4957,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3298</v>
+        <v>6461</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>484017</v>
+        <v>483607</v>
       </c>
       <c r="R41" t="n">
-        <v>7145437</v>
+        <v>7145621</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5025,28 +5028,29 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129726810</v>
+        <v>129726948</v>
       </c>
       <c r="B42" t="n">
-        <v>57737</v>
+        <v>91625</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5054,48 +5058,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>483760</v>
+        <v>483501</v>
       </c>
       <c r="R42" t="n">
-        <v>7145583</v>
+        <v>7145621</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5125,19 +5118,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>09:41</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>09:41</t>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar i en levande gran.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5146,63 +5134,89 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129727936</v>
+        <v>129716464</v>
       </c>
       <c r="B43" t="n">
-        <v>57737</v>
+        <v>92323</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>483750</v>
+        <v>484017</v>
       </c>
       <c r="R43" t="n">
-        <v>7145579</v>
+        <v>7145437</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5237,11 +5251,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5254,22 +5263,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129727938</v>
+        <v>129726821</v>
       </c>
       <c r="B44" t="n">
-        <v>57737</v>
+        <v>79087</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5277,34 +5286,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>483975</v>
+        <v>483922</v>
       </c>
       <c r="R44" t="n">
-        <v>7145511</v>
+        <v>7145570</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5334,14 +5343,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5356,22 +5370,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129726821</v>
+        <v>129726960</v>
       </c>
       <c r="B45" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5397,16 +5411,19 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>483922</v>
+        <v>483376</v>
       </c>
       <c r="R45" t="n">
-        <v>7145570</v>
+        <v>7145540</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5436,19 +5453,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>09:05</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>09:05</t>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På en levande gran.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5457,28 +5469,54 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129726948</v>
+        <v>129726810</v>
       </c>
       <c r="B46" t="n">
-        <v>91622</v>
+        <v>57740</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5486,37 +5524,48 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>483501</v>
+        <v>483760</v>
       </c>
       <c r="R46" t="n">
-        <v>7145621</v>
+        <v>7145583</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5546,14 +5595,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar i en levande gran.</t>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5562,92 +5616,63 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129726946</v>
+        <v>129727936</v>
       </c>
       <c r="B47" t="n">
-        <v>80217</v>
+        <v>57740</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>483607</v>
+        <v>483750</v>
       </c>
       <c r="R47" t="n">
-        <v>7145621</v>
+        <v>7145579</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5682,35 +5707,39 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129726960</v>
+        <v>129727938</v>
       </c>
       <c r="B48" t="n">
-        <v>79084</v>
+        <v>57740</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5718,37 +5747,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>483376</v>
+        <v>483975</v>
       </c>
       <c r="R48" t="n">
-        <v>7145540</v>
+        <v>7145511</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5785,7 +5811,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På en levande gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5794,54 +5820,28 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129716462</v>
+        <v>129726800</v>
       </c>
       <c r="B49" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5869,14 +5869,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>483666</v>
+        <v>483439</v>
       </c>
       <c r="R49" t="n">
-        <v>7145612</v>
+        <v>7145513</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5906,9 +5906,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5923,22 +5933,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129726800</v>
+        <v>129716462</v>
       </c>
       <c r="B50" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5966,14 +5976,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>483439</v>
+        <v>483666</v>
       </c>
       <c r="R50" t="n">
-        <v>7145513</v>
+        <v>7145612</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6003,19 +6013,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>10:13</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6030,12 +6030,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -6045,7 +6045,7 @@
         <v>129727935</v>
       </c>
       <c r="B51" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
         <v>129727914</v>
       </c>
       <c r="B52" t="n">
-        <v>92320</v>
+        <v>92323</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6241,48 +6241,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129726944</v>
+        <v>129727922</v>
       </c>
       <c r="B53" t="n">
-        <v>80217</v>
+        <v>57740</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>483597</v>
+        <v>483507</v>
       </c>
       <c r="R53" t="n">
-        <v>7145735</v>
+        <v>7145556</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6317,35 +6314,39 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129716458</v>
+        <v>129727924</v>
       </c>
       <c r="B54" t="n">
-        <v>83055</v>
+        <v>57740</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6353,34 +6354,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>483701</v>
+        <v>483548</v>
       </c>
       <c r="R54" t="n">
-        <v>7145588</v>
+        <v>7145488</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6415,6 +6416,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6427,57 +6433,60 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129726811</v>
+        <v>129726944</v>
       </c>
       <c r="B55" t="n">
-        <v>79084</v>
+        <v>80220</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>483760</v>
+        <v>483597</v>
       </c>
       <c r="R55" t="n">
-        <v>7145575</v>
+        <v>7145735</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6507,49 +6516,40 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>09:35</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>09:35</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129727922</v>
+        <v>129716458</v>
       </c>
       <c r="B56" t="n">
-        <v>57737</v>
+        <v>83058</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6557,34 +6557,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>483507</v>
+        <v>483701</v>
       </c>
       <c r="R56" t="n">
-        <v>7145556</v>
+        <v>7145588</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6619,11 +6619,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -6636,22 +6631,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129727924</v>
+        <v>129726811</v>
       </c>
       <c r="B57" t="n">
-        <v>57737</v>
+        <v>79087</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6659,34 +6654,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>483548</v>
+        <v>483760</v>
       </c>
       <c r="R57" t="n">
-        <v>7145488</v>
+        <v>7145575</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6716,14 +6711,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6738,22 +6738,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129716453</v>
+        <v>129726828</v>
       </c>
       <c r="B58" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6781,14 +6781,14 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>484032</v>
+        <v>483988</v>
       </c>
       <c r="R58" t="n">
-        <v>7145416</v>
+        <v>7145444</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6818,9 +6818,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6835,22 +6845,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129726953</v>
+        <v>129716453</v>
       </c>
       <c r="B59" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6876,19 +6886,16 @@
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>483555</v>
+        <v>484032</v>
       </c>
       <c r="R59" t="n">
-        <v>7145531</v>
+        <v>7145416</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6923,65 +6930,34 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129726788</v>
+        <v>129726953</v>
       </c>
       <c r="B60" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7007,16 +6983,19 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>483665</v>
+        <v>483555</v>
       </c>
       <c r="R60" t="n">
-        <v>7145479</v>
+        <v>7145531</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7046,19 +7025,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>11:18</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>11:18</t>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7067,28 +7041,54 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129726828</v>
+        <v>129716449</v>
       </c>
       <c r="B61" t="n">
-        <v>79084</v>
+        <v>83058</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7096,34 +7096,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>483988</v>
+        <v>483889</v>
       </c>
       <c r="R61" t="n">
-        <v>7145444</v>
+        <v>7145589</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7153,19 +7153,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>08:48</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>08:48</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7180,22 +7170,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129716449</v>
+        <v>129726806</v>
       </c>
       <c r="B62" t="n">
-        <v>83055</v>
+        <v>79087</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7203,34 +7193,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>483889</v>
+        <v>483558</v>
       </c>
       <c r="R62" t="n">
-        <v>7145589</v>
+        <v>7145588</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7260,9 +7250,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7277,22 +7277,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129726806</v>
+        <v>129726788</v>
       </c>
       <c r="B63" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7324,10 +7324,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>483558</v>
+        <v>483665</v>
       </c>
       <c r="R63" t="n">
-        <v>7145588</v>
+        <v>7145479</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7359,7 +7359,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7369,7 +7369,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7399,7 +7399,7 @@
         <v>129727929</v>
       </c>
       <c r="B64" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7501,7 +7501,7 @@
         <v>129727932</v>
       </c>
       <c r="B65" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7603,7 +7603,7 @@
         <v>129727930</v>
       </c>
       <c r="B66" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7702,10 +7702,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129726958</v>
+        <v>129716448</v>
       </c>
       <c r="B67" t="n">
-        <v>79084</v>
+        <v>91556</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7713,37 +7713,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>483482</v>
+        <v>483443</v>
       </c>
       <c r="R67" t="n">
-        <v>7145330</v>
+        <v>7145540</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7778,65 +7775,34 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>På en levande gran.</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129726966</v>
+        <v>129726958</v>
       </c>
       <c r="B68" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7871,10 +7837,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>483764</v>
+        <v>483482</v>
       </c>
       <c r="R68" t="n">
-        <v>7145582</v>
+        <v>7145330</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7911,7 +7877,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en levande gran.</t>
+          <t>På en levande gran.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7964,10 +7930,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129716448</v>
+        <v>129726966</v>
       </c>
       <c r="B69" t="n">
-        <v>91553</v>
+        <v>79087</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7975,34 +7941,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>483443</v>
+        <v>483764</v>
       </c>
       <c r="R69" t="n">
-        <v>7145540</v>
+        <v>7145582</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8037,24 +8006,55 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på en levande gran.</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -8064,7 +8064,7 @@
         <v>129726797</v>
       </c>
       <c r="B70" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8171,7 +8171,7 @@
         <v>129726937</v>
       </c>
       <c r="B71" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         <v>129727916</v>
       </c>
       <c r="B72" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8412,7 +8412,7 @@
         <v>129727918</v>
       </c>
       <c r="B73" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8511,10 +8511,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129726947</v>
+        <v>129726787</v>
       </c>
       <c r="B74" t="n">
-        <v>91598</v>
+        <v>78100</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8522,41 +8522,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1108</v>
+        <v>228579</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>483784</v>
+        <v>483914</v>
       </c>
       <c r="R74" t="n">
-        <v>7145639</v>
+        <v>7145602</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8586,14 +8579,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>I levande gran i granskog vid brant.</t>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8602,54 +8600,28 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AH74" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129726964</v>
+        <v>129726826</v>
       </c>
       <c r="B75" t="n">
-        <v>79084</v>
+        <v>78100</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8657,37 +8629,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>483553</v>
+        <v>483988</v>
       </c>
       <c r="R75" t="n">
-        <v>7145611</v>
+        <v>7145444</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8717,14 +8686,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>På levande gran i barrblandskog.</t>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8733,54 +8707,28 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
-      </c>
-      <c r="AH75" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129726787</v>
+        <v>129726947</v>
       </c>
       <c r="B76" t="n">
-        <v>78097</v>
+        <v>91601</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8788,34 +8736,41 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>228579</v>
+        <v>1108</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>483914</v>
+        <v>483784</v>
       </c>
       <c r="R76" t="n">
-        <v>7145602</v>
+        <v>7145639</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8845,19 +8800,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>11:26</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>11:26</t>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>I levande gran i granskog vid brant.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8866,28 +8816,54 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM76" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129726826</v>
+        <v>129726964</v>
       </c>
       <c r="B77" t="n">
-        <v>78097</v>
+        <v>79087</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8895,34 +8871,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>483988</v>
+        <v>483553</v>
       </c>
       <c r="R77" t="n">
-        <v>7145444</v>
+        <v>7145611</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8952,19 +8931,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>08:49</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>08:49</t>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>På levande gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8973,28 +8947,54 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129726793</v>
+        <v>129727942</v>
       </c>
       <c r="B78" t="n">
-        <v>57895</v>
+        <v>91625</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9002,46 +9002,33 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>483572</v>
+        <v>483495</v>
       </c>
       <c r="R78" t="n">
-        <v>7145322</v>
+        <v>7145618</v>
       </c>
       <c r="S78" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9068,19 +9055,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>10:55</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9095,22 +9072,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129727941</v>
+        <v>129726795</v>
       </c>
       <c r="B79" t="n">
-        <v>91598</v>
+        <v>83063</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9118,34 +9095,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1108</v>
+        <v>1467</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>483551</v>
+        <v>483545</v>
       </c>
       <c r="R79" t="n">
-        <v>7145323</v>
+        <v>7145343</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9175,9 +9152,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9192,12 +9179,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -9207,7 +9194,7 @@
         <v>129716465</v>
       </c>
       <c r="B80" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9301,10 +9288,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129726795</v>
+        <v>129727941</v>
       </c>
       <c r="B81" t="n">
-        <v>83060</v>
+        <v>91601</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9312,34 +9299,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1467</v>
+        <v>1108</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>483545</v>
+        <v>483551</v>
       </c>
       <c r="R81" t="n">
-        <v>7145343</v>
+        <v>7145323</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9369,19 +9356,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>10:35</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>10:35</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9396,57 +9373,57 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129716451</v>
+        <v>129726796</v>
       </c>
       <c r="B82" t="n">
-        <v>79084</v>
+        <v>83056</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>6486</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>483989</v>
+        <v>483545</v>
       </c>
       <c r="R82" t="n">
-        <v>7145511</v>
+        <v>7145343</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9476,9 +9453,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9493,22 +9480,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129726798</v>
+        <v>129727940</v>
       </c>
       <c r="B83" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9516,34 +9503,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>483429</v>
+        <v>483677</v>
       </c>
       <c r="R83" t="n">
-        <v>7145430</v>
+        <v>7145478</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9573,19 +9560,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>10:16</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>10:16</t>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Hack ganska färska</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9600,22 +9582,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129727942</v>
+        <v>129726831</v>
       </c>
       <c r="B84" t="n">
-        <v>91622</v>
+        <v>83058</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9623,30 +9605,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr"/>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>483495</v>
+        <v>484008</v>
       </c>
       <c r="R84" t="n">
-        <v>7145618</v>
+        <v>7145455</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9676,9 +9662,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>08:42</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9693,22 +9689,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129726831</v>
+        <v>129726963</v>
       </c>
       <c r="B85" t="n">
-        <v>83055</v>
+        <v>79087</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9716,34 +9712,37 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>484008</v>
+        <v>483498</v>
       </c>
       <c r="R85" t="n">
-        <v>7145455</v>
+        <v>7145585</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9773,19 +9772,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>08:42</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>08:42</t>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>På levande gran.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9794,50 +9788,76 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM85" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129726796</v>
+        <v>129726812</v>
       </c>
       <c r="B86" t="n">
-        <v>83053</v>
+        <v>79087</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6486</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9847,10 +9867,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>483545</v>
+        <v>483764</v>
       </c>
       <c r="R86" t="n">
-        <v>7145343</v>
+        <v>7145589</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9882,7 +9902,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9892,7 +9912,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9919,10 +9939,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129726963</v>
+        <v>129726823</v>
       </c>
       <c r="B87" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9948,19 +9968,16 @@
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>483498</v>
+        <v>483959</v>
       </c>
       <c r="R87" t="n">
-        <v>7145585</v>
+        <v>7145539</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9990,14 +10007,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>På levande gran.</t>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10006,54 +10028,28 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
-      </c>
-      <c r="AH87" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ87" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK87" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO87" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129726812</v>
+        <v>129716451</v>
       </c>
       <c r="B88" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10081,14 +10077,14 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>483764</v>
+        <v>483989</v>
       </c>
       <c r="R88" t="n">
-        <v>7145589</v>
+        <v>7145511</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10118,19 +10114,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>09:34</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>09:34</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10145,22 +10131,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129726823</v>
+        <v>129726798</v>
       </c>
       <c r="B89" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10192,10 +10178,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>483959</v>
+        <v>483429</v>
       </c>
       <c r="R89" t="n">
-        <v>7145539</v>
+        <v>7145430</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10227,7 +10213,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10237,7 +10223,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10264,10 +10250,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129727940</v>
+        <v>129726793</v>
       </c>
       <c r="B90" t="n">
-        <v>57734</v>
+        <v>57898</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10275,37 +10261,46 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>483677</v>
+        <v>483572</v>
       </c>
       <c r="R90" t="n">
-        <v>7145478</v>
+        <v>7145322</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10332,14 +10327,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Hack ganska färska</t>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10354,12 +10354,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
@@ -10369,7 +10369,7 @@
         <v>129726832</v>
       </c>
       <c r="B91" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10473,48 +10473,45 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129726945</v>
+        <v>129726799</v>
       </c>
       <c r="B92" t="n">
-        <v>80217</v>
+        <v>79087</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>483364</v>
+        <v>483426</v>
       </c>
       <c r="R92" t="n">
-        <v>7145533</v>
+        <v>7145464</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10544,75 +10541,87 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129726799</v>
+        <v>129726945</v>
       </c>
       <c r="B93" t="n">
-        <v>79084</v>
+        <v>80220</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>483426</v>
+        <v>483364</v>
       </c>
       <c r="R93" t="n">
-        <v>7145464</v>
+        <v>7145533</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10642,49 +10651,40 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129716457</v>
+        <v>129726967</v>
       </c>
       <c r="B94" t="n">
-        <v>91622</v>
+        <v>79087</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10692,30 +10692,37 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>483922</v>
+        <v>483745</v>
       </c>
       <c r="R94" t="n">
-        <v>7145565</v>
+        <v>7145588</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10750,34 +10757,65 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>På en levande gran i granskog.</t>
+        </is>
+      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
+      </c>
+      <c r="AH94" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ94" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK94" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM94" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129726940</v>
+        <v>129726951</v>
       </c>
       <c r="B95" t="n">
-        <v>57734</v>
+        <v>79087</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10785,31 +10823,26 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -10817,10 +10850,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>483382</v>
+        <v>483599</v>
       </c>
       <c r="R95" t="n">
-        <v>7145460</v>
+        <v>7145738</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10857,7 +10890,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Äldre och färska hackspår i en grov stående död gran av full längd.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10866,6 +10899,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10886,12 +10920,12 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -10909,10 +10943,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129726942</v>
+        <v>129726965</v>
       </c>
       <c r="B96" t="n">
-        <v>80190</v>
+        <v>79087</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10920,30 +10954,26 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K96" t="inlineStr"/>
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
@@ -10951,10 +10981,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>483377</v>
+        <v>483794</v>
       </c>
       <c r="R96" t="n">
-        <v>7145537</v>
+        <v>7145597</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10991,7 +11021,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>På en levande sälg i granskog.</t>
+          <t>På levande granar i granskog.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11011,22 +11041,22 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM96" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -11044,10 +11074,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129716456</v>
+        <v>129716457</v>
       </c>
       <c r="B97" t="n">
-        <v>82921</v>
+        <v>91625</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11055,23 +11085,19 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
@@ -11079,10 +11105,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>483445</v>
+        <v>483922</v>
       </c>
       <c r="R97" t="n">
-        <v>7145393</v>
+        <v>7145565</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11141,10 +11167,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129726951</v>
+        <v>129726942</v>
       </c>
       <c r="B98" t="n">
-        <v>79084</v>
+        <v>80193</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11152,26 +11178,30 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
@@ -11179,10 +11209,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>483599</v>
+        <v>483377</v>
       </c>
       <c r="R98" t="n">
-        <v>7145738</v>
+        <v>7145537</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11219,7 +11249,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På en levande sälg i granskog.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11234,27 +11264,27 @@
       </c>
       <c r="AH98" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM98" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -11272,10 +11302,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129726965</v>
+        <v>129716456</v>
       </c>
       <c r="B99" t="n">
-        <v>79084</v>
+        <v>82924</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11283,37 +11313,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>483794</v>
+        <v>483445</v>
       </c>
       <c r="R99" t="n">
-        <v>7145597</v>
+        <v>7145393</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11348,65 +11375,34 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>På levande granar i granskog.</t>
-        </is>
-      </c>
       <c r="AD99" t="b">
         <v>0</v>
       </c>
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
-      </c>
-      <c r="AH99" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ99" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK99" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM99" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO99" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129726967</v>
+        <v>129726940</v>
       </c>
       <c r="B100" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11414,26 +11410,31 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
@@ -11441,10 +11442,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>483745</v>
+        <v>483382</v>
       </c>
       <c r="R100" t="n">
-        <v>7145588</v>
+        <v>7145460</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11481,7 +11482,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>På en levande gran i granskog.</t>
+          <t>Äldre och färska hackspår i en grov stående död gran av full längd.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11490,13 +11491,12 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ100" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="AM100" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -11537,7 +11537,7 @@
         <v>129726962</v>
       </c>
       <c r="B101" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11665,10 +11665,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129716467</v>
+        <v>129726956</v>
       </c>
       <c r="B102" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11694,16 +11694,19 @@
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>483805</v>
+        <v>483519</v>
       </c>
       <c r="R102" t="n">
-        <v>7145587</v>
+        <v>7145306</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11738,34 +11741,60 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD102" t="b">
         <v>0</v>
       </c>
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
+      </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129726956</v>
+        <v>129716467</v>
       </c>
       <c r="B103" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11791,19 +11820,16 @@
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>483519</v>
+        <v>483805</v>
       </c>
       <c r="R103" t="n">
-        <v>7145306</v>
+        <v>7145587</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11838,50 +11864,24 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD103" t="b">
         <v>0</v>
       </c>
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
-      </c>
-      <c r="AH103" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ103" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK103" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO103" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
@@ -11891,7 +11891,7 @@
         <v>129726934</v>
       </c>
       <c r="B104" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12027,10 +12027,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129727937</v>
+        <v>129726957</v>
       </c>
       <c r="B105" t="n">
-        <v>57737</v>
+        <v>79087</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12038,34 +12038,37 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>483824</v>
+        <v>483497</v>
       </c>
       <c r="R105" t="n">
-        <v>7145592</v>
+        <v>7145327</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12102,7 +12105,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12111,28 +12114,54 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
+      </c>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM105" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129727933</v>
+        <v>129727937</v>
       </c>
       <c r="B106" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12164,10 +12193,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>483593</v>
+        <v>483824</v>
       </c>
       <c r="R106" t="n">
-        <v>7145594</v>
+        <v>7145592</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12204,7 +12233,7 @@
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12231,10 +12260,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129726830</v>
+        <v>129727933</v>
       </c>
       <c r="B107" t="n">
-        <v>78097</v>
+        <v>57740</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12242,34 +12271,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>484008</v>
+        <v>483593</v>
       </c>
       <c r="R107" t="n">
-        <v>7145455</v>
+        <v>7145594</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12299,19 +12328,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>08:43</t>
-        </is>
-      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>08:43</t>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12326,22 +12350,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129726957</v>
+        <v>129726830</v>
       </c>
       <c r="B108" t="n">
-        <v>79084</v>
+        <v>78100</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12349,37 +12373,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>483497</v>
+        <v>484008</v>
       </c>
       <c r="R108" t="n">
-        <v>7145327</v>
+        <v>7145455</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12409,14 +12430,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>08:43</t>
+        </is>
+      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12425,54 +12451,28 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
-      </c>
-      <c r="AH108" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ108" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK108" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM108" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO108" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129726949</v>
+        <v>129716454</v>
       </c>
       <c r="B109" t="n">
-        <v>79084</v>
+        <v>91601</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12480,37 +12480,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>483735</v>
+        <v>484017</v>
       </c>
       <c r="R109" t="n">
-        <v>7145746</v>
+        <v>7145437</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12545,65 +12542,34 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
-      </c>
-      <c r="AH109" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ109" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK109" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM109" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO109" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129726792</v>
+        <v>129726949</v>
       </c>
       <c r="B110" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12629,16 +12595,19 @@
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>483571</v>
+        <v>483735</v>
       </c>
       <c r="R110" t="n">
-        <v>7145360</v>
+        <v>7145746</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12668,19 +12637,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>10:58</t>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12689,28 +12653,54 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
+      </c>
+      <c r="AH110" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM110" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129726827</v>
+        <v>129726792</v>
       </c>
       <c r="B111" t="n">
-        <v>83055</v>
+        <v>79087</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12718,21 +12708,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12742,10 +12732,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>483988</v>
+        <v>483571</v>
       </c>
       <c r="R111" t="n">
-        <v>7145444</v>
+        <v>7145360</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12777,7 +12767,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12787,7 +12777,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12814,10 +12804,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129726817</v>
+        <v>129726827</v>
       </c>
       <c r="B112" t="n">
-        <v>79084</v>
+        <v>83058</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12825,21 +12815,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12849,10 +12839,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>483834</v>
+        <v>483988</v>
       </c>
       <c r="R112" t="n">
-        <v>7145605</v>
+        <v>7145444</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12884,7 +12874,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12894,7 +12884,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12924,7 +12914,7 @@
         <v>129726789</v>
       </c>
       <c r="B113" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13028,10 +13018,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129716454</v>
+        <v>129726950</v>
       </c>
       <c r="B114" t="n">
-        <v>91598</v>
+        <v>79087</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13039,34 +13029,37 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>484017</v>
+        <v>483720</v>
       </c>
       <c r="R114" t="n">
-        <v>7145437</v>
+        <v>7145756</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13101,34 +13094,65 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD114" t="b">
         <v>0</v>
       </c>
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
+      </c>
+      <c r="AH114" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ114" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK114" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM114" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO114" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129726950</v>
+        <v>129726959</v>
       </c>
       <c r="B115" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13163,10 +13187,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>483720</v>
+        <v>483422</v>
       </c>
       <c r="R115" t="n">
-        <v>7145756</v>
+        <v>7145360</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13203,7 +13227,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På en levande gran.</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13256,10 +13280,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129726959</v>
+        <v>129726817</v>
       </c>
       <c r="B116" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13285,19 +13309,16 @@
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>483422</v>
+        <v>483834</v>
       </c>
       <c r="R116" t="n">
-        <v>7145360</v>
+        <v>7145605</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13327,14 +13348,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>På en levande gran.</t>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13343,44 +13369,18 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
-      </c>
-      <c r="AH116" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ116" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK116" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM116" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO116" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
@@ -13390,7 +13390,7 @@
         <v>129726954</v>
       </c>
       <c r="B117" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13521,7 +13521,7 @@
         <v>129727939</v>
       </c>
       <c r="B118" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13623,7 +13623,7 @@
         <v>129727925</v>
       </c>
       <c r="B119" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13725,7 +13725,7 @@
         <v>129727917</v>
       </c>
       <c r="B120" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13827,7 +13827,7 @@
         <v>129730288</v>
       </c>
       <c r="B121" t="n">
-        <v>91622</v>
+        <v>91625</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13920,7 +13920,7 @@
         <v>129730246</v>
       </c>
       <c r="B122" t="n">
-        <v>80190</v>
+        <v>80193</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14017,7 +14017,7 @@
         <v>129730292</v>
       </c>
       <c r="B123" t="n">
-        <v>83047</v>
+        <v>83050</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14114,7 +14114,7 @@
         <v>129730241</v>
       </c>
       <c r="B124" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14213,10 +14213,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129730291</v>
+        <v>129730253</v>
       </c>
       <c r="B125" t="n">
-        <v>79084</v>
+        <v>78844</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14224,21 +14224,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14248,10 +14248,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>483364</v>
+        <v>483421</v>
       </c>
       <c r="R125" t="n">
-        <v>7145506</v>
+        <v>7145545</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14310,10 +14310,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129730253</v>
+        <v>129730291</v>
       </c>
       <c r="B126" t="n">
-        <v>78841</v>
+        <v>79087</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14321,21 +14321,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14345,10 +14345,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>483421</v>
+        <v>483364</v>
       </c>
       <c r="R126" t="n">
-        <v>7145545</v>
+        <v>7145506</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14410,7 +14410,7 @@
         <v>129730268</v>
       </c>
       <c r="B127" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14509,10 +14509,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129730244</v>
+        <v>129730274</v>
       </c>
       <c r="B128" t="n">
-        <v>80190</v>
+        <v>57740</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14520,21 +14520,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14544,10 +14544,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>483599</v>
+        <v>483612</v>
       </c>
       <c r="R128" t="n">
-        <v>7145190</v>
+        <v>7145596</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14580,6 +14580,11 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14606,10 +14611,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129730248</v>
+        <v>129730290</v>
       </c>
       <c r="B129" t="n">
-        <v>80189</v>
+        <v>91625</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14617,23 +14622,19 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
@@ -14641,10 +14642,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>483599</v>
+        <v>483766</v>
       </c>
       <c r="R129" t="n">
-        <v>7145185</v>
+        <v>7145610</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14703,10 +14704,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129730247</v>
+        <v>129730244</v>
       </c>
       <c r="B130" t="n">
-        <v>80189</v>
+        <v>80193</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14714,21 +14715,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14738,10 +14739,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>483595</v>
+        <v>483599</v>
       </c>
       <c r="R130" t="n">
-        <v>7145180</v>
+        <v>7145190</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14800,10 +14801,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129730274</v>
+        <v>129730248</v>
       </c>
       <c r="B131" t="n">
-        <v>57737</v>
+        <v>80192</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14811,21 +14812,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14835,10 +14836,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>483612</v>
+        <v>483599</v>
       </c>
       <c r="R131" t="n">
-        <v>7145596</v>
+        <v>7145185</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14871,11 +14872,6 @@
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14902,10 +14898,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129730290</v>
+        <v>129730247</v>
       </c>
       <c r="B132" t="n">
-        <v>91622</v>
+        <v>80192</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14913,19 +14909,23 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
@@ -14933,10 +14933,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>483766</v>
+        <v>483595</v>
       </c>
       <c r="R132" t="n">
-        <v>7145610</v>
+        <v>7145180</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14998,7 +14998,7 @@
         <v>129730255</v>
       </c>
       <c r="B133" t="n">
-        <v>91622</v>
+        <v>91625</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15088,10 +15088,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129730252</v>
+        <v>129730287</v>
       </c>
       <c r="B134" t="n">
-        <v>78841</v>
+        <v>91601</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15099,21 +15099,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6446</v>
+        <v>1108</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -15123,10 +15123,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>483407</v>
+        <v>483608</v>
       </c>
       <c r="R134" t="n">
-        <v>7145540</v>
+        <v>7145490</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15185,10 +15185,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129730242</v>
+        <v>129730252</v>
       </c>
       <c r="B135" t="n">
-        <v>79674</v>
+        <v>78844</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15196,21 +15196,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15220,10 +15220,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>483421</v>
+        <v>483407</v>
       </c>
       <c r="R135" t="n">
-        <v>7145545</v>
+        <v>7145540</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15282,10 +15282,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129730287</v>
+        <v>129730242</v>
       </c>
       <c r="B136" t="n">
-        <v>91598</v>
+        <v>79677</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15293,21 +15293,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1108</v>
+        <v>229821</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15317,10 +15317,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>483608</v>
+        <v>483421</v>
       </c>
       <c r="R136" t="n">
-        <v>7145490</v>
+        <v>7145545</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15382,7 +15382,7 @@
         <v>129730284</v>
       </c>
       <c r="B137" t="n">
-        <v>78097</v>
+        <v>78100</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15476,10 +15476,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129730262</v>
+        <v>129730250</v>
       </c>
       <c r="B138" t="n">
-        <v>57737</v>
+        <v>78844</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15487,21 +15487,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15511,10 +15511,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>483284</v>
+        <v>483564</v>
       </c>
       <c r="R138" t="n">
-        <v>7145578</v>
+        <v>7145430</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15547,11 +15547,6 @@
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15581,7 +15576,7 @@
         <v>129730293</v>
       </c>
       <c r="B139" t="n">
-        <v>83047</v>
+        <v>83050</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15675,10 +15670,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129730250</v>
+        <v>129730262</v>
       </c>
       <c r="B140" t="n">
-        <v>78841</v>
+        <v>57740</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15686,21 +15681,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15710,10 +15705,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>483564</v>
+        <v>483284</v>
       </c>
       <c r="R140" t="n">
-        <v>7145430</v>
+        <v>7145578</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15746,6 +15741,11 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15772,10 +15772,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129730249</v>
+        <v>129730254</v>
       </c>
       <c r="B141" t="n">
-        <v>80189</v>
+        <v>78844</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15783,21 +15783,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15807,10 +15807,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>483253</v>
+        <v>483454</v>
       </c>
       <c r="R141" t="n">
-        <v>7145561</v>
+        <v>7145556</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15869,32 +15869,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129730281</v>
+        <v>129730249</v>
       </c>
       <c r="B142" t="n">
-        <v>80093</v>
+        <v>80192</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15904,10 +15904,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>483572</v>
+        <v>483253</v>
       </c>
       <c r="R142" t="n">
-        <v>7145441</v>
+        <v>7145561</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15966,32 +15966,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129730254</v>
+        <v>129730281</v>
       </c>
       <c r="B143" t="n">
-        <v>78841</v>
+        <v>80096</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6446</v>
+        <v>6456</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -16001,10 +16001,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>483454</v>
+        <v>483572</v>
       </c>
       <c r="R143" t="n">
-        <v>7145556</v>
+        <v>7145441</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16066,7 +16066,7 @@
         <v>129730285</v>
       </c>
       <c r="B144" t="n">
-        <v>83063</v>
+        <v>83066</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16160,10 +16160,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129730289</v>
+        <v>129730261</v>
       </c>
       <c r="B145" t="n">
-        <v>91622</v>
+        <v>79087</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16171,19 +16171,23 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
@@ -16191,10 +16195,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>483238</v>
+        <v>483247</v>
       </c>
       <c r="R145" t="n">
-        <v>7145599</v>
+        <v>7145585</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16253,10 +16257,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129730261</v>
+        <v>129730289</v>
       </c>
       <c r="B146" t="n">
-        <v>79084</v>
+        <v>91625</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16264,23 +16268,19 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr"/>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
@@ -16288,10 +16288,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>483247</v>
+        <v>483238</v>
       </c>
       <c r="R146" t="n">
-        <v>7145585</v>
+        <v>7145599</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16353,7 +16353,7 @@
         <v>129730294</v>
       </c>
       <c r="B147" t="n">
-        <v>83047</v>
+        <v>83050</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16450,7 +16450,7 @@
         <v>129730240</v>
       </c>
       <c r="B148" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16552,7 +16552,7 @@
         <v>129730295</v>
       </c>
       <c r="B149" t="n">
-        <v>83047</v>
+        <v>83050</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16649,7 +16649,7 @@
         <v>129730260</v>
       </c>
       <c r="B150" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16746,7 +16746,7 @@
         <v>129730296</v>
       </c>
       <c r="B151" t="n">
-        <v>83047</v>
+        <v>83050</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16843,7 +16843,7 @@
         <v>129730282</v>
       </c>
       <c r="B152" t="n">
-        <v>80093</v>
+        <v>80096</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16937,10 +16937,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129730267</v>
+        <v>129730269</v>
       </c>
       <c r="B153" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16972,10 +16972,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>483426</v>
+        <v>483364</v>
       </c>
       <c r="R153" t="n">
-        <v>7145362</v>
+        <v>7145545</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17039,27 +17039,27 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129730269</v>
+        <v>129730286</v>
       </c>
       <c r="B154" t="n">
-        <v>57737</v>
+        <v>57844</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -17074,10 +17074,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>483364</v>
+        <v>483251</v>
       </c>
       <c r="R154" t="n">
-        <v>7145545</v>
+        <v>7145567</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17110,11 +17110,6 @@
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC154" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17141,27 +17136,27 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129730286</v>
+        <v>129730267</v>
       </c>
       <c r="B155" t="n">
-        <v>57841</v>
+        <v>57740</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -17176,10 +17171,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>483251</v>
+        <v>483426</v>
       </c>
       <c r="R155" t="n">
-        <v>7145567</v>
+        <v>7145362</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17212,6 +17207,11 @@
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17241,7 +17241,7 @@
         <v>129730258</v>
       </c>
       <c r="B156" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17338,7 +17338,7 @@
         <v>129730257</v>
       </c>
       <c r="B157" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17432,10 +17432,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129730264</v>
+        <v>129730265</v>
       </c>
       <c r="B158" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17467,10 +17467,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>483665</v>
+        <v>483564</v>
       </c>
       <c r="R158" t="n">
-        <v>7145576</v>
+        <v>7145344</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17534,10 +17534,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129730276</v>
+        <v>129730264</v>
       </c>
       <c r="B159" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17562,37 +17562,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L159" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N159" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
           <t>Bodknulen, Jmt</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>483545</v>
+        <v>483665</v>
       </c>
       <c r="R159" t="n">
-        <v>7145332</v>
+        <v>7145576</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17625,6 +17605,11 @@
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17651,10 +17636,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129730265</v>
+        <v>129730276</v>
       </c>
       <c r="B160" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17679,17 +17664,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I160" t="inlineStr"/>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
           <t>Bodknulen, Jmt</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>483564</v>
+        <v>483545</v>
       </c>
       <c r="R160" t="n">
-        <v>7145344</v>
+        <v>7145332</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17722,11 +17727,6 @@
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC160" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17756,7 +17756,7 @@
         <v>129730256</v>
       </c>
       <c r="B161" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17853,7 +17853,7 @@
         <v>129730263</v>
       </c>
       <c r="B162" t="n">
-        <v>83055</v>
+        <v>83058</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17950,7 +17950,7 @@
         <v>129730259</v>
       </c>
       <c r="B163" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18044,10 +18044,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129730273</v>
+        <v>129730271</v>
       </c>
       <c r="B164" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18079,10 +18079,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>483589</v>
+        <v>483461</v>
       </c>
       <c r="R164" t="n">
-        <v>7145604</v>
+        <v>7145552</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18146,10 +18146,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129730272</v>
+        <v>129730270</v>
       </c>
       <c r="B165" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18181,10 +18181,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>483583</v>
+        <v>483426</v>
       </c>
       <c r="R165" t="n">
-        <v>7145605</v>
+        <v>7145560</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18248,10 +18248,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129730271</v>
+        <v>129730273</v>
       </c>
       <c r="B166" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18283,10 +18283,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>483461</v>
+        <v>483589</v>
       </c>
       <c r="R166" t="n">
-        <v>7145552</v>
+        <v>7145604</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18350,10 +18350,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129730270</v>
+        <v>129730272</v>
       </c>
       <c r="B167" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18385,10 +18385,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>483426</v>
+        <v>483583</v>
       </c>
       <c r="R167" t="n">
-        <v>7145560</v>
+        <v>7145605</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>

--- a/artfynd/A 52753-2025 artfynd.xlsx
+++ b/artfynd/A 52753-2025 artfynd.xlsx
@@ -2892,32 +2892,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129727915</v>
+        <v>129727934</v>
       </c>
       <c r="B22" t="n">
-        <v>92323</v>
+        <v>57740</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2927,10 +2927,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483493</v>
+        <v>483619</v>
       </c>
       <c r="R22" t="n">
-        <v>7145538</v>
+        <v>7145595</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2963,6 +2963,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2989,32 +2994,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129727934</v>
+        <v>129727915</v>
       </c>
       <c r="B23" t="n">
-        <v>57740</v>
+        <v>92323</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3024,10 +3029,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483619</v>
+        <v>483493</v>
       </c>
       <c r="R23" t="n">
-        <v>7145595</v>
+        <v>7145538</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3060,11 +3065,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -4946,37 +4946,37 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129726946</v>
+        <v>129726948</v>
       </c>
       <c r="B41" t="n">
-        <v>80220</v>
+        <v>91625</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6461</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>483607</v>
+        <v>483501</v>
       </c>
       <c r="R41" t="n">
         <v>7145621</v>
@@ -5022,6 +5022,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar i en levande gran.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5031,6 +5036,31 @@
       <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5047,48 +5077,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129726948</v>
+        <v>129716464</v>
       </c>
       <c r="B42" t="n">
-        <v>91625</v>
+        <v>92323</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>483501</v>
+        <v>484017</v>
       </c>
       <c r="R42" t="n">
-        <v>7145621</v>
+        <v>7145437</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5123,100 +5150,69 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar i en levande gran.</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129716464</v>
+        <v>129726821</v>
       </c>
       <c r="B43" t="n">
-        <v>92323</v>
+        <v>79087</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>484017</v>
+        <v>483922</v>
       </c>
       <c r="R43" t="n">
-        <v>7145437</v>
+        <v>7145570</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5246,9 +5242,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5263,19 +5269,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129726821</v>
+        <v>129726960</v>
       </c>
       <c r="B44" t="n">
         <v>79087</v>
@@ -5304,16 +5310,19 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>483922</v>
+        <v>483376</v>
       </c>
       <c r="R44" t="n">
-        <v>7145570</v>
+        <v>7145540</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5343,19 +5352,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>09:05</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>09:05</t>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På en levande gran.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5364,50 +5368,76 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129726960</v>
+        <v>129726946</v>
       </c>
       <c r="B45" t="n">
-        <v>79087</v>
+        <v>80220</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5420,10 +5450,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>483376</v>
+        <v>483607</v>
       </c>
       <c r="R45" t="n">
-        <v>7145540</v>
+        <v>7145621</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5458,11 +5488,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På en levande gran.</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5472,31 +5497,6 @@
       <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -6144,45 +6144,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129727914</v>
+        <v>129716458</v>
       </c>
       <c r="B52" t="n">
-        <v>92323</v>
+        <v>83058</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3298</v>
+        <v>6440</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>483577</v>
+        <v>483701</v>
       </c>
       <c r="R52" t="n">
-        <v>7145438</v>
+        <v>7145588</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6229,22 +6229,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129727922</v>
+        <v>129726811</v>
       </c>
       <c r="B53" t="n">
-        <v>57740</v>
+        <v>79087</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6252,34 +6252,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>483507</v>
+        <v>483760</v>
       </c>
       <c r="R53" t="n">
-        <v>7145556</v>
+        <v>7145575</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6309,14 +6309,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6331,57 +6336,60 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129727924</v>
+        <v>129726944</v>
       </c>
       <c r="B54" t="n">
-        <v>57740</v>
+        <v>80220</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>483548</v>
+        <v>483597</v>
       </c>
       <c r="R54" t="n">
-        <v>7145488</v>
+        <v>7145735</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6416,39 +6424,35 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129726944</v>
+        <v>129727914</v>
       </c>
       <c r="B55" t="n">
-        <v>80220</v>
+        <v>92323</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6456,37 +6460,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6461</v>
+        <v>3298</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>483597</v>
+        <v>483577</v>
       </c>
       <c r="R55" t="n">
-        <v>7145735</v>
+        <v>7145438</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6527,29 +6528,28 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129716458</v>
+        <v>129727922</v>
       </c>
       <c r="B56" t="n">
-        <v>83058</v>
+        <v>57740</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6557,34 +6557,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>483701</v>
+        <v>483507</v>
       </c>
       <c r="R56" t="n">
-        <v>7145588</v>
+        <v>7145556</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6619,6 +6619,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -6631,22 +6636,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129726811</v>
+        <v>129727924</v>
       </c>
       <c r="B57" t="n">
-        <v>79087</v>
+        <v>57740</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6654,34 +6659,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>483760</v>
+        <v>483548</v>
       </c>
       <c r="R57" t="n">
-        <v>7145575</v>
+        <v>7145488</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6711,19 +6716,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>09:35</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>09:35</t>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6738,22 +6738,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129726828</v>
+        <v>129727929</v>
       </c>
       <c r="B58" t="n">
-        <v>79087</v>
+        <v>57740</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6761,34 +6761,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>483988</v>
+        <v>483677</v>
       </c>
       <c r="R58" t="n">
-        <v>7145444</v>
+        <v>7145477</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6818,19 +6818,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>08:48</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>08:48</t>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6845,22 +6840,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129716453</v>
+        <v>129727932</v>
       </c>
       <c r="B59" t="n">
-        <v>79087</v>
+        <v>57740</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6868,34 +6863,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>484032</v>
+        <v>483527</v>
       </c>
       <c r="R59" t="n">
-        <v>7145416</v>
+        <v>7145534</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6930,6 +6925,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -6942,22 +6942,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129726953</v>
+        <v>129727930</v>
       </c>
       <c r="B60" t="n">
-        <v>79087</v>
+        <v>57740</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6965,37 +6965,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>483555</v>
+        <v>483658</v>
       </c>
       <c r="R60" t="n">
-        <v>7145531</v>
+        <v>7145503</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7032,7 +7029,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7041,54 +7038,28 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129716449</v>
+        <v>129726828</v>
       </c>
       <c r="B61" t="n">
-        <v>83058</v>
+        <v>79087</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7096,34 +7067,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>483889</v>
+        <v>483988</v>
       </c>
       <c r="R61" t="n">
-        <v>7145589</v>
+        <v>7145444</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7153,9 +7124,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7170,19 +7151,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129726806</v>
+        <v>129716453</v>
       </c>
       <c r="B62" t="n">
         <v>79087</v>
@@ -7213,14 +7194,14 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>483558</v>
+        <v>484032</v>
       </c>
       <c r="R62" t="n">
-        <v>7145588</v>
+        <v>7145416</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7250,19 +7231,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>09:51</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>09:51</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7277,19 +7248,19 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129726788</v>
+        <v>129726953</v>
       </c>
       <c r="B63" t="n">
         <v>79087</v>
@@ -7318,16 +7289,19 @@
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>483665</v>
+        <v>483555</v>
       </c>
       <c r="R63" t="n">
-        <v>7145479</v>
+        <v>7145531</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7357,19 +7331,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>11:18</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>11:18</t>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7378,28 +7347,54 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129727929</v>
+        <v>129716449</v>
       </c>
       <c r="B64" t="n">
-        <v>57740</v>
+        <v>83058</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7407,34 +7402,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>483677</v>
+        <v>483889</v>
       </c>
       <c r="R64" t="n">
-        <v>7145477</v>
+        <v>7145589</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7469,11 +7464,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -7486,22 +7476,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129727932</v>
+        <v>129726806</v>
       </c>
       <c r="B65" t="n">
-        <v>57740</v>
+        <v>79087</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7509,34 +7499,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>483527</v>
+        <v>483558</v>
       </c>
       <c r="R65" t="n">
-        <v>7145534</v>
+        <v>7145588</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7566,14 +7556,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7588,22 +7583,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129727930</v>
+        <v>129726788</v>
       </c>
       <c r="B66" t="n">
-        <v>57740</v>
+        <v>79087</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7611,34 +7606,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>483658</v>
+        <v>483665</v>
       </c>
       <c r="R66" t="n">
-        <v>7145503</v>
+        <v>7145479</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7668,14 +7663,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7690,12 +7690,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -9084,10 +9084,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129726795</v>
+        <v>129716465</v>
       </c>
       <c r="B79" t="n">
-        <v>83063</v>
+        <v>91605</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9095,34 +9095,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1467</v>
+        <v>1202</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>483545</v>
+        <v>483983</v>
       </c>
       <c r="R79" t="n">
-        <v>7145343</v>
+        <v>7145507</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9152,19 +9152,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>10:35</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>10:35</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9179,22 +9169,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129716465</v>
+        <v>129727941</v>
       </c>
       <c r="B80" t="n">
-        <v>91605</v>
+        <v>91601</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9202,34 +9192,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>483983</v>
+        <v>483551</v>
       </c>
       <c r="R80" t="n">
-        <v>7145507</v>
+        <v>7145323</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9276,22 +9266,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129727941</v>
+        <v>129726831</v>
       </c>
       <c r="B81" t="n">
-        <v>91601</v>
+        <v>83058</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9299,34 +9289,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>483551</v>
+        <v>484008</v>
       </c>
       <c r="R81" t="n">
-        <v>7145323</v>
+        <v>7145455</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9356,9 +9346,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>08:42</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9373,57 +9373,60 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129726796</v>
+        <v>129726963</v>
       </c>
       <c r="B82" t="n">
-        <v>83056</v>
+        <v>79087</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6486</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>483545</v>
+        <v>483498</v>
       </c>
       <c r="R82" t="n">
-        <v>7145343</v>
+        <v>7145585</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9453,19 +9456,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>10:34</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>10:34</t>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>På levande gran.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9474,28 +9472,54 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
+      </c>
+      <c r="AH82" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM82" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129727940</v>
+        <v>129726812</v>
       </c>
       <c r="B83" t="n">
-        <v>57737</v>
+        <v>79087</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9503,34 +9527,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>483677</v>
+        <v>483764</v>
       </c>
       <c r="R83" t="n">
-        <v>7145478</v>
+        <v>7145589</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9560,14 +9584,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Hack ganska färska</t>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9582,22 +9611,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129726831</v>
+        <v>129726823</v>
       </c>
       <c r="B84" t="n">
-        <v>83058</v>
+        <v>79087</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9605,21 +9634,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9629,10 +9658,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>484008</v>
+        <v>483959</v>
       </c>
       <c r="R84" t="n">
-        <v>7145455</v>
+        <v>7145539</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9664,7 +9693,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9674,7 +9703,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9701,7 +9730,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129726963</v>
+        <v>129716451</v>
       </c>
       <c r="B85" t="n">
         <v>79087</v>
@@ -9730,19 +9759,16 @@
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>483498</v>
+        <v>483989</v>
       </c>
       <c r="R85" t="n">
-        <v>7145585</v>
+        <v>7145511</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9777,62 +9803,31 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>På levande gran.</t>
-        </is>
-      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
-      </c>
-      <c r="AH85" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ85" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK85" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129726812</v>
+        <v>129726798</v>
       </c>
       <c r="B86" t="n">
         <v>79087</v>
@@ -9867,10 +9862,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>483764</v>
+        <v>483429</v>
       </c>
       <c r="R86" t="n">
-        <v>7145589</v>
+        <v>7145430</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9902,7 +9897,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9912,7 +9907,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9939,32 +9934,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129726823</v>
+        <v>129726796</v>
       </c>
       <c r="B87" t="n">
-        <v>79087</v>
+        <v>83056</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>6486</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9974,10 +9969,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>483959</v>
+        <v>483545</v>
       </c>
       <c r="R87" t="n">
-        <v>7145539</v>
+        <v>7145343</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10009,7 +10004,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10019,7 +10014,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10046,10 +10041,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129716451</v>
+        <v>129727940</v>
       </c>
       <c r="B88" t="n">
-        <v>79087</v>
+        <v>57737</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10057,34 +10052,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>483989</v>
+        <v>483677</v>
       </c>
       <c r="R88" t="n">
-        <v>7145511</v>
+        <v>7145478</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10119,6 +10114,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Hack ganska färska</t>
+        </is>
+      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
@@ -10131,22 +10131,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129726798</v>
+        <v>129726795</v>
       </c>
       <c r="B89" t="n">
-        <v>79087</v>
+        <v>83063</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10154,21 +10154,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10178,10 +10178,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>483429</v>
+        <v>483545</v>
       </c>
       <c r="R89" t="n">
-        <v>7145430</v>
+        <v>7145343</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10213,7 +10213,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10223,7 +10223,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -12027,10 +12027,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129726957</v>
+        <v>129727937</v>
       </c>
       <c r="B105" t="n">
-        <v>79087</v>
+        <v>57740</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12038,37 +12038,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>483497</v>
+        <v>483824</v>
       </c>
       <c r="R105" t="n">
-        <v>7145327</v>
+        <v>7145592</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12105,7 +12102,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12114,51 +12111,25 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
-      </c>
-      <c r="AH105" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ105" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK105" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM105" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO105" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129727937</v>
+        <v>129727933</v>
       </c>
       <c r="B106" t="n">
         <v>57740</v>
@@ -12193,10 +12164,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>483824</v>
+        <v>483593</v>
       </c>
       <c r="R106" t="n">
-        <v>7145592</v>
+        <v>7145594</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12233,7 +12204,7 @@
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12260,10 +12231,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129727933</v>
+        <v>129726830</v>
       </c>
       <c r="B107" t="n">
-        <v>57740</v>
+        <v>78100</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12271,34 +12242,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>483593</v>
+        <v>484008</v>
       </c>
       <c r="R107" t="n">
-        <v>7145594</v>
+        <v>7145455</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12328,14 +12299,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>08:43</t>
+        </is>
+      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12350,22 +12326,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129726830</v>
+        <v>129726957</v>
       </c>
       <c r="B108" t="n">
-        <v>78100</v>
+        <v>79087</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12373,34 +12349,37 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>484008</v>
+        <v>483497</v>
       </c>
       <c r="R108" t="n">
-        <v>7145455</v>
+        <v>7145327</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12430,19 +12409,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>08:43</t>
-        </is>
-      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>08:43</t>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12451,18 +12425,44 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
+      </c>
+      <c r="AH108" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ108" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK108" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM108" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO108" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
@@ -14509,10 +14509,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129730274</v>
+        <v>129730248</v>
       </c>
       <c r="B128" t="n">
-        <v>57740</v>
+        <v>80192</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14520,21 +14520,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14544,10 +14544,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>483612</v>
+        <v>483599</v>
       </c>
       <c r="R128" t="n">
-        <v>7145596</v>
+        <v>7145185</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14580,11 +14580,6 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14611,10 +14606,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129730290</v>
+        <v>129730247</v>
       </c>
       <c r="B129" t="n">
-        <v>91625</v>
+        <v>80192</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14622,19 +14617,23 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
@@ -14642,10 +14641,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>483766</v>
+        <v>483595</v>
       </c>
       <c r="R129" t="n">
-        <v>7145610</v>
+        <v>7145180</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14704,10 +14703,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129730244</v>
+        <v>129730274</v>
       </c>
       <c r="B130" t="n">
-        <v>80193</v>
+        <v>57740</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14715,21 +14714,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14739,10 +14738,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>483599</v>
+        <v>483612</v>
       </c>
       <c r="R130" t="n">
-        <v>7145190</v>
+        <v>7145596</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14775,6 +14774,11 @@
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14801,10 +14805,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129730248</v>
+        <v>129730290</v>
       </c>
       <c r="B131" t="n">
-        <v>80192</v>
+        <v>91625</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14812,23 +14816,19 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
@@ -14836,10 +14836,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>483599</v>
+        <v>483766</v>
       </c>
       <c r="R131" t="n">
-        <v>7145185</v>
+        <v>7145610</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14898,10 +14898,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129730247</v>
+        <v>129730244</v>
       </c>
       <c r="B132" t="n">
-        <v>80192</v>
+        <v>80193</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14909,21 +14909,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14933,10 +14933,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>483595</v>
+        <v>483599</v>
       </c>
       <c r="R132" t="n">
-        <v>7145180</v>
+        <v>7145190</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15476,10 +15476,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129730250</v>
+        <v>129730262</v>
       </c>
       <c r="B138" t="n">
-        <v>78844</v>
+        <v>57740</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15487,21 +15487,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15511,10 +15511,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>483564</v>
+        <v>483284</v>
       </c>
       <c r="R138" t="n">
-        <v>7145430</v>
+        <v>7145578</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15547,6 +15547,11 @@
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15670,10 +15675,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129730262</v>
+        <v>129730250</v>
       </c>
       <c r="B140" t="n">
-        <v>57740</v>
+        <v>78844</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15681,21 +15686,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15705,10 +15710,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>483284</v>
+        <v>483564</v>
       </c>
       <c r="R140" t="n">
-        <v>7145578</v>
+        <v>7145430</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15741,11 +15746,6 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16160,10 +16160,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129730261</v>
+        <v>129730289</v>
       </c>
       <c r="B145" t="n">
-        <v>79087</v>
+        <v>91625</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16171,23 +16171,19 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr"/>
       <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
@@ -16195,10 +16191,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>483247</v>
+        <v>483238</v>
       </c>
       <c r="R145" t="n">
-        <v>7145585</v>
+        <v>7145599</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16257,10 +16253,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129730289</v>
+        <v>129730261</v>
       </c>
       <c r="B146" t="n">
-        <v>91625</v>
+        <v>79087</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16268,19 +16264,23 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H146" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
@@ -16288,10 +16288,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>483238</v>
+        <v>483247</v>
       </c>
       <c r="R146" t="n">
-        <v>7145599</v>
+        <v>7145585</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -17947,10 +17947,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129730259</v>
+        <v>129730271</v>
       </c>
       <c r="B163" t="n">
-        <v>79087</v>
+        <v>57740</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17958,21 +17958,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17982,10 +17982,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>483432</v>
+        <v>483461</v>
       </c>
       <c r="R163" t="n">
-        <v>7145357</v>
+        <v>7145552</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18018,6 +18018,11 @@
       <c r="AA163" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC163" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -18044,7 +18049,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129730271</v>
+        <v>129730270</v>
       </c>
       <c r="B164" t="n">
         <v>57740</v>
@@ -18079,10 +18084,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>483461</v>
+        <v>483426</v>
       </c>
       <c r="R164" t="n">
-        <v>7145552</v>
+        <v>7145560</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18146,7 +18151,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129730270</v>
+        <v>129730273</v>
       </c>
       <c r="B165" t="n">
         <v>57740</v>
@@ -18181,10 +18186,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>483426</v>
+        <v>483589</v>
       </c>
       <c r="R165" t="n">
-        <v>7145560</v>
+        <v>7145604</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18248,7 +18253,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129730273</v>
+        <v>129730272</v>
       </c>
       <c r="B166" t="n">
         <v>57740</v>
@@ -18283,10 +18288,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>483589</v>
+        <v>483583</v>
       </c>
       <c r="R166" t="n">
-        <v>7145604</v>
+        <v>7145605</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18350,10 +18355,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129730272</v>
+        <v>129730259</v>
       </c>
       <c r="B167" t="n">
-        <v>57740</v>
+        <v>79087</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18361,21 +18366,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -18385,10 +18390,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>483583</v>
+        <v>483432</v>
       </c>
       <c r="R167" t="n">
-        <v>7145605</v>
+        <v>7145357</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18421,11 +18426,6 @@
       <c r="AA167" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC167" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD167" t="b">

--- a/artfynd/A 52753-2025 artfynd.xlsx
+++ b/artfynd/A 52753-2025 artfynd.xlsx
@@ -4946,37 +4946,37 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129726948</v>
+        <v>129726946</v>
       </c>
       <c r="B41" t="n">
-        <v>91625</v>
+        <v>80220</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>6461</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>483501</v>
+        <v>483607</v>
       </c>
       <c r="R41" t="n">
         <v>7145621</v>
@@ -5022,11 +5022,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar i en levande gran.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5036,31 +5031,6 @@
       <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5077,45 +5047,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129716464</v>
+        <v>129726948</v>
       </c>
       <c r="B42" t="n">
-        <v>92323</v>
+        <v>91625</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>484017</v>
+        <v>483501</v>
       </c>
       <c r="R42" t="n">
-        <v>7145437</v>
+        <v>7145621</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5150,69 +5123,100 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar i en levande gran.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129726821</v>
+        <v>129716464</v>
       </c>
       <c r="B43" t="n">
-        <v>79087</v>
+        <v>92323</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>483922</v>
+        <v>484017</v>
       </c>
       <c r="R43" t="n">
-        <v>7145570</v>
+        <v>7145437</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5242,19 +5246,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>09:05</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>09:05</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5269,19 +5263,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129726960</v>
+        <v>129726821</v>
       </c>
       <c r="B44" t="n">
         <v>79087</v>
@@ -5310,19 +5304,16 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>483376</v>
+        <v>483922</v>
       </c>
       <c r="R44" t="n">
-        <v>7145540</v>
+        <v>7145570</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5352,14 +5343,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>På en levande gran.</t>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5368,76 +5364,50 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129726946</v>
+        <v>129726960</v>
       </c>
       <c r="B45" t="n">
-        <v>80220</v>
+        <v>79087</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5450,10 +5420,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>483607</v>
+        <v>483376</v>
       </c>
       <c r="R45" t="n">
-        <v>7145621</v>
+        <v>7145540</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5488,6 +5458,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På en levande gran.</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5497,6 +5472,31 @@
       <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -6144,45 +6144,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129716458</v>
+        <v>129727914</v>
       </c>
       <c r="B52" t="n">
-        <v>83058</v>
+        <v>92323</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6440</v>
+        <v>3298</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>483701</v>
+        <v>483577</v>
       </c>
       <c r="R52" t="n">
-        <v>7145588</v>
+        <v>7145438</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6229,22 +6229,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129726811</v>
+        <v>129727922</v>
       </c>
       <c r="B53" t="n">
-        <v>79087</v>
+        <v>57740</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6252,34 +6252,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Fiskåvattnet V, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>483760</v>
+        <v>483507</v>
       </c>
       <c r="R53" t="n">
-        <v>7145575</v>
+        <v>7145556</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6309,19 +6309,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>09:35</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>09:35</t>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6336,60 +6331,57 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129726944</v>
+        <v>129727924</v>
       </c>
       <c r="B54" t="n">
-        <v>80220</v>
+        <v>57740</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Åviken, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>483597</v>
+        <v>483548</v>
       </c>
       <c r="R54" t="n">
-        <v>7145735</v>
+        <v>7145488</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6424,35 +6416,39 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129727914</v>
+        <v>129726944</v>
       </c>
       <c r="B55" t="n">
-        <v>92323</v>
+        <v>80220</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6460,34 +6456,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3298</v>
+        <v>6461</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>483577</v>
+        <v>483597</v>
       </c>
       <c r="R55" t="n">
-        <v>7145438</v>
+        <v>7145735</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6528,28 +6527,29 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129727922</v>
+        <v>129716458</v>
       </c>
       <c r="B56" t="n">
-        <v>57740</v>
+        <v>83058</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6557,34 +6557,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>483507</v>
+        <v>483701</v>
       </c>
       <c r="R56" t="n">
-        <v>7145556</v>
+        <v>7145588</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6619,11 +6619,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -6636,22 +6631,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129727924</v>
+        <v>129726811</v>
       </c>
       <c r="B57" t="n">
-        <v>57740</v>
+        <v>79087</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6659,34 +6654,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>483548</v>
+        <v>483760</v>
       </c>
       <c r="R57" t="n">
-        <v>7145488</v>
+        <v>7145575</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6716,14 +6711,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6738,12 +6738,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -7702,10 +7702,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129716448</v>
+        <v>129726958</v>
       </c>
       <c r="B67" t="n">
-        <v>91556</v>
+        <v>79087</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7713,34 +7713,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>483443</v>
+        <v>483482</v>
       </c>
       <c r="R67" t="n">
-        <v>7145540</v>
+        <v>7145330</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7775,31 +7778,62 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>På en levande gran.</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129726958</v>
+        <v>129726966</v>
       </c>
       <c r="B68" t="n">
         <v>79087</v>
@@ -7837,10 +7871,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>483482</v>
+        <v>483764</v>
       </c>
       <c r="R68" t="n">
-        <v>7145330</v>
+        <v>7145582</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7877,7 +7911,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>På en levande gran.</t>
+          <t>Långväxta bålar på en levande gran.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7930,7 +7964,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129726966</v>
+        <v>129726797</v>
       </c>
       <c r="B69" t="n">
         <v>79087</v>
@@ -7959,19 +7993,16 @@
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet V, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>483764</v>
+        <v>483540</v>
       </c>
       <c r="R69" t="n">
-        <v>7145582</v>
+        <v>7145349</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8001,14 +8032,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på en levande gran.</t>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8017,54 +8053,28 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
-      </c>
-      <c r="AH69" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129726797</v>
+        <v>129726937</v>
       </c>
       <c r="B70" t="n">
-        <v>79087</v>
+        <v>57740</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8072,34 +8082,46 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+  